--- a/40_数据库/学习笔记_RDBMS_GaussDB.xlsx
+++ b/40_数据库/学习笔记_RDBMS_GaussDB.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C910CA8-84CB-432A-A33D-6F206B292D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAFA1AFB-677C-4207-B240-89C94B7A117C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概述" sheetId="1" r:id="rId1"/>
@@ -225,8 +225,70 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>作者</author>
+  </authors>
+  <commentList>
+    <comment ref="C128" authorId="0" shapeId="0" xr:uid="{83BAAAC4-3EDC-4F72-9295-A02EFEF736B4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>作者:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+表对象作为入出参时，表不能带索引！</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C130" authorId="0" shapeId="0" xr:uid="{8BE69E10-1347-4C26-AB10-F1DF719E9DCD}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>作者:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+函数内的子函数会导致benin end报错（主要是GaussDB内部的解析机制不够完善导致），提升为包内私有函数可解决该问题！</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="289">
   <si>
     <r>
       <rPr>
@@ -568,10 +630,6 @@
   </si>
   <si>
     <t>文档中 P_PartTemplate_Imp 使用了 sys_guid()，GaussDB 需替换为 gen_random_uuid()。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>gen_random_uuid()</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1655,103 +1713,6 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>'o_return_code: %'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000080"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>COALESCE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">(o_return_code, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF008000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>'NULL'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>;</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>RAISE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF800000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>NOTICE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF008000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
       <t>'o_error_message: %'</t>
     </r>
     <r>
@@ -2997,12 +2958,1921 @@
     <t>OpenGauss</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>ALTER TABLE common.if_t_baseinfo SET SCHEMA bomif;</t>
+  </si>
+  <si>
+    <t>修改表到另外一个scmema：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>function getval(jsonstr varchar2, nodename varchar2) return varchar2 as
+    language java name 'JAVA_JSON_UTIL.getValue(java.lang.String,java.lang.String) return java.lang.String';</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CREATE FUNCTION getval(VARCHAR, VARCHAR)
+    RETURNS VARCHAR
+    AS 'JAVA_JSON_UTIL.getValue'
+    LANGUAGE JAVA;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VAR_PASSWORD := LOWER(MD5(VAR_PASSWORD));</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VAR_PASSWORD := LOWER(utl_raw.cast_to_raw(DBMS_OBFUSCATION_TOOLKIT.MD5(INPUT_STRING =&gt; VAR_PASSWORD)));</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MD5加密</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>调用jar包方法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>支持Json格式，不需要借助jar包的工具方法，可以进一步改造为：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gen_random_uuid()、uuid()</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LIMIT 2、LIMIT 2,3、LIMIT 2 OFFSET 3 的区别?</t>
+  </si>
+  <si>
+    <t>答：LIMIT和OFFSET是用于限制SELECT语句中查询数据返回结果数量的关键字。</t>
+  </si>
+  <si>
+    <t>● LIMIT 2：表示查询结果只返回前2行数据。</t>
+  </si>
+  <si>
+    <t>● LIMIT 2,3：表示查询结果从第3行开始返回，一共返回3行数据。</t>
+  </si>
+  <si>
+    <t>● LIMIT 2 OFFSET 3：表示查询结果从第4行开始返回，一共返回2行数据。</t>
+  </si>
+  <si>
+    <t>GaussDB 数据库一个汉字占几个字节？</t>
+  </si>
+  <si>
+    <t>答：取决于数据库的字符集编码，GBK字符集一个汉字占2个字节，UTF8字符集一个汉字占3个字节。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>RAISE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>NOTICE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'o_return_code: %'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>COALESCE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">(o_return_code, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'NULL'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>EXPLAIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ANALYZE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>select</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>count</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(1) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>from</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> if_v_batch_sel;</t>
+    </r>
+  </si>
+  <si>
+    <t>查询解析计划</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Oracle包转换为GaussDB中的包：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>注：varchar为小写</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6、如果不能按提示很好地修正错误，那么将新包体复制出来，放到一个文本中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7、逐步复制其中一个或多个函数或存储过程放到新包中，尝试执行。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>报错则按提示修改正确；不报错则再复制一个或多个函数或存储过程到新包中，如此反复操作，直到复制完全部包体内容。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>执行包的数据库及模式要选正确，不然包创建到其他模式下了！！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5、尝试全部执行一次，一般会报错，并且因为存过或函数太多，不好找是哪个出错了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>错误包含：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改前的Oracle旧对象，和修改后的GaussDB新对象都要做好备份，包括关联对象！！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、在Dbeaver创建同名新包：包名会自动转为小写</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有时遇到包声明为空了，需要将包体内容复制下来。然后删除原包，再创建新包，再将包体内容复制过去并保存。注：一定要保证复制时的内容是最新的，不然写好的内容不见就over了！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> map_type1 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Is</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Table</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Of</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Varchar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>4000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Open</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> c_CncType(i_CncArea =&gt; i_CncArea)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Open</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> c_CncType(i_CncArea)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>部分函数或存储过程转换，可借助AI更快</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"text"</t>
+  </si>
+  <si>
+    <t>去掉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Table_Check_Type </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Is</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Table</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Of</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> Rec_Check_Type </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>By</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>varchar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>32</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Index</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>By</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>varchar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>32</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.1 对象缺少模式前缀导找不到：增加模式前缀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.2 引用包不存在或未加模式前缀：按本说明迁移旧包。最怕的就是当前对象引用了其他对象，而其他对象又引用了一大堆相关对象，这样重写前先得把依赖的对象迁移过来先！！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.3 表名未迁移或缺少模式前缀：迁移旧表通过旧表的ViewSQL，去掉tablespace部分，然后在新模式下执行即可。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.4 视图未迁移或缺少模式前缀：迁移旧视图。如旧视图引用其他视图，又得先重写其他视图！！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.6 一些关键字作为查询字段别名时要加上双引号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.7 Function do not support table of index Or record nested tabel of index as in, out args.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.99 其他略</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改为</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2、类型定义放到包声明中。暂时没有时，可以将以下内容复制到包声明中，让保存时声明有内容，不然包声明有时会莫名地为空白了！！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3、复制旧包中的包体到新包体中。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4、【可选】替换varchar2为varchar，不替换也行。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.8 package name end is not match the one begin! at or near ";"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>消灭了包内的 DECLARE...BEGIN...END 匿名块：这是导致 package name end is not match 的罪魁祸首。OpenGauss 的包解析器在处理这种结构时极易发生标签匹配错位。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>将辅助函数提升为包级私有函数：get_unit_char、convert_group 和 convert_int_part 都作为包内的独立函数存在，END 标签严格对应，解析器绝对不会报错。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>部分表不迁移，要将原来用到的地方注释掉，并说明一下，以后改为新表。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>com_t_std_object、t, com_t_object_property，要将每种类型转换为实际的物理表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9、迁移完成，后续还得测试是否正常。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8、再复制旧包声明到新包声明中。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.5 打开游标、调用函数、存储过程，直接传入参数，不要使用=&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>包总体说明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>包中函数说明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>包中存储过程说明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/*
+  *对象名称：【】函数
+  *对象描述：
+  *重点说明：
+  *业务规则：
+  *修改历史：
+  *   20260702 新增 huangguohui   
+  */</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/*
+   * 包名称：【系统公用方法及常量定义】
+   * 包简述：   
+   * 创建人：wujc   
+   * 创建日期：20100623
+   * 修订历史：
+   *   20260702 将Oracle版本转换为GaussDB适用版本 huangguohui
+   */</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/*
+  *对象名称：【】存储过程
+  *对象描述：
+  *重点说明：
+  *业务规则：
+  *修改历史：
+  *   20260702 新增 huangguohui   
+  */</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Select n.* From dp_sys_t_organization n</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">                                 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Connect By Prior n.org_parentid = n.org_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.9  递归语法（Start with …. Connect By Prior ）需要修改</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  Start With n.org_code = i_orgcode </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>WITH</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>RECURSIVE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>org_hierarchy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.*,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>level_num</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF956037"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>public</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>t_eap_sys_organization_real</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>org_code</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF6C5151"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>i_orgcode</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>UNION</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ALL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.*,</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>oh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>level_num</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF956037"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>public</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>t_eap_sys_organization_real</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>n</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>JOIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>org_hierarchy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>oh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ON</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>parent_org_realation_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>oh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>org_realation_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> *,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ROW_NUMBER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">() </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>OVER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ORDER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>BY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> level_num </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>DESC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>AS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>dd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>org_hierarchy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ORDER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>BY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>dd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>DESC</t>
+    </r>
+  </si>
+  <si>
+    <t>改为</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.10 分组拼接字符（listagg）修改为STRING_AGG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Oracle: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.6"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>LISTAGG(column, delimiter) WITHIN GROUP (ORDER BY ...)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>OpenGauss: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.6"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>STRING_AGG(column, delimiter ORDER BY ...)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>LISTAGG → STRING_AGG</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>* GaussDB/PostgreSQL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>在预处理语句中，当</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.6"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ILIKE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>与</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9.6"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>CONCAT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>结合使用时，可能无法正确推断参数类型，特别是当参数可能为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>NULL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>或需要隐式类型转换时。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>或</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>b.user_name ILIKE CONCAT('%', ?, '%')</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>b.user_name ILIKE CONCAT('%', CAST(? AS VARCHAR), '%')</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>b.user_name ILIKE '%' || ? || '%'</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>POSITION(? IN b.user_name) &gt; 0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>注意，POSITION是大小写敏感的，而ILIKE是大小写不敏感的。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Oracle &gt; GaussDB代码层面的Mybatis配置：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="34" x14ac:knownFonts="1">
+  <fonts count="52" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3250,8 +5120,127 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF800000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF8E00C6"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF006464"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF956037"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF8E00C6"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006464"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF6C5151"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000080"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9.6"/>
+      <color rgb="FF0F1115"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0F1115"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0F1115"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3267,6 +5256,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3441,7 +5436,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3472,6 +5467,127 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3514,15 +5630,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -3544,68 +5651,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3727,8 +5774,8 @@
       <xdr:rowOff>135391</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>647699</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>85724</xdr:colOff>
       <xdr:row>49</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
@@ -3862,15 +5909,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>137983</xdr:colOff>
+      <xdr:colOff>99883</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>161924</xdr:rowOff>
+      <xdr:rowOff>152399</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>171449</xdr:colOff>
+      <xdr:colOff>133349</xdr:colOff>
       <xdr:row>49</xdr:row>
-      <xdr:rowOff>76199</xdr:rowOff>
+      <xdr:rowOff>66674</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3900,7 +5947,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="11796583" y="3133724"/>
+          <a:off x="11758483" y="3305174"/>
           <a:ext cx="5519866" cy="5705475"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3938,7 +5985,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>638175</xdr:colOff>
+      <xdr:colOff>647700</xdr:colOff>
       <xdr:row>104</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
@@ -4350,35 +6397,35 @@
     </row>
     <row r="10" spans="1:2" ht="25.5" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B12" s="68"/>
+      <c r="B12" s="38"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B13" s="68" t="s">
+      <c r="B13" s="38" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B14" s="38" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B15" s="38" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B14" s="68" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B16" s="38" t="s">
         <v>199</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B15" s="68" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B16" s="68" t="s">
-        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -4436,7 +6483,7 @@
       </c>
     </row>
     <row r="2" spans="1:24" ht="18" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="87" t="s">
         <v>41</v>
       </c>
       <c r="B2" s="17" t="s">
@@ -4457,1601 +6504,1836 @@
       <c r="M2" s="11"/>
       <c r="N2" s="11"/>
       <c r="O2" s="12"/>
-      <c r="P2" s="20" t="s">
+      <c r="P2" s="75" t="s">
         <v>32</v>
       </c>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="21"/>
-      <c r="S2" s="21"/>
-      <c r="T2" s="21"/>
-      <c r="U2" s="21"/>
-      <c r="V2" s="21"/>
-      <c r="W2" s="21"/>
-      <c r="X2" s="22"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
+      <c r="U2" s="76"/>
+      <c r="V2" s="76"/>
+      <c r="W2" s="76"/>
+      <c r="X2" s="77"/>
     </row>
     <row r="3" spans="1:24" ht="18" x14ac:dyDescent="0.25">
-      <c r="A3" s="33"/>
-      <c r="B3" s="26" t="s">
+      <c r="A3" s="88"/>
+      <c r="B3" s="81" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="28" t="s">
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="83" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="29"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="26" t="s">
+      <c r="G3" s="84"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="81" t="s">
         <v>34</v>
       </c>
-      <c r="J3" s="27"/>
-      <c r="K3" s="27"/>
-      <c r="L3" s="27"/>
-      <c r="M3" s="28" t="s">
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
+      <c r="L3" s="82"/>
+      <c r="M3" s="83" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="29"/>
-      <c r="O3" s="30"/>
-      <c r="P3" s="23"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
-      <c r="S3" s="24"/>
-      <c r="T3" s="24"/>
-      <c r="U3" s="24"/>
-      <c r="V3" s="24"/>
-      <c r="W3" s="24"/>
-      <c r="X3" s="25"/>
+      <c r="N3" s="84"/>
+      <c r="O3" s="85"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="79"/>
+      <c r="R3" s="79"/>
+      <c r="S3" s="79"/>
+      <c r="T3" s="79"/>
+      <c r="U3" s="79"/>
+      <c r="V3" s="79"/>
+      <c r="W3" s="79"/>
+      <c r="X3" s="80"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" s="50" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="49" t="s">
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="36"/>
-      <c r="M4" s="50"/>
-      <c r="N4" s="50"/>
-      <c r="O4" s="50"/>
-      <c r="P4" s="50"/>
-      <c r="Q4" s="50"/>
-      <c r="R4" s="50"/>
-      <c r="S4" s="50"/>
-      <c r="T4" s="50"/>
-      <c r="U4" s="50"/>
-      <c r="V4" s="50"/>
-      <c r="W4" s="50"/>
-      <c r="X4" s="50"/>
+      <c r="J4" s="70"/>
+      <c r="K4" s="70"/>
+      <c r="L4" s="71"/>
+      <c r="M4" s="67"/>
+      <c r="N4" s="67"/>
+      <c r="O4" s="67"/>
+      <c r="P4" s="67"/>
+      <c r="Q4" s="67"/>
+      <c r="R4" s="67"/>
+      <c r="S4" s="67"/>
+      <c r="T4" s="67"/>
+      <c r="U4" s="67"/>
+      <c r="V4" s="67"/>
+      <c r="W4" s="67"/>
+      <c r="X4" s="67"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="50" t="s">
+      <c r="B5" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50" t="s">
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="49" t="s">
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="69" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="35"/>
-      <c r="K5" s="35"/>
-      <c r="L5" s="36"/>
-      <c r="M5" s="50" t="s">
+      <c r="J5" s="70"/>
+      <c r="K5" s="70"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="N5" s="50"/>
-      <c r="O5" s="50"/>
-      <c r="P5" s="50" t="s">
+      <c r="N5" s="67"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="Q5" s="50"/>
-      <c r="R5" s="50"/>
-      <c r="S5" s="50"/>
-      <c r="T5" s="50"/>
-      <c r="U5" s="50"/>
-      <c r="V5" s="50"/>
-      <c r="W5" s="50"/>
-      <c r="X5" s="50"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="67"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="67"/>
+      <c r="U5" s="67"/>
+      <c r="V5" s="67"/>
+      <c r="W5" s="67"/>
+      <c r="X5" s="67"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="50" t="s">
+      <c r="B6" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50" t="s">
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="49" t="s">
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="69" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="35"/>
-      <c r="K6" s="35"/>
-      <c r="L6" s="36"/>
-      <c r="M6" s="50" t="s">
+      <c r="J6" s="70"/>
+      <c r="K6" s="70"/>
+      <c r="L6" s="71"/>
+      <c r="M6" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="N6" s="50"/>
-      <c r="O6" s="50"/>
-      <c r="P6" s="50"/>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50"/>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
-      <c r="V6" s="50"/>
-      <c r="W6" s="50"/>
-      <c r="X6" s="50"/>
+      <c r="N6" s="67"/>
+      <c r="O6" s="67"/>
+      <c r="P6" s="67"/>
+      <c r="Q6" s="67"/>
+      <c r="R6" s="67"/>
+      <c r="S6" s="67"/>
+      <c r="T6" s="67"/>
+      <c r="U6" s="67"/>
+      <c r="V6" s="67"/>
+      <c r="W6" s="67"/>
+      <c r="X6" s="67"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B7" s="50" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="67" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="50"/>
-      <c r="I7" s="49" t="s">
-        <v>108</v>
-      </c>
-      <c r="J7" s="35"/>
-      <c r="K7" s="35"/>
-      <c r="L7" s="36"/>
-      <c r="M7" s="50"/>
-      <c r="N7" s="50"/>
-      <c r="O7" s="50"/>
-      <c r="P7" s="50"/>
-      <c r="Q7" s="50"/>
-      <c r="R7" s="50"/>
-      <c r="S7" s="50"/>
-      <c r="T7" s="50"/>
-      <c r="U7" s="50"/>
-      <c r="V7" s="50"/>
-      <c r="W7" s="50"/>
-      <c r="X7" s="50"/>
+      <c r="C7" s="67"/>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="67"/>
+      <c r="I7" s="69" t="s">
+        <v>107</v>
+      </c>
+      <c r="J7" s="70"/>
+      <c r="K7" s="70"/>
+      <c r="L7" s="71"/>
+      <c r="M7" s="67"/>
+      <c r="N7" s="67"/>
+      <c r="O7" s="67"/>
+      <c r="P7" s="67"/>
+      <c r="Q7" s="67"/>
+      <c r="R7" s="67"/>
+      <c r="S7" s="67"/>
+      <c r="T7" s="67"/>
+      <c r="U7" s="67"/>
+      <c r="V7" s="67"/>
+      <c r="W7" s="67"/>
+      <c r="X7" s="67"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="50" t="s">
+      <c r="B8" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="50"/>
-      <c r="D8" s="50"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="50" t="s">
+      <c r="C8" s="67"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="G8" s="50"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="49" t="s">
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="J8" s="35"/>
-      <c r="K8" s="35"/>
-      <c r="L8" s="36"/>
-      <c r="M8" s="50" t="s">
+      <c r="J8" s="70"/>
+      <c r="K8" s="70"/>
+      <c r="L8" s="71"/>
+      <c r="M8" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="N8" s="50"/>
-      <c r="O8" s="50"/>
-      <c r="P8" s="50" t="s">
+      <c r="N8" s="67"/>
+      <c r="O8" s="67"/>
+      <c r="P8" s="67" t="s">
         <v>37</v>
       </c>
-      <c r="Q8" s="50"/>
-      <c r="R8" s="50"/>
-      <c r="S8" s="50"/>
-      <c r="T8" s="50"/>
-      <c r="U8" s="50"/>
-      <c r="V8" s="50"/>
-      <c r="W8" s="50"/>
-      <c r="X8" s="50"/>
+      <c r="Q8" s="67"/>
+      <c r="R8" s="67"/>
+      <c r="S8" s="67"/>
+      <c r="T8" s="67"/>
+      <c r="U8" s="67"/>
+      <c r="V8" s="67"/>
+      <c r="W8" s="67"/>
+      <c r="X8" s="67"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="B9" s="67" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="50"/>
-      <c r="D9" s="50"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="50"/>
-      <c r="I9" s="49" t="s">
+      <c r="C9" s="67"/>
+      <c r="D9" s="67"/>
+      <c r="E9" s="67"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="67"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="69" t="s">
         <v>29</v>
       </c>
-      <c r="J9" s="35"/>
-      <c r="K9" s="35"/>
-      <c r="L9" s="36"/>
-      <c r="M9" s="50"/>
-      <c r="N9" s="50"/>
-      <c r="O9" s="50"/>
-      <c r="P9" s="50"/>
-      <c r="Q9" s="50"/>
-      <c r="R9" s="50"/>
-      <c r="S9" s="50"/>
-      <c r="T9" s="50"/>
-      <c r="U9" s="50"/>
-      <c r="V9" s="50"/>
-      <c r="W9" s="50"/>
-      <c r="X9" s="50"/>
+      <c r="J9" s="70"/>
+      <c r="K9" s="70"/>
+      <c r="L9" s="71"/>
+      <c r="M9" s="67"/>
+      <c r="N9" s="67"/>
+      <c r="O9" s="67"/>
+      <c r="P9" s="67"/>
+      <c r="Q9" s="67"/>
+      <c r="R9" s="67"/>
+      <c r="S9" s="67"/>
+      <c r="T9" s="67"/>
+      <c r="U9" s="67"/>
+      <c r="V9" s="67"/>
+      <c r="W9" s="67"/>
+      <c r="X9" s="67"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="50" t="s">
+      <c r="B10" s="67" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="50"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="50" t="s">
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="67" t="s">
         <v>38</v>
       </c>
-      <c r="G10" s="50"/>
-      <c r="H10" s="50"/>
-      <c r="I10" s="49" t="s">
+      <c r="G10" s="67"/>
+      <c r="H10" s="67"/>
+      <c r="I10" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="J10" s="35"/>
-      <c r="K10" s="35"/>
-      <c r="L10" s="36"/>
-      <c r="M10" s="50" t="s">
+      <c r="J10" s="70"/>
+      <c r="K10" s="70"/>
+      <c r="L10" s="71"/>
+      <c r="M10" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="N10" s="50"/>
-      <c r="O10" s="50"/>
-      <c r="P10" s="50"/>
-      <c r="Q10" s="50"/>
-      <c r="R10" s="50"/>
-      <c r="S10" s="50"/>
-      <c r="T10" s="50"/>
-      <c r="U10" s="50"/>
-      <c r="V10" s="50"/>
-      <c r="W10" s="50"/>
-      <c r="X10" s="50"/>
+      <c r="N10" s="67"/>
+      <c r="O10" s="67"/>
+      <c r="P10" s="67"/>
+      <c r="Q10" s="67"/>
+      <c r="R10" s="67"/>
+      <c r="S10" s="67"/>
+      <c r="T10" s="67"/>
+      <c r="U10" s="67"/>
+      <c r="V10" s="67"/>
+      <c r="W10" s="67"/>
+      <c r="X10" s="67"/>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="50" t="s">
+      <c r="B11" s="67" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="50"/>
-      <c r="I11" s="49" t="s">
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="69" t="s">
         <v>52</v>
       </c>
-      <c r="J11" s="35"/>
-      <c r="K11" s="35"/>
-      <c r="L11" s="36"/>
-      <c r="M11" s="50"/>
-      <c r="N11" s="50"/>
-      <c r="O11" s="50"/>
-      <c r="P11" s="50" t="s">
+      <c r="J11" s="70"/>
+      <c r="K11" s="70"/>
+      <c r="L11" s="71"/>
+      <c r="M11" s="67"/>
+      <c r="N11" s="67"/>
+      <c r="O11" s="67"/>
+      <c r="P11" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="Q11" s="50"/>
-      <c r="R11" s="50"/>
-      <c r="S11" s="50"/>
-      <c r="T11" s="50"/>
-      <c r="U11" s="50"/>
-      <c r="V11" s="50"/>
-      <c r="W11" s="50"/>
-      <c r="X11" s="50"/>
+      <c r="Q11" s="67"/>
+      <c r="R11" s="67"/>
+      <c r="S11" s="67"/>
+      <c r="T11" s="67"/>
+      <c r="U11" s="67"/>
+      <c r="V11" s="67"/>
+      <c r="W11" s="67"/>
+      <c r="X11" s="67"/>
     </row>
     <row r="12" spans="1:24" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="67" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67" t="s">
         <v>97</v>
       </c>
-      <c r="B12" s="50" t="s">
-        <v>93</v>
-      </c>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50" t="s">
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="69" t="s">
         <v>98</v>
       </c>
-      <c r="G12" s="50"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="49" t="s">
+      <c r="J12" s="70"/>
+      <c r="K12" s="70"/>
+      <c r="L12" s="71"/>
+      <c r="M12" s="68" t="s">
         <v>99</v>
       </c>
-      <c r="J12" s="35"/>
-      <c r="K12" s="35"/>
-      <c r="L12" s="36"/>
-      <c r="M12" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="N12" s="50"/>
-      <c r="O12" s="50"/>
-      <c r="P12" s="50"/>
-      <c r="Q12" s="50"/>
-      <c r="R12" s="50"/>
-      <c r="S12" s="50"/>
-      <c r="T12" s="50"/>
-      <c r="U12" s="50"/>
-      <c r="V12" s="50"/>
-      <c r="W12" s="50"/>
-      <c r="X12" s="50"/>
+      <c r="N12" s="67"/>
+      <c r="O12" s="67"/>
+      <c r="P12" s="67"/>
+      <c r="Q12" s="67"/>
+      <c r="R12" s="67"/>
+      <c r="S12" s="67"/>
+      <c r="T12" s="67"/>
+      <c r="U12" s="67"/>
+      <c r="V12" s="67"/>
+      <c r="W12" s="67"/>
+      <c r="X12" s="67"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50" t="s">
-        <v>101</v>
-      </c>
-      <c r="G13" s="50"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="49"/>
-      <c r="J13" s="35"/>
-      <c r="K13" s="35"/>
-      <c r="L13" s="36"/>
-      <c r="M13" s="51" t="s">
-        <v>103</v>
-      </c>
-      <c r="N13" s="50"/>
-      <c r="O13" s="50"/>
-      <c r="P13" s="50"/>
-      <c r="Q13" s="50"/>
-      <c r="R13" s="50"/>
-      <c r="S13" s="50"/>
-      <c r="T13" s="50"/>
-      <c r="U13" s="50"/>
-      <c r="V13" s="50"/>
-      <c r="W13" s="50"/>
-      <c r="X13" s="50"/>
+        <v>93</v>
+      </c>
+      <c r="B13" s="67"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="67"/>
+      <c r="F13" s="67" t="s">
+        <v>100</v>
+      </c>
+      <c r="G13" s="67"/>
+      <c r="H13" s="67"/>
+      <c r="I13" s="69"/>
+      <c r="J13" s="70"/>
+      <c r="K13" s="70"/>
+      <c r="L13" s="71"/>
+      <c r="M13" s="68" t="s">
+        <v>102</v>
+      </c>
+      <c r="N13" s="67"/>
+      <c r="O13" s="67"/>
+      <c r="P13" s="67"/>
+      <c r="Q13" s="67"/>
+      <c r="R13" s="67"/>
+      <c r="S13" s="67"/>
+      <c r="T13" s="67"/>
+      <c r="U13" s="67"/>
+      <c r="V13" s="67"/>
+      <c r="W13" s="67"/>
+      <c r="X13" s="67"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="50" t="s">
-        <v>101</v>
-      </c>
-      <c r="G14" s="50"/>
-      <c r="H14" s="50"/>
-      <c r="I14" s="49"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="35"/>
-      <c r="L14" s="36"/>
-      <c r="M14" s="51" t="s">
-        <v>104</v>
-      </c>
-      <c r="N14" s="50"/>
-      <c r="O14" s="50"/>
-      <c r="P14" s="50"/>
-      <c r="Q14" s="50"/>
-      <c r="R14" s="50"/>
-      <c r="S14" s="50"/>
-      <c r="T14" s="50"/>
-      <c r="U14" s="50"/>
-      <c r="V14" s="50"/>
-      <c r="W14" s="50"/>
-      <c r="X14" s="50"/>
+        <v>94</v>
+      </c>
+      <c r="B14" s="67"/>
+      <c r="C14" s="67"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="67"/>
+      <c r="F14" s="67" t="s">
+        <v>100</v>
+      </c>
+      <c r="G14" s="67"/>
+      <c r="H14" s="67"/>
+      <c r="I14" s="69"/>
+      <c r="J14" s="70"/>
+      <c r="K14" s="70"/>
+      <c r="L14" s="71"/>
+      <c r="M14" s="68" t="s">
+        <v>103</v>
+      </c>
+      <c r="N14" s="67"/>
+      <c r="O14" s="67"/>
+      <c r="P14" s="67"/>
+      <c r="Q14" s="67"/>
+      <c r="R14" s="67"/>
+      <c r="S14" s="67"/>
+      <c r="T14" s="67"/>
+      <c r="U14" s="67"/>
+      <c r="V14" s="67"/>
+      <c r="W14" s="67"/>
+      <c r="X14" s="67"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B15" s="50"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="50" t="s">
-        <v>102</v>
-      </c>
-      <c r="G15" s="50"/>
-      <c r="H15" s="50"/>
-      <c r="I15" s="49"/>
-      <c r="J15" s="35"/>
-      <c r="K15" s="35"/>
-      <c r="L15" s="36"/>
-      <c r="M15" s="51" t="s">
-        <v>105</v>
-      </c>
-      <c r="N15" s="50"/>
-      <c r="O15" s="50"/>
-      <c r="P15" s="50"/>
-      <c r="Q15" s="50"/>
-      <c r="R15" s="50"/>
-      <c r="S15" s="50"/>
-      <c r="T15" s="50"/>
-      <c r="U15" s="50"/>
-      <c r="V15" s="50"/>
-      <c r="W15" s="50"/>
-      <c r="X15" s="50"/>
+        <v>95</v>
+      </c>
+      <c r="B15" s="67"/>
+      <c r="C15" s="67"/>
+      <c r="D15" s="67"/>
+      <c r="E15" s="67"/>
+      <c r="F15" s="67" t="s">
+        <v>101</v>
+      </c>
+      <c r="G15" s="67"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="69"/>
+      <c r="J15" s="70"/>
+      <c r="K15" s="70"/>
+      <c r="L15" s="71"/>
+      <c r="M15" s="68" t="s">
+        <v>104</v>
+      </c>
+      <c r="N15" s="67"/>
+      <c r="O15" s="67"/>
+      <c r="P15" s="67"/>
+      <c r="Q15" s="67"/>
+      <c r="R15" s="67"/>
+      <c r="S15" s="67"/>
+      <c r="T15" s="67"/>
+      <c r="U15" s="67"/>
+      <c r="V15" s="67"/>
+      <c r="W15" s="67"/>
+      <c r="X15" s="67"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B16" s="50" t="s">
-        <v>107</v>
-      </c>
-      <c r="C16" s="50"/>
-      <c r="D16" s="50"/>
-      <c r="E16" s="50"/>
-      <c r="F16" s="50" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="67" t="s">
         <v>106</v>
       </c>
-      <c r="G16" s="50"/>
-      <c r="H16" s="50"/>
-      <c r="I16" s="49" t="s">
-        <v>87</v>
-      </c>
-      <c r="J16" s="35"/>
-      <c r="K16" s="35"/>
-      <c r="L16" s="36"/>
-      <c r="M16" s="50"/>
-      <c r="N16" s="50"/>
-      <c r="O16" s="50"/>
-      <c r="P16" s="50" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q16" s="50"/>
-      <c r="R16" s="50"/>
-      <c r="S16" s="50"/>
-      <c r="T16" s="50"/>
-      <c r="U16" s="50"/>
-      <c r="V16" s="50"/>
-      <c r="W16" s="50"/>
-      <c r="X16" s="50"/>
+      <c r="C16" s="67"/>
+      <c r="D16" s="67"/>
+      <c r="E16" s="67"/>
+      <c r="F16" s="67" t="s">
+        <v>105</v>
+      </c>
+      <c r="G16" s="67"/>
+      <c r="H16" s="67"/>
+      <c r="I16" s="69" t="s">
+        <v>86</v>
+      </c>
+      <c r="J16" s="70"/>
+      <c r="K16" s="70"/>
+      <c r="L16" s="71"/>
+      <c r="M16" s="67"/>
+      <c r="N16" s="67"/>
+      <c r="O16" s="67"/>
+      <c r="P16" s="67" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q16" s="67"/>
+      <c r="R16" s="67"/>
+      <c r="S16" s="67"/>
+      <c r="T16" s="67"/>
+      <c r="U16" s="67"/>
+      <c r="V16" s="67"/>
+      <c r="W16" s="67"/>
+      <c r="X16" s="67"/>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="50" t="s">
+      <c r="B17" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="50"/>
-      <c r="D17" s="50"/>
-      <c r="E17" s="50"/>
-      <c r="F17" s="50"/>
-      <c r="G17" s="50"/>
-      <c r="H17" s="50"/>
-      <c r="I17" s="49" t="s">
+      <c r="C17" s="67"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="67"/>
+      <c r="F17" s="67"/>
+      <c r="G17" s="67"/>
+      <c r="H17" s="67"/>
+      <c r="I17" s="69" t="s">
         <v>55</v>
       </c>
-      <c r="J17" s="35"/>
-      <c r="K17" s="35"/>
-      <c r="L17" s="36"/>
-      <c r="M17" s="50"/>
-      <c r="N17" s="50"/>
-      <c r="O17" s="50"/>
-      <c r="P17" s="50" t="s">
+      <c r="J17" s="70"/>
+      <c r="K17" s="70"/>
+      <c r="L17" s="71"/>
+      <c r="M17" s="67"/>
+      <c r="N17" s="67"/>
+      <c r="O17" s="67"/>
+      <c r="P17" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="Q17" s="50"/>
-      <c r="R17" s="50"/>
-      <c r="S17" s="50"/>
-      <c r="T17" s="50"/>
-      <c r="U17" s="50"/>
-      <c r="V17" s="50"/>
-      <c r="W17" s="50"/>
-      <c r="X17" s="50"/>
+      <c r="Q17" s="67"/>
+      <c r="R17" s="67"/>
+      <c r="S17" s="67"/>
+      <c r="T17" s="67"/>
+      <c r="U17" s="67"/>
+      <c r="V17" s="67"/>
+      <c r="W17" s="67"/>
+      <c r="X17" s="67"/>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B18" s="50" t="s">
+      <c r="B18" s="67" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="50"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="50"/>
-      <c r="H18" s="50"/>
-      <c r="I18" s="49" t="s">
-        <v>61</v>
-      </c>
-      <c r="J18" s="35"/>
-      <c r="K18" s="35"/>
-      <c r="L18" s="36"/>
-      <c r="M18" s="50"/>
-      <c r="N18" s="50"/>
-      <c r="O18" s="50"/>
-      <c r="P18" s="50" t="s">
+      <c r="C18" s="67"/>
+      <c r="D18" s="67"/>
+      <c r="E18" s="67"/>
+      <c r="F18" s="67"/>
+      <c r="G18" s="67"/>
+      <c r="H18" s="67"/>
+      <c r="I18" s="69" t="s">
+        <v>211</v>
+      </c>
+      <c r="J18" s="70"/>
+      <c r="K18" s="70"/>
+      <c r="L18" s="71"/>
+      <c r="M18" s="67"/>
+      <c r="N18" s="67"/>
+      <c r="O18" s="67"/>
+      <c r="P18" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="Q18" s="50"/>
-      <c r="R18" s="50"/>
-      <c r="S18" s="50"/>
-      <c r="T18" s="50"/>
-      <c r="U18" s="50"/>
-      <c r="V18" s="50"/>
-      <c r="W18" s="50"/>
-      <c r="X18" s="50"/>
+      <c r="Q18" s="67"/>
+      <c r="R18" s="67"/>
+      <c r="S18" s="67"/>
+      <c r="T18" s="67"/>
+      <c r="U18" s="67"/>
+      <c r="V18" s="67"/>
+      <c r="W18" s="67"/>
+      <c r="X18" s="67"/>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B19" s="50" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19" s="50"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="49" t="s">
-        <v>63</v>
-      </c>
-      <c r="J19" s="35"/>
-      <c r="K19" s="35"/>
-      <c r="L19" s="36"/>
-      <c r="M19" s="50"/>
-      <c r="N19" s="50"/>
-      <c r="O19" s="50"/>
-      <c r="P19" s="50" t="s">
+      <c r="B19" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="Q19" s="50"/>
-      <c r="R19" s="50"/>
-      <c r="S19" s="50"/>
-      <c r="T19" s="50"/>
-      <c r="U19" s="50"/>
-      <c r="V19" s="50"/>
-      <c r="W19" s="50"/>
-      <c r="X19" s="50"/>
+      <c r="C19" s="67"/>
+      <c r="D19" s="67"/>
+      <c r="E19" s="67"/>
+      <c r="F19" s="67"/>
+      <c r="G19" s="67"/>
+      <c r="H19" s="67"/>
+      <c r="I19" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="J19" s="70"/>
+      <c r="K19" s="70"/>
+      <c r="L19" s="71"/>
+      <c r="M19" s="67"/>
+      <c r="N19" s="67"/>
+      <c r="O19" s="67"/>
+      <c r="P19" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q19" s="67"/>
+      <c r="R19" s="67"/>
+      <c r="S19" s="67"/>
+      <c r="T19" s="67"/>
+      <c r="U19" s="67"/>
+      <c r="V19" s="67"/>
+      <c r="W19" s="67"/>
+      <c r="X19" s="67"/>
     </row>
     <row r="20" spans="1:24" ht="45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" s="67" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" s="67"/>
+      <c r="D20" s="67"/>
+      <c r="E20" s="67"/>
+      <c r="F20" s="68" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="50" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" s="50"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="51" t="s">
+      <c r="G20" s="67"/>
+      <c r="H20" s="67"/>
+      <c r="I20" s="72" t="s">
+        <v>73</v>
+      </c>
+      <c r="J20" s="73"/>
+      <c r="K20" s="73"/>
+      <c r="L20" s="74"/>
+      <c r="M20" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="G20" s="50"/>
-      <c r="H20" s="50"/>
-      <c r="I20" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="J20" s="52"/>
-      <c r="K20" s="52"/>
-      <c r="L20" s="53"/>
-      <c r="M20" s="51" t="s">
-        <v>73</v>
-      </c>
-      <c r="N20" s="50"/>
-      <c r="O20" s="50"/>
-      <c r="P20" s="50"/>
-      <c r="Q20" s="50"/>
-      <c r="R20" s="50"/>
-      <c r="S20" s="50"/>
-      <c r="T20" s="50"/>
-      <c r="U20" s="50"/>
-      <c r="V20" s="50"/>
-      <c r="W20" s="50"/>
-      <c r="X20" s="50"/>
+      <c r="N20" s="67"/>
+      <c r="O20" s="67"/>
+      <c r="P20" s="67"/>
+      <c r="Q20" s="67"/>
+      <c r="R20" s="67"/>
+      <c r="S20" s="67"/>
+      <c r="T20" s="67"/>
+      <c r="U20" s="67"/>
+      <c r="V20" s="67"/>
+      <c r="W20" s="67"/>
+      <c r="X20" s="67"/>
     </row>
     <row r="21" spans="1:24" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="68" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" s="67"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="67"/>
+      <c r="H21" s="67"/>
+      <c r="I21" s="69" t="s">
+        <v>78</v>
+      </c>
+      <c r="J21" s="70"/>
+      <c r="K21" s="70"/>
+      <c r="L21" s="71"/>
+      <c r="M21" s="68" t="s">
+        <v>77</v>
+      </c>
+      <c r="N21" s="67"/>
+      <c r="O21" s="67"/>
+      <c r="P21" s="67" t="s">
         <v>75</v>
       </c>
-      <c r="B21" s="51" t="s">
-        <v>77</v>
-      </c>
-      <c r="C21" s="50"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="50"/>
-      <c r="F21" s="50"/>
-      <c r="G21" s="50"/>
-      <c r="H21" s="50"/>
-      <c r="I21" s="49" t="s">
-        <v>79</v>
-      </c>
-      <c r="J21" s="35"/>
-      <c r="K21" s="35"/>
-      <c r="L21" s="36"/>
-      <c r="M21" s="51" t="s">
-        <v>78</v>
-      </c>
-      <c r="N21" s="50"/>
-      <c r="O21" s="50"/>
-      <c r="P21" s="50" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q21" s="50"/>
-      <c r="R21" s="50"/>
-      <c r="S21" s="50"/>
-      <c r="T21" s="50"/>
-      <c r="U21" s="50"/>
-      <c r="V21" s="50"/>
-      <c r="W21" s="50"/>
-      <c r="X21" s="50"/>
+      <c r="Q21" s="67"/>
+      <c r="R21" s="67"/>
+      <c r="S21" s="67"/>
+      <c r="T21" s="67"/>
+      <c r="U21" s="67"/>
+      <c r="V21" s="67"/>
+      <c r="W21" s="67"/>
+      <c r="X21" s="67"/>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B22" s="67" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" s="67"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="67" t="s">
+        <v>82</v>
+      </c>
+      <c r="G22" s="67"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="69" t="s">
         <v>80</v>
       </c>
-      <c r="B22" s="50" t="s">
-        <v>82</v>
-      </c>
-      <c r="C22" s="50"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="50"/>
-      <c r="F22" s="50" t="s">
+      <c r="J22" s="70"/>
+      <c r="K22" s="70"/>
+      <c r="L22" s="71"/>
+      <c r="M22" s="67" t="s">
         <v>83</v>
       </c>
-      <c r="G22" s="50"/>
-      <c r="H22" s="50"/>
-      <c r="I22" s="49" t="s">
-        <v>81</v>
-      </c>
-      <c r="J22" s="35"/>
-      <c r="K22" s="35"/>
-      <c r="L22" s="36"/>
-      <c r="M22" s="50" t="s">
-        <v>84</v>
-      </c>
-      <c r="N22" s="50"/>
-      <c r="O22" s="50"/>
-      <c r="P22" s="50" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q22" s="50"/>
-      <c r="R22" s="50"/>
-      <c r="S22" s="50"/>
-      <c r="T22" s="50"/>
-      <c r="U22" s="50"/>
-      <c r="V22" s="50"/>
-      <c r="W22" s="50"/>
-      <c r="X22" s="50"/>
+      <c r="N22" s="67"/>
+      <c r="O22" s="67"/>
+      <c r="P22" s="67" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q22" s="67"/>
+      <c r="R22" s="67"/>
+      <c r="S22" s="67"/>
+      <c r="T22" s="67"/>
+      <c r="U22" s="67"/>
+      <c r="V22" s="67"/>
+      <c r="W22" s="67"/>
+      <c r="X22" s="67"/>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B23" s="50" t="s">
+        <v>85</v>
+      </c>
+      <c r="B23" s="67" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" s="67"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="67"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="67"/>
+      <c r="H23" s="67"/>
+      <c r="I23" s="69" t="s">
+        <v>84</v>
+      </c>
+      <c r="J23" s="70"/>
+      <c r="K23" s="70"/>
+      <c r="L23" s="71"/>
+      <c r="M23" s="67"/>
+      <c r="N23" s="67"/>
+      <c r="O23" s="67"/>
+      <c r="P23" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="C23" s="50"/>
-      <c r="D23" s="50"/>
-      <c r="E23" s="50"/>
-      <c r="F23" s="50"/>
-      <c r="G23" s="50"/>
-      <c r="H23" s="50"/>
-      <c r="I23" s="49" t="s">
-        <v>85</v>
-      </c>
-      <c r="J23" s="35"/>
-      <c r="K23" s="35"/>
-      <c r="L23" s="36"/>
-      <c r="M23" s="50"/>
-      <c r="N23" s="50"/>
-      <c r="O23" s="50"/>
-      <c r="P23" s="50" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q23" s="50"/>
-      <c r="R23" s="50"/>
-      <c r="S23" s="50"/>
-      <c r="T23" s="50"/>
-      <c r="U23" s="50"/>
-      <c r="V23" s="50"/>
-      <c r="W23" s="50"/>
-      <c r="X23" s="50"/>
+      <c r="Q23" s="67"/>
+      <c r="R23" s="67"/>
+      <c r="S23" s="67"/>
+      <c r="T23" s="67"/>
+      <c r="U23" s="67"/>
+      <c r="V23" s="67"/>
+      <c r="W23" s="67"/>
+      <c r="X23" s="67"/>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B24" s="50"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="50"/>
-      <c r="I24" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="J24" s="35"/>
-      <c r="K24" s="35"/>
-      <c r="L24" s="36"/>
-      <c r="M24" s="50"/>
-      <c r="N24" s="50"/>
-      <c r="O24" s="50"/>
-      <c r="P24" s="50"/>
-      <c r="Q24" s="50"/>
-      <c r="R24" s="50"/>
-      <c r="S24" s="50"/>
-      <c r="T24" s="50"/>
-      <c r="U24" s="50"/>
-      <c r="V24" s="50"/>
-      <c r="W24" s="50"/>
-      <c r="X24" s="50"/>
+      <c r="B24" s="67"/>
+      <c r="C24" s="67"/>
+      <c r="D24" s="67"/>
+      <c r="E24" s="67"/>
+      <c r="F24" s="67"/>
+      <c r="G24" s="67"/>
+      <c r="H24" s="67"/>
+      <c r="I24" s="69" t="s">
+        <v>90</v>
+      </c>
+      <c r="J24" s="70"/>
+      <c r="K24" s="70"/>
+      <c r="L24" s="71"/>
+      <c r="M24" s="67"/>
+      <c r="N24" s="67"/>
+      <c r="O24" s="67"/>
+      <c r="P24" s="67"/>
+      <c r="Q24" s="67"/>
+      <c r="R24" s="67"/>
+      <c r="S24" s="67"/>
+      <c r="T24" s="67"/>
+      <c r="U24" s="67"/>
+      <c r="V24" s="67"/>
+      <c r="W24" s="67"/>
+      <c r="X24" s="67"/>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B25" s="67"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="67"/>
+      <c r="F25" s="67" t="s">
         <v>109</v>
       </c>
-      <c r="B25" s="50"/>
-      <c r="C25" s="50"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="50"/>
-      <c r="F25" s="50" t="s">
+      <c r="G25" s="67"/>
+      <c r="H25" s="67"/>
+      <c r="I25" s="69" t="s">
+        <v>112</v>
+      </c>
+      <c r="J25" s="70"/>
+      <c r="K25" s="70"/>
+      <c r="L25" s="71"/>
+      <c r="M25" s="68" t="s">
         <v>110</v>
       </c>
-      <c r="G25" s="50"/>
-      <c r="H25" s="50"/>
-      <c r="I25" s="49" t="s">
-        <v>113</v>
-      </c>
-      <c r="J25" s="35"/>
-      <c r="K25" s="35"/>
-      <c r="L25" s="36"/>
-      <c r="M25" s="51" t="s">
+      <c r="N25" s="67"/>
+      <c r="O25" s="67"/>
+      <c r="P25" s="67" t="s">
         <v>111</v>
       </c>
-      <c r="N25" s="50"/>
-      <c r="O25" s="50"/>
-      <c r="P25" s="50" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q25" s="50"/>
-      <c r="R25" s="50"/>
-      <c r="S25" s="50"/>
-      <c r="T25" s="50"/>
-      <c r="U25" s="50"/>
-      <c r="V25" s="50"/>
-      <c r="W25" s="50"/>
-      <c r="X25" s="50"/>
+      <c r="Q25" s="67"/>
+      <c r="R25" s="67"/>
+      <c r="S25" s="67"/>
+      <c r="T25" s="67"/>
+      <c r="U25" s="67"/>
+      <c r="V25" s="67"/>
+      <c r="W25" s="67"/>
+      <c r="X25" s="67"/>
     </row>
     <row r="26" spans="1:24" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B26" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="C26" s="50"/>
-      <c r="D26" s="50"/>
-      <c r="E26" s="50"/>
-      <c r="F26" s="51" t="s">
+      <c r="B26" s="67" t="s">
+        <v>114</v>
+      </c>
+      <c r="C26" s="67"/>
+      <c r="D26" s="67"/>
+      <c r="E26" s="67"/>
+      <c r="F26" s="68" t="s">
+        <v>132</v>
+      </c>
+      <c r="G26" s="67"/>
+      <c r="H26" s="67"/>
+      <c r="I26" s="69" t="s">
+        <v>113</v>
+      </c>
+      <c r="J26" s="70"/>
+      <c r="K26" s="70"/>
+      <c r="L26" s="71"/>
+      <c r="M26" s="68" t="s">
         <v>133</v>
       </c>
-      <c r="G26" s="50"/>
-      <c r="H26" s="50"/>
-      <c r="I26" s="49" t="s">
-        <v>114</v>
-      </c>
-      <c r="J26" s="35"/>
-      <c r="K26" s="35"/>
-      <c r="L26" s="36"/>
-      <c r="M26" s="51" t="s">
-        <v>134</v>
-      </c>
-      <c r="N26" s="50"/>
-      <c r="O26" s="50"/>
-      <c r="P26" s="51" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q26" s="51"/>
-      <c r="R26" s="51"/>
-      <c r="S26" s="51"/>
-      <c r="T26" s="51"/>
-      <c r="U26" s="51"/>
-      <c r="V26" s="51"/>
-      <c r="W26" s="51"/>
-      <c r="X26" s="51"/>
+      <c r="N26" s="67"/>
+      <c r="O26" s="67"/>
+      <c r="P26" s="68" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q26" s="68"/>
+      <c r="R26" s="68"/>
+      <c r="S26" s="68"/>
+      <c r="T26" s="68"/>
+      <c r="U26" s="68"/>
+      <c r="V26" s="68"/>
+      <c r="W26" s="68"/>
+      <c r="X26" s="68"/>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B27" s="67"/>
+      <c r="C27" s="67"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="67"/>
+      <c r="F27" s="67"/>
+      <c r="G27" s="67"/>
+      <c r="H27" s="67"/>
+      <c r="I27" s="69" t="s">
         <v>117</v>
       </c>
-      <c r="B27" s="50"/>
-      <c r="C27" s="50"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="50"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="50"/>
-      <c r="I27" s="49" t="s">
-        <v>118</v>
-      </c>
-      <c r="J27" s="35"/>
-      <c r="K27" s="35"/>
-      <c r="L27" s="36"/>
-      <c r="M27" s="50"/>
-      <c r="N27" s="50"/>
-      <c r="O27" s="50"/>
-      <c r="P27" s="50"/>
-      <c r="Q27" s="50"/>
-      <c r="R27" s="50"/>
-      <c r="S27" s="50"/>
-      <c r="T27" s="50"/>
-      <c r="U27" s="50"/>
-      <c r="V27" s="50"/>
-      <c r="W27" s="50"/>
-      <c r="X27" s="50"/>
+      <c r="J27" s="70"/>
+      <c r="K27" s="70"/>
+      <c r="L27" s="71"/>
+      <c r="M27" s="67"/>
+      <c r="N27" s="67"/>
+      <c r="O27" s="67"/>
+      <c r="P27" s="67"/>
+      <c r="Q27" s="67"/>
+      <c r="R27" s="67"/>
+      <c r="S27" s="67"/>
+      <c r="T27" s="67"/>
+      <c r="U27" s="67"/>
+      <c r="V27" s="67"/>
+      <c r="W27" s="67"/>
+      <c r="X27" s="67"/>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B28" s="67"/>
+      <c r="C28" s="67"/>
+      <c r="D28" s="67"/>
+      <c r="E28" s="67"/>
+      <c r="F28" s="67"/>
+      <c r="G28" s="67"/>
+      <c r="H28" s="67"/>
+      <c r="I28" s="69" t="s">
         <v>119</v>
       </c>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="50"/>
-      <c r="E28" s="50"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="50"/>
-      <c r="H28" s="50"/>
-      <c r="I28" s="49" t="s">
-        <v>120</v>
-      </c>
-      <c r="J28" s="35"/>
-      <c r="K28" s="35"/>
-      <c r="L28" s="36"/>
-      <c r="M28" s="50"/>
-      <c r="N28" s="50"/>
-      <c r="O28" s="50"/>
-      <c r="P28" s="50"/>
-      <c r="Q28" s="50"/>
-      <c r="R28" s="50"/>
-      <c r="S28" s="50"/>
-      <c r="T28" s="50"/>
-      <c r="U28" s="50"/>
-      <c r="V28" s="50"/>
-      <c r="W28" s="50"/>
-      <c r="X28" s="50"/>
+      <c r="J28" s="70"/>
+      <c r="K28" s="70"/>
+      <c r="L28" s="71"/>
+      <c r="M28" s="67"/>
+      <c r="N28" s="67"/>
+      <c r="O28" s="67"/>
+      <c r="P28" s="67"/>
+      <c r="Q28" s="67"/>
+      <c r="R28" s="67"/>
+      <c r="S28" s="67"/>
+      <c r="T28" s="67"/>
+      <c r="U28" s="67"/>
+      <c r="V28" s="67"/>
+      <c r="W28" s="67"/>
+      <c r="X28" s="67"/>
     </row>
     <row r="29" spans="1:24" ht="56.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B29" s="68" t="s">
+        <v>125</v>
+      </c>
+      <c r="C29" s="68"/>
+      <c r="D29" s="68"/>
+      <c r="E29" s="68"/>
+      <c r="F29" s="68" t="s">
+        <v>120</v>
+      </c>
+      <c r="G29" s="67"/>
+      <c r="H29" s="67"/>
+      <c r="I29" s="69" t="s">
         <v>122</v>
       </c>
-      <c r="B29" s="51" t="s">
-        <v>126</v>
-      </c>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51"/>
-      <c r="F29" s="51" t="s">
-        <v>121</v>
-      </c>
-      <c r="G29" s="50"/>
-      <c r="H29" s="50"/>
-      <c r="I29" s="49" t="s">
+      <c r="J29" s="70"/>
+      <c r="K29" s="70"/>
+      <c r="L29" s="71"/>
+      <c r="M29" s="68" t="s">
         <v>123</v>
       </c>
-      <c r="J29" s="35"/>
-      <c r="K29" s="35"/>
-      <c r="L29" s="36"/>
-      <c r="M29" s="51" t="s">
+      <c r="N29" s="67"/>
+      <c r="O29" s="67"/>
+      <c r="P29" s="68" t="s">
         <v>124</v>
       </c>
-      <c r="N29" s="50"/>
-      <c r="O29" s="50"/>
-      <c r="P29" s="51" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q29" s="51"/>
-      <c r="R29" s="51"/>
-      <c r="S29" s="51"/>
-      <c r="T29" s="51"/>
-      <c r="U29" s="51"/>
-      <c r="V29" s="51"/>
-      <c r="W29" s="51"/>
-      <c r="X29" s="51"/>
+      <c r="Q29" s="68"/>
+      <c r="R29" s="68"/>
+      <c r="S29" s="68"/>
+      <c r="T29" s="68"/>
+      <c r="U29" s="68"/>
+      <c r="V29" s="68"/>
+      <c r="W29" s="68"/>
+      <c r="X29" s="68"/>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B30" s="67"/>
+      <c r="C30" s="67"/>
+      <c r="D30" s="67"/>
+      <c r="E30" s="67"/>
+      <c r="F30" s="67" t="s">
+        <v>136</v>
+      </c>
+      <c r="G30" s="67"/>
+      <c r="H30" s="67"/>
+      <c r="I30" s="69" t="s">
         <v>135</v>
       </c>
-      <c r="B30" s="50"/>
-      <c r="C30" s="50"/>
-      <c r="D30" s="50"/>
-      <c r="E30" s="50"/>
-      <c r="F30" s="50" t="s">
+      <c r="J30" s="70"/>
+      <c r="K30" s="70"/>
+      <c r="L30" s="71"/>
+      <c r="M30" s="67" t="s">
         <v>137</v>
       </c>
-      <c r="G30" s="50"/>
-      <c r="H30" s="50"/>
-      <c r="I30" s="49" t="s">
-        <v>136</v>
-      </c>
-      <c r="J30" s="35"/>
-      <c r="K30" s="35"/>
-      <c r="L30" s="36"/>
-      <c r="M30" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="N30" s="50"/>
-      <c r="O30" s="50"/>
-      <c r="P30" s="50"/>
-      <c r="Q30" s="50"/>
-      <c r="R30" s="50"/>
-      <c r="S30" s="50"/>
-      <c r="T30" s="50"/>
-      <c r="U30" s="50"/>
-      <c r="V30" s="50"/>
-      <c r="W30" s="50"/>
-      <c r="X30" s="50"/>
+      <c r="N30" s="67"/>
+      <c r="O30" s="67"/>
+      <c r="P30" s="67"/>
+      <c r="Q30" s="67"/>
+      <c r="R30" s="67"/>
+      <c r="S30" s="67"/>
+      <c r="T30" s="67"/>
+      <c r="U30" s="67"/>
+      <c r="V30" s="67"/>
+      <c r="W30" s="67"/>
+      <c r="X30" s="67"/>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B31" s="67" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" s="67"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="67"/>
+      <c r="F31" s="68" t="s">
         <v>143</v>
       </c>
-      <c r="B31" s="50" t="s">
+      <c r="G31" s="67"/>
+      <c r="H31" s="67"/>
+      <c r="I31" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="C31" s="50"/>
-      <c r="D31" s="50"/>
-      <c r="E31" s="50"/>
-      <c r="F31" s="51" t="s">
-        <v>144</v>
-      </c>
-      <c r="G31" s="50"/>
-      <c r="H31" s="50"/>
-      <c r="I31" s="49" t="s">
+      <c r="J31" s="70"/>
+      <c r="K31" s="70"/>
+      <c r="L31" s="71"/>
+      <c r="M31" s="68" t="s">
         <v>146</v>
       </c>
-      <c r="J31" s="35"/>
-      <c r="K31" s="35"/>
-      <c r="L31" s="36"/>
-      <c r="M31" s="51" t="s">
-        <v>147</v>
-      </c>
-      <c r="N31" s="50"/>
-      <c r="O31" s="50"/>
-      <c r="P31" s="50"/>
-      <c r="Q31" s="50"/>
-      <c r="R31" s="50"/>
-      <c r="S31" s="50"/>
-      <c r="T31" s="50"/>
-      <c r="U31" s="50"/>
-      <c r="V31" s="50"/>
-      <c r="W31" s="50"/>
-      <c r="X31" s="50"/>
+      <c r="N31" s="67"/>
+      <c r="O31" s="67"/>
+      <c r="P31" s="67"/>
+      <c r="Q31" s="67"/>
+      <c r="R31" s="67"/>
+      <c r="S31" s="67"/>
+      <c r="T31" s="67"/>
+      <c r="U31" s="67"/>
+      <c r="V31" s="67"/>
+      <c r="W31" s="67"/>
+      <c r="X31" s="67"/>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A32" s="3"/>
-      <c r="B32" s="50"/>
-      <c r="C32" s="50"/>
-      <c r="D32" s="50"/>
-      <c r="E32" s="50"/>
-      <c r="F32" s="50"/>
-      <c r="G32" s="50"/>
-      <c r="H32" s="50"/>
-      <c r="I32" s="49"/>
-      <c r="J32" s="35"/>
-      <c r="K32" s="35"/>
-      <c r="L32" s="36"/>
-      <c r="M32" s="50"/>
-      <c r="N32" s="50"/>
-      <c r="O32" s="50"/>
-      <c r="P32" s="50"/>
-      <c r="Q32" s="50"/>
-      <c r="R32" s="50"/>
-      <c r="S32" s="50"/>
-      <c r="T32" s="50"/>
-      <c r="U32" s="50"/>
-      <c r="V32" s="50"/>
-      <c r="W32" s="50"/>
-      <c r="X32" s="50"/>
+      <c r="A32" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B32" s="67"/>
+      <c r="C32" s="67"/>
+      <c r="D32" s="67"/>
+      <c r="E32" s="67"/>
+      <c r="F32" s="68" t="s">
+        <v>204</v>
+      </c>
+      <c r="G32" s="67"/>
+      <c r="H32" s="67"/>
+      <c r="I32" s="69"/>
+      <c r="J32" s="70"/>
+      <c r="K32" s="70"/>
+      <c r="L32" s="71"/>
+      <c r="M32" s="68" t="s">
+        <v>205</v>
+      </c>
+      <c r="N32" s="67"/>
+      <c r="O32" s="67"/>
+      <c r="P32" s="67" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q32" s="67"/>
+      <c r="R32" s="67"/>
+      <c r="S32" s="67"/>
+      <c r="T32" s="67"/>
+      <c r="U32" s="67"/>
+      <c r="V32" s="67"/>
+      <c r="W32" s="67"/>
+      <c r="X32" s="67"/>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A33" s="3"/>
-      <c r="B33" s="50"/>
-      <c r="C33" s="50"/>
-      <c r="D33" s="50"/>
-      <c r="E33" s="50"/>
-      <c r="F33" s="50"/>
-      <c r="G33" s="50"/>
-      <c r="H33" s="50"/>
-      <c r="I33" s="49"/>
-      <c r="J33" s="35"/>
-      <c r="K33" s="35"/>
-      <c r="L33" s="36"/>
-      <c r="M33" s="50"/>
-      <c r="N33" s="50"/>
-      <c r="O33" s="50"/>
-      <c r="P33" s="50"/>
-      <c r="Q33" s="50"/>
-      <c r="R33" s="50"/>
-      <c r="S33" s="50"/>
-      <c r="T33" s="50"/>
-      <c r="U33" s="50"/>
-      <c r="V33" s="50"/>
-      <c r="W33" s="50"/>
-      <c r="X33" s="50"/>
+      <c r="A33" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B33" s="67"/>
+      <c r="C33" s="67"/>
+      <c r="D33" s="67"/>
+      <c r="E33" s="67"/>
+      <c r="F33" s="67" t="s">
+        <v>207</v>
+      </c>
+      <c r="G33" s="67"/>
+      <c r="H33" s="67"/>
+      <c r="I33" s="69"/>
+      <c r="J33" s="70"/>
+      <c r="K33" s="70"/>
+      <c r="L33" s="71"/>
+      <c r="M33" s="67" t="s">
+        <v>206</v>
+      </c>
+      <c r="N33" s="67"/>
+      <c r="O33" s="67"/>
+      <c r="P33" s="67"/>
+      <c r="Q33" s="67"/>
+      <c r="R33" s="67"/>
+      <c r="S33" s="67"/>
+      <c r="T33" s="67"/>
+      <c r="U33" s="67"/>
+      <c r="V33" s="67"/>
+      <c r="W33" s="67"/>
+      <c r="X33" s="67"/>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A34" s="3"/>
-      <c r="B34" s="50"/>
-      <c r="C34" s="50"/>
-      <c r="D34" s="50"/>
-      <c r="E34" s="50"/>
-      <c r="F34" s="50"/>
-      <c r="G34" s="50"/>
-      <c r="H34" s="50"/>
-      <c r="I34" s="49"/>
-      <c r="J34" s="35"/>
-      <c r="K34" s="35"/>
-      <c r="L34" s="36"/>
-      <c r="M34" s="50"/>
-      <c r="N34" s="50"/>
-      <c r="O34" s="50"/>
-      <c r="P34" s="50"/>
-      <c r="Q34" s="50"/>
-      <c r="R34" s="50"/>
-      <c r="S34" s="50"/>
-      <c r="T34" s="50"/>
-      <c r="U34" s="50"/>
-      <c r="V34" s="50"/>
-      <c r="W34" s="50"/>
-      <c r="X34" s="50"/>
+      <c r="B34" s="67"/>
+      <c r="C34" s="67"/>
+      <c r="D34" s="67"/>
+      <c r="E34" s="67"/>
+      <c r="F34" s="67"/>
+      <c r="G34" s="67"/>
+      <c r="H34" s="67"/>
+      <c r="I34" s="69"/>
+      <c r="J34" s="70"/>
+      <c r="K34" s="70"/>
+      <c r="L34" s="71"/>
+      <c r="M34" s="67"/>
+      <c r="N34" s="67"/>
+      <c r="O34" s="67"/>
+      <c r="P34" s="67"/>
+      <c r="Q34" s="67"/>
+      <c r="R34" s="67"/>
+      <c r="S34" s="67"/>
+      <c r="T34" s="67"/>
+      <c r="U34" s="67"/>
+      <c r="V34" s="67"/>
+      <c r="W34" s="67"/>
+      <c r="X34" s="67"/>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A35" s="3"/>
-      <c r="B35" s="50"/>
-      <c r="C35" s="50"/>
-      <c r="D35" s="50"/>
-      <c r="E35" s="50"/>
-      <c r="F35" s="50"/>
-      <c r="G35" s="50"/>
-      <c r="H35" s="50"/>
-      <c r="I35" s="49"/>
-      <c r="J35" s="35"/>
-      <c r="K35" s="35"/>
-      <c r="L35" s="36"/>
-      <c r="M35" s="50"/>
-      <c r="N35" s="50"/>
-      <c r="O35" s="50"/>
-      <c r="P35" s="50"/>
-      <c r="Q35" s="50"/>
-      <c r="R35" s="50"/>
-      <c r="S35" s="50"/>
-      <c r="T35" s="50"/>
-      <c r="U35" s="50"/>
-      <c r="V35" s="50"/>
-      <c r="W35" s="50"/>
-      <c r="X35" s="50"/>
+      <c r="B35" s="67"/>
+      <c r="C35" s="67"/>
+      <c r="D35" s="67"/>
+      <c r="E35" s="67"/>
+      <c r="F35" s="67"/>
+      <c r="G35" s="67"/>
+      <c r="H35" s="67"/>
+      <c r="I35" s="69"/>
+      <c r="J35" s="70"/>
+      <c r="K35" s="70"/>
+      <c r="L35" s="71"/>
+      <c r="M35" s="67"/>
+      <c r="N35" s="67"/>
+      <c r="O35" s="67"/>
+      <c r="P35" s="67"/>
+      <c r="Q35" s="67"/>
+      <c r="R35" s="67"/>
+      <c r="S35" s="67"/>
+      <c r="T35" s="67"/>
+      <c r="U35" s="67"/>
+      <c r="V35" s="67"/>
+      <c r="W35" s="67"/>
+      <c r="X35" s="67"/>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A36" s="3"/>
-      <c r="B36" s="50"/>
-      <c r="C36" s="50"/>
-      <c r="D36" s="50"/>
-      <c r="E36" s="50"/>
-      <c r="F36" s="50"/>
-      <c r="G36" s="50"/>
-      <c r="H36" s="50"/>
-      <c r="I36" s="49"/>
-      <c r="J36" s="35"/>
-      <c r="K36" s="35"/>
-      <c r="L36" s="36"/>
-      <c r="M36" s="50"/>
-      <c r="N36" s="50"/>
-      <c r="O36" s="50"/>
-      <c r="P36" s="50"/>
-      <c r="Q36" s="50"/>
-      <c r="R36" s="50"/>
-      <c r="S36" s="50"/>
-      <c r="T36" s="50"/>
-      <c r="U36" s="50"/>
-      <c r="V36" s="50"/>
-      <c r="W36" s="50"/>
-      <c r="X36" s="50"/>
+      <c r="B36" s="67"/>
+      <c r="C36" s="67"/>
+      <c r="D36" s="67"/>
+      <c r="E36" s="67"/>
+      <c r="F36" s="67"/>
+      <c r="G36" s="67"/>
+      <c r="H36" s="67"/>
+      <c r="I36" s="69"/>
+      <c r="J36" s="70"/>
+      <c r="K36" s="70"/>
+      <c r="L36" s="71"/>
+      <c r="M36" s="67"/>
+      <c r="N36" s="67"/>
+      <c r="O36" s="67"/>
+      <c r="P36" s="67"/>
+      <c r="Q36" s="67"/>
+      <c r="R36" s="67"/>
+      <c r="S36" s="67"/>
+      <c r="T36" s="67"/>
+      <c r="U36" s="67"/>
+      <c r="V36" s="67"/>
+      <c r="W36" s="67"/>
+      <c r="X36" s="67"/>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A37" s="3"/>
-      <c r="B37" s="50"/>
-      <c r="C37" s="50"/>
-      <c r="D37" s="50"/>
-      <c r="E37" s="50"/>
-      <c r="F37" s="50"/>
-      <c r="G37" s="50"/>
-      <c r="H37" s="50"/>
-      <c r="I37" s="49"/>
-      <c r="J37" s="35"/>
-      <c r="K37" s="35"/>
-      <c r="L37" s="36"/>
-      <c r="M37" s="50"/>
-      <c r="N37" s="50"/>
-      <c r="O37" s="50"/>
-      <c r="P37" s="50"/>
-      <c r="Q37" s="50"/>
-      <c r="R37" s="50"/>
-      <c r="S37" s="50"/>
-      <c r="T37" s="50"/>
-      <c r="U37" s="50"/>
-      <c r="V37" s="50"/>
-      <c r="W37" s="50"/>
-      <c r="X37" s="50"/>
+      <c r="B37" s="67"/>
+      <c r="C37" s="67"/>
+      <c r="D37" s="67"/>
+      <c r="E37" s="67"/>
+      <c r="F37" s="67"/>
+      <c r="G37" s="67"/>
+      <c r="H37" s="67"/>
+      <c r="I37" s="69"/>
+      <c r="J37" s="70"/>
+      <c r="K37" s="70"/>
+      <c r="L37" s="71"/>
+      <c r="M37" s="67"/>
+      <c r="N37" s="67"/>
+      <c r="O37" s="67"/>
+      <c r="P37" s="67"/>
+      <c r="Q37" s="67"/>
+      <c r="R37" s="67"/>
+      <c r="S37" s="67"/>
+      <c r="T37" s="67"/>
+      <c r="U37" s="67"/>
+      <c r="V37" s="67"/>
+      <c r="W37" s="67"/>
+      <c r="X37" s="67"/>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A38" s="3"/>
-      <c r="B38" s="50"/>
-      <c r="C38" s="50"/>
-      <c r="D38" s="50"/>
-      <c r="E38" s="50"/>
-      <c r="F38" s="50"/>
-      <c r="G38" s="50"/>
-      <c r="H38" s="50"/>
-      <c r="I38" s="49"/>
-      <c r="J38" s="35"/>
-      <c r="K38" s="35"/>
-      <c r="L38" s="36"/>
-      <c r="M38" s="50"/>
-      <c r="N38" s="50"/>
-      <c r="O38" s="50"/>
-      <c r="P38" s="50"/>
-      <c r="Q38" s="50"/>
-      <c r="R38" s="50"/>
-      <c r="S38" s="50"/>
-      <c r="T38" s="50"/>
-      <c r="U38" s="50"/>
-      <c r="V38" s="50"/>
-      <c r="W38" s="50"/>
-      <c r="X38" s="50"/>
+      <c r="B38" s="67"/>
+      <c r="C38" s="67"/>
+      <c r="D38" s="67"/>
+      <c r="E38" s="67"/>
+      <c r="F38" s="67"/>
+      <c r="G38" s="67"/>
+      <c r="H38" s="67"/>
+      <c r="I38" s="69"/>
+      <c r="J38" s="70"/>
+      <c r="K38" s="70"/>
+      <c r="L38" s="71"/>
+      <c r="M38" s="67"/>
+      <c r="N38" s="67"/>
+      <c r="O38" s="67"/>
+      <c r="P38" s="67"/>
+      <c r="Q38" s="67"/>
+      <c r="R38" s="67"/>
+      <c r="S38" s="67"/>
+      <c r="T38" s="67"/>
+      <c r="U38" s="67"/>
+      <c r="V38" s="67"/>
+      <c r="W38" s="67"/>
+      <c r="X38" s="67"/>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A39" s="3"/>
-      <c r="B39" s="50"/>
-      <c r="C39" s="50"/>
-      <c r="D39" s="50"/>
-      <c r="E39" s="50"/>
-      <c r="F39" s="50"/>
-      <c r="G39" s="50"/>
-      <c r="H39" s="50"/>
-      <c r="I39" s="49"/>
-      <c r="J39" s="35"/>
-      <c r="K39" s="35"/>
-      <c r="L39" s="36"/>
-      <c r="M39" s="50"/>
-      <c r="N39" s="50"/>
-      <c r="O39" s="50"/>
-      <c r="P39" s="50"/>
-      <c r="Q39" s="50"/>
-      <c r="R39" s="50"/>
-      <c r="S39" s="50"/>
-      <c r="T39" s="50"/>
-      <c r="U39" s="50"/>
-      <c r="V39" s="50"/>
-      <c r="W39" s="50"/>
-      <c r="X39" s="50"/>
+      <c r="B39" s="67"/>
+      <c r="C39" s="67"/>
+      <c r="D39" s="67"/>
+      <c r="E39" s="67"/>
+      <c r="F39" s="67"/>
+      <c r="G39" s="67"/>
+      <c r="H39" s="67"/>
+      <c r="I39" s="69"/>
+      <c r="J39" s="70"/>
+      <c r="K39" s="70"/>
+      <c r="L39" s="71"/>
+      <c r="M39" s="67"/>
+      <c r="N39" s="67"/>
+      <c r="O39" s="67"/>
+      <c r="P39" s="67"/>
+      <c r="Q39" s="67"/>
+      <c r="R39" s="67"/>
+      <c r="S39" s="67"/>
+      <c r="T39" s="67"/>
+      <c r="U39" s="67"/>
+      <c r="V39" s="67"/>
+      <c r="W39" s="67"/>
+      <c r="X39" s="67"/>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A40" s="3"/>
-      <c r="B40" s="50"/>
-      <c r="C40" s="50"/>
-      <c r="D40" s="50"/>
-      <c r="E40" s="50"/>
-      <c r="F40" s="50"/>
-      <c r="G40" s="50"/>
-      <c r="H40" s="50"/>
-      <c r="I40" s="49"/>
-      <c r="J40" s="35"/>
-      <c r="K40" s="35"/>
-      <c r="L40" s="36"/>
-      <c r="M40" s="50"/>
-      <c r="N40" s="50"/>
-      <c r="O40" s="50"/>
-      <c r="P40" s="50"/>
-      <c r="Q40" s="50"/>
-      <c r="R40" s="50"/>
-      <c r="S40" s="50"/>
-      <c r="T40" s="50"/>
-      <c r="U40" s="50"/>
-      <c r="V40" s="50"/>
-      <c r="W40" s="50"/>
-      <c r="X40" s="50"/>
+      <c r="B40" s="67"/>
+      <c r="C40" s="67"/>
+      <c r="D40" s="67"/>
+      <c r="E40" s="67"/>
+      <c r="F40" s="67"/>
+      <c r="G40" s="67"/>
+      <c r="H40" s="67"/>
+      <c r="I40" s="69"/>
+      <c r="J40" s="70"/>
+      <c r="K40" s="70"/>
+      <c r="L40" s="71"/>
+      <c r="M40" s="67"/>
+      <c r="N40" s="67"/>
+      <c r="O40" s="67"/>
+      <c r="P40" s="67"/>
+      <c r="Q40" s="67"/>
+      <c r="R40" s="67"/>
+      <c r="S40" s="67"/>
+      <c r="T40" s="67"/>
+      <c r="U40" s="67"/>
+      <c r="V40" s="67"/>
+      <c r="W40" s="67"/>
+      <c r="X40" s="67"/>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A41" s="3"/>
-      <c r="B41" s="50"/>
-      <c r="C41" s="50"/>
-      <c r="D41" s="50"/>
-      <c r="E41" s="50"/>
-      <c r="F41" s="50"/>
-      <c r="G41" s="50"/>
-      <c r="H41" s="50"/>
-      <c r="I41" s="49"/>
-      <c r="J41" s="35"/>
-      <c r="K41" s="35"/>
-      <c r="L41" s="36"/>
-      <c r="M41" s="50"/>
-      <c r="N41" s="50"/>
-      <c r="O41" s="50"/>
-      <c r="P41" s="50"/>
-      <c r="Q41" s="50"/>
-      <c r="R41" s="50"/>
-      <c r="S41" s="50"/>
-      <c r="T41" s="50"/>
-      <c r="U41" s="50"/>
-      <c r="V41" s="50"/>
-      <c r="W41" s="50"/>
-      <c r="X41" s="50"/>
+      <c r="B41" s="67"/>
+      <c r="C41" s="67"/>
+      <c r="D41" s="67"/>
+      <c r="E41" s="67"/>
+      <c r="F41" s="67"/>
+      <c r="G41" s="67"/>
+      <c r="H41" s="67"/>
+      <c r="I41" s="69"/>
+      <c r="J41" s="70"/>
+      <c r="K41" s="70"/>
+      <c r="L41" s="71"/>
+      <c r="M41" s="67"/>
+      <c r="N41" s="67"/>
+      <c r="O41" s="67"/>
+      <c r="P41" s="67"/>
+      <c r="Q41" s="67"/>
+      <c r="R41" s="67"/>
+      <c r="S41" s="67"/>
+      <c r="T41" s="67"/>
+      <c r="U41" s="67"/>
+      <c r="V41" s="67"/>
+      <c r="W41" s="67"/>
+      <c r="X41" s="67"/>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A42" s="3"/>
-      <c r="B42" s="50"/>
-      <c r="C42" s="50"/>
-      <c r="D42" s="50"/>
-      <c r="E42" s="50"/>
-      <c r="F42" s="50"/>
-      <c r="G42" s="50"/>
-      <c r="H42" s="50"/>
-      <c r="I42" s="49"/>
-      <c r="J42" s="35"/>
-      <c r="K42" s="35"/>
-      <c r="L42" s="36"/>
-      <c r="M42" s="50"/>
-      <c r="N42" s="50"/>
-      <c r="O42" s="50"/>
-      <c r="P42" s="50"/>
-      <c r="Q42" s="50"/>
-      <c r="R42" s="50"/>
-      <c r="S42" s="50"/>
-      <c r="T42" s="50"/>
-      <c r="U42" s="50"/>
-      <c r="V42" s="50"/>
-      <c r="W42" s="50"/>
-      <c r="X42" s="50"/>
+      <c r="B42" s="67"/>
+      <c r="C42" s="67"/>
+      <c r="D42" s="67"/>
+      <c r="E42" s="67"/>
+      <c r="F42" s="67"/>
+      <c r="G42" s="67"/>
+      <c r="H42" s="67"/>
+      <c r="I42" s="69"/>
+      <c r="J42" s="70"/>
+      <c r="K42" s="70"/>
+      <c r="L42" s="71"/>
+      <c r="M42" s="67"/>
+      <c r="N42" s="67"/>
+      <c r="O42" s="67"/>
+      <c r="P42" s="67"/>
+      <c r="Q42" s="67"/>
+      <c r="R42" s="67"/>
+      <c r="S42" s="67"/>
+      <c r="T42" s="67"/>
+      <c r="U42" s="67"/>
+      <c r="V42" s="67"/>
+      <c r="W42" s="67"/>
+      <c r="X42" s="67"/>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A43" s="3"/>
-      <c r="B43" s="50"/>
-      <c r="C43" s="50"/>
-      <c r="D43" s="50"/>
-      <c r="E43" s="50"/>
-      <c r="F43" s="50"/>
-      <c r="G43" s="50"/>
-      <c r="H43" s="50"/>
-      <c r="I43" s="49"/>
-      <c r="J43" s="35"/>
-      <c r="K43" s="35"/>
-      <c r="L43" s="36"/>
-      <c r="M43" s="50"/>
-      <c r="N43" s="50"/>
-      <c r="O43" s="50"/>
-      <c r="P43" s="50"/>
-      <c r="Q43" s="50"/>
-      <c r="R43" s="50"/>
-      <c r="S43" s="50"/>
-      <c r="T43" s="50"/>
-      <c r="U43" s="50"/>
-      <c r="V43" s="50"/>
-      <c r="W43" s="50"/>
-      <c r="X43" s="50"/>
+      <c r="B43" s="67"/>
+      <c r="C43" s="67"/>
+      <c r="D43" s="67"/>
+      <c r="E43" s="67"/>
+      <c r="F43" s="67"/>
+      <c r="G43" s="67"/>
+      <c r="H43" s="67"/>
+      <c r="I43" s="69"/>
+      <c r="J43" s="70"/>
+      <c r="K43" s="70"/>
+      <c r="L43" s="71"/>
+      <c r="M43" s="67"/>
+      <c r="N43" s="67"/>
+      <c r="O43" s="67"/>
+      <c r="P43" s="67"/>
+      <c r="Q43" s="67"/>
+      <c r="R43" s="67"/>
+      <c r="S43" s="67"/>
+      <c r="T43" s="67"/>
+      <c r="U43" s="67"/>
+      <c r="V43" s="67"/>
+      <c r="W43" s="67"/>
+      <c r="X43" s="67"/>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A44" s="3"/>
-      <c r="B44" s="50"/>
-      <c r="C44" s="50"/>
-      <c r="D44" s="50"/>
-      <c r="E44" s="50"/>
-      <c r="F44" s="50"/>
-      <c r="G44" s="50"/>
-      <c r="H44" s="50"/>
-      <c r="I44" s="49"/>
-      <c r="J44" s="35"/>
-      <c r="K44" s="35"/>
-      <c r="L44" s="36"/>
-      <c r="M44" s="50"/>
-      <c r="N44" s="50"/>
-      <c r="O44" s="50"/>
-      <c r="P44" s="50"/>
-      <c r="Q44" s="50"/>
-      <c r="R44" s="50"/>
-      <c r="S44" s="50"/>
-      <c r="T44" s="50"/>
-      <c r="U44" s="50"/>
-      <c r="V44" s="50"/>
-      <c r="W44" s="50"/>
-      <c r="X44" s="50"/>
+      <c r="B44" s="67"/>
+      <c r="C44" s="67"/>
+      <c r="D44" s="67"/>
+      <c r="E44" s="67"/>
+      <c r="F44" s="67"/>
+      <c r="G44" s="67"/>
+      <c r="H44" s="67"/>
+      <c r="I44" s="69"/>
+      <c r="J44" s="70"/>
+      <c r="K44" s="70"/>
+      <c r="L44" s="71"/>
+      <c r="M44" s="67"/>
+      <c r="N44" s="67"/>
+      <c r="O44" s="67"/>
+      <c r="P44" s="67"/>
+      <c r="Q44" s="67"/>
+      <c r="R44" s="67"/>
+      <c r="S44" s="67"/>
+      <c r="T44" s="67"/>
+      <c r="U44" s="67"/>
+      <c r="V44" s="67"/>
+      <c r="W44" s="67"/>
+      <c r="X44" s="67"/>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A45" s="3"/>
-      <c r="B45" s="50"/>
-      <c r="C45" s="50"/>
-      <c r="D45" s="50"/>
-      <c r="E45" s="50"/>
-      <c r="F45" s="50"/>
-      <c r="G45" s="50"/>
-      <c r="H45" s="50"/>
-      <c r="I45" s="49"/>
-      <c r="J45" s="35"/>
-      <c r="K45" s="35"/>
-      <c r="L45" s="36"/>
-      <c r="M45" s="50"/>
-      <c r="N45" s="50"/>
-      <c r="O45" s="50"/>
-      <c r="P45" s="50"/>
-      <c r="Q45" s="50"/>
-      <c r="R45" s="50"/>
-      <c r="S45" s="50"/>
-      <c r="T45" s="50"/>
-      <c r="U45" s="50"/>
-      <c r="V45" s="50"/>
-      <c r="W45" s="50"/>
-      <c r="X45" s="50"/>
+      <c r="B45" s="67"/>
+      <c r="C45" s="67"/>
+      <c r="D45" s="67"/>
+      <c r="E45" s="67"/>
+      <c r="F45" s="67"/>
+      <c r="G45" s="67"/>
+      <c r="H45" s="67"/>
+      <c r="I45" s="69"/>
+      <c r="J45" s="70"/>
+      <c r="K45" s="70"/>
+      <c r="L45" s="71"/>
+      <c r="M45" s="67"/>
+      <c r="N45" s="67"/>
+      <c r="O45" s="67"/>
+      <c r="P45" s="67"/>
+      <c r="Q45" s="67"/>
+      <c r="R45" s="67"/>
+      <c r="S45" s="67"/>
+      <c r="T45" s="67"/>
+      <c r="U45" s="67"/>
+      <c r="V45" s="67"/>
+      <c r="W45" s="67"/>
+      <c r="X45" s="67"/>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A46" s="3"/>
-      <c r="B46" s="50"/>
-      <c r="C46" s="50"/>
-      <c r="D46" s="50"/>
-      <c r="E46" s="50"/>
-      <c r="F46" s="50"/>
-      <c r="G46" s="50"/>
-      <c r="H46" s="50"/>
-      <c r="I46" s="49"/>
-      <c r="J46" s="35"/>
-      <c r="K46" s="35"/>
-      <c r="L46" s="36"/>
-      <c r="M46" s="50"/>
-      <c r="N46" s="50"/>
-      <c r="O46" s="50"/>
-      <c r="P46" s="50"/>
-      <c r="Q46" s="50"/>
-      <c r="R46" s="50"/>
-      <c r="S46" s="50"/>
-      <c r="T46" s="50"/>
-      <c r="U46" s="50"/>
-      <c r="V46" s="50"/>
-      <c r="W46" s="50"/>
-      <c r="X46" s="50"/>
+      <c r="B46" s="67"/>
+      <c r="C46" s="67"/>
+      <c r="D46" s="67"/>
+      <c r="E46" s="67"/>
+      <c r="F46" s="67"/>
+      <c r="G46" s="67"/>
+      <c r="H46" s="67"/>
+      <c r="I46" s="69"/>
+      <c r="J46" s="70"/>
+      <c r="K46" s="70"/>
+      <c r="L46" s="71"/>
+      <c r="M46" s="67"/>
+      <c r="N46" s="67"/>
+      <c r="O46" s="67"/>
+      <c r="P46" s="67"/>
+      <c r="Q46" s="67"/>
+      <c r="R46" s="67"/>
+      <c r="S46" s="67"/>
+      <c r="T46" s="67"/>
+      <c r="U46" s="67"/>
+      <c r="V46" s="67"/>
+      <c r="W46" s="67"/>
+      <c r="X46" s="67"/>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A47" s="3"/>
-      <c r="B47" s="50"/>
-      <c r="C47" s="50"/>
-      <c r="D47" s="50"/>
-      <c r="E47" s="50"/>
-      <c r="F47" s="50"/>
-      <c r="G47" s="50"/>
-      <c r="H47" s="50"/>
-      <c r="I47" s="49"/>
-      <c r="J47" s="35"/>
-      <c r="K47" s="35"/>
-      <c r="L47" s="36"/>
-      <c r="M47" s="50"/>
-      <c r="N47" s="50"/>
-      <c r="O47" s="50"/>
-      <c r="P47" s="50"/>
-      <c r="Q47" s="50"/>
-      <c r="R47" s="50"/>
-      <c r="S47" s="50"/>
-      <c r="T47" s="50"/>
-      <c r="U47" s="50"/>
-      <c r="V47" s="50"/>
-      <c r="W47" s="50"/>
-      <c r="X47" s="50"/>
+      <c r="B47" s="67"/>
+      <c r="C47" s="67"/>
+      <c r="D47" s="67"/>
+      <c r="E47" s="67"/>
+      <c r="F47" s="67"/>
+      <c r="G47" s="67"/>
+      <c r="H47" s="67"/>
+      <c r="I47" s="69"/>
+      <c r="J47" s="70"/>
+      <c r="K47" s="70"/>
+      <c r="L47" s="71"/>
+      <c r="M47" s="67"/>
+      <c r="N47" s="67"/>
+      <c r="O47" s="67"/>
+      <c r="P47" s="67"/>
+      <c r="Q47" s="67"/>
+      <c r="R47" s="67"/>
+      <c r="S47" s="67"/>
+      <c r="T47" s="67"/>
+      <c r="U47" s="67"/>
+      <c r="V47" s="67"/>
+      <c r="W47" s="67"/>
+      <c r="X47" s="67"/>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A48" s="3"/>
-      <c r="B48" s="50"/>
-      <c r="C48" s="50"/>
-      <c r="D48" s="50"/>
-      <c r="E48" s="50"/>
-      <c r="F48" s="50"/>
-      <c r="G48" s="50"/>
-      <c r="H48" s="50"/>
-      <c r="I48" s="49"/>
-      <c r="J48" s="35"/>
-      <c r="K48" s="35"/>
-      <c r="L48" s="36"/>
-      <c r="M48" s="50"/>
-      <c r="N48" s="50"/>
-      <c r="O48" s="50"/>
-      <c r="P48" s="50"/>
-      <c r="Q48" s="50"/>
-      <c r="R48" s="50"/>
-      <c r="S48" s="50"/>
-      <c r="T48" s="50"/>
-      <c r="U48" s="50"/>
-      <c r="V48" s="50"/>
-      <c r="W48" s="50"/>
-      <c r="X48" s="50"/>
+      <c r="B48" s="67"/>
+      <c r="C48" s="67"/>
+      <c r="D48" s="67"/>
+      <c r="E48" s="67"/>
+      <c r="F48" s="67"/>
+      <c r="G48" s="67"/>
+      <c r="H48" s="67"/>
+      <c r="I48" s="69"/>
+      <c r="J48" s="70"/>
+      <c r="K48" s="70"/>
+      <c r="L48" s="71"/>
+      <c r="M48" s="67"/>
+      <c r="N48" s="67"/>
+      <c r="O48" s="67"/>
+      <c r="P48" s="67"/>
+      <c r="Q48" s="67"/>
+      <c r="R48" s="67"/>
+      <c r="S48" s="67"/>
+      <c r="T48" s="67"/>
+      <c r="U48" s="67"/>
+      <c r="V48" s="67"/>
+      <c r="W48" s="67"/>
+      <c r="X48" s="67"/>
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A49" s="3"/>
-      <c r="B49" s="50"/>
-      <c r="C49" s="50"/>
-      <c r="D49" s="50"/>
-      <c r="E49" s="50"/>
-      <c r="F49" s="50"/>
-      <c r="G49" s="50"/>
-      <c r="H49" s="50"/>
-      <c r="I49" s="49"/>
-      <c r="J49" s="35"/>
-      <c r="K49" s="35"/>
-      <c r="L49" s="36"/>
-      <c r="M49" s="50"/>
-      <c r="N49" s="50"/>
-      <c r="O49" s="50"/>
-      <c r="P49" s="50"/>
-      <c r="Q49" s="50"/>
-      <c r="R49" s="50"/>
-      <c r="S49" s="50"/>
-      <c r="T49" s="50"/>
-      <c r="U49" s="50"/>
-      <c r="V49" s="50"/>
-      <c r="W49" s="50"/>
-      <c r="X49" s="50"/>
+      <c r="B49" s="67"/>
+      <c r="C49" s="67"/>
+      <c r="D49" s="67"/>
+      <c r="E49" s="67"/>
+      <c r="F49" s="67"/>
+      <c r="G49" s="67"/>
+      <c r="H49" s="67"/>
+      <c r="I49" s="69"/>
+      <c r="J49" s="70"/>
+      <c r="K49" s="70"/>
+      <c r="L49" s="71"/>
+      <c r="M49" s="67"/>
+      <c r="N49" s="67"/>
+      <c r="O49" s="67"/>
+      <c r="P49" s="67"/>
+      <c r="Q49" s="67"/>
+      <c r="R49" s="67"/>
+      <c r="S49" s="67"/>
+      <c r="T49" s="67"/>
+      <c r="U49" s="67"/>
+      <c r="V49" s="67"/>
+      <c r="W49" s="67"/>
+      <c r="X49" s="67"/>
     </row>
     <row r="50" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A50" s="3"/>
-      <c r="B50" s="50"/>
-      <c r="C50" s="50"/>
-      <c r="D50" s="50"/>
-      <c r="E50" s="50"/>
-      <c r="F50" s="50"/>
-      <c r="G50" s="50"/>
-      <c r="H50" s="50"/>
-      <c r="I50" s="49"/>
-      <c r="J50" s="35"/>
-      <c r="K50" s="35"/>
-      <c r="L50" s="36"/>
-      <c r="M50" s="50"/>
-      <c r="N50" s="50"/>
-      <c r="O50" s="50"/>
-      <c r="P50" s="50"/>
-      <c r="Q50" s="50"/>
-      <c r="R50" s="50"/>
-      <c r="S50" s="50"/>
-      <c r="T50" s="50"/>
-      <c r="U50" s="50"/>
-      <c r="V50" s="50"/>
-      <c r="W50" s="50"/>
-      <c r="X50" s="50"/>
+      <c r="B50" s="67"/>
+      <c r="C50" s="67"/>
+      <c r="D50" s="67"/>
+      <c r="E50" s="67"/>
+      <c r="F50" s="67"/>
+      <c r="G50" s="67"/>
+      <c r="H50" s="67"/>
+      <c r="I50" s="69"/>
+      <c r="J50" s="70"/>
+      <c r="K50" s="70"/>
+      <c r="L50" s="71"/>
+      <c r="M50" s="67"/>
+      <c r="N50" s="67"/>
+      <c r="O50" s="67"/>
+      <c r="P50" s="67"/>
+      <c r="Q50" s="67"/>
+      <c r="R50" s="67"/>
+      <c r="S50" s="67"/>
+      <c r="T50" s="67"/>
+      <c r="U50" s="67"/>
+      <c r="V50" s="67"/>
+      <c r="W50" s="67"/>
+      <c r="X50" s="67"/>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A51" s="3"/>
-      <c r="B51" s="50"/>
-      <c r="C51" s="50"/>
-      <c r="D51" s="50"/>
-      <c r="E51" s="50"/>
-      <c r="F51" s="50"/>
-      <c r="G51" s="50"/>
-      <c r="H51" s="50"/>
-      <c r="I51" s="49"/>
-      <c r="J51" s="35"/>
-      <c r="K51" s="35"/>
-      <c r="L51" s="36"/>
-      <c r="M51" s="50"/>
-      <c r="N51" s="50"/>
-      <c r="O51" s="50"/>
-      <c r="P51" s="50"/>
-      <c r="Q51" s="50"/>
-      <c r="R51" s="50"/>
-      <c r="S51" s="50"/>
-      <c r="T51" s="50"/>
-      <c r="U51" s="50"/>
-      <c r="V51" s="50"/>
-      <c r="W51" s="50"/>
-      <c r="X51" s="50"/>
+      <c r="B51" s="67"/>
+      <c r="C51" s="67"/>
+      <c r="D51" s="67"/>
+      <c r="E51" s="67"/>
+      <c r="F51" s="67"/>
+      <c r="G51" s="67"/>
+      <c r="H51" s="67"/>
+      <c r="I51" s="69"/>
+      <c r="J51" s="70"/>
+      <c r="K51" s="70"/>
+      <c r="L51" s="71"/>
+      <c r="M51" s="67"/>
+      <c r="N51" s="67"/>
+      <c r="O51" s="67"/>
+      <c r="P51" s="67"/>
+      <c r="Q51" s="67"/>
+      <c r="R51" s="67"/>
+      <c r="S51" s="67"/>
+      <c r="T51" s="67"/>
+      <c r="U51" s="67"/>
+      <c r="V51" s="67"/>
+      <c r="W51" s="67"/>
+      <c r="X51" s="67"/>
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A52" s="3"/>
-      <c r="B52" s="50"/>
-      <c r="C52" s="50"/>
-      <c r="D52" s="50"/>
-      <c r="E52" s="50"/>
-      <c r="F52" s="50"/>
-      <c r="G52" s="50"/>
-      <c r="H52" s="50"/>
-      <c r="I52" s="49"/>
-      <c r="J52" s="35"/>
-      <c r="K52" s="35"/>
-      <c r="L52" s="36"/>
-      <c r="M52" s="50"/>
-      <c r="N52" s="50"/>
-      <c r="O52" s="50"/>
-      <c r="P52" s="50"/>
-      <c r="Q52" s="50"/>
-      <c r="R52" s="50"/>
-      <c r="S52" s="50"/>
-      <c r="T52" s="50"/>
-      <c r="U52" s="50"/>
-      <c r="V52" s="50"/>
-      <c r="W52" s="50"/>
-      <c r="X52" s="50"/>
+      <c r="B52" s="67"/>
+      <c r="C52" s="67"/>
+      <c r="D52" s="67"/>
+      <c r="E52" s="67"/>
+      <c r="F52" s="67"/>
+      <c r="G52" s="67"/>
+      <c r="H52" s="67"/>
+      <c r="I52" s="69"/>
+      <c r="J52" s="70"/>
+      <c r="K52" s="70"/>
+      <c r="L52" s="71"/>
+      <c r="M52" s="67"/>
+      <c r="N52" s="67"/>
+      <c r="O52" s="67"/>
+      <c r="P52" s="67"/>
+      <c r="Q52" s="67"/>
+      <c r="R52" s="67"/>
+      <c r="S52" s="67"/>
+      <c r="T52" s="67"/>
+      <c r="U52" s="67"/>
+      <c r="V52" s="67"/>
+      <c r="W52" s="67"/>
+      <c r="X52" s="67"/>
     </row>
     <row r="53" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A53" s="3"/>
-      <c r="B53" s="50"/>
-      <c r="C53" s="50"/>
-      <c r="D53" s="50"/>
-      <c r="E53" s="50"/>
-      <c r="F53" s="50"/>
-      <c r="G53" s="50"/>
-      <c r="H53" s="50"/>
-      <c r="I53" s="50"/>
-      <c r="J53" s="50"/>
-      <c r="K53" s="50"/>
-      <c r="L53" s="50"/>
-      <c r="M53" s="50"/>
-      <c r="N53" s="50"/>
-      <c r="O53" s="50"/>
-      <c r="P53" s="50"/>
-      <c r="Q53" s="50"/>
-      <c r="R53" s="50"/>
-      <c r="S53" s="50"/>
-      <c r="T53" s="50"/>
-      <c r="U53" s="50"/>
-      <c r="V53" s="50"/>
-      <c r="W53" s="50"/>
-      <c r="X53" s="50"/>
+      <c r="B53" s="67"/>
+      <c r="C53" s="67"/>
+      <c r="D53" s="67"/>
+      <c r="E53" s="67"/>
+      <c r="F53" s="67"/>
+      <c r="G53" s="67"/>
+      <c r="H53" s="67"/>
+      <c r="I53" s="67"/>
+      <c r="J53" s="67"/>
+      <c r="K53" s="67"/>
+      <c r="L53" s="67"/>
+      <c r="M53" s="67"/>
+      <c r="N53" s="67"/>
+      <c r="O53" s="67"/>
+      <c r="P53" s="67"/>
+      <c r="Q53" s="67"/>
+      <c r="R53" s="67"/>
+      <c r="S53" s="67"/>
+      <c r="T53" s="67"/>
+      <c r="U53" s="67"/>
+      <c r="V53" s="67"/>
+      <c r="W53" s="67"/>
+      <c r="X53" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="256">
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="M20:O20"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="M5:O5"/>
+    <mergeCell ref="M6:O6"/>
+    <mergeCell ref="M7:O7"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="M17:O17"/>
+    <mergeCell ref="M18:O18"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="M16:O16"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="M13:O13"/>
+    <mergeCell ref="M14:O14"/>
+    <mergeCell ref="M15:O15"/>
+    <mergeCell ref="M25:O25"/>
+    <mergeCell ref="M26:O26"/>
+    <mergeCell ref="M27:O27"/>
+    <mergeCell ref="M43:O43"/>
+    <mergeCell ref="P2:X3"/>
+    <mergeCell ref="P16:X16"/>
+    <mergeCell ref="M44:O44"/>
+    <mergeCell ref="M35:O35"/>
+    <mergeCell ref="M36:O36"/>
+    <mergeCell ref="M37:O37"/>
+    <mergeCell ref="M38:O38"/>
+    <mergeCell ref="M39:O39"/>
+    <mergeCell ref="M21:O21"/>
+    <mergeCell ref="M22:O22"/>
+    <mergeCell ref="M23:O23"/>
+    <mergeCell ref="M33:O33"/>
+    <mergeCell ref="M34:O34"/>
+    <mergeCell ref="M28:O28"/>
+    <mergeCell ref="M29:O29"/>
+    <mergeCell ref="M32:O32"/>
+    <mergeCell ref="M30:O30"/>
+    <mergeCell ref="M31:O31"/>
+    <mergeCell ref="M24:O24"/>
+    <mergeCell ref="P12:X12"/>
+    <mergeCell ref="M50:O50"/>
+    <mergeCell ref="M51:O51"/>
+    <mergeCell ref="M52:O52"/>
+    <mergeCell ref="M53:O53"/>
+    <mergeCell ref="I4:L4"/>
+    <mergeCell ref="I5:L5"/>
+    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="I7:L7"/>
+    <mergeCell ref="I8:L8"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="I10:L10"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="M45:O45"/>
+    <mergeCell ref="M46:O46"/>
+    <mergeCell ref="M47:O47"/>
+    <mergeCell ref="M48:O48"/>
+    <mergeCell ref="M49:O49"/>
+    <mergeCell ref="M40:O40"/>
+    <mergeCell ref="M41:O41"/>
+    <mergeCell ref="M42:O42"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="I43:L43"/>
+    <mergeCell ref="I51:L51"/>
+    <mergeCell ref="I52:L52"/>
+    <mergeCell ref="I53:L53"/>
+    <mergeCell ref="P4:X4"/>
+    <mergeCell ref="P5:X5"/>
+    <mergeCell ref="P6:X6"/>
+    <mergeCell ref="P7:X7"/>
+    <mergeCell ref="P8:X8"/>
+    <mergeCell ref="P9:X9"/>
+    <mergeCell ref="P10:X10"/>
+    <mergeCell ref="P11:X11"/>
+    <mergeCell ref="P17:X17"/>
+    <mergeCell ref="P18:X18"/>
+    <mergeCell ref="P19:X19"/>
+    <mergeCell ref="P20:X20"/>
+    <mergeCell ref="I45:L45"/>
+    <mergeCell ref="I46:L46"/>
+    <mergeCell ref="I47:L47"/>
+    <mergeCell ref="I48:L48"/>
+    <mergeCell ref="I49:L49"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="I41:L41"/>
+    <mergeCell ref="I42:L42"/>
+    <mergeCell ref="I44:L44"/>
+    <mergeCell ref="P13:X13"/>
+    <mergeCell ref="P14:X14"/>
+    <mergeCell ref="P15:X15"/>
+    <mergeCell ref="P25:X25"/>
+    <mergeCell ref="P26:X26"/>
+    <mergeCell ref="P27:X27"/>
+    <mergeCell ref="P43:X43"/>
+    <mergeCell ref="I50:L50"/>
+    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="I36:L36"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="I33:L33"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="I29:L29"/>
     <mergeCell ref="I32:L32"/>
-    <mergeCell ref="M32:O32"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="P44:X44"/>
+    <mergeCell ref="P35:X35"/>
+    <mergeCell ref="P36:X36"/>
+    <mergeCell ref="P37:X37"/>
+    <mergeCell ref="P38:X38"/>
+    <mergeCell ref="P39:X39"/>
+    <mergeCell ref="P21:X21"/>
+    <mergeCell ref="P22:X22"/>
+    <mergeCell ref="P23:X23"/>
+    <mergeCell ref="P33:X33"/>
+    <mergeCell ref="P34:X34"/>
+    <mergeCell ref="P28:X28"/>
+    <mergeCell ref="P29:X29"/>
     <mergeCell ref="P32:X32"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="M30:O30"/>
     <mergeCell ref="P30:X30"/>
+    <mergeCell ref="P31:X31"/>
+    <mergeCell ref="P24:X24"/>
+    <mergeCell ref="P50:X50"/>
+    <mergeCell ref="P51:X51"/>
+    <mergeCell ref="P52:X52"/>
+    <mergeCell ref="P53:X53"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="P45:X45"/>
+    <mergeCell ref="P46:X46"/>
+    <mergeCell ref="P47:X47"/>
+    <mergeCell ref="P48:X48"/>
+    <mergeCell ref="P49:X49"/>
+    <mergeCell ref="P40:X40"/>
+    <mergeCell ref="P41:X41"/>
+    <mergeCell ref="P42:X42"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B32:E32"/>
     <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="F44:H44"/>
+    <mergeCell ref="F45:H45"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F32:H32"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="M31:O31"/>
-    <mergeCell ref="P31:X31"/>
     <mergeCell ref="F51:H51"/>
     <mergeCell ref="F52:H52"/>
     <mergeCell ref="F53:H53"/>
@@ -6076,227 +8358,6 @@
     <mergeCell ref="F41:H41"/>
     <mergeCell ref="F42:H42"/>
     <mergeCell ref="F43:H43"/>
-    <mergeCell ref="F44:H44"/>
-    <mergeCell ref="F45:H45"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="P50:X50"/>
-    <mergeCell ref="P51:X51"/>
-    <mergeCell ref="P52:X52"/>
-    <mergeCell ref="P53:X53"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="P45:X45"/>
-    <mergeCell ref="P46:X46"/>
-    <mergeCell ref="P47:X47"/>
-    <mergeCell ref="P48:X48"/>
-    <mergeCell ref="P49:X49"/>
-    <mergeCell ref="P40:X40"/>
-    <mergeCell ref="P41:X41"/>
-    <mergeCell ref="P42:X42"/>
-    <mergeCell ref="P43:X43"/>
-    <mergeCell ref="P44:X44"/>
-    <mergeCell ref="P35:X35"/>
-    <mergeCell ref="P36:X36"/>
-    <mergeCell ref="P37:X37"/>
-    <mergeCell ref="P38:X38"/>
-    <mergeCell ref="P39:X39"/>
-    <mergeCell ref="P21:X21"/>
-    <mergeCell ref="P22:X22"/>
-    <mergeCell ref="P23:X23"/>
-    <mergeCell ref="P33:X33"/>
-    <mergeCell ref="P34:X34"/>
-    <mergeCell ref="P16:X16"/>
-    <mergeCell ref="P24:X24"/>
-    <mergeCell ref="P12:X12"/>
-    <mergeCell ref="P13:X13"/>
-    <mergeCell ref="P14:X14"/>
-    <mergeCell ref="P15:X15"/>
-    <mergeCell ref="P25:X25"/>
-    <mergeCell ref="P26:X26"/>
-    <mergeCell ref="P27:X27"/>
-    <mergeCell ref="P28:X28"/>
-    <mergeCell ref="P29:X29"/>
-    <mergeCell ref="I50:L50"/>
-    <mergeCell ref="I51:L51"/>
-    <mergeCell ref="I52:L52"/>
-    <mergeCell ref="I53:L53"/>
-    <mergeCell ref="P4:X4"/>
-    <mergeCell ref="P5:X5"/>
-    <mergeCell ref="P6:X6"/>
-    <mergeCell ref="P7:X7"/>
-    <mergeCell ref="P8:X8"/>
-    <mergeCell ref="P9:X9"/>
-    <mergeCell ref="P10:X10"/>
-    <mergeCell ref="P11:X11"/>
-    <mergeCell ref="P17:X17"/>
-    <mergeCell ref="P18:X18"/>
-    <mergeCell ref="P19:X19"/>
-    <mergeCell ref="P20:X20"/>
-    <mergeCell ref="I45:L45"/>
-    <mergeCell ref="I46:L46"/>
-    <mergeCell ref="I47:L47"/>
-    <mergeCell ref="I48:L48"/>
-    <mergeCell ref="I49:L49"/>
-    <mergeCell ref="I40:L40"/>
-    <mergeCell ref="I41:L41"/>
-    <mergeCell ref="I42:L42"/>
-    <mergeCell ref="I43:L43"/>
-    <mergeCell ref="I44:L44"/>
-    <mergeCell ref="I35:L35"/>
-    <mergeCell ref="I36:L36"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="I33:L33"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="I27:L27"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="M50:O50"/>
-    <mergeCell ref="M51:O51"/>
-    <mergeCell ref="M52:O52"/>
-    <mergeCell ref="M53:O53"/>
-    <mergeCell ref="I4:L4"/>
-    <mergeCell ref="I5:L5"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="I7:L7"/>
-    <mergeCell ref="I8:L8"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="M45:O45"/>
-    <mergeCell ref="M46:O46"/>
-    <mergeCell ref="M47:O47"/>
-    <mergeCell ref="M48:O48"/>
-    <mergeCell ref="M49:O49"/>
-    <mergeCell ref="M40:O40"/>
-    <mergeCell ref="M41:O41"/>
-    <mergeCell ref="M42:O42"/>
-    <mergeCell ref="M43:O43"/>
-    <mergeCell ref="M44:O44"/>
-    <mergeCell ref="M35:O35"/>
-    <mergeCell ref="M36:O36"/>
-    <mergeCell ref="M37:O37"/>
-    <mergeCell ref="M38:O38"/>
-    <mergeCell ref="M39:O39"/>
-    <mergeCell ref="M21:O21"/>
-    <mergeCell ref="M22:O22"/>
-    <mergeCell ref="M23:O23"/>
-    <mergeCell ref="M33:O33"/>
-    <mergeCell ref="M34:O34"/>
-    <mergeCell ref="M16:O16"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="M13:O13"/>
-    <mergeCell ref="M14:O14"/>
-    <mergeCell ref="M15:O15"/>
-    <mergeCell ref="M25:O25"/>
-    <mergeCell ref="M26:O26"/>
-    <mergeCell ref="M27:O27"/>
-    <mergeCell ref="M28:O28"/>
-    <mergeCell ref="M29:O29"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="M20:O20"/>
-    <mergeCell ref="M4:O4"/>
-    <mergeCell ref="M5:O5"/>
-    <mergeCell ref="M6:O6"/>
-    <mergeCell ref="M7:O7"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="M17:O17"/>
-    <mergeCell ref="M18:O18"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="P2:X3"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="B3:E3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6306,9 +8367,12 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B96454FA-A95E-4D58-81B9-E68FAAFA79D0}">
-  <dimension ref="A1:G108"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B96454FA-A95E-4D58-81B9-E68FAAFA79D0}">
+  <dimension ref="A1:W163"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
@@ -6339,102 +8403,102 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B8" s="34" t="s">
+      <c r="B8" s="72" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
-      <c r="F8" s="35"/>
-      <c r="G8" s="36"/>
+      <c r="C8" s="70"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="70"/>
+      <c r="F8" s="70"/>
+      <c r="G8" s="71"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B9" s="37"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="39"/>
+      <c r="B9" s="89"/>
+      <c r="C9" s="90"/>
+      <c r="D9" s="90"/>
+      <c r="E9" s="90"/>
+      <c r="F9" s="90"/>
+      <c r="G9" s="91"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B10" s="37"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="39"/>
+      <c r="B10" s="89"/>
+      <c r="C10" s="90"/>
+      <c r="D10" s="90"/>
+      <c r="E10" s="90"/>
+      <c r="F10" s="90"/>
+      <c r="G10" s="91"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B11" s="37"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="38"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="39"/>
+      <c r="B11" s="89"/>
+      <c r="C11" s="90"/>
+      <c r="D11" s="90"/>
+      <c r="E11" s="90"/>
+      <c r="F11" s="90"/>
+      <c r="G11" s="91"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B12" s="37"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="39"/>
+      <c r="B12" s="89"/>
+      <c r="C12" s="90"/>
+      <c r="D12" s="90"/>
+      <c r="E12" s="90"/>
+      <c r="F12" s="90"/>
+      <c r="G12" s="91"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B13" s="37"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="39"/>
+      <c r="B13" s="89"/>
+      <c r="C13" s="90"/>
+      <c r="D13" s="90"/>
+      <c r="E13" s="90"/>
+      <c r="F13" s="90"/>
+      <c r="G13" s="91"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B14" s="37"/>
-      <c r="C14" s="38"/>
-      <c r="D14" s="38"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="39"/>
+      <c r="B14" s="89"/>
+      <c r="C14" s="90"/>
+      <c r="D14" s="90"/>
+      <c r="E14" s="90"/>
+      <c r="F14" s="90"/>
+      <c r="G14" s="91"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="37"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="39"/>
+      <c r="B15" s="89"/>
+      <c r="C15" s="90"/>
+      <c r="D15" s="90"/>
+      <c r="E15" s="90"/>
+      <c r="F15" s="90"/>
+      <c r="G15" s="91"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B16" s="40"/>
-      <c r="C16" s="38"/>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="39"/>
+      <c r="B16" s="92"/>
+      <c r="C16" s="90"/>
+      <c r="D16" s="90"/>
+      <c r="E16" s="90"/>
+      <c r="F16" s="90"/>
+      <c r="G16" s="91"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B17" s="40"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="39"/>
+      <c r="B17" s="92"/>
+      <c r="C17" s="90"/>
+      <c r="D17" s="90"/>
+      <c r="E17" s="90"/>
+      <c r="F17" s="90"/>
+      <c r="G17" s="91"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B18" s="40"/>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="39"/>
+      <c r="B18" s="92"/>
+      <c r="C18" s="90"/>
+      <c r="D18" s="90"/>
+      <c r="E18" s="90"/>
+      <c r="F18" s="90"/>
+      <c r="G18" s="91"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B19" s="41"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="43"/>
+      <c r="B19" s="93"/>
+      <c r="C19" s="94"/>
+      <c r="D19" s="94"/>
+      <c r="E19" s="94"/>
+      <c r="F19" s="94"/>
+      <c r="G19" s="95"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B21" s="10" t="s">
@@ -6447,28 +8511,515 @@
       </c>
     </row>
     <row r="89" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A89" s="46" t="s">
+      <c r="A89" s="22" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B90" s="22" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="90" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B90" s="46" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B106" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B107" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="107" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B107" t="s">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B108" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="108" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B108" t="s">
-        <v>130</v>
+    <row r="110" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A110" s="9" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B111" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B112" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="113" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C113" s="42" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="114" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B114" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="115" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B115" t="s">
+        <v>251</v>
+      </c>
+      <c r="H115" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="116" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B116" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="117" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B117" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="118" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B118" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="119" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B119" s="41" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="120" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="B120" s="41" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="121" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="C121" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="122" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="C122" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="123" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="C123" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="124" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="C124" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="125" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="C125" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="126" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D126" s="43" t="s">
+        <v>234</v>
+      </c>
+      <c r="E126" s="40"/>
+      <c r="F126" s="40"/>
+      <c r="G126" s="40"/>
+      <c r="H126" s="40"/>
+      <c r="J126" t="s">
+        <v>248</v>
+      </c>
+      <c r="K126" s="43" t="s">
+        <v>235</v>
+      </c>
+      <c r="L126" s="43"/>
+      <c r="M126" s="43"/>
+      <c r="N126" s="40"/>
+      <c r="O126" s="40"/>
+      <c r="P126" s="40"/>
+    </row>
+    <row r="127" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C127" t="s">
+        <v>245</v>
+      </c>
+      <c r="D127" s="42"/>
+      <c r="I127" s="44" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="128" spans="2:16" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C128" t="s">
+        <v>246</v>
+      </c>
+      <c r="D128" s="42"/>
+    </row>
+    <row r="129" spans="2:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="D129" s="43" t="s">
+        <v>239</v>
+      </c>
+      <c r="E129" s="40"/>
+      <c r="F129" s="40"/>
+      <c r="G129" s="40"/>
+      <c r="H129" s="40"/>
+      <c r="I129" s="40"/>
+      <c r="J129" s="40"/>
+      <c r="K129" s="40"/>
+      <c r="L129" s="40"/>
+      <c r="M129" s="40"/>
+      <c r="N129" s="40"/>
+      <c r="P129" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q129" s="43" t="s">
+        <v>240</v>
+      </c>
+      <c r="R129" s="40"/>
+      <c r="S129" s="40"/>
+    </row>
+    <row r="130" spans="2:23" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C130" t="s">
+        <v>252</v>
+      </c>
+      <c r="D130" s="45"/>
+      <c r="E130" s="46"/>
+      <c r="F130" s="46"/>
+      <c r="G130" s="46"/>
+      <c r="H130" s="46"/>
+      <c r="I130" s="46"/>
+      <c r="J130" s="46"/>
+      <c r="K130" s="46"/>
+      <c r="L130" s="46"/>
+      <c r="M130" s="46"/>
+      <c r="N130" s="46"/>
+      <c r="O130" s="46"/>
+      <c r="P130" s="46"/>
+      <c r="Q130" s="45"/>
+      <c r="R130" s="46"/>
+      <c r="S130" s="46"/>
+    </row>
+    <row r="131" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="D131" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="132" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="D132" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="133" spans="2:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="C133" t="s">
+        <v>269</v>
+      </c>
+      <c r="K133" s="54" t="s">
+        <v>271</v>
+      </c>
+      <c r="L133" s="62"/>
+      <c r="M133" s="62"/>
+      <c r="N133" s="13"/>
+      <c r="O133" s="13"/>
+      <c r="P133" s="13"/>
+      <c r="Q133" s="13"/>
+      <c r="R133" s="13"/>
+      <c r="S133" s="13"/>
+      <c r="T133" s="13"/>
+      <c r="U133" s="13"/>
+      <c r="V133" s="13"/>
+      <c r="W133" s="15"/>
+    </row>
+    <row r="134" spans="2:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="D134" s="49" t="s">
+        <v>266</v>
+      </c>
+      <c r="E134" s="13"/>
+      <c r="F134" s="13"/>
+      <c r="G134" s="13"/>
+      <c r="H134" s="15"/>
+      <c r="K134" s="55" t="s">
+        <v>272</v>
+      </c>
+      <c r="L134" s="57"/>
+      <c r="M134" s="57"/>
+      <c r="N134" s="14"/>
+      <c r="O134" s="14"/>
+      <c r="P134" s="14"/>
+      <c r="Q134" s="14"/>
+      <c r="R134" s="14"/>
+      <c r="S134" s="14"/>
+      <c r="T134" s="14"/>
+      <c r="U134" s="14"/>
+      <c r="V134" s="14"/>
+      <c r="W134" s="16"/>
+    </row>
+    <row r="135" spans="2:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="D135" s="50" t="s">
+        <v>270</v>
+      </c>
+      <c r="E135" s="14"/>
+      <c r="F135" s="14"/>
+      <c r="G135" s="14"/>
+      <c r="H135" s="16"/>
+      <c r="J135" t="s">
+        <v>276</v>
+      </c>
+      <c r="K135" s="55" t="s">
+        <v>273</v>
+      </c>
+      <c r="L135" s="57"/>
+      <c r="M135" s="57"/>
+      <c r="N135" s="14"/>
+      <c r="O135" s="14"/>
+      <c r="P135" s="14"/>
+      <c r="Q135" s="14"/>
+      <c r="R135" s="14"/>
+      <c r="S135" s="14"/>
+      <c r="T135" s="14"/>
+      <c r="U135" s="14"/>
+      <c r="V135" s="14"/>
+      <c r="W135" s="16"/>
+    </row>
+    <row r="136" spans="2:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="D136" s="51" t="s">
+        <v>268</v>
+      </c>
+      <c r="E136" s="18"/>
+      <c r="F136" s="18"/>
+      <c r="G136" s="18"/>
+      <c r="H136" s="19"/>
+      <c r="K136" s="55" t="s">
+        <v>274</v>
+      </c>
+      <c r="L136" s="57"/>
+      <c r="M136" s="57"/>
+      <c r="N136" s="14"/>
+      <c r="O136" s="14"/>
+      <c r="P136" s="14"/>
+      <c r="Q136" s="14"/>
+      <c r="R136" s="14"/>
+      <c r="S136" s="14"/>
+      <c r="T136" s="14"/>
+      <c r="U136" s="14"/>
+      <c r="V136" s="14"/>
+      <c r="W136" s="16"/>
+    </row>
+    <row r="137" spans="2:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="K137" s="56" t="s">
+        <v>275</v>
+      </c>
+      <c r="L137" s="63"/>
+      <c r="M137" s="63"/>
+      <c r="N137" s="18"/>
+      <c r="O137" s="18"/>
+      <c r="P137" s="18"/>
+      <c r="Q137" s="18"/>
+      <c r="R137" s="18"/>
+      <c r="S137" s="18"/>
+      <c r="T137" s="18"/>
+      <c r="U137" s="18"/>
+      <c r="V137" s="18"/>
+      <c r="W137" s="19"/>
+    </row>
+    <row r="138" spans="2:23" ht="15" x14ac:dyDescent="0.2">
+      <c r="C138" t="s">
+        <v>277</v>
+      </c>
+      <c r="K138" s="57"/>
+      <c r="L138" s="57"/>
+      <c r="M138" s="57"/>
+      <c r="N138" s="14"/>
+      <c r="O138" s="14"/>
+      <c r="P138" s="14"/>
+      <c r="Q138" s="14"/>
+      <c r="R138" s="14"/>
+      <c r="S138" s="14"/>
+      <c r="T138" s="14"/>
+      <c r="U138" s="14"/>
+      <c r="V138" s="14"/>
+      <c r="W138" s="14"/>
+    </row>
+    <row r="139" spans="2:23" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="D139" s="59" t="s">
+        <v>280</v>
+      </c>
+      <c r="K139" s="57"/>
+      <c r="L139" s="57"/>
+      <c r="M139" s="57"/>
+      <c r="N139" s="14"/>
+      <c r="O139" s="14"/>
+      <c r="P139" s="14"/>
+      <c r="Q139" s="14"/>
+      <c r="R139" s="14"/>
+      <c r="S139" s="14"/>
+      <c r="T139" s="14"/>
+      <c r="U139" s="14"/>
+      <c r="V139" s="14"/>
+      <c r="W139" s="14"/>
+    </row>
+    <row r="140" spans="2:23" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="D140" s="60" t="s">
+        <v>278</v>
+      </c>
+      <c r="K140" s="57"/>
+      <c r="L140" s="57"/>
+      <c r="M140" s="57"/>
+      <c r="N140" s="14"/>
+      <c r="O140" s="14"/>
+      <c r="P140" s="14"/>
+      <c r="Q140" s="14"/>
+      <c r="R140" s="14"/>
+      <c r="S140" s="14"/>
+      <c r="T140" s="14"/>
+      <c r="U140" s="14"/>
+      <c r="V140" s="14"/>
+      <c r="W140" s="14"/>
+    </row>
+    <row r="141" spans="2:23" ht="17.25" x14ac:dyDescent="0.2">
+      <c r="D141" s="60" t="s">
+        <v>279</v>
+      </c>
+      <c r="K141" s="57"/>
+      <c r="L141" s="57"/>
+      <c r="M141" s="57"/>
+      <c r="N141" s="14"/>
+      <c r="O141" s="14"/>
+      <c r="P141" s="14"/>
+      <c r="Q141" s="14"/>
+      <c r="R141" s="14"/>
+      <c r="S141" s="14"/>
+      <c r="T141" s="14"/>
+      <c r="U141" s="14"/>
+      <c r="V141" s="14"/>
+      <c r="W141" s="14"/>
+    </row>
+    <row r="142" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="C142" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="143" spans="2:23" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="B143" t="s">
+        <v>258</v>
+      </c>
+      <c r="K143" s="52"/>
+      <c r="L143" s="52"/>
+      <c r="M143" s="52"/>
+    </row>
+    <row r="144" spans="2:23" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="B144" t="s">
+        <v>257</v>
+      </c>
+      <c r="K144" s="52"/>
+      <c r="L144" s="52"/>
+      <c r="M144" s="52"/>
+    </row>
+    <row r="145" spans="1:13" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="B145" t="s">
+        <v>138</v>
+      </c>
+      <c r="K145" s="53"/>
+      <c r="L145" s="53"/>
+      <c r="M145" s="53"/>
+    </row>
+    <row r="146" spans="1:13" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="C146" t="s">
+        <v>227</v>
+      </c>
+      <c r="K146" s="52"/>
+      <c r="L146" s="52"/>
+      <c r="M146" s="52"/>
+    </row>
+    <row r="147" spans="1:13" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="C147" t="s">
+        <v>230</v>
+      </c>
+      <c r="K147" s="52"/>
+      <c r="L147" s="52"/>
+      <c r="M147" s="52"/>
+    </row>
+    <row r="148" spans="1:13" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="C148" t="s">
+        <v>232</v>
+      </c>
+      <c r="K148" s="52"/>
+      <c r="L148" s="52"/>
+      <c r="M148" s="52"/>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="C149" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="C150" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="E151" s="47" t="s">
+        <v>256</v>
+      </c>
+      <c r="F151" s="48"/>
+      <c r="G151" s="48"/>
+      <c r="H151" s="48"/>
+      <c r="I151" s="48"/>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="C156" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A159" s="61" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B160" s="58" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="161" spans="2:14" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="B161" s="66" t="s">
+        <v>283</v>
+      </c>
+      <c r="C161" s="14"/>
+      <c r="D161" s="14"/>
+      <c r="G161" t="s">
+        <v>248</v>
+      </c>
+      <c r="H161" s="64" t="s">
+        <v>284</v>
+      </c>
+      <c r="I161" s="14"/>
+      <c r="J161" s="14"/>
+      <c r="K161" s="14"/>
+      <c r="L161" s="14"/>
+      <c r="M161" s="14"/>
+      <c r="N161" s="14"/>
+    </row>
+    <row r="162" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="G162" t="s">
+        <v>282</v>
+      </c>
+      <c r="H162" s="65" t="s">
+        <v>285</v>
+      </c>
+      <c r="I162" s="14"/>
+      <c r="J162" s="14"/>
+      <c r="K162" s="14"/>
+      <c r="L162" s="14"/>
+      <c r="M162" s="14"/>
+      <c r="N162" s="14"/>
+    </row>
+    <row r="163" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="G163" t="s">
+        <v>282</v>
+      </c>
+      <c r="H163" t="s">
+        <v>286</v>
+      </c>
+      <c r="M163" t="s">
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -6477,7 +9028,9 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -6493,77 +9046,123 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="23" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B2" s="20" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B2" s="44" t="s">
+      <c r="D2" s="21" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B3" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="45" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B3" s="44" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3" s="45" t="s">
-        <v>69</v>
-      </c>
     </row>
     <row r="10" spans="1:11" ht="18" x14ac:dyDescent="0.25">
-      <c r="A10" s="47" t="s">
-        <v>139</v>
+      <c r="A10" s="23" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>142</v>
-      </c>
-      <c r="K12" s="54" t="s">
         <v>141</v>
+      </c>
+      <c r="K12" s="24" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+      <c r="A14" s="23" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="22" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="22" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:2" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="22" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="22" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B22" s="46" t="s">
-        <v>197</v>
-      </c>
-    </row>
     <row r="23" spans="2:11" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B23" s="63" t="s">
-        <v>189</v>
+      <c r="B23" s="33" t="s">
+        <v>187</v>
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
@@ -6576,8 +9175,8 @@
       <c r="K23" s="15"/>
     </row>
     <row r="24" spans="2:11" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B24" s="65" t="s">
-        <v>190</v>
+      <c r="B24" s="35" t="s">
+        <v>188</v>
       </c>
       <c r="C24" s="14"/>
       <c r="D24" s="14"/>
@@ -6590,8 +9189,8 @@
       <c r="K24" s="16"/>
     </row>
     <row r="25" spans="2:11" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B25" s="66" t="s">
-        <v>187</v>
+      <c r="B25" s="36" t="s">
+        <v>185</v>
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="14"/>
@@ -6604,8 +9203,8 @@
       <c r="K25" s="16"/>
     </row>
     <row r="26" spans="2:11" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B26" s="56" t="s">
-        <v>188</v>
+      <c r="B26" s="26" t="s">
+        <v>186</v>
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="14"/>
@@ -6618,8 +9217,8 @@
       <c r="K26" s="16"/>
     </row>
     <row r="27" spans="2:11" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B27" s="56" t="s">
-        <v>191</v>
+      <c r="B27" s="26" t="s">
+        <v>189</v>
       </c>
       <c r="C27" s="14"/>
       <c r="D27" s="14"/>
@@ -6632,8 +9231,8 @@
       <c r="K27" s="16"/>
     </row>
     <row r="28" spans="2:11" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B28" s="60" t="s">
-        <v>181</v>
+      <c r="B28" s="30" t="s">
+        <v>179</v>
       </c>
       <c r="C28" s="14"/>
       <c r="D28" s="14"/>
@@ -6646,7 +9245,7 @@
       <c r="K28" s="16"/>
     </row>
     <row r="29" spans="2:11" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B29" s="67"/>
+      <c r="B29" s="37"/>
       <c r="C29" s="14"/>
       <c r="D29" s="14"/>
       <c r="E29" s="14"/>
@@ -6658,8 +9257,8 @@
       <c r="K29" s="16"/>
     </row>
     <row r="30" spans="2:11" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B30" s="56" t="s">
-        <v>192</v>
+      <c r="B30" s="26" t="s">
+        <v>190</v>
       </c>
       <c r="C30" s="14"/>
       <c r="D30" s="14"/>
@@ -6672,8 +9271,8 @@
       <c r="K30" s="16"/>
     </row>
     <row r="31" spans="2:11" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B31" s="65" t="s">
-        <v>193</v>
+      <c r="B31" s="35" t="s">
+        <v>191</v>
       </c>
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
@@ -6686,8 +9285,8 @@
       <c r="K31" s="16"/>
     </row>
     <row r="32" spans="2:11" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B32" s="56" t="s">
-        <v>194</v>
+      <c r="B32" s="26" t="s">
+        <v>192</v>
       </c>
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
@@ -6699,9 +9298,9 @@
       <c r="J32" s="14"/>
       <c r="K32" s="16"/>
     </row>
-    <row r="33" spans="2:11" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B33" s="64" t="s">
-        <v>181</v>
+    <row r="33" spans="1:11" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B33" s="34" t="s">
+        <v>179</v>
       </c>
       <c r="C33" s="18"/>
       <c r="D33" s="18"/>
@@ -6712,6 +9311,21 @@
       <c r="I33" s="18"/>
       <c r="J33" s="18"/>
       <c r="K33" s="19"/>
+    </row>
+    <row r="36" spans="1:11" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A36" s="9" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B37" s="39" t="s">
+        <v>220</v>
+      </c>
+      <c r="C37" s="40"/>
+      <c r="D37" s="40"/>
+      <c r="E37" s="40"/>
+      <c r="F37" s="40"/>
+      <c r="G37" s="40"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -7129,17 +9743,20 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:T55"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="62" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B2" s="55" t="s">
-        <v>148</v>
+    <row r="1" spans="1:20" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A1" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B2" s="25" t="s">
+        <v>147</v>
       </c>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
@@ -7149,10 +9766,19 @@
       <c r="H2" s="13"/>
       <c r="I2" s="13"/>
       <c r="J2" s="15"/>
-    </row>
-    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B3" s="56" t="s">
-        <v>159</v>
+      <c r="N2" s="72" t="s">
+        <v>264</v>
+      </c>
+      <c r="O2" s="70"/>
+      <c r="P2" s="70"/>
+      <c r="Q2" s="70"/>
+      <c r="R2" s="70"/>
+      <c r="S2" s="70"/>
+      <c r="T2" s="71"/>
+    </row>
+    <row r="3" spans="1:20" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B3" s="26" t="s">
+        <v>158</v>
       </c>
       <c r="C3" s="14"/>
       <c r="D3" s="14"/>
@@ -7162,10 +9788,17 @@
       <c r="H3" s="14"/>
       <c r="I3" s="14"/>
       <c r="J3" s="16"/>
-    </row>
-    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B4" s="56" t="s">
-        <v>160</v>
+      <c r="N3" s="92"/>
+      <c r="O3" s="96"/>
+      <c r="P3" s="96"/>
+      <c r="Q3" s="96"/>
+      <c r="R3" s="96"/>
+      <c r="S3" s="96"/>
+      <c r="T3" s="91"/>
+    </row>
+    <row r="4" spans="1:20" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B4" s="26" t="s">
+        <v>159</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
@@ -7175,10 +9808,17 @@
       <c r="H4" s="14"/>
       <c r="I4" s="14"/>
       <c r="J4" s="16"/>
-    </row>
-    <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B5" s="56" t="s">
-        <v>149</v>
+      <c r="N4" s="92"/>
+      <c r="O4" s="96"/>
+      <c r="P4" s="96"/>
+      <c r="Q4" s="96"/>
+      <c r="R4" s="96"/>
+      <c r="S4" s="96"/>
+      <c r="T4" s="91"/>
+    </row>
+    <row r="5" spans="1:20" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B5" s="26" t="s">
+        <v>148</v>
       </c>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
@@ -7188,10 +9828,17 @@
       <c r="H5" s="14"/>
       <c r="I5" s="14"/>
       <c r="J5" s="16"/>
-    </row>
-    <row r="6" spans="1:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B6" s="57" t="s">
-        <v>161</v>
+      <c r="N5" s="92"/>
+      <c r="O5" s="96"/>
+      <c r="P5" s="96"/>
+      <c r="Q5" s="96"/>
+      <c r="R5" s="96"/>
+      <c r="S5" s="96"/>
+      <c r="T5" s="91"/>
+    </row>
+    <row r="6" spans="1:20" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B6" s="27" t="s">
+        <v>160</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
@@ -7201,10 +9848,17 @@
       <c r="H6" s="14"/>
       <c r="I6" s="14"/>
       <c r="J6" s="16"/>
-    </row>
-    <row r="7" spans="1:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B7" s="57" t="s">
-        <v>162</v>
+      <c r="N6" s="92"/>
+      <c r="O6" s="96"/>
+      <c r="P6" s="96"/>
+      <c r="Q6" s="96"/>
+      <c r="R6" s="96"/>
+      <c r="S6" s="96"/>
+      <c r="T6" s="91"/>
+    </row>
+    <row r="7" spans="1:20" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B7" s="27" t="s">
+        <v>161</v>
       </c>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
@@ -7214,10 +9868,17 @@
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
       <c r="J7" s="16"/>
-    </row>
-    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B8" s="57" t="s">
-        <v>163</v>
+      <c r="N7" s="92"/>
+      <c r="O7" s="96"/>
+      <c r="P7" s="96"/>
+      <c r="Q7" s="96"/>
+      <c r="R7" s="96"/>
+      <c r="S7" s="96"/>
+      <c r="T7" s="91"/>
+    </row>
+    <row r="8" spans="1:20" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B8" s="27" t="s">
+        <v>162</v>
       </c>
       <c r="C8" s="14"/>
       <c r="D8" s="14"/>
@@ -7227,10 +9888,17 @@
       <c r="H8" s="14"/>
       <c r="I8" s="14"/>
       <c r="J8" s="16"/>
-    </row>
-    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B9" s="57" t="s">
-        <v>164</v>
+      <c r="N8" s="92"/>
+      <c r="O8" s="96"/>
+      <c r="P8" s="96"/>
+      <c r="Q8" s="96"/>
+      <c r="R8" s="96"/>
+      <c r="S8" s="96"/>
+      <c r="T8" s="91"/>
+    </row>
+    <row r="9" spans="1:20" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B9" s="27" t="s">
+        <v>163</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="14"/>
@@ -7240,10 +9908,17 @@
       <c r="H9" s="14"/>
       <c r="I9" s="14"/>
       <c r="J9" s="16"/>
-    </row>
-    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B10" s="57" t="s">
-        <v>165</v>
+      <c r="N9" s="93"/>
+      <c r="O9" s="94"/>
+      <c r="P9" s="94"/>
+      <c r="Q9" s="94"/>
+      <c r="R9" s="94"/>
+      <c r="S9" s="94"/>
+      <c r="T9" s="95"/>
+    </row>
+    <row r="10" spans="1:20" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B10" s="27" t="s">
+        <v>164</v>
       </c>
       <c r="C10" s="14"/>
       <c r="D10" s="14"/>
@@ -7253,10 +9928,13 @@
       <c r="H10" s="14"/>
       <c r="I10" s="14"/>
       <c r="J10" s="16"/>
-    </row>
-    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B11" s="57" t="s">
-        <v>166</v>
+      <c r="M10" s="10" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B11" s="27" t="s">
+        <v>165</v>
       </c>
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
@@ -7266,10 +9944,19 @@
       <c r="H11" s="14"/>
       <c r="I11" s="14"/>
       <c r="J11" s="16"/>
-    </row>
-    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B12" s="56" t="s">
-        <v>150</v>
+      <c r="N11" s="72" t="s">
+        <v>263</v>
+      </c>
+      <c r="O11" s="70"/>
+      <c r="P11" s="70"/>
+      <c r="Q11" s="70"/>
+      <c r="R11" s="70"/>
+      <c r="S11" s="70"/>
+      <c r="T11" s="71"/>
+    </row>
+    <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B12" s="26" t="s">
+        <v>149</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
@@ -7279,10 +9966,17 @@
       <c r="H12" s="14"/>
       <c r="I12" s="14"/>
       <c r="J12" s="16"/>
-    </row>
-    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B13" s="57" t="s">
-        <v>151</v>
+      <c r="N12" s="92"/>
+      <c r="O12" s="96"/>
+      <c r="P12" s="96"/>
+      <c r="Q12" s="96"/>
+      <c r="R12" s="96"/>
+      <c r="S12" s="96"/>
+      <c r="T12" s="91"/>
+    </row>
+    <row r="13" spans="1:20" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B13" s="27" t="s">
+        <v>150</v>
       </c>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
@@ -7292,10 +9986,17 @@
       <c r="H13" s="14"/>
       <c r="I13" s="14"/>
       <c r="J13" s="16"/>
-    </row>
-    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B14" s="58" t="s">
-        <v>167</v>
+      <c r="N13" s="92"/>
+      <c r="O13" s="96"/>
+      <c r="P13" s="96"/>
+      <c r="Q13" s="96"/>
+      <c r="R13" s="96"/>
+      <c r="S13" s="96"/>
+      <c r="T13" s="91"/>
+    </row>
+    <row r="14" spans="1:20" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B14" s="28" t="s">
+        <v>166</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
@@ -7305,10 +10006,17 @@
       <c r="H14" s="14"/>
       <c r="I14" s="14"/>
       <c r="J14" s="16"/>
-    </row>
-    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B15" s="58" t="s">
-        <v>167</v>
+      <c r="N14" s="92"/>
+      <c r="O14" s="96"/>
+      <c r="P14" s="96"/>
+      <c r="Q14" s="96"/>
+      <c r="R14" s="96"/>
+      <c r="S14" s="96"/>
+      <c r="T14" s="91"/>
+    </row>
+    <row r="15" spans="1:20" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B15" s="28" t="s">
+        <v>166</v>
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>
@@ -7318,10 +10026,17 @@
       <c r="H15" s="14"/>
       <c r="I15" s="14"/>
       <c r="J15" s="16"/>
-    </row>
-    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B16" s="58" t="s">
-        <v>168</v>
+      <c r="N15" s="92"/>
+      <c r="O15" s="96"/>
+      <c r="P15" s="96"/>
+      <c r="Q15" s="96"/>
+      <c r="R15" s="96"/>
+      <c r="S15" s="96"/>
+      <c r="T15" s="91"/>
+    </row>
+    <row r="16" spans="1:20" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B16" s="28" t="s">
+        <v>167</v>
       </c>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
@@ -7331,10 +10046,17 @@
       <c r="H16" s="14"/>
       <c r="I16" s="14"/>
       <c r="J16" s="16"/>
-    </row>
-    <row r="17" spans="2:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B17" s="57" t="s">
-        <v>152</v>
+      <c r="N16" s="92"/>
+      <c r="O16" s="96"/>
+      <c r="P16" s="96"/>
+      <c r="Q16" s="96"/>
+      <c r="R16" s="96"/>
+      <c r="S16" s="96"/>
+      <c r="T16" s="91"/>
+    </row>
+    <row r="17" spans="2:20" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B17" s="27" t="s">
+        <v>151</v>
       </c>
       <c r="C17" s="14"/>
       <c r="D17" s="14"/>
@@ -7344,10 +10066,17 @@
       <c r="H17" s="14"/>
       <c r="I17" s="14"/>
       <c r="J17" s="16"/>
-    </row>
-    <row r="18" spans="2:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B18" s="57" t="s">
-        <v>153</v>
+      <c r="N17" s="92"/>
+      <c r="O17" s="96"/>
+      <c r="P17" s="96"/>
+      <c r="Q17" s="96"/>
+      <c r="R17" s="96"/>
+      <c r="S17" s="96"/>
+      <c r="T17" s="91"/>
+    </row>
+    <row r="18" spans="2:20" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B18" s="27" t="s">
+        <v>152</v>
       </c>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
@@ -7357,10 +10086,17 @@
       <c r="H18" s="14"/>
       <c r="I18" s="14"/>
       <c r="J18" s="16"/>
-    </row>
-    <row r="19" spans="2:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B19" s="57" t="s">
-        <v>154</v>
+      <c r="N18" s="93"/>
+      <c r="O18" s="94"/>
+      <c r="P18" s="94"/>
+      <c r="Q18" s="94"/>
+      <c r="R18" s="94"/>
+      <c r="S18" s="94"/>
+      <c r="T18" s="95"/>
+    </row>
+    <row r="19" spans="2:20" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B19" s="27" t="s">
+        <v>153</v>
       </c>
       <c r="C19" s="14"/>
       <c r="D19" s="14"/>
@@ -7370,10 +10106,13 @@
       <c r="H19" s="14"/>
       <c r="I19" s="14"/>
       <c r="J19" s="16"/>
-    </row>
-    <row r="20" spans="2:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B20" s="57" t="s">
-        <v>155</v>
+      <c r="M19" s="10" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="20" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="27" t="s">
+        <v>154</v>
       </c>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
@@ -7383,10 +10122,19 @@
       <c r="H20" s="14"/>
       <c r="I20" s="14"/>
       <c r="J20" s="16"/>
-    </row>
-    <row r="21" spans="2:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B21" s="57" t="s">
-        <v>169</v>
+      <c r="N20" s="72" t="s">
+        <v>265</v>
+      </c>
+      <c r="O20" s="70"/>
+      <c r="P20" s="70"/>
+      <c r="Q20" s="70"/>
+      <c r="R20" s="70"/>
+      <c r="S20" s="70"/>
+      <c r="T20" s="71"/>
+    </row>
+    <row r="21" spans="2:20" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B21" s="27" t="s">
+        <v>168</v>
       </c>
       <c r="C21" s="14"/>
       <c r="D21" s="14"/>
@@ -7396,10 +10144,17 @@
       <c r="H21" s="14"/>
       <c r="I21" s="14"/>
       <c r="J21" s="16"/>
-    </row>
-    <row r="22" spans="2:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B22" s="59" t="s">
-        <v>156</v>
+      <c r="N21" s="92"/>
+      <c r="O21" s="96"/>
+      <c r="P21" s="96"/>
+      <c r="Q21" s="96"/>
+      <c r="R21" s="96"/>
+      <c r="S21" s="96"/>
+      <c r="T21" s="91"/>
+    </row>
+    <row r="22" spans="2:20" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B22" s="29" t="s">
+        <v>155</v>
       </c>
       <c r="C22" s="14"/>
       <c r="D22" s="14"/>
@@ -7409,10 +10164,17 @@
       <c r="H22" s="14"/>
       <c r="I22" s="14"/>
       <c r="J22" s="16"/>
-    </row>
-    <row r="23" spans="2:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B23" s="56" t="s">
-        <v>170</v>
+      <c r="N22" s="92"/>
+      <c r="O22" s="96"/>
+      <c r="P22" s="96"/>
+      <c r="Q22" s="96"/>
+      <c r="R22" s="96"/>
+      <c r="S22" s="96"/>
+      <c r="T22" s="91"/>
+    </row>
+    <row r="23" spans="2:20" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B23" s="26" t="s">
+        <v>219</v>
       </c>
       <c r="C23" s="14"/>
       <c r="D23" s="14"/>
@@ -7422,10 +10184,17 @@
       <c r="H23" s="14"/>
       <c r="I23" s="14"/>
       <c r="J23" s="16"/>
-    </row>
-    <row r="24" spans="2:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B24" s="56" t="s">
-        <v>171</v>
+      <c r="N23" s="92"/>
+      <c r="O23" s="96"/>
+      <c r="P23" s="96"/>
+      <c r="Q23" s="96"/>
+      <c r="R23" s="96"/>
+      <c r="S23" s="96"/>
+      <c r="T23" s="91"/>
+    </row>
+    <row r="24" spans="2:20" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B24" s="26" t="s">
+        <v>169</v>
       </c>
       <c r="C24" s="14"/>
       <c r="D24" s="14"/>
@@ -7435,10 +10204,17 @@
       <c r="H24" s="14"/>
       <c r="I24" s="14"/>
       <c r="J24" s="16"/>
-    </row>
-    <row r="25" spans="2:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B25" s="56" t="s">
-        <v>172</v>
+      <c r="N24" s="92"/>
+      <c r="O24" s="96"/>
+      <c r="P24" s="96"/>
+      <c r="Q24" s="96"/>
+      <c r="R24" s="96"/>
+      <c r="S24" s="96"/>
+      <c r="T24" s="91"/>
+    </row>
+    <row r="25" spans="2:20" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B25" s="26" t="s">
+        <v>170</v>
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="14"/>
@@ -7448,10 +10224,17 @@
       <c r="H25" s="14"/>
       <c r="I25" s="14"/>
       <c r="J25" s="16"/>
-    </row>
-    <row r="26" spans="2:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B26" s="59" t="s">
-        <v>157</v>
+      <c r="N25" s="92"/>
+      <c r="O25" s="96"/>
+      <c r="P25" s="96"/>
+      <c r="Q25" s="96"/>
+      <c r="R25" s="96"/>
+      <c r="S25" s="96"/>
+      <c r="T25" s="91"/>
+    </row>
+    <row r="26" spans="2:20" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B26" s="29" t="s">
+        <v>156</v>
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="14"/>
@@ -7461,10 +10244,17 @@
       <c r="H26" s="14"/>
       <c r="I26" s="14"/>
       <c r="J26" s="16"/>
-    </row>
-    <row r="27" spans="2:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B27" s="56" t="s">
-        <v>173</v>
+      <c r="N26" s="92"/>
+      <c r="O26" s="96"/>
+      <c r="P26" s="96"/>
+      <c r="Q26" s="96"/>
+      <c r="R26" s="96"/>
+      <c r="S26" s="96"/>
+      <c r="T26" s="91"/>
+    </row>
+    <row r="27" spans="2:20" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B27" s="26" t="s">
+        <v>171</v>
       </c>
       <c r="C27" s="14"/>
       <c r="D27" s="14"/>
@@ -7474,10 +10264,17 @@
       <c r="H27" s="14"/>
       <c r="I27" s="14"/>
       <c r="J27" s="16"/>
-    </row>
-    <row r="28" spans="2:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B28" s="56" t="s">
-        <v>158</v>
+      <c r="N27" s="93"/>
+      <c r="O27" s="94"/>
+      <c r="P27" s="94"/>
+      <c r="Q27" s="94"/>
+      <c r="R27" s="94"/>
+      <c r="S27" s="94"/>
+      <c r="T27" s="95"/>
+    </row>
+    <row r="28" spans="2:20" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B28" s="26" t="s">
+        <v>157</v>
       </c>
       <c r="C28" s="14"/>
       <c r="D28" s="14"/>
@@ -7488,9 +10285,9 @@
       <c r="I28" s="14"/>
       <c r="J28" s="16"/>
     </row>
-    <row r="29" spans="2:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B29" s="56" t="s">
-        <v>174</v>
+    <row r="29" spans="2:20" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B29" s="26" t="s">
+        <v>172</v>
       </c>
       <c r="C29" s="14"/>
       <c r="D29" s="14"/>
@@ -7501,9 +10298,9 @@
       <c r="I29" s="14"/>
       <c r="J29" s="16"/>
     </row>
-    <row r="30" spans="2:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B30" s="56" t="s">
-        <v>175</v>
+    <row r="30" spans="2:20" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B30" s="26" t="s">
+        <v>173</v>
       </c>
       <c r="C30" s="14"/>
       <c r="D30" s="14"/>
@@ -7514,9 +10311,9 @@
       <c r="I30" s="14"/>
       <c r="J30" s="16"/>
     </row>
-    <row r="31" spans="2:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B31" s="56" t="s">
-        <v>176</v>
+    <row r="31" spans="2:20" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B31" s="26" t="s">
+        <v>174</v>
       </c>
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
@@ -7527,9 +10324,9 @@
       <c r="I31" s="14"/>
       <c r="J31" s="16"/>
     </row>
-    <row r="32" spans="2:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B32" s="56" t="s">
-        <v>177</v>
+    <row r="32" spans="2:20" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="B32" s="26" t="s">
+        <v>175</v>
       </c>
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
@@ -7541,8 +10338,8 @@
       <c r="J32" s="16"/>
     </row>
     <row r="33" spans="1:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B33" s="56" t="s">
-        <v>178</v>
+      <c r="B33" s="26" t="s">
+        <v>176</v>
       </c>
       <c r="C33" s="14"/>
       <c r="D33" s="14"/>
@@ -7554,8 +10351,8 @@
       <c r="J33" s="16"/>
     </row>
     <row r="34" spans="1:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B34" s="56" t="s">
-        <v>179</v>
+      <c r="B34" s="26" t="s">
+        <v>177</v>
       </c>
       <c r="C34" s="14"/>
       <c r="D34" s="14"/>
@@ -7567,8 +10364,8 @@
       <c r="J34" s="16"/>
     </row>
     <row r="35" spans="1:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B35" s="56" t="s">
-        <v>180</v>
+      <c r="B35" s="26" t="s">
+        <v>178</v>
       </c>
       <c r="C35" s="14"/>
       <c r="D35" s="14"/>
@@ -7580,8 +10377,8 @@
       <c r="J35" s="16"/>
     </row>
     <row r="36" spans="1:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B36" s="60" t="s">
-        <v>181</v>
+      <c r="B36" s="30" t="s">
+        <v>179</v>
       </c>
       <c r="C36" s="14"/>
       <c r="D36" s="14"/>
@@ -7593,8 +10390,8 @@
       <c r="J36" s="16"/>
     </row>
     <row r="37" spans="1:10" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="B37" s="61" t="s">
-        <v>182</v>
+      <c r="B37" s="31" t="s">
+        <v>180</v>
       </c>
       <c r="C37" s="18"/>
       <c r="D37" s="18"/>
@@ -7607,193 +10404,197 @@
     </row>
     <row r="39" spans="1:10" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B40" s="34" t="s">
-        <v>184</v>
-      </c>
-      <c r="C40" s="35"/>
-      <c r="D40" s="35"/>
-      <c r="E40" s="35"/>
-      <c r="F40" s="35"/>
-      <c r="G40" s="35"/>
-      <c r="H40" s="35"/>
-      <c r="I40" s="35"/>
-      <c r="J40" s="36"/>
+      <c r="B40" s="72" t="s">
+        <v>182</v>
+      </c>
+      <c r="C40" s="70"/>
+      <c r="D40" s="70"/>
+      <c r="E40" s="70"/>
+      <c r="F40" s="70"/>
+      <c r="G40" s="70"/>
+      <c r="H40" s="70"/>
+      <c r="I40" s="70"/>
+      <c r="J40" s="71"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B41" s="40"/>
-      <c r="C41" s="48"/>
-      <c r="D41" s="48"/>
-      <c r="E41" s="48"/>
-      <c r="F41" s="48"/>
-      <c r="G41" s="48"/>
-      <c r="H41" s="48"/>
-      <c r="I41" s="48"/>
-      <c r="J41" s="39"/>
+      <c r="B41" s="92"/>
+      <c r="C41" s="96"/>
+      <c r="D41" s="96"/>
+      <c r="E41" s="96"/>
+      <c r="F41" s="96"/>
+      <c r="G41" s="96"/>
+      <c r="H41" s="96"/>
+      <c r="I41" s="96"/>
+      <c r="J41" s="91"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B42" s="40"/>
-      <c r="C42" s="48"/>
-      <c r="D42" s="48"/>
-      <c r="E42" s="48"/>
-      <c r="F42" s="48"/>
-      <c r="G42" s="48"/>
-      <c r="H42" s="48"/>
-      <c r="I42" s="48"/>
-      <c r="J42" s="39"/>
+      <c r="B42" s="92"/>
+      <c r="C42" s="96"/>
+      <c r="D42" s="96"/>
+      <c r="E42" s="96"/>
+      <c r="F42" s="96"/>
+      <c r="G42" s="96"/>
+      <c r="H42" s="96"/>
+      <c r="I42" s="96"/>
+      <c r="J42" s="91"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B43" s="40"/>
-      <c r="C43" s="48"/>
-      <c r="D43" s="48"/>
-      <c r="E43" s="48"/>
-      <c r="F43" s="48"/>
-      <c r="G43" s="48"/>
-      <c r="H43" s="48"/>
-      <c r="I43" s="48"/>
-      <c r="J43" s="39"/>
+      <c r="B43" s="92"/>
+      <c r="C43" s="96"/>
+      <c r="D43" s="96"/>
+      <c r="E43" s="96"/>
+      <c r="F43" s="96"/>
+      <c r="G43" s="96"/>
+      <c r="H43" s="96"/>
+      <c r="I43" s="96"/>
+      <c r="J43" s="91"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B44" s="40"/>
-      <c r="C44" s="48"/>
-      <c r="D44" s="48"/>
-      <c r="E44" s="48"/>
-      <c r="F44" s="48"/>
-      <c r="G44" s="48"/>
-      <c r="H44" s="48"/>
-      <c r="I44" s="48"/>
-      <c r="J44" s="39"/>
+      <c r="B44" s="92"/>
+      <c r="C44" s="96"/>
+      <c r="D44" s="96"/>
+      <c r="E44" s="96"/>
+      <c r="F44" s="96"/>
+      <c r="G44" s="96"/>
+      <c r="H44" s="96"/>
+      <c r="I44" s="96"/>
+      <c r="J44" s="91"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B45" s="40"/>
-      <c r="C45" s="48"/>
-      <c r="D45" s="48"/>
-      <c r="E45" s="48"/>
-      <c r="F45" s="48"/>
-      <c r="G45" s="48"/>
-      <c r="H45" s="48"/>
-      <c r="I45" s="48"/>
-      <c r="J45" s="39"/>
+      <c r="B45" s="92"/>
+      <c r="C45" s="96"/>
+      <c r="D45" s="96"/>
+      <c r="E45" s="96"/>
+      <c r="F45" s="96"/>
+      <c r="G45" s="96"/>
+      <c r="H45" s="96"/>
+      <c r="I45" s="96"/>
+      <c r="J45" s="91"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B46" s="40"/>
-      <c r="C46" s="48"/>
-      <c r="D46" s="48"/>
-      <c r="E46" s="48"/>
-      <c r="F46" s="48"/>
-      <c r="G46" s="48"/>
-      <c r="H46" s="48"/>
-      <c r="I46" s="48"/>
-      <c r="J46" s="39"/>
+      <c r="B46" s="92"/>
+      <c r="C46" s="96"/>
+      <c r="D46" s="96"/>
+      <c r="E46" s="96"/>
+      <c r="F46" s="96"/>
+      <c r="G46" s="96"/>
+      <c r="H46" s="96"/>
+      <c r="I46" s="96"/>
+      <c r="J46" s="91"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B47" s="40"/>
-      <c r="C47" s="48"/>
-      <c r="D47" s="48"/>
-      <c r="E47" s="48"/>
-      <c r="F47" s="48"/>
-      <c r="G47" s="48"/>
-      <c r="H47" s="48"/>
-      <c r="I47" s="48"/>
-      <c r="J47" s="39"/>
+      <c r="B47" s="92"/>
+      <c r="C47" s="96"/>
+      <c r="D47" s="96"/>
+      <c r="E47" s="96"/>
+      <c r="F47" s="96"/>
+      <c r="G47" s="96"/>
+      <c r="H47" s="96"/>
+      <c r="I47" s="96"/>
+      <c r="J47" s="91"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="B48" s="40"/>
-      <c r="C48" s="48"/>
-      <c r="D48" s="48"/>
-      <c r="E48" s="48"/>
-      <c r="F48" s="48"/>
-      <c r="G48" s="48"/>
-      <c r="H48" s="48"/>
-      <c r="I48" s="48"/>
-      <c r="J48" s="39"/>
+      <c r="B48" s="92"/>
+      <c r="C48" s="96"/>
+      <c r="D48" s="96"/>
+      <c r="E48" s="96"/>
+      <c r="F48" s="96"/>
+      <c r="G48" s="96"/>
+      <c r="H48" s="96"/>
+      <c r="I48" s="96"/>
+      <c r="J48" s="91"/>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B49" s="40"/>
-      <c r="C49" s="48"/>
-      <c r="D49" s="48"/>
-      <c r="E49" s="48"/>
-      <c r="F49" s="48"/>
-      <c r="G49" s="48"/>
-      <c r="H49" s="48"/>
-      <c r="I49" s="48"/>
-      <c r="J49" s="39"/>
+      <c r="B49" s="92"/>
+      <c r="C49" s="96"/>
+      <c r="D49" s="96"/>
+      <c r="E49" s="96"/>
+      <c r="F49" s="96"/>
+      <c r="G49" s="96"/>
+      <c r="H49" s="96"/>
+      <c r="I49" s="96"/>
+      <c r="J49" s="91"/>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B50" s="40"/>
-      <c r="C50" s="48"/>
-      <c r="D50" s="48"/>
-      <c r="E50" s="48"/>
-      <c r="F50" s="48"/>
-      <c r="G50" s="48"/>
-      <c r="H50" s="48"/>
-      <c r="I50" s="48"/>
-      <c r="J50" s="39"/>
+      <c r="B50" s="92"/>
+      <c r="C50" s="96"/>
+      <c r="D50" s="96"/>
+      <c r="E50" s="96"/>
+      <c r="F50" s="96"/>
+      <c r="G50" s="96"/>
+      <c r="H50" s="96"/>
+      <c r="I50" s="96"/>
+      <c r="J50" s="91"/>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B51" s="40"/>
-      <c r="C51" s="48"/>
-      <c r="D51" s="48"/>
-      <c r="E51" s="48"/>
-      <c r="F51" s="48"/>
-      <c r="G51" s="48"/>
-      <c r="H51" s="48"/>
-      <c r="I51" s="48"/>
-      <c r="J51" s="39"/>
+      <c r="B51" s="92"/>
+      <c r="C51" s="96"/>
+      <c r="D51" s="96"/>
+      <c r="E51" s="96"/>
+      <c r="F51" s="96"/>
+      <c r="G51" s="96"/>
+      <c r="H51" s="96"/>
+      <c r="I51" s="96"/>
+      <c r="J51" s="91"/>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B52" s="40"/>
-      <c r="C52" s="48"/>
-      <c r="D52" s="48"/>
-      <c r="E52" s="48"/>
-      <c r="F52" s="48"/>
-      <c r="G52" s="48"/>
-      <c r="H52" s="48"/>
-      <c r="I52" s="48"/>
-      <c r="J52" s="39"/>
+      <c r="B52" s="92"/>
+      <c r="C52" s="96"/>
+      <c r="D52" s="96"/>
+      <c r="E52" s="96"/>
+      <c r="F52" s="96"/>
+      <c r="G52" s="96"/>
+      <c r="H52" s="96"/>
+      <c r="I52" s="96"/>
+      <c r="J52" s="91"/>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B53" s="40"/>
-      <c r="C53" s="48"/>
-      <c r="D53" s="48"/>
-      <c r="E53" s="48"/>
-      <c r="F53" s="48"/>
-      <c r="G53" s="48"/>
-      <c r="H53" s="48"/>
-      <c r="I53" s="48"/>
-      <c r="J53" s="39"/>
+      <c r="B53" s="92"/>
+      <c r="C53" s="96"/>
+      <c r="D53" s="96"/>
+      <c r="E53" s="96"/>
+      <c r="F53" s="96"/>
+      <c r="G53" s="96"/>
+      <c r="H53" s="96"/>
+      <c r="I53" s="96"/>
+      <c r="J53" s="91"/>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B54" s="40"/>
-      <c r="C54" s="48"/>
-      <c r="D54" s="48"/>
-      <c r="E54" s="48"/>
-      <c r="F54" s="48"/>
-      <c r="G54" s="48"/>
-      <c r="H54" s="48"/>
-      <c r="I54" s="48"/>
-      <c r="J54" s="39"/>
+      <c r="B54" s="92"/>
+      <c r="C54" s="96"/>
+      <c r="D54" s="96"/>
+      <c r="E54" s="96"/>
+      <c r="F54" s="96"/>
+      <c r="G54" s="96"/>
+      <c r="H54" s="96"/>
+      <c r="I54" s="96"/>
+      <c r="J54" s="91"/>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B55" s="41"/>
-      <c r="C55" s="42"/>
-      <c r="D55" s="42"/>
-      <c r="E55" s="42"/>
-      <c r="F55" s="42"/>
-      <c r="G55" s="42"/>
-      <c r="H55" s="42"/>
-      <c r="I55" s="42"/>
-      <c r="J55" s="43"/>
+      <c r="B55" s="93"/>
+      <c r="C55" s="94"/>
+      <c r="D55" s="94"/>
+      <c r="E55" s="94"/>
+      <c r="F55" s="94"/>
+      <c r="G55" s="94"/>
+      <c r="H55" s="94"/>
+      <c r="I55" s="94"/>
+      <c r="J55" s="95"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="4">
     <mergeCell ref="B40:J55"/>
+    <mergeCell ref="N2:T9"/>
+    <mergeCell ref="N11:T18"/>
+    <mergeCell ref="N20:T27"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/40_数据库/学习笔记_RDBMS_GaussDB.xlsx
+++ b/40_数据库/学习笔记_RDBMS_GaussDB.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F83ABC0C-F13F-4FED-A6F8-62BD59D08B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8117F442-9E4A-4E00-973B-2BBDE7A9F337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概述" sheetId="1" r:id="rId1"/>
@@ -22,10 +22,19 @@
     <sheet name="问题" sheetId="8" r:id="rId12"/>
     <sheet name="参考" sheetId="7" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -284,7 +293,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D149" authorId="0" shapeId="0" xr:uid="{813AC34D-6AAB-4FEA-A333-CBC43C5B81B0}">
+    <comment ref="D150" authorId="0" shapeId="0" xr:uid="{813AC34D-6AAB-4FEA-A333-CBC43C5B81B0}">
       <text>
         <r>
           <rPr>
@@ -323,7 +332,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L149" authorId="0" shapeId="0" xr:uid="{99BA361C-218A-4BE6-9241-657B27A83CB0}">
+    <comment ref="L150" authorId="0" shapeId="0" xr:uid="{99BA361C-218A-4BE6-9241-657B27A83CB0}">
       <text>
         <r>
           <rPr>
@@ -380,7 +389,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="375">
   <si>
     <r>
       <rPr>
@@ -3051,9 +3060,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ALTER TABLE common.if_t_baseinfo SET SCHEMA bomif;</t>
-  </si>
-  <si>
     <t>修改表到另外一个scmema：</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -3758,10 +3764,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>7.9  递归语法（Start with …. Connect By Prior ）需要修改</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">  Start With n.org_code = i_orgcode </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5197,103 +5199,6 @@
   </si>
   <si>
     <r>
-      <t>From</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000080"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>unnest</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF000080"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>string_to_array</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF008000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>'a,b,c'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF008000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>','</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>;</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>Function</t>
     </r>
     <r>
@@ -5904,13 +5809,1005 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>--查询存储过程</t>
+  </si>
+  <si>
+    <t>prosrc</t>
+  </si>
+  <si>
+    <t>-- 查询名为'pkg_jf_pcoutil_new' 的Package</t>
+  </si>
+  <si>
+    <t>系统对象</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>proname</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>pg_proc</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>prokind</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'p'</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>and</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>proname</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'p_newcnccode_add'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SELECT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>pkgname</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>nspname</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.*</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FROM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>GS_PACKAGE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>p</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>JOIN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>PG_NAMESPACE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ON</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>p</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>pkgnamespace</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>oid</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>WHERE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>pkgname</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'pkg_jf_pcoutil_new'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <t>7.14 在Merge into... using...中不支持行变量的插入，要修改为实际的新增语句</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.15 函数返回使用RETURN，不要后面加S。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pipe Row(FF_GetCncRelaRec('jfmc', '07', 'jfma', '07')); --整车准产通知书 &lt;- 整车生产准备通知书</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>v_result := FF_GetCncRelaRec(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'jfmc'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'07'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'jfma'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'07'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>RETURN</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>NEXT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> v_result</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF808080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>-- 整车准产通知书 &lt;- 整车生产准备通知书</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>v_result Rec_CncRela_Type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <t>7.16 Pipe不支持，并且将返回表修改为返回SETOF 表类型，且内置函数放到外面。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.17 Oracle支持在不同if分支中定义相同的跳转标签，GaussDB不支持，需要改为不同标签名。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Function定义中最后为【END;】，如为【END 函数名;】可能会报上述错误（有些加了也不报错，很奇怪）！！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> --todo-huangguohui-20260715 待源包好后重新启用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALTER TABLE common.if_t_baseinfo SET SCHEMA bomif;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>ALTER</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>TABLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF956037"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>common</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF8E00C6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>ebom_t_queue_temp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>RENAME</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>TO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FF006464"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>temp_t_data_queue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <t>重命名表：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.18 排序的列必须在查询结果中，对查询结果二次处理后的值排序也不行。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Select Distinct P.id, -- 正真的树结构
+                      P.pid, -- 正真的树结构
+                      P.PRD_PID, --       节点父ID
+                      P.PRD_ID, --       节点ID
+                      P.PRD_CODE, --        节点编码
+                      P.PRD_NAME, --        节点名称
+                      P.PRD_TYPE, --        节点类型
+                      P.CHILD_COUNT, --是否存在子项   
+                      eti.ITEM_STAGE
+        From ebom.SC_T_PRODUCTLINE_TMP P
+        LEFT JOIN  (
+            SELECT ITEM_ID, ITEM_STAGE, CREAT_TIME,
+                   ROW_NUMBER() OVER (PARTITION BY ITEM_ID ORDER BY CREAT_TIME DESC) AS rn
+            FROM ebom.EBOM_T_ITMENGC
+        ) eti ON eti.ITEM_ID = P.PRD_CODE AND eti.rn = 1 
+       Where OPER_ID = i_OperID
+       Order By NVL(PRD_PID, '-'), PRD_CODE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Order</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>By</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>NVL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">(PRD_PID, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'-'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>), PRD_CODE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>NVL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">(PRD_PID, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF008000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>'-'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>as</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> PRD_PID_SORT</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Order</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF800000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>By</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> PRD_PID_SORT, PRD_CODE</t>
+    </r>
+  </si>
+  <si>
     <t>/*
-   * 包名称：【系统公用方法及常量定义】
+   * 包名称：【定义】
    * 包简述：   
-   * 创建人：wujc   
-   * 创建日期：20100623
+   * 创建人：  
+   * 创建日期：20180623
    * 修订历史：
-   *   20260709 将Oracle版本转换为GaussDB适用版本 huangguohui
+   *   20180623 新增 
+   *   20260715 将Oracle版本转换为GaussDB适用版本 huangguohui
    */</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5921,7 +6818,8 @@
   *重点说明：
   *业务规则：
   *修改历史：
-  *   20260709 转换为GaussDB版本 huangguohui   
+  *   20180623 新增 
+  *   20260715 转换为GaussDB版本 huangguohui   
   */</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5932,26 +6830,66 @@
   *重点说明：
   *业务规则：
   *修改历史：
-  *   20260709 转换为GaussDB版本 huangguohui   
+  *   20180623 新增 
+  *   20260715 转换为GaussDB版本 huangguohui   
   */</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>--查询存储过程</t>
-  </si>
-  <si>
-    <t>prosrc</t>
-  </si>
-  <si>
-    <t>-- 查询名为'pkg_jf_pcoutil_new' 的Package</t>
-  </si>
-  <si>
-    <t>系统对象</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>SELECT</t>
+    <t xml:space="preserve">7.19 游标更新语句，需要修改update from </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Declare
+      Cursor up_cur Is
+        Select p.name_chn,
+               p.ver_num_orig,
+               p.item_type,
+               p.item_type_desc,
+               a.name_chn       As name_chn_,
+               a.ver_num_orig   As ver_num_orig_,
+               a.item_type      As item_type_,
+               b.biz_dic_name   As item_type_desc_
+          From ebom.EBOM_T_CNC_ECOSTRU_ALL p, 
+          		ebom.Ebom_t_Itmengc a, 
+          		common.dp_sys_t_busidic b
+         Where p.cnc_id = i_CncID_Str
+           And p.item_cid = a.item_id
+           And a.tag_new = '1'
+           And a.item_type = b.biz_dic_code
+           For Update Of p.name_chn, p.ver_num_orig, p.item_type, p.item_type_desc;
+    Begin
+      For rec In up_cur Loop
+        Update ebom.EBOM_T_CNC_ECOSTRU_ALL t
+           Set t.name_chn       = rec.name_chn_,
+               t.ver_num_orig   = rec.ver_num_orig_,
+               t.item_type      = rec.item_type_,
+               t.item_type_desc = rec.item_type_desc_
+         Where Current Of up_cur;
+      End Loop;
+    End;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UPDATE ebom.EBOM_T_CNC_ECOSTRU_ALL AS t
+SET 
+    name_chn       = a.name_chn,
+    ver_num_orig   = a.ver_num_orig,
+    item_type      = a.item_type,
+    item_type_desc = b.biz_dic_name
+FROM 
+    ebom.Ebom_t_Itmengc AS a,
+    common.dp_sys_t_busidic AS b
+WHERE 
+    t.cnc_id = i_CncID_Str
+    AND t.item_cid = a.item_id
+    AND a.tag_new = '1'
+    AND a.item_type = b.biz_dic_code;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>From</t>
     </r>
     <r>
       <rPr>
@@ -5964,76 +6902,41 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
-        <color rgb="FF006464"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>proname</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>,</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>FROM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF8E00C6"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>pg_proc</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>WHERE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF006464"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>prokind</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> = </t>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>unnest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000080"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>string_to_array</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
     </r>
     <r>
       <rPr>
@@ -6042,39 +6945,16 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>'p'</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>and</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF006464"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>proname</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> = </t>
+      <t>'a,b,c'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
     </r>
     <r>
       <rPr>
@@ -6083,7 +6963,16 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>'p_newcnccode_add'</t>
+      <t>','</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>))</t>
     </r>
     <r>
       <rPr>
@@ -6094,319 +6983,156 @@
       </rPr>
       <t>;</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <t>SELECT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF006464"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>pkgname</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>,</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>n</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF006464"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>nspname</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF8E00C6"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>n</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>.*</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>FROM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF8E00C6"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>GS_PACKAGE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF8E00C6"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>p</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>JOIN</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF8E00C6"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>PG_NAMESPACE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF8E00C6"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>n</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FF800000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>ON</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF8E00C6"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>p</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF006464"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>pkgnamespace</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> = </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color rgb="FF8E00C6"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>n</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF006464"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>oid</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>WHERE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF006464"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>pkgname</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> = </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF008000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>'pkg_jf_pcoutil_new'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>;</t>
-    </r>
-  </si>
-  <si>
-    <t>7.14 在Merge into... using...中不支持行变量的插入，要修改为实际的新增语句</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>var_FactoryIds     sys.odcivarchar2list;
+var_FactoryIds := New sys.odcivarchar2list();
+ For lrc_mfg In (Select Distinct a.mfg_center_code From mbom_t_eco_mfgct a Where a.task_id = var_batch_no) Loop
+        var_FactoryIds.Extend;
+        var_FactoryIds(var_FactoryIds.Last) := lrc_mfg.mfg_center_code;
+ End Loop;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>var_FactoryIds text[];  -- OpenGauss中使用text数组
+var_FactoryIds := '{}'::text[];  -- 初始化为空数组
+    -- 使用array_agg直接聚合，更简洁
+    SELECT array_agg(DISTINCT a.mfg_center_code) 
+    INTO var_FactoryIds
+    FROM mbom_t_eco_mfgct a 
+    WHERE a.task_id = var_batch_no;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.20 sys.odcivarchar2list的转换：直接使用数组来替换</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查看所有运行记录摘要：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>查看存储过程的运行时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> -- 查看所有运行记录摘要，每次 START/STOP 会生成一条记录
+SELECT t.run_comment as 调试记录名,t1.unit_name as 执行存过名,t1.total_time as 存过总耗时,t2."line#" as 存过行数,t2.total_time as 本行总耗时  
+FROM gms_profiler.plsql_profiler_runs t
+left join gms_profiler.plsql_profiler_units t1
+on t1.runid =t.runid 
+left join  gms_profiler.plsql_profiler_data t2
+on t2.unit_number =t1.unit_number 
+where t.run_comment='我的存储过程分析' order by t1.unit_name,t2.total_time desc
+;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.9  递归语法（Start with …. Connect By Prior ）：旧语法也支持，也可以修改</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一个具体的转换示例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>声明了变量 v_rec rec_cnc_package_type</t>
+  </si>
+  <si>
+    <t>先将函数返回值赋值给 v_rec，再用 RETURN NEXT v_rec 返回记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  --通知书相关处理过程包
+  Function F_Tabel_CncPackage Return Table_CncPackage_Type
+    Pipelined Is
+    Function FF_GetCncPackageRec(i_CncType     In Varchar2, --通知书类型
+                                 i_PackageName In Varchar2, --通知书类型相关包
+                                 i_Comments    In Varchar2 Default Null --说明
+                                 ) Return Rec_CncPackage_Type Is
+      var_CncPackage_Rec Rec_CncPackage_Type;
+    Begin
+      var_CncPackage_Rec := Null;
+      Select nvl2(i_CncType, 'dt_cnctype_' || i_CncType, Null), --通知书类型
+             nvl(i_PackageName, '-'), --通知书类型相关包
+             i_Comments --说明
+        Into var_CncPackage_Rec.CNC_TYPE, --通知书类型
+             var_CncPackage_Rec.PACKAGE_NAME, --通知书类型相关包
+             var_CncPackage_Rec.COMMENTS --说明
+        From dual;
+      Return var_CncPackage_Rec;
+    End FF_GetCncPackageRec;
+  Begin
+    --构建字典
+    --整车类
+    Pipe Row(FF_GetCncPackageRec('jfma', 'pkg_jf_mbom_cncvehicle', '整车生产准备通知书')); --整车生产准备通知书
+    Pipe Row(FF_GetCncPackageRec('jfmx', 'pkg_jf_pbom_modeldefinedsale', '车型码定义通知书')); --整车生产准备通知书 
+    Pipe Row(FF_GetCncPackageRec('jfmy', 'pkg_jf_mbom2_cncvehiclemy', '整车预发放通知书')); --整车预发放通知书--add by loujiangyun 20210107++
+  End F_Tabel_CncPackage;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">	--F_Tabel_CncPackage函数内的内置函数
+	FUNCTION FF_GetCncPackageRec(
+	    i_CncType     VARCHAR, --通知书类型
+	    i_PackageName VARCHAR, --通知书类型相关包
+	    i_Comments    VARCHAR DEFAULT NULL --说明
+		) RETURN Rec_CncPackage_Type	
+		AS 
+	    v_rec Rec_CncPackage_Type;
+    BEGIN
+        v_rec.CNC_TYPE := CASE WHEN i_CncType IS NOT NULL THEN 'dt_cnctype_' || i_CncType ELSE NULL END;
+        v_rec.PACKAGE_NAME := COALESCE(i_PackageName, '-');
+        v_rec.COMMENTS := i_Comments;
+        RETURN v_rec;
+    END;
+	--通知书相关处理过程包
+	FUNCTION F_Tabel_CncPackage() RETURN SETOF Rec_CncPackage_Type
+	 AS 
+		v_rec Rec_CncPackage_Type;
+	BEGIN
+    --构建字典
+    --整车类
+    v_rec := FF_GetCncPackageRec('jfma', 'pkg_jf_mbom_cncvehicle', '整车生产准备通知书');
+    RETURN NEXT v_rec; --整车生产准备通知书
+    v_rec := FF_GetCncPackageRec('jfmx', 'pkg_jf_pbom_modeldefinedsale', '车型码定义通知书');
+    RETURN NEXT v_rec; --整车生产准备通知书 
+    v_rec := FF_GetCncPackageRec('jfmy', 'pkg_jf_mbom2_cncvehiclemy', '整车预发放通知书');
+    RETURN NEXT v_rec; --整车预发放通知书--add by loujiangyun 20210107++
+    RETURN;
+	END;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>And Prior SYS_GUID() Is Not Null</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21 存储过程中有以下内容会报错（说什么左括号附近有错，这种提示不知所云），要注释掉： </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>comment on view MBOM_V_JF_CNC_TRIAL is 'JF-MBOM通知书';</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>comment on table MBOM_V_JF_CNC_TRIAL is 'JF-MBOM通知书';</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>视图增加注释</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>comment on column COM_V_JF_CNC.CNC_ID is '通知书ID（唯一标识）';</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>视图的列增加注释</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>两者语法一样</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6414,7 +7140,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="66">
+  <fonts count="69">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6871,6 +7597,24 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF956037"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF8E00C6"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF006464"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -7068,7 +7812,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7230,52 +7974,33 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -7300,6 +8025,48 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -7321,24 +8088,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8277,37 +9064,37 @@
   <sheetData>
     <row r="1" spans="1:2" ht="23.25">
       <c r="A1" s="67" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="B2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="36" spans="2:2" ht="15.75">
       <c r="B36" s="22" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="37" spans="2:2" ht="17.25">
       <c r="B37" s="69" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="38" spans="2:2" ht="17.25">
       <c r="B38" s="70" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="39" spans="2:2" ht="17.25">
       <c r="B39" s="70" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="70" spans="2:2" ht="17.25">
       <c r="B70" s="68" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -8325,6 +9112,7 @@
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8345,7 +9133,7 @@
       </c>
     </row>
     <row r="2" spans="1:24" ht="18">
-      <c r="A2" s="103" t="s">
+      <c r="A2" s="100" t="s">
         <v>41</v>
       </c>
       <c r="B2" s="17" t="s">
@@ -8366,1604 +9154,1850 @@
       <c r="M2" s="11"/>
       <c r="N2" s="11"/>
       <c r="O2" s="12"/>
-      <c r="P2" s="91" t="s">
+      <c r="P2" s="107" t="s">
         <v>32</v>
       </c>
-      <c r="Q2" s="92"/>
-      <c r="R2" s="92"/>
-      <c r="S2" s="92"/>
-      <c r="T2" s="92"/>
-      <c r="U2" s="92"/>
-      <c r="V2" s="92"/>
-      <c r="W2" s="92"/>
-      <c r="X2" s="93"/>
+      <c r="Q2" s="108"/>
+      <c r="R2" s="108"/>
+      <c r="S2" s="108"/>
+      <c r="T2" s="108"/>
+      <c r="U2" s="108"/>
+      <c r="V2" s="108"/>
+      <c r="W2" s="108"/>
+      <c r="X2" s="109"/>
     </row>
     <row r="3" spans="1:24" ht="18">
-      <c r="A3" s="104"/>
-      <c r="B3" s="97" t="s">
+      <c r="A3" s="101"/>
+      <c r="B3" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="98"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="102"/>
-      <c r="F3" s="99" t="s">
+      <c r="C3" s="95"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="96" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="100"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="97" t="s">
+      <c r="G3" s="97"/>
+      <c r="H3" s="98"/>
+      <c r="I3" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="J3" s="98"/>
-      <c r="K3" s="98"/>
-      <c r="L3" s="98"/>
-      <c r="M3" s="99" t="s">
+      <c r="J3" s="95"/>
+      <c r="K3" s="95"/>
+      <c r="L3" s="95"/>
+      <c r="M3" s="96" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="100"/>
-      <c r="O3" s="101"/>
-      <c r="P3" s="94"/>
-      <c r="Q3" s="95"/>
-      <c r="R3" s="95"/>
-      <c r="S3" s="95"/>
-      <c r="T3" s="95"/>
-      <c r="U3" s="95"/>
-      <c r="V3" s="95"/>
-      <c r="W3" s="95"/>
-      <c r="X3" s="96"/>
+      <c r="N3" s="97"/>
+      <c r="O3" s="98"/>
+      <c r="P3" s="110"/>
+      <c r="Q3" s="111"/>
+      <c r="R3" s="111"/>
+      <c r="S3" s="111"/>
+      <c r="T3" s="111"/>
+      <c r="U3" s="111"/>
+      <c r="V3" s="111"/>
+      <c r="W3" s="111"/>
+      <c r="X3" s="112"/>
     </row>
     <row r="4" spans="1:24">
       <c r="A4" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="83" t="s">
+      <c r="B4" s="103" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="85" t="s">
+      <c r="C4" s="103"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="103"/>
+      <c r="H4" s="103"/>
+      <c r="I4" s="104" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="86"/>
-      <c r="K4" s="86"/>
-      <c r="L4" s="87"/>
-      <c r="M4" s="83"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="W4" s="83"/>
-      <c r="X4" s="83"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="105"/>
+      <c r="L4" s="106"/>
+      <c r="M4" s="103"/>
+      <c r="N4" s="103"/>
+      <c r="O4" s="103"/>
+      <c r="P4" s="103"/>
+      <c r="Q4" s="103"/>
+      <c r="R4" s="103"/>
+      <c r="S4" s="103"/>
+      <c r="T4" s="103"/>
+      <c r="U4" s="103"/>
+      <c r="V4" s="103"/>
+      <c r="W4" s="103"/>
+      <c r="X4" s="103"/>
     </row>
     <row r="5" spans="1:24">
       <c r="A5" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="83" t="s">
+      <c r="B5" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="83"/>
-      <c r="D5" s="83"/>
-      <c r="E5" s="83"/>
-      <c r="F5" s="83" t="s">
+      <c r="C5" s="103"/>
+      <c r="D5" s="103"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="103" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="83"/>
-      <c r="H5" s="83"/>
-      <c r="I5" s="85" t="s">
+      <c r="G5" s="103"/>
+      <c r="H5" s="103"/>
+      <c r="I5" s="104" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="86"/>
-      <c r="K5" s="86"/>
-      <c r="L5" s="87"/>
-      <c r="M5" s="83" t="s">
+      <c r="J5" s="105"/>
+      <c r="K5" s="105"/>
+      <c r="L5" s="106"/>
+      <c r="M5" s="103" t="s">
         <v>36</v>
       </c>
-      <c r="N5" s="83"/>
-      <c r="O5" s="83"/>
-      <c r="P5" s="83" t="s">
+      <c r="N5" s="103"/>
+      <c r="O5" s="103"/>
+      <c r="P5" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="Q5" s="83"/>
-      <c r="R5" s="83"/>
-      <c r="S5" s="83"/>
-      <c r="T5" s="83"/>
-      <c r="U5" s="83"/>
-      <c r="V5" s="83"/>
-      <c r="W5" s="83"/>
-      <c r="X5" s="83"/>
+      <c r="Q5" s="103"/>
+      <c r="R5" s="103"/>
+      <c r="S5" s="103"/>
+      <c r="T5" s="103"/>
+      <c r="U5" s="103"/>
+      <c r="V5" s="103"/>
+      <c r="W5" s="103"/>
+      <c r="X5" s="103"/>
     </row>
     <row r="6" spans="1:24">
       <c r="A6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="83" t="s">
+      <c r="B6" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83" t="s">
+      <c r="C6" s="103"/>
+      <c r="D6" s="103"/>
+      <c r="E6" s="103"/>
+      <c r="F6" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="83"/>
-      <c r="H6" s="83"/>
-      <c r="I6" s="85" t="s">
+      <c r="G6" s="103"/>
+      <c r="H6" s="103"/>
+      <c r="I6" s="104" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="86"/>
-      <c r="K6" s="86"/>
-      <c r="L6" s="87"/>
-      <c r="M6" s="83" t="s">
+      <c r="J6" s="105"/>
+      <c r="K6" s="105"/>
+      <c r="L6" s="106"/>
+      <c r="M6" s="103" t="s">
         <v>24</v>
       </c>
-      <c r="N6" s="83"/>
-      <c r="O6" s="83"/>
-      <c r="P6" s="83"/>
-      <c r="Q6" s="83"/>
-      <c r="R6" s="83"/>
-      <c r="S6" s="83"/>
-      <c r="T6" s="83"/>
-      <c r="U6" s="83"/>
-      <c r="V6" s="83"/>
-      <c r="W6" s="83"/>
-      <c r="X6" s="83"/>
+      <c r="N6" s="103"/>
+      <c r="O6" s="103"/>
+      <c r="P6" s="103"/>
+      <c r="Q6" s="103"/>
+      <c r="R6" s="103"/>
+      <c r="S6" s="103"/>
+      <c r="T6" s="103"/>
+      <c r="U6" s="103"/>
+      <c r="V6" s="103"/>
+      <c r="W6" s="103"/>
+      <c r="X6" s="103"/>
     </row>
     <row r="7" spans="1:24">
       <c r="A7" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B7" s="83" t="s">
+      <c r="B7" s="103" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="83"/>
-      <c r="D7" s="83"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="83"/>
-      <c r="I7" s="85" t="s">
+      <c r="C7" s="103"/>
+      <c r="D7" s="103"/>
+      <c r="E7" s="103"/>
+      <c r="F7" s="103"/>
+      <c r="G7" s="103"/>
+      <c r="H7" s="103"/>
+      <c r="I7" s="104" t="s">
         <v>107</v>
       </c>
-      <c r="J7" s="86"/>
-      <c r="K7" s="86"/>
-      <c r="L7" s="87"/>
-      <c r="M7" s="83"/>
-      <c r="N7" s="83"/>
-      <c r="O7" s="83"/>
-      <c r="P7" s="83"/>
-      <c r="Q7" s="83"/>
-      <c r="R7" s="83"/>
-      <c r="S7" s="83"/>
-      <c r="T7" s="83"/>
-      <c r="U7" s="83"/>
-      <c r="V7" s="83"/>
-      <c r="W7" s="83"/>
-      <c r="X7" s="83"/>
+      <c r="J7" s="105"/>
+      <c r="K7" s="105"/>
+      <c r="L7" s="106"/>
+      <c r="M7" s="103"/>
+      <c r="N7" s="103"/>
+      <c r="O7" s="103"/>
+      <c r="P7" s="103"/>
+      <c r="Q7" s="103"/>
+      <c r="R7" s="103"/>
+      <c r="S7" s="103"/>
+      <c r="T7" s="103"/>
+      <c r="U7" s="103"/>
+      <c r="V7" s="103"/>
+      <c r="W7" s="103"/>
+      <c r="X7" s="103"/>
     </row>
     <row r="8" spans="1:24">
       <c r="A8" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="83" t="s">
+      <c r="B8" s="103" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="83"/>
-      <c r="D8" s="83"/>
-      <c r="E8" s="83"/>
-      <c r="F8" s="83" t="s">
+      <c r="C8" s="103"/>
+      <c r="D8" s="103"/>
+      <c r="E8" s="103"/>
+      <c r="F8" s="103" t="s">
         <v>46</v>
       </c>
-      <c r="G8" s="83"/>
-      <c r="H8" s="83"/>
-      <c r="I8" s="85" t="s">
+      <c r="G8" s="103"/>
+      <c r="H8" s="103"/>
+      <c r="I8" s="104" t="s">
         <v>27</v>
       </c>
-      <c r="J8" s="86"/>
-      <c r="K8" s="86"/>
-      <c r="L8" s="87"/>
-      <c r="M8" s="83" t="s">
+      <c r="J8" s="105"/>
+      <c r="K8" s="105"/>
+      <c r="L8" s="106"/>
+      <c r="M8" s="103" t="s">
         <v>47</v>
       </c>
-      <c r="N8" s="83"/>
-      <c r="O8" s="83"/>
-      <c r="P8" s="83" t="s">
+      <c r="N8" s="103"/>
+      <c r="O8" s="103"/>
+      <c r="P8" s="103" t="s">
         <v>37</v>
       </c>
-      <c r="Q8" s="83"/>
-      <c r="R8" s="83"/>
-      <c r="S8" s="83"/>
-      <c r="T8" s="83"/>
-      <c r="U8" s="83"/>
-      <c r="V8" s="83"/>
-      <c r="W8" s="83"/>
-      <c r="X8" s="83"/>
+      <c r="Q8" s="103"/>
+      <c r="R8" s="103"/>
+      <c r="S8" s="103"/>
+      <c r="T8" s="103"/>
+      <c r="U8" s="103"/>
+      <c r="V8" s="103"/>
+      <c r="W8" s="103"/>
+      <c r="X8" s="103"/>
     </row>
     <row r="9" spans="1:24">
       <c r="A9" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="83" t="s">
+      <c r="B9" s="103" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="83"/>
-      <c r="D9" s="83"/>
-      <c r="E9" s="83"/>
-      <c r="F9" s="83"/>
-      <c r="G9" s="83"/>
-      <c r="H9" s="83"/>
-      <c r="I9" s="85" t="s">
+      <c r="C9" s="103"/>
+      <c r="D9" s="103"/>
+      <c r="E9" s="103"/>
+      <c r="F9" s="103"/>
+      <c r="G9" s="103"/>
+      <c r="H9" s="103"/>
+      <c r="I9" s="104" t="s">
         <v>29</v>
       </c>
-      <c r="J9" s="86"/>
-      <c r="K9" s="86"/>
-      <c r="L9" s="87"/>
-      <c r="M9" s="83"/>
-      <c r="N9" s="83"/>
-      <c r="O9" s="83"/>
-      <c r="P9" s="83"/>
-      <c r="Q9" s="83"/>
-      <c r="R9" s="83"/>
-      <c r="S9" s="83"/>
-      <c r="T9" s="83"/>
-      <c r="U9" s="83"/>
-      <c r="V9" s="83"/>
-      <c r="W9" s="83"/>
-      <c r="X9" s="83"/>
+      <c r="J9" s="105"/>
+      <c r="K9" s="105"/>
+      <c r="L9" s="106"/>
+      <c r="M9" s="103"/>
+      <c r="N9" s="103"/>
+      <c r="O9" s="103"/>
+      <c r="P9" s="103"/>
+      <c r="Q9" s="103"/>
+      <c r="R9" s="103"/>
+      <c r="S9" s="103"/>
+      <c r="T9" s="103"/>
+      <c r="U9" s="103"/>
+      <c r="V9" s="103"/>
+      <c r="W9" s="103"/>
+      <c r="X9" s="103"/>
     </row>
     <row r="10" spans="1:24">
       <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="83" t="s">
+      <c r="B10" s="103" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="83"/>
-      <c r="D10" s="83"/>
-      <c r="E10" s="83"/>
-      <c r="F10" s="83" t="s">
+      <c r="C10" s="103"/>
+      <c r="D10" s="103"/>
+      <c r="E10" s="103"/>
+      <c r="F10" s="103" t="s">
         <v>38</v>
       </c>
-      <c r="G10" s="83"/>
-      <c r="H10" s="83"/>
-      <c r="I10" s="85" t="s">
+      <c r="G10" s="103"/>
+      <c r="H10" s="103"/>
+      <c r="I10" s="104" t="s">
         <v>43</v>
       </c>
-      <c r="J10" s="86"/>
-      <c r="K10" s="86"/>
-      <c r="L10" s="87"/>
-      <c r="M10" s="83" t="s">
+      <c r="J10" s="105"/>
+      <c r="K10" s="105"/>
+      <c r="L10" s="106"/>
+      <c r="M10" s="103" t="s">
         <v>39</v>
       </c>
-      <c r="N10" s="83"/>
-      <c r="O10" s="83"/>
-      <c r="P10" s="83"/>
-      <c r="Q10" s="83"/>
-      <c r="R10" s="83"/>
-      <c r="S10" s="83"/>
-      <c r="T10" s="83"/>
-      <c r="U10" s="83"/>
-      <c r="V10" s="83"/>
-      <c r="W10" s="83"/>
-      <c r="X10" s="83"/>
+      <c r="N10" s="103"/>
+      <c r="O10" s="103"/>
+      <c r="P10" s="103"/>
+      <c r="Q10" s="103"/>
+      <c r="R10" s="103"/>
+      <c r="S10" s="103"/>
+      <c r="T10" s="103"/>
+      <c r="U10" s="103"/>
+      <c r="V10" s="103"/>
+      <c r="W10" s="103"/>
+      <c r="X10" s="103"/>
     </row>
     <row r="11" spans="1:24">
       <c r="A11" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="83" t="s">
+      <c r="B11" s="103" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="83"/>
-      <c r="D11" s="83"/>
-      <c r="E11" s="83"/>
-      <c r="F11" s="83"/>
-      <c r="G11" s="83"/>
-      <c r="H11" s="83"/>
-      <c r="I11" s="85" t="s">
+      <c r="C11" s="103"/>
+      <c r="D11" s="103"/>
+      <c r="E11" s="103"/>
+      <c r="F11" s="103"/>
+      <c r="G11" s="103"/>
+      <c r="H11" s="103"/>
+      <c r="I11" s="104" t="s">
         <v>52</v>
       </c>
-      <c r="J11" s="86"/>
-      <c r="K11" s="86"/>
-      <c r="L11" s="87"/>
-      <c r="M11" s="83"/>
-      <c r="N11" s="83"/>
-      <c r="O11" s="83"/>
-      <c r="P11" s="83" t="s">
+      <c r="J11" s="105"/>
+      <c r="K11" s="105"/>
+      <c r="L11" s="106"/>
+      <c r="M11" s="103"/>
+      <c r="N11" s="103"/>
+      <c r="O11" s="103"/>
+      <c r="P11" s="103" t="s">
         <v>53</v>
       </c>
-      <c r="Q11" s="83"/>
-      <c r="R11" s="83"/>
-      <c r="S11" s="83"/>
-      <c r="T11" s="83"/>
-      <c r="U11" s="83"/>
-      <c r="V11" s="83"/>
-      <c r="W11" s="83"/>
-      <c r="X11" s="83"/>
+      <c r="Q11" s="103"/>
+      <c r="R11" s="103"/>
+      <c r="S11" s="103"/>
+      <c r="T11" s="103"/>
+      <c r="U11" s="103"/>
+      <c r="V11" s="103"/>
+      <c r="W11" s="103"/>
+      <c r="X11" s="103"/>
     </row>
     <row r="12" spans="1:24" ht="34.5" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B12" s="83" t="s">
+      <c r="B12" s="103" t="s">
         <v>92</v>
       </c>
-      <c r="C12" s="83"/>
-      <c r="D12" s="83"/>
-      <c r="E12" s="83"/>
-      <c r="F12" s="83" t="s">
+      <c r="C12" s="103"/>
+      <c r="D12" s="103"/>
+      <c r="E12" s="103"/>
+      <c r="F12" s="103" t="s">
         <v>97</v>
       </c>
-      <c r="G12" s="83"/>
-      <c r="H12" s="83"/>
-      <c r="I12" s="85" t="s">
+      <c r="G12" s="103"/>
+      <c r="H12" s="103"/>
+      <c r="I12" s="104" t="s">
         <v>98</v>
       </c>
-      <c r="J12" s="86"/>
-      <c r="K12" s="86"/>
-      <c r="L12" s="87"/>
-      <c r="M12" s="84" t="s">
+      <c r="J12" s="105"/>
+      <c r="K12" s="105"/>
+      <c r="L12" s="106"/>
+      <c r="M12" s="102" t="s">
         <v>99</v>
       </c>
-      <c r="N12" s="83"/>
-      <c r="O12" s="83"/>
-      <c r="P12" s="83"/>
-      <c r="Q12" s="83"/>
-      <c r="R12" s="83"/>
-      <c r="S12" s="83"/>
-      <c r="T12" s="83"/>
-      <c r="U12" s="83"/>
-      <c r="V12" s="83"/>
-      <c r="W12" s="83"/>
-      <c r="X12" s="83"/>
+      <c r="N12" s="103"/>
+      <c r="O12" s="103"/>
+      <c r="P12" s="103"/>
+      <c r="Q12" s="103"/>
+      <c r="R12" s="103"/>
+      <c r="S12" s="103"/>
+      <c r="T12" s="103"/>
+      <c r="U12" s="103"/>
+      <c r="V12" s="103"/>
+      <c r="W12" s="103"/>
+      <c r="X12" s="103"/>
     </row>
     <row r="13" spans="1:24">
       <c r="A13" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B13" s="83"/>
-      <c r="C13" s="83"/>
-      <c r="D13" s="83"/>
-      <c r="E13" s="83"/>
-      <c r="F13" s="83" t="s">
+      <c r="B13" s="103"/>
+      <c r="C13" s="103"/>
+      <c r="D13" s="103"/>
+      <c r="E13" s="103"/>
+      <c r="F13" s="103" t="s">
         <v>100</v>
       </c>
-      <c r="G13" s="83"/>
-      <c r="H13" s="83"/>
-      <c r="I13" s="85"/>
-      <c r="J13" s="86"/>
-      <c r="K13" s="86"/>
-      <c r="L13" s="87"/>
-      <c r="M13" s="84" t="s">
+      <c r="G13" s="103"/>
+      <c r="H13" s="103"/>
+      <c r="I13" s="104"/>
+      <c r="J13" s="105"/>
+      <c r="K13" s="105"/>
+      <c r="L13" s="106"/>
+      <c r="M13" s="102" t="s">
         <v>102</v>
       </c>
-      <c r="N13" s="83"/>
-      <c r="O13" s="83"/>
-      <c r="P13" s="83"/>
-      <c r="Q13" s="83"/>
-      <c r="R13" s="83"/>
-      <c r="S13" s="83"/>
-      <c r="T13" s="83"/>
-      <c r="U13" s="83"/>
-      <c r="V13" s="83"/>
-      <c r="W13" s="83"/>
-      <c r="X13" s="83"/>
+      <c r="N13" s="103"/>
+      <c r="O13" s="103"/>
+      <c r="P13" s="103"/>
+      <c r="Q13" s="103"/>
+      <c r="R13" s="103"/>
+      <c r="S13" s="103"/>
+      <c r="T13" s="103"/>
+      <c r="U13" s="103"/>
+      <c r="V13" s="103"/>
+      <c r="W13" s="103"/>
+      <c r="X13" s="103"/>
     </row>
     <row r="14" spans="1:24">
       <c r="A14" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B14" s="83"/>
-      <c r="C14" s="83"/>
-      <c r="D14" s="83"/>
-      <c r="E14" s="83"/>
-      <c r="F14" s="83" t="s">
+      <c r="B14" s="103"/>
+      <c r="C14" s="103"/>
+      <c r="D14" s="103"/>
+      <c r="E14" s="103"/>
+      <c r="F14" s="103" t="s">
         <v>100</v>
       </c>
-      <c r="G14" s="83"/>
-      <c r="H14" s="83"/>
-      <c r="I14" s="85"/>
-      <c r="J14" s="86"/>
-      <c r="K14" s="86"/>
-      <c r="L14" s="87"/>
-      <c r="M14" s="84" t="s">
+      <c r="G14" s="103"/>
+      <c r="H14" s="103"/>
+      <c r="I14" s="104"/>
+      <c r="J14" s="105"/>
+      <c r="K14" s="105"/>
+      <c r="L14" s="106"/>
+      <c r="M14" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="N14" s="83"/>
-      <c r="O14" s="83"/>
-      <c r="P14" s="83"/>
-      <c r="Q14" s="83"/>
-      <c r="R14" s="83"/>
-      <c r="S14" s="83"/>
-      <c r="T14" s="83"/>
-      <c r="U14" s="83"/>
-      <c r="V14" s="83"/>
-      <c r="W14" s="83"/>
-      <c r="X14" s="83"/>
+      <c r="N14" s="103"/>
+      <c r="O14" s="103"/>
+      <c r="P14" s="103"/>
+      <c r="Q14" s="103"/>
+      <c r="R14" s="103"/>
+      <c r="S14" s="103"/>
+      <c r="T14" s="103"/>
+      <c r="U14" s="103"/>
+      <c r="V14" s="103"/>
+      <c r="W14" s="103"/>
+      <c r="X14" s="103"/>
     </row>
     <row r="15" spans="1:24">
       <c r="A15" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B15" s="83"/>
-      <c r="C15" s="83"/>
-      <c r="D15" s="83"/>
-      <c r="E15" s="83"/>
-      <c r="F15" s="83" t="s">
+      <c r="B15" s="103"/>
+      <c r="C15" s="103"/>
+      <c r="D15" s="103"/>
+      <c r="E15" s="103"/>
+      <c r="F15" s="103" t="s">
         <v>101</v>
       </c>
-      <c r="G15" s="83"/>
-      <c r="H15" s="83"/>
-      <c r="I15" s="85"/>
-      <c r="J15" s="86"/>
-      <c r="K15" s="86"/>
-      <c r="L15" s="87"/>
-      <c r="M15" s="84" t="s">
+      <c r="G15" s="103"/>
+      <c r="H15" s="103"/>
+      <c r="I15" s="104"/>
+      <c r="J15" s="105"/>
+      <c r="K15" s="105"/>
+      <c r="L15" s="106"/>
+      <c r="M15" s="102" t="s">
         <v>104</v>
       </c>
-      <c r="N15" s="83"/>
-      <c r="O15" s="83"/>
-      <c r="P15" s="83"/>
-      <c r="Q15" s="83"/>
-      <c r="R15" s="83"/>
-      <c r="S15" s="83"/>
-      <c r="T15" s="83"/>
-      <c r="U15" s="83"/>
-      <c r="V15" s="83"/>
-      <c r="W15" s="83"/>
-      <c r="X15" s="83"/>
+      <c r="N15" s="103"/>
+      <c r="O15" s="103"/>
+      <c r="P15" s="103"/>
+      <c r="Q15" s="103"/>
+      <c r="R15" s="103"/>
+      <c r="S15" s="103"/>
+      <c r="T15" s="103"/>
+      <c r="U15" s="103"/>
+      <c r="V15" s="103"/>
+      <c r="W15" s="103"/>
+      <c r="X15" s="103"/>
     </row>
     <row r="16" spans="1:24">
       <c r="A16" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B16" s="83" t="s">
+      <c r="B16" s="103" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="83"/>
-      <c r="D16" s="83"/>
-      <c r="E16" s="83"/>
-      <c r="F16" s="83" t="s">
+      <c r="C16" s="103"/>
+      <c r="D16" s="103"/>
+      <c r="E16" s="103"/>
+      <c r="F16" s="103" t="s">
         <v>105</v>
       </c>
-      <c r="G16" s="83"/>
-      <c r="H16" s="83"/>
-      <c r="I16" s="85" t="s">
+      <c r="G16" s="103"/>
+      <c r="H16" s="103"/>
+      <c r="I16" s="104" t="s">
         <v>86</v>
       </c>
-      <c r="J16" s="86"/>
-      <c r="K16" s="86"/>
-      <c r="L16" s="87"/>
-      <c r="M16" s="83"/>
-      <c r="N16" s="83"/>
-      <c r="O16" s="83"/>
-      <c r="P16" s="83" t="s">
+      <c r="J16" s="105"/>
+      <c r="K16" s="105"/>
+      <c r="L16" s="106"/>
+      <c r="M16" s="103"/>
+      <c r="N16" s="103"/>
+      <c r="O16" s="103"/>
+      <c r="P16" s="103" t="s">
         <v>89</v>
       </c>
-      <c r="Q16" s="83"/>
-      <c r="R16" s="83"/>
-      <c r="S16" s="83"/>
-      <c r="T16" s="83"/>
-      <c r="U16" s="83"/>
-      <c r="V16" s="83"/>
-      <c r="W16" s="83"/>
-      <c r="X16" s="83"/>
+      <c r="Q16" s="103"/>
+      <c r="R16" s="103"/>
+      <c r="S16" s="103"/>
+      <c r="T16" s="103"/>
+      <c r="U16" s="103"/>
+      <c r="V16" s="103"/>
+      <c r="W16" s="103"/>
+      <c r="X16" s="103"/>
     </row>
     <row r="17" spans="1:24">
       <c r="A17" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="83" t="s">
+      <c r="B17" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="83"/>
-      <c r="D17" s="83"/>
-      <c r="E17" s="83"/>
-      <c r="F17" s="83"/>
-      <c r="G17" s="83"/>
-      <c r="H17" s="83"/>
-      <c r="I17" s="85" t="s">
+      <c r="C17" s="103"/>
+      <c r="D17" s="103"/>
+      <c r="E17" s="103"/>
+      <c r="F17" s="103"/>
+      <c r="G17" s="103"/>
+      <c r="H17" s="103"/>
+      <c r="I17" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J17" s="86"/>
-      <c r="K17" s="86"/>
-      <c r="L17" s="87"/>
-      <c r="M17" s="83"/>
-      <c r="N17" s="83"/>
-      <c r="O17" s="83"/>
-      <c r="P17" s="83" t="s">
+      <c r="J17" s="105"/>
+      <c r="K17" s="105"/>
+      <c r="L17" s="106"/>
+      <c r="M17" s="103"/>
+      <c r="N17" s="103"/>
+      <c r="O17" s="103"/>
+      <c r="P17" s="103" t="s">
         <v>56</v>
       </c>
-      <c r="Q17" s="83"/>
-      <c r="R17" s="83"/>
-      <c r="S17" s="83"/>
-      <c r="T17" s="83"/>
-      <c r="U17" s="83"/>
-      <c r="V17" s="83"/>
-      <c r="W17" s="83"/>
-      <c r="X17" s="83"/>
+      <c r="Q17" s="103"/>
+      <c r="R17" s="103"/>
+      <c r="S17" s="103"/>
+      <c r="T17" s="103"/>
+      <c r="U17" s="103"/>
+      <c r="V17" s="103"/>
+      <c r="W17" s="103"/>
+      <c r="X17" s="103"/>
     </row>
     <row r="18" spans="1:24">
       <c r="A18" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B18" s="83" t="s">
+      <c r="B18" s="103" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="83"/>
-      <c r="D18" s="83"/>
-      <c r="E18" s="83"/>
-      <c r="F18" s="83"/>
-      <c r="G18" s="83"/>
-      <c r="H18" s="83"/>
-      <c r="I18" s="85" t="s">
-        <v>211</v>
-      </c>
-      <c r="J18" s="86"/>
-      <c r="K18" s="86"/>
-      <c r="L18" s="87"/>
-      <c r="M18" s="83"/>
-      <c r="N18" s="83"/>
-      <c r="O18" s="83"/>
-      <c r="P18" s="83" t="s">
+      <c r="C18" s="103"/>
+      <c r="D18" s="103"/>
+      <c r="E18" s="103"/>
+      <c r="F18" s="103"/>
+      <c r="G18" s="103"/>
+      <c r="H18" s="103"/>
+      <c r="I18" s="104" t="s">
+        <v>210</v>
+      </c>
+      <c r="J18" s="105"/>
+      <c r="K18" s="105"/>
+      <c r="L18" s="106"/>
+      <c r="M18" s="103"/>
+      <c r="N18" s="103"/>
+      <c r="O18" s="103"/>
+      <c r="P18" s="103" t="s">
         <v>60</v>
       </c>
-      <c r="Q18" s="83"/>
-      <c r="R18" s="83"/>
-      <c r="S18" s="83"/>
-      <c r="T18" s="83"/>
-      <c r="U18" s="83"/>
-      <c r="V18" s="83"/>
-      <c r="W18" s="83"/>
-      <c r="X18" s="83"/>
+      <c r="Q18" s="103"/>
+      <c r="R18" s="103"/>
+      <c r="S18" s="103"/>
+      <c r="T18" s="103"/>
+      <c r="U18" s="103"/>
+      <c r="V18" s="103"/>
+      <c r="W18" s="103"/>
+      <c r="X18" s="103"/>
     </row>
     <row r="19" spans="1:24">
       <c r="A19" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B19" s="83" t="s">
+      <c r="B19" s="103" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="83"/>
-      <c r="D19" s="83"/>
-      <c r="E19" s="83"/>
-      <c r="F19" s="83"/>
-      <c r="G19" s="83"/>
-      <c r="H19" s="83"/>
-      <c r="I19" s="85" t="s">
+      <c r="C19" s="103"/>
+      <c r="D19" s="103"/>
+      <c r="E19" s="103"/>
+      <c r="F19" s="103"/>
+      <c r="G19" s="103"/>
+      <c r="H19" s="103"/>
+      <c r="I19" s="104" t="s">
         <v>62</v>
       </c>
-      <c r="J19" s="86"/>
-      <c r="K19" s="86"/>
-      <c r="L19" s="87"/>
-      <c r="M19" s="83"/>
-      <c r="N19" s="83"/>
-      <c r="O19" s="83"/>
-      <c r="P19" s="83" t="s">
+      <c r="J19" s="105"/>
+      <c r="K19" s="105"/>
+      <c r="L19" s="106"/>
+      <c r="M19" s="103"/>
+      <c r="N19" s="103"/>
+      <c r="O19" s="103"/>
+      <c r="P19" s="103" t="s">
         <v>61</v>
       </c>
-      <c r="Q19" s="83"/>
-      <c r="R19" s="83"/>
-      <c r="S19" s="83"/>
-      <c r="T19" s="83"/>
-      <c r="U19" s="83"/>
-      <c r="V19" s="83"/>
-      <c r="W19" s="83"/>
-      <c r="X19" s="83"/>
+      <c r="Q19" s="103"/>
+      <c r="R19" s="103"/>
+      <c r="S19" s="103"/>
+      <c r="T19" s="103"/>
+      <c r="U19" s="103"/>
+      <c r="V19" s="103"/>
+      <c r="W19" s="103"/>
+      <c r="X19" s="103"/>
     </row>
     <row r="20" spans="1:24" ht="45" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B20" s="83" t="s">
+      <c r="B20" s="103" t="s">
         <v>69</v>
       </c>
-      <c r="C20" s="83"/>
-      <c r="D20" s="83"/>
-      <c r="E20" s="83"/>
-      <c r="F20" s="84" t="s">
+      <c r="C20" s="103"/>
+      <c r="D20" s="103"/>
+      <c r="E20" s="103"/>
+      <c r="F20" s="102" t="s">
         <v>71</v>
       </c>
-      <c r="G20" s="83"/>
-      <c r="H20" s="83"/>
-      <c r="I20" s="88" t="s">
+      <c r="G20" s="103"/>
+      <c r="H20" s="103"/>
+      <c r="I20" s="113" t="s">
         <v>73</v>
       </c>
-      <c r="J20" s="89"/>
-      <c r="K20" s="89"/>
-      <c r="L20" s="90"/>
-      <c r="M20" s="84" t="s">
+      <c r="J20" s="114"/>
+      <c r="K20" s="114"/>
+      <c r="L20" s="115"/>
+      <c r="M20" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="N20" s="83"/>
-      <c r="O20" s="83"/>
-      <c r="P20" s="83"/>
-      <c r="Q20" s="83"/>
-      <c r="R20" s="83"/>
-      <c r="S20" s="83"/>
-      <c r="T20" s="83"/>
-      <c r="U20" s="83"/>
-      <c r="V20" s="83"/>
-      <c r="W20" s="83"/>
-      <c r="X20" s="83"/>
+      <c r="N20" s="103"/>
+      <c r="O20" s="103"/>
+      <c r="P20" s="103"/>
+      <c r="Q20" s="103"/>
+      <c r="R20" s="103"/>
+      <c r="S20" s="103"/>
+      <c r="T20" s="103"/>
+      <c r="U20" s="103"/>
+      <c r="V20" s="103"/>
+      <c r="W20" s="103"/>
+      <c r="X20" s="103"/>
     </row>
     <row r="21" spans="1:24" ht="61.5" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B21" s="84" t="s">
+      <c r="B21" s="102" t="s">
         <v>76</v>
       </c>
-      <c r="C21" s="83"/>
-      <c r="D21" s="83"/>
-      <c r="E21" s="83"/>
-      <c r="F21" s="83"/>
-      <c r="G21" s="83"/>
-      <c r="H21" s="83"/>
-      <c r="I21" s="85" t="s">
+      <c r="C21" s="103"/>
+      <c r="D21" s="103"/>
+      <c r="E21" s="103"/>
+      <c r="F21" s="103"/>
+      <c r="G21" s="103"/>
+      <c r="H21" s="103"/>
+      <c r="I21" s="104" t="s">
         <v>78</v>
       </c>
-      <c r="J21" s="86"/>
-      <c r="K21" s="86"/>
-      <c r="L21" s="87"/>
-      <c r="M21" s="84" t="s">
+      <c r="J21" s="105"/>
+      <c r="K21" s="105"/>
+      <c r="L21" s="106"/>
+      <c r="M21" s="102" t="s">
         <v>77</v>
       </c>
-      <c r="N21" s="83"/>
-      <c r="O21" s="83"/>
-      <c r="P21" s="83" t="s">
+      <c r="N21" s="103"/>
+      <c r="O21" s="103"/>
+      <c r="P21" s="103" t="s">
         <v>75</v>
       </c>
-      <c r="Q21" s="83"/>
-      <c r="R21" s="83"/>
-      <c r="S21" s="83"/>
-      <c r="T21" s="83"/>
-      <c r="U21" s="83"/>
-      <c r="V21" s="83"/>
-      <c r="W21" s="83"/>
-      <c r="X21" s="83"/>
+      <c r="Q21" s="103"/>
+      <c r="R21" s="103"/>
+      <c r="S21" s="103"/>
+      <c r="T21" s="103"/>
+      <c r="U21" s="103"/>
+      <c r="V21" s="103"/>
+      <c r="W21" s="103"/>
+      <c r="X21" s="103"/>
     </row>
     <row r="22" spans="1:24">
       <c r="A22" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B22" s="83" t="s">
+      <c r="B22" s="103" t="s">
         <v>81</v>
       </c>
-      <c r="C22" s="83"/>
-      <c r="D22" s="83"/>
-      <c r="E22" s="83"/>
-      <c r="F22" s="83" t="s">
+      <c r="C22" s="103"/>
+      <c r="D22" s="103"/>
+      <c r="E22" s="103"/>
+      <c r="F22" s="103" t="s">
         <v>82</v>
       </c>
-      <c r="G22" s="83"/>
-      <c r="H22" s="83"/>
-      <c r="I22" s="85" t="s">
+      <c r="G22" s="103"/>
+      <c r="H22" s="103"/>
+      <c r="I22" s="104" t="s">
         <v>80</v>
       </c>
-      <c r="J22" s="86"/>
-      <c r="K22" s="86"/>
-      <c r="L22" s="87"/>
-      <c r="M22" s="83" t="s">
+      <c r="J22" s="105"/>
+      <c r="K22" s="105"/>
+      <c r="L22" s="106"/>
+      <c r="M22" s="103" t="s">
         <v>83</v>
       </c>
-      <c r="N22" s="83"/>
-      <c r="O22" s="83"/>
-      <c r="P22" s="83" t="s">
+      <c r="N22" s="103"/>
+      <c r="O22" s="103"/>
+      <c r="P22" s="103" t="s">
         <v>89</v>
       </c>
-      <c r="Q22" s="83"/>
-      <c r="R22" s="83"/>
-      <c r="S22" s="83"/>
-      <c r="T22" s="83"/>
-      <c r="U22" s="83"/>
-      <c r="V22" s="83"/>
-      <c r="W22" s="83"/>
-      <c r="X22" s="83"/>
+      <c r="Q22" s="103"/>
+      <c r="R22" s="103"/>
+      <c r="S22" s="103"/>
+      <c r="T22" s="103"/>
+      <c r="U22" s="103"/>
+      <c r="V22" s="103"/>
+      <c r="W22" s="103"/>
+      <c r="X22" s="103"/>
     </row>
     <row r="23" spans="1:24">
       <c r="A23" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B23" s="83" t="s">
+      <c r="B23" s="103" t="s">
         <v>88</v>
       </c>
-      <c r="C23" s="83"/>
-      <c r="D23" s="83"/>
-      <c r="E23" s="83"/>
-      <c r="F23" s="83"/>
-      <c r="G23" s="83"/>
-      <c r="H23" s="83"/>
-      <c r="I23" s="85" t="s">
+      <c r="C23" s="103"/>
+      <c r="D23" s="103"/>
+      <c r="E23" s="103"/>
+      <c r="F23" s="103"/>
+      <c r="G23" s="103"/>
+      <c r="H23" s="103"/>
+      <c r="I23" s="104" t="s">
         <v>84</v>
       </c>
-      <c r="J23" s="86"/>
-      <c r="K23" s="86"/>
-      <c r="L23" s="87"/>
-      <c r="M23" s="83"/>
-      <c r="N23" s="83"/>
-      <c r="O23" s="83"/>
-      <c r="P23" s="83" t="s">
+      <c r="J23" s="105"/>
+      <c r="K23" s="105"/>
+      <c r="L23" s="106"/>
+      <c r="M23" s="103"/>
+      <c r="N23" s="103"/>
+      <c r="O23" s="103"/>
+      <c r="P23" s="103" t="s">
         <v>89</v>
       </c>
-      <c r="Q23" s="83"/>
-      <c r="R23" s="83"/>
-      <c r="S23" s="83"/>
-      <c r="T23" s="83"/>
-      <c r="U23" s="83"/>
-      <c r="V23" s="83"/>
-      <c r="W23" s="83"/>
-      <c r="X23" s="83"/>
+      <c r="Q23" s="103"/>
+      <c r="R23" s="103"/>
+      <c r="S23" s="103"/>
+      <c r="T23" s="103"/>
+      <c r="U23" s="103"/>
+      <c r="V23" s="103"/>
+      <c r="W23" s="103"/>
+      <c r="X23" s="103"/>
     </row>
     <row r="24" spans="1:24">
       <c r="A24" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B24" s="83"/>
-      <c r="C24" s="83"/>
-      <c r="D24" s="83"/>
-      <c r="E24" s="83"/>
-      <c r="F24" s="83"/>
-      <c r="G24" s="83"/>
-      <c r="H24" s="83"/>
-      <c r="I24" s="85" t="s">
+      <c r="B24" s="103"/>
+      <c r="C24" s="103"/>
+      <c r="D24" s="103"/>
+      <c r="E24" s="103"/>
+      <c r="F24" s="103"/>
+      <c r="G24" s="103"/>
+      <c r="H24" s="103"/>
+      <c r="I24" s="104" t="s">
         <v>90</v>
       </c>
-      <c r="J24" s="86"/>
-      <c r="K24" s="86"/>
-      <c r="L24" s="87"/>
-      <c r="M24" s="83"/>
-      <c r="N24" s="83"/>
-      <c r="O24" s="83"/>
-      <c r="P24" s="83"/>
-      <c r="Q24" s="83"/>
-      <c r="R24" s="83"/>
-      <c r="S24" s="83"/>
-      <c r="T24" s="83"/>
-      <c r="U24" s="83"/>
-      <c r="V24" s="83"/>
-      <c r="W24" s="83"/>
-      <c r="X24" s="83"/>
+      <c r="J24" s="105"/>
+      <c r="K24" s="105"/>
+      <c r="L24" s="106"/>
+      <c r="M24" s="103"/>
+      <c r="N24" s="103"/>
+      <c r="O24" s="103"/>
+      <c r="P24" s="103"/>
+      <c r="Q24" s="103"/>
+      <c r="R24" s="103"/>
+      <c r="S24" s="103"/>
+      <c r="T24" s="103"/>
+      <c r="U24" s="103"/>
+      <c r="V24" s="103"/>
+      <c r="W24" s="103"/>
+      <c r="X24" s="103"/>
     </row>
     <row r="25" spans="1:24">
       <c r="A25" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B25" s="83"/>
-      <c r="C25" s="83"/>
-      <c r="D25" s="83"/>
-      <c r="E25" s="83"/>
-      <c r="F25" s="83" t="s">
+      <c r="B25" s="103"/>
+      <c r="C25" s="103"/>
+      <c r="D25" s="103"/>
+      <c r="E25" s="103"/>
+      <c r="F25" s="103" t="s">
         <v>109</v>
       </c>
-      <c r="G25" s="83"/>
-      <c r="H25" s="83"/>
-      <c r="I25" s="85" t="s">
+      <c r="G25" s="103"/>
+      <c r="H25" s="103"/>
+      <c r="I25" s="104" t="s">
         <v>112</v>
       </c>
-      <c r="J25" s="86"/>
-      <c r="K25" s="86"/>
-      <c r="L25" s="87"/>
-      <c r="M25" s="84" t="s">
+      <c r="J25" s="105"/>
+      <c r="K25" s="105"/>
+      <c r="L25" s="106"/>
+      <c r="M25" s="102" t="s">
         <v>110</v>
       </c>
-      <c r="N25" s="83"/>
-      <c r="O25" s="83"/>
-      <c r="P25" s="83" t="s">
+      <c r="N25" s="103"/>
+      <c r="O25" s="103"/>
+      <c r="P25" s="103" t="s">
         <v>111</v>
       </c>
-      <c r="Q25" s="83"/>
-      <c r="R25" s="83"/>
-      <c r="S25" s="83"/>
-      <c r="T25" s="83"/>
-      <c r="U25" s="83"/>
-      <c r="V25" s="83"/>
-      <c r="W25" s="83"/>
-      <c r="X25" s="83"/>
+      <c r="Q25" s="103"/>
+      <c r="R25" s="103"/>
+      <c r="S25" s="103"/>
+      <c r="T25" s="103"/>
+      <c r="U25" s="103"/>
+      <c r="V25" s="103"/>
+      <c r="W25" s="103"/>
+      <c r="X25" s="103"/>
     </row>
     <row r="26" spans="1:24" ht="45.75" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B26" s="83" t="s">
+      <c r="B26" s="103" t="s">
         <v>114</v>
       </c>
-      <c r="C26" s="83"/>
-      <c r="D26" s="83"/>
-      <c r="E26" s="83"/>
-      <c r="F26" s="84" t="s">
+      <c r="C26" s="103"/>
+      <c r="D26" s="103"/>
+      <c r="E26" s="103"/>
+      <c r="F26" s="102" t="s">
         <v>132</v>
       </c>
-      <c r="G26" s="83"/>
-      <c r="H26" s="83"/>
-      <c r="I26" s="85" t="s">
+      <c r="G26" s="103"/>
+      <c r="H26" s="103"/>
+      <c r="I26" s="104" t="s">
         <v>113</v>
       </c>
-      <c r="J26" s="86"/>
-      <c r="K26" s="86"/>
-      <c r="L26" s="87"/>
-      <c r="M26" s="84" t="s">
+      <c r="J26" s="105"/>
+      <c r="K26" s="105"/>
+      <c r="L26" s="106"/>
+      <c r="M26" s="102" t="s">
         <v>133</v>
       </c>
-      <c r="N26" s="83"/>
-      <c r="O26" s="83"/>
-      <c r="P26" s="84" t="s">
+      <c r="N26" s="103"/>
+      <c r="O26" s="103"/>
+      <c r="P26" s="102" t="s">
         <v>126</v>
       </c>
-      <c r="Q26" s="84"/>
-      <c r="R26" s="84"/>
-      <c r="S26" s="84"/>
-      <c r="T26" s="84"/>
-      <c r="U26" s="84"/>
-      <c r="V26" s="84"/>
-      <c r="W26" s="84"/>
-      <c r="X26" s="84"/>
+      <c r="Q26" s="102"/>
+      <c r="R26" s="102"/>
+      <c r="S26" s="102"/>
+      <c r="T26" s="102"/>
+      <c r="U26" s="102"/>
+      <c r="V26" s="102"/>
+      <c r="W26" s="102"/>
+      <c r="X26" s="102"/>
     </row>
     <row r="27" spans="1:24">
       <c r="A27" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B27" s="83"/>
-      <c r="C27" s="83"/>
-      <c r="D27" s="83"/>
-      <c r="E27" s="83"/>
-      <c r="F27" s="83"/>
-      <c r="G27" s="83"/>
-      <c r="H27" s="83"/>
-      <c r="I27" s="85" t="s">
+      <c r="B27" s="103"/>
+      <c r="C27" s="103"/>
+      <c r="D27" s="103"/>
+      <c r="E27" s="103"/>
+      <c r="F27" s="103"/>
+      <c r="G27" s="103"/>
+      <c r="H27" s="103"/>
+      <c r="I27" s="104" t="s">
         <v>117</v>
       </c>
-      <c r="J27" s="86"/>
-      <c r="K27" s="86"/>
-      <c r="L27" s="87"/>
-      <c r="M27" s="83"/>
-      <c r="N27" s="83"/>
-      <c r="O27" s="83"/>
-      <c r="P27" s="83"/>
-      <c r="Q27" s="83"/>
-      <c r="R27" s="83"/>
-      <c r="S27" s="83"/>
-      <c r="T27" s="83"/>
-      <c r="U27" s="83"/>
-      <c r="V27" s="83"/>
-      <c r="W27" s="83"/>
-      <c r="X27" s="83"/>
+      <c r="J27" s="105"/>
+      <c r="K27" s="105"/>
+      <c r="L27" s="106"/>
+      <c r="M27" s="103"/>
+      <c r="N27" s="103"/>
+      <c r="O27" s="103"/>
+      <c r="P27" s="103"/>
+      <c r="Q27" s="103"/>
+      <c r="R27" s="103"/>
+      <c r="S27" s="103"/>
+      <c r="T27" s="103"/>
+      <c r="U27" s="103"/>
+      <c r="V27" s="103"/>
+      <c r="W27" s="103"/>
+      <c r="X27" s="103"/>
     </row>
     <row r="28" spans="1:24">
       <c r="A28" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B28" s="83"/>
-      <c r="C28" s="83"/>
-      <c r="D28" s="83"/>
-      <c r="E28" s="83"/>
-      <c r="F28" s="83"/>
-      <c r="G28" s="83"/>
-      <c r="H28" s="83"/>
-      <c r="I28" s="85" t="s">
+      <c r="B28" s="103"/>
+      <c r="C28" s="103"/>
+      <c r="D28" s="103"/>
+      <c r="E28" s="103"/>
+      <c r="F28" s="103"/>
+      <c r="G28" s="103"/>
+      <c r="H28" s="103"/>
+      <c r="I28" s="104" t="s">
         <v>119</v>
       </c>
-      <c r="J28" s="86"/>
-      <c r="K28" s="86"/>
-      <c r="L28" s="87"/>
-      <c r="M28" s="83"/>
-      <c r="N28" s="83"/>
-      <c r="O28" s="83"/>
-      <c r="P28" s="83"/>
-      <c r="Q28" s="83"/>
-      <c r="R28" s="83"/>
-      <c r="S28" s="83"/>
-      <c r="T28" s="83"/>
-      <c r="U28" s="83"/>
-      <c r="V28" s="83"/>
-      <c r="W28" s="83"/>
-      <c r="X28" s="83"/>
+      <c r="J28" s="105"/>
+      <c r="K28" s="105"/>
+      <c r="L28" s="106"/>
+      <c r="M28" s="103"/>
+      <c r="N28" s="103"/>
+      <c r="O28" s="103"/>
+      <c r="P28" s="103"/>
+      <c r="Q28" s="103"/>
+      <c r="R28" s="103"/>
+      <c r="S28" s="103"/>
+      <c r="T28" s="103"/>
+      <c r="U28" s="103"/>
+      <c r="V28" s="103"/>
+      <c r="W28" s="103"/>
+      <c r="X28" s="103"/>
     </row>
     <row r="29" spans="1:24" ht="56.25" customHeight="1">
       <c r="A29" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B29" s="84" t="s">
+      <c r="B29" s="102" t="s">
         <v>125</v>
       </c>
-      <c r="C29" s="84"/>
-      <c r="D29" s="84"/>
-      <c r="E29" s="84"/>
-      <c r="F29" s="84" t="s">
+      <c r="C29" s="102"/>
+      <c r="D29" s="102"/>
+      <c r="E29" s="102"/>
+      <c r="F29" s="102" t="s">
         <v>120</v>
       </c>
-      <c r="G29" s="83"/>
-      <c r="H29" s="83"/>
-      <c r="I29" s="85" t="s">
+      <c r="G29" s="103"/>
+      <c r="H29" s="103"/>
+      <c r="I29" s="104" t="s">
         <v>122</v>
       </c>
-      <c r="J29" s="86"/>
-      <c r="K29" s="86"/>
-      <c r="L29" s="87"/>
-      <c r="M29" s="84" t="s">
+      <c r="J29" s="105"/>
+      <c r="K29" s="105"/>
+      <c r="L29" s="106"/>
+      <c r="M29" s="102" t="s">
         <v>123</v>
       </c>
-      <c r="N29" s="83"/>
-      <c r="O29" s="83"/>
-      <c r="P29" s="84" t="s">
+      <c r="N29" s="103"/>
+      <c r="O29" s="103"/>
+      <c r="P29" s="102" t="s">
         <v>124</v>
       </c>
-      <c r="Q29" s="84"/>
-      <c r="R29" s="84"/>
-      <c r="S29" s="84"/>
-      <c r="T29" s="84"/>
-      <c r="U29" s="84"/>
-      <c r="V29" s="84"/>
-      <c r="W29" s="84"/>
-      <c r="X29" s="84"/>
+      <c r="Q29" s="102"/>
+      <c r="R29" s="102"/>
+      <c r="S29" s="102"/>
+      <c r="T29" s="102"/>
+      <c r="U29" s="102"/>
+      <c r="V29" s="102"/>
+      <c r="W29" s="102"/>
+      <c r="X29" s="102"/>
     </row>
     <row r="30" spans="1:24">
       <c r="A30" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B30" s="83"/>
-      <c r="C30" s="83"/>
-      <c r="D30" s="83"/>
-      <c r="E30" s="83"/>
-      <c r="F30" s="83" t="s">
+      <c r="B30" s="103"/>
+      <c r="C30" s="103"/>
+      <c r="D30" s="103"/>
+      <c r="E30" s="103"/>
+      <c r="F30" s="103" t="s">
         <v>136</v>
       </c>
-      <c r="G30" s="83"/>
-      <c r="H30" s="83"/>
-      <c r="I30" s="85" t="s">
+      <c r="G30" s="103"/>
+      <c r="H30" s="103"/>
+      <c r="I30" s="104" t="s">
         <v>135</v>
       </c>
-      <c r="J30" s="86"/>
-      <c r="K30" s="86"/>
-      <c r="L30" s="87"/>
-      <c r="M30" s="83" t="s">
+      <c r="J30" s="105"/>
+      <c r="K30" s="105"/>
+      <c r="L30" s="106"/>
+      <c r="M30" s="103" t="s">
         <v>137</v>
       </c>
-      <c r="N30" s="83"/>
-      <c r="O30" s="83"/>
-      <c r="P30" s="83"/>
-      <c r="Q30" s="83"/>
-      <c r="R30" s="83"/>
-      <c r="S30" s="83"/>
-      <c r="T30" s="83"/>
-      <c r="U30" s="83"/>
-      <c r="V30" s="83"/>
-      <c r="W30" s="83"/>
-      <c r="X30" s="83"/>
+      <c r="N30" s="103"/>
+      <c r="O30" s="103"/>
+      <c r="P30" s="103"/>
+      <c r="Q30" s="103"/>
+      <c r="R30" s="103"/>
+      <c r="S30" s="103"/>
+      <c r="T30" s="103"/>
+      <c r="U30" s="103"/>
+      <c r="V30" s="103"/>
+      <c r="W30" s="103"/>
+      <c r="X30" s="103"/>
     </row>
     <row r="31" spans="1:24">
       <c r="A31" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B31" s="83" t="s">
+      <c r="B31" s="103" t="s">
         <v>144</v>
       </c>
-      <c r="C31" s="83"/>
-      <c r="D31" s="83"/>
-      <c r="E31" s="83"/>
-      <c r="F31" s="84" t="s">
+      <c r="C31" s="103"/>
+      <c r="D31" s="103"/>
+      <c r="E31" s="103"/>
+      <c r="F31" s="102" t="s">
         <v>143</v>
       </c>
-      <c r="G31" s="83"/>
-      <c r="H31" s="83"/>
-      <c r="I31" s="85" t="s">
+      <c r="G31" s="103"/>
+      <c r="H31" s="103"/>
+      <c r="I31" s="104" t="s">
         <v>145</v>
       </c>
-      <c r="J31" s="86"/>
-      <c r="K31" s="86"/>
-      <c r="L31" s="87"/>
-      <c r="M31" s="84" t="s">
+      <c r="J31" s="105"/>
+      <c r="K31" s="105"/>
+      <c r="L31" s="106"/>
+      <c r="M31" s="102" t="s">
         <v>146</v>
       </c>
-      <c r="N31" s="83"/>
-      <c r="O31" s="83"/>
-      <c r="P31" s="83"/>
-      <c r="Q31" s="83"/>
-      <c r="R31" s="83"/>
-      <c r="S31" s="83"/>
-      <c r="T31" s="83"/>
-      <c r="U31" s="83"/>
-      <c r="V31" s="83"/>
-      <c r="W31" s="83"/>
-      <c r="X31" s="83"/>
+      <c r="N31" s="103"/>
+      <c r="O31" s="103"/>
+      <c r="P31" s="103"/>
+      <c r="Q31" s="103"/>
+      <c r="R31" s="103"/>
+      <c r="S31" s="103"/>
+      <c r="T31" s="103"/>
+      <c r="U31" s="103"/>
+      <c r="V31" s="103"/>
+      <c r="W31" s="103"/>
+      <c r="X31" s="103"/>
     </row>
     <row r="32" spans="1:24">
       <c r="A32" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B32" s="103"/>
+      <c r="C32" s="103"/>
+      <c r="D32" s="103"/>
+      <c r="E32" s="103"/>
+      <c r="F32" s="102" t="s">
+        <v>203</v>
+      </c>
+      <c r="G32" s="103"/>
+      <c r="H32" s="103"/>
+      <c r="I32" s="104"/>
+      <c r="J32" s="105"/>
+      <c r="K32" s="105"/>
+      <c r="L32" s="106"/>
+      <c r="M32" s="102" t="s">
+        <v>204</v>
+      </c>
+      <c r="N32" s="103"/>
+      <c r="O32" s="103"/>
+      <c r="P32" s="103" t="s">
         <v>209</v>
       </c>
-      <c r="B32" s="83"/>
-      <c r="C32" s="83"/>
-      <c r="D32" s="83"/>
-      <c r="E32" s="83"/>
-      <c r="F32" s="84" t="s">
-        <v>204</v>
-      </c>
-      <c r="G32" s="83"/>
-      <c r="H32" s="83"/>
-      <c r="I32" s="85"/>
-      <c r="J32" s="86"/>
-      <c r="K32" s="86"/>
-      <c r="L32" s="87"/>
-      <c r="M32" s="84" t="s">
-        <v>205</v>
-      </c>
-      <c r="N32" s="83"/>
-      <c r="O32" s="83"/>
-      <c r="P32" s="83" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q32" s="83"/>
-      <c r="R32" s="83"/>
-      <c r="S32" s="83"/>
-      <c r="T32" s="83"/>
-      <c r="U32" s="83"/>
-      <c r="V32" s="83"/>
-      <c r="W32" s="83"/>
-      <c r="X32" s="83"/>
+      <c r="Q32" s="103"/>
+      <c r="R32" s="103"/>
+      <c r="S32" s="103"/>
+      <c r="T32" s="103"/>
+      <c r="U32" s="103"/>
+      <c r="V32" s="103"/>
+      <c r="W32" s="103"/>
+      <c r="X32" s="103"/>
     </row>
     <row r="33" spans="1:24">
       <c r="A33" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="B33" s="83"/>
-      <c r="C33" s="83"/>
-      <c r="D33" s="83"/>
-      <c r="E33" s="83"/>
-      <c r="F33" s="83" t="s">
         <v>207</v>
       </c>
-      <c r="G33" s="83"/>
-      <c r="H33" s="83"/>
-      <c r="I33" s="85"/>
-      <c r="J33" s="86"/>
-      <c r="K33" s="86"/>
-      <c r="L33" s="87"/>
-      <c r="M33" s="83" t="s">
+      <c r="B33" s="103"/>
+      <c r="C33" s="103"/>
+      <c r="D33" s="103"/>
+      <c r="E33" s="103"/>
+      <c r="F33" s="103" t="s">
         <v>206</v>
       </c>
-      <c r="N33" s="83"/>
-      <c r="O33" s="83"/>
-      <c r="P33" s="83"/>
-      <c r="Q33" s="83"/>
-      <c r="R33" s="83"/>
-      <c r="S33" s="83"/>
-      <c r="T33" s="83"/>
-      <c r="U33" s="83"/>
-      <c r="V33" s="83"/>
-      <c r="W33" s="83"/>
-      <c r="X33" s="83"/>
+      <c r="G33" s="103"/>
+      <c r="H33" s="103"/>
+      <c r="I33" s="104"/>
+      <c r="J33" s="105"/>
+      <c r="K33" s="105"/>
+      <c r="L33" s="106"/>
+      <c r="M33" s="103" t="s">
+        <v>205</v>
+      </c>
+      <c r="N33" s="103"/>
+      <c r="O33" s="103"/>
+      <c r="P33" s="103"/>
+      <c r="Q33" s="103"/>
+      <c r="R33" s="103"/>
+      <c r="S33" s="103"/>
+      <c r="T33" s="103"/>
+      <c r="U33" s="103"/>
+      <c r="V33" s="103"/>
+      <c r="W33" s="103"/>
+      <c r="X33" s="103"/>
     </row>
     <row r="34" spans="1:24">
-      <c r="A34" s="3"/>
-      <c r="B34" s="83"/>
-      <c r="C34" s="83"/>
-      <c r="D34" s="83"/>
-      <c r="E34" s="83"/>
-      <c r="F34" s="83"/>
-      <c r="G34" s="83"/>
-      <c r="H34" s="83"/>
-      <c r="I34" s="85"/>
-      <c r="J34" s="86"/>
-      <c r="K34" s="86"/>
-      <c r="L34" s="87"/>
-      <c r="M34" s="83"/>
-      <c r="N34" s="83"/>
-      <c r="O34" s="83"/>
-      <c r="P34" s="83"/>
-      <c r="Q34" s="83"/>
-      <c r="R34" s="83"/>
-      <c r="S34" s="83"/>
-      <c r="T34" s="83"/>
-      <c r="U34" s="83"/>
-      <c r="V34" s="83"/>
-      <c r="W34" s="83"/>
-      <c r="X34" s="83"/>
+      <c r="A34" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B34" s="103" t="s">
+        <v>370</v>
+      </c>
+      <c r="C34" s="103"/>
+      <c r="D34" s="103"/>
+      <c r="E34" s="103"/>
+      <c r="F34" s="103"/>
+      <c r="G34" s="103"/>
+      <c r="H34" s="103"/>
+      <c r="I34" s="104" t="s">
+        <v>369</v>
+      </c>
+      <c r="J34" s="105"/>
+      <c r="K34" s="105"/>
+      <c r="L34" s="106"/>
+      <c r="M34" s="103"/>
+      <c r="N34" s="103"/>
+      <c r="O34" s="103"/>
+      <c r="P34" s="103"/>
+      <c r="Q34" s="103"/>
+      <c r="R34" s="103"/>
+      <c r="S34" s="103"/>
+      <c r="T34" s="103"/>
+      <c r="U34" s="103"/>
+      <c r="V34" s="103"/>
+      <c r="W34" s="103"/>
+      <c r="X34" s="103"/>
     </row>
     <row r="35" spans="1:24">
-      <c r="A35" s="3"/>
-      <c r="B35" s="83"/>
-      <c r="C35" s="83"/>
-      <c r="D35" s="83"/>
-      <c r="E35" s="83"/>
-      <c r="F35" s="83"/>
-      <c r="G35" s="83"/>
-      <c r="H35" s="83"/>
-      <c r="I35" s="85"/>
-      <c r="J35" s="86"/>
-      <c r="K35" s="86"/>
-      <c r="L35" s="87"/>
-      <c r="M35" s="83"/>
-      <c r="N35" s="83"/>
-      <c r="O35" s="83"/>
-      <c r="P35" s="83"/>
-      <c r="Q35" s="83"/>
-      <c r="R35" s="83"/>
-      <c r="S35" s="83"/>
-      <c r="T35" s="83"/>
-      <c r="U35" s="83"/>
-      <c r="V35" s="83"/>
-      <c r="W35" s="83"/>
-      <c r="X35" s="83"/>
+      <c r="A35" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="B35" s="103" t="s">
+        <v>372</v>
+      </c>
+      <c r="C35" s="103"/>
+      <c r="D35" s="103"/>
+      <c r="E35" s="103"/>
+      <c r="F35" s="103"/>
+      <c r="G35" s="103"/>
+      <c r="H35" s="103"/>
+      <c r="I35" s="104" t="s">
+        <v>372</v>
+      </c>
+      <c r="J35" s="105"/>
+      <c r="K35" s="105"/>
+      <c r="L35" s="106"/>
+      <c r="M35" s="103"/>
+      <c r="N35" s="103"/>
+      <c r="O35" s="103"/>
+      <c r="P35" s="103" t="s">
+        <v>374</v>
+      </c>
+      <c r="Q35" s="103"/>
+      <c r="R35" s="103"/>
+      <c r="S35" s="103"/>
+      <c r="T35" s="103"/>
+      <c r="U35" s="103"/>
+      <c r="V35" s="103"/>
+      <c r="W35" s="103"/>
+      <c r="X35" s="103"/>
     </row>
     <row r="36" spans="1:24">
       <c r="A36" s="3"/>
-      <c r="B36" s="83"/>
-      <c r="C36" s="83"/>
-      <c r="D36" s="83"/>
-      <c r="E36" s="83"/>
-      <c r="F36" s="83"/>
-      <c r="G36" s="83"/>
-      <c r="H36" s="83"/>
-      <c r="I36" s="85"/>
-      <c r="J36" s="86"/>
-      <c r="K36" s="86"/>
-      <c r="L36" s="87"/>
-      <c r="M36" s="83"/>
-      <c r="N36" s="83"/>
-      <c r="O36" s="83"/>
-      <c r="P36" s="83"/>
-      <c r="Q36" s="83"/>
-      <c r="R36" s="83"/>
-      <c r="S36" s="83"/>
-      <c r="T36" s="83"/>
-      <c r="U36" s="83"/>
-      <c r="V36" s="83"/>
-      <c r="W36" s="83"/>
-      <c r="X36" s="83"/>
+      <c r="B36" s="103"/>
+      <c r="C36" s="103"/>
+      <c r="D36" s="103"/>
+      <c r="E36" s="103"/>
+      <c r="F36" s="103"/>
+      <c r="G36" s="103"/>
+      <c r="H36" s="103"/>
+      <c r="I36" s="104"/>
+      <c r="J36" s="105"/>
+      <c r="K36" s="105"/>
+      <c r="L36" s="106"/>
+      <c r="M36" s="103"/>
+      <c r="N36" s="103"/>
+      <c r="O36" s="103"/>
+      <c r="P36" s="103"/>
+      <c r="Q36" s="103"/>
+      <c r="R36" s="103"/>
+      <c r="S36" s="103"/>
+      <c r="T36" s="103"/>
+      <c r="U36" s="103"/>
+      <c r="V36" s="103"/>
+      <c r="W36" s="103"/>
+      <c r="X36" s="103"/>
     </row>
     <row r="37" spans="1:24">
       <c r="A37" s="3"/>
-      <c r="B37" s="83"/>
-      <c r="C37" s="83"/>
-      <c r="D37" s="83"/>
-      <c r="E37" s="83"/>
-      <c r="F37" s="83"/>
-      <c r="G37" s="83"/>
-      <c r="H37" s="83"/>
-      <c r="I37" s="85"/>
-      <c r="J37" s="86"/>
-      <c r="K37" s="86"/>
-      <c r="L37" s="87"/>
-      <c r="M37" s="83"/>
-      <c r="N37" s="83"/>
-      <c r="O37" s="83"/>
-      <c r="P37" s="83"/>
-      <c r="Q37" s="83"/>
-      <c r="R37" s="83"/>
-      <c r="S37" s="83"/>
-      <c r="T37" s="83"/>
-      <c r="U37" s="83"/>
-      <c r="V37" s="83"/>
-      <c r="W37" s="83"/>
-      <c r="X37" s="83"/>
+      <c r="B37" s="103"/>
+      <c r="C37" s="103"/>
+      <c r="D37" s="103"/>
+      <c r="E37" s="103"/>
+      <c r="F37" s="103"/>
+      <c r="G37" s="103"/>
+      <c r="H37" s="103"/>
+      <c r="I37" s="104"/>
+      <c r="J37" s="105"/>
+      <c r="K37" s="105"/>
+      <c r="L37" s="106"/>
+      <c r="M37" s="103"/>
+      <c r="N37" s="103"/>
+      <c r="O37" s="103"/>
+      <c r="P37" s="103"/>
+      <c r="Q37" s="103"/>
+      <c r="R37" s="103"/>
+      <c r="S37" s="103"/>
+      <c r="T37" s="103"/>
+      <c r="U37" s="103"/>
+      <c r="V37" s="103"/>
+      <c r="W37" s="103"/>
+      <c r="X37" s="103"/>
     </row>
     <row r="38" spans="1:24">
       <c r="A38" s="3"/>
-      <c r="B38" s="83"/>
-      <c r="C38" s="83"/>
-      <c r="D38" s="83"/>
-      <c r="E38" s="83"/>
-      <c r="F38" s="83"/>
-      <c r="G38" s="83"/>
-      <c r="H38" s="83"/>
-      <c r="I38" s="85"/>
-      <c r="J38" s="86"/>
-      <c r="K38" s="86"/>
-      <c r="L38" s="87"/>
-      <c r="M38" s="83"/>
-      <c r="N38" s="83"/>
-      <c r="O38" s="83"/>
-      <c r="P38" s="83"/>
-      <c r="Q38" s="83"/>
-      <c r="R38" s="83"/>
-      <c r="S38" s="83"/>
-      <c r="T38" s="83"/>
-      <c r="U38" s="83"/>
-      <c r="V38" s="83"/>
-      <c r="W38" s="83"/>
-      <c r="X38" s="83"/>
+      <c r="B38" s="103"/>
+      <c r="C38" s="103"/>
+      <c r="D38" s="103"/>
+      <c r="E38" s="103"/>
+      <c r="F38" s="103"/>
+      <c r="G38" s="103"/>
+      <c r="H38" s="103"/>
+      <c r="I38" s="104"/>
+      <c r="J38" s="105"/>
+      <c r="K38" s="105"/>
+      <c r="L38" s="106"/>
+      <c r="M38" s="103"/>
+      <c r="N38" s="103"/>
+      <c r="O38" s="103"/>
+      <c r="P38" s="103"/>
+      <c r="Q38" s="103"/>
+      <c r="R38" s="103"/>
+      <c r="S38" s="103"/>
+      <c r="T38" s="103"/>
+      <c r="U38" s="103"/>
+      <c r="V38" s="103"/>
+      <c r="W38" s="103"/>
+      <c r="X38" s="103"/>
     </row>
     <row r="39" spans="1:24">
       <c r="A39" s="3"/>
-      <c r="B39" s="83"/>
-      <c r="C39" s="83"/>
-      <c r="D39" s="83"/>
-      <c r="E39" s="83"/>
-      <c r="F39" s="83"/>
-      <c r="G39" s="83"/>
-      <c r="H39" s="83"/>
-      <c r="I39" s="85"/>
-      <c r="J39" s="86"/>
-      <c r="K39" s="86"/>
-      <c r="L39" s="87"/>
-      <c r="M39" s="83"/>
-      <c r="N39" s="83"/>
-      <c r="O39" s="83"/>
-      <c r="P39" s="83"/>
-      <c r="Q39" s="83"/>
-      <c r="R39" s="83"/>
-      <c r="S39" s="83"/>
-      <c r="T39" s="83"/>
-      <c r="U39" s="83"/>
-      <c r="V39" s="83"/>
-      <c r="W39" s="83"/>
-      <c r="X39" s="83"/>
+      <c r="B39" s="103"/>
+      <c r="C39" s="103"/>
+      <c r="D39" s="103"/>
+      <c r="E39" s="103"/>
+      <c r="F39" s="103"/>
+      <c r="G39" s="103"/>
+      <c r="H39" s="103"/>
+      <c r="I39" s="104"/>
+      <c r="J39" s="105"/>
+      <c r="K39" s="105"/>
+      <c r="L39" s="106"/>
+      <c r="M39" s="103"/>
+      <c r="N39" s="103"/>
+      <c r="O39" s="103"/>
+      <c r="P39" s="103"/>
+      <c r="Q39" s="103"/>
+      <c r="R39" s="103"/>
+      <c r="S39" s="103"/>
+      <c r="T39" s="103"/>
+      <c r="U39" s="103"/>
+      <c r="V39" s="103"/>
+      <c r="W39" s="103"/>
+      <c r="X39" s="103"/>
     </row>
     <row r="40" spans="1:24">
       <c r="A40" s="3"/>
-      <c r="B40" s="83"/>
-      <c r="C40" s="83"/>
-      <c r="D40" s="83"/>
-      <c r="E40" s="83"/>
-      <c r="F40" s="83"/>
-      <c r="G40" s="83"/>
-      <c r="H40" s="83"/>
-      <c r="I40" s="85"/>
-      <c r="J40" s="86"/>
-      <c r="K40" s="86"/>
-      <c r="L40" s="87"/>
-      <c r="M40" s="83"/>
-      <c r="N40" s="83"/>
-      <c r="O40" s="83"/>
-      <c r="P40" s="83"/>
-      <c r="Q40" s="83"/>
-      <c r="R40" s="83"/>
-      <c r="S40" s="83"/>
-      <c r="T40" s="83"/>
-      <c r="U40" s="83"/>
-      <c r="V40" s="83"/>
-      <c r="W40" s="83"/>
-      <c r="X40" s="83"/>
+      <c r="B40" s="103"/>
+      <c r="C40" s="103"/>
+      <c r="D40" s="103"/>
+      <c r="E40" s="103"/>
+      <c r="F40" s="103"/>
+      <c r="G40" s="103"/>
+      <c r="H40" s="103"/>
+      <c r="I40" s="104"/>
+      <c r="J40" s="105"/>
+      <c r="K40" s="105"/>
+      <c r="L40" s="106"/>
+      <c r="M40" s="103"/>
+      <c r="N40" s="103"/>
+      <c r="O40" s="103"/>
+      <c r="P40" s="103"/>
+      <c r="Q40" s="103"/>
+      <c r="R40" s="103"/>
+      <c r="S40" s="103"/>
+      <c r="T40" s="103"/>
+      <c r="U40" s="103"/>
+      <c r="V40" s="103"/>
+      <c r="W40" s="103"/>
+      <c r="X40" s="103"/>
     </row>
     <row r="41" spans="1:24">
       <c r="A41" s="3"/>
-      <c r="B41" s="83"/>
-      <c r="C41" s="83"/>
-      <c r="D41" s="83"/>
-      <c r="E41" s="83"/>
-      <c r="F41" s="83"/>
-      <c r="G41" s="83"/>
-      <c r="H41" s="83"/>
-      <c r="I41" s="85"/>
-      <c r="J41" s="86"/>
-      <c r="K41" s="86"/>
-      <c r="L41" s="87"/>
-      <c r="M41" s="83"/>
-      <c r="N41" s="83"/>
-      <c r="O41" s="83"/>
-      <c r="P41" s="83"/>
-      <c r="Q41" s="83"/>
-      <c r="R41" s="83"/>
-      <c r="S41" s="83"/>
-      <c r="T41" s="83"/>
-      <c r="U41" s="83"/>
-      <c r="V41" s="83"/>
-      <c r="W41" s="83"/>
-      <c r="X41" s="83"/>
+      <c r="B41" s="103"/>
+      <c r="C41" s="103"/>
+      <c r="D41" s="103"/>
+      <c r="E41" s="103"/>
+      <c r="F41" s="103"/>
+      <c r="G41" s="103"/>
+      <c r="H41" s="103"/>
+      <c r="I41" s="104"/>
+      <c r="J41" s="105"/>
+      <c r="K41" s="105"/>
+      <c r="L41" s="106"/>
+      <c r="M41" s="103"/>
+      <c r="N41" s="103"/>
+      <c r="O41" s="103"/>
+      <c r="P41" s="103"/>
+      <c r="Q41" s="103"/>
+      <c r="R41" s="103"/>
+      <c r="S41" s="103"/>
+      <c r="T41" s="103"/>
+      <c r="U41" s="103"/>
+      <c r="V41" s="103"/>
+      <c r="W41" s="103"/>
+      <c r="X41" s="103"/>
     </row>
     <row r="42" spans="1:24">
       <c r="A42" s="3"/>
-      <c r="B42" s="83"/>
-      <c r="C42" s="83"/>
-      <c r="D42" s="83"/>
-      <c r="E42" s="83"/>
-      <c r="F42" s="83"/>
-      <c r="G42" s="83"/>
-      <c r="H42" s="83"/>
-      <c r="I42" s="85"/>
-      <c r="J42" s="86"/>
-      <c r="K42" s="86"/>
-      <c r="L42" s="87"/>
-      <c r="M42" s="83"/>
-      <c r="N42" s="83"/>
-      <c r="O42" s="83"/>
-      <c r="P42" s="83"/>
-      <c r="Q42" s="83"/>
-      <c r="R42" s="83"/>
-      <c r="S42" s="83"/>
-      <c r="T42" s="83"/>
-      <c r="U42" s="83"/>
-      <c r="V42" s="83"/>
-      <c r="W42" s="83"/>
-      <c r="X42" s="83"/>
+      <c r="B42" s="103"/>
+      <c r="C42" s="103"/>
+      <c r="D42" s="103"/>
+      <c r="E42" s="103"/>
+      <c r="F42" s="103"/>
+      <c r="G42" s="103"/>
+      <c r="H42" s="103"/>
+      <c r="I42" s="104"/>
+      <c r="J42" s="105"/>
+      <c r="K42" s="105"/>
+      <c r="L42" s="106"/>
+      <c r="M42" s="103"/>
+      <c r="N42" s="103"/>
+      <c r="O42" s="103"/>
+      <c r="P42" s="103"/>
+      <c r="Q42" s="103"/>
+      <c r="R42" s="103"/>
+      <c r="S42" s="103"/>
+      <c r="T42" s="103"/>
+      <c r="U42" s="103"/>
+      <c r="V42" s="103"/>
+      <c r="W42" s="103"/>
+      <c r="X42" s="103"/>
     </row>
     <row r="43" spans="1:24">
       <c r="A43" s="3"/>
-      <c r="B43" s="83"/>
-      <c r="C43" s="83"/>
-      <c r="D43" s="83"/>
-      <c r="E43" s="83"/>
-      <c r="F43" s="83"/>
-      <c r="G43" s="83"/>
-      <c r="H43" s="83"/>
-      <c r="I43" s="85"/>
-      <c r="J43" s="86"/>
-      <c r="K43" s="86"/>
-      <c r="L43" s="87"/>
-      <c r="M43" s="83"/>
-      <c r="N43" s="83"/>
-      <c r="O43" s="83"/>
-      <c r="P43" s="83"/>
-      <c r="Q43" s="83"/>
-      <c r="R43" s="83"/>
-      <c r="S43" s="83"/>
-      <c r="T43" s="83"/>
-      <c r="U43" s="83"/>
-      <c r="V43" s="83"/>
-      <c r="W43" s="83"/>
-      <c r="X43" s="83"/>
+      <c r="B43" s="103"/>
+      <c r="C43" s="103"/>
+      <c r="D43" s="103"/>
+      <c r="E43" s="103"/>
+      <c r="F43" s="103"/>
+      <c r="G43" s="103"/>
+      <c r="H43" s="103"/>
+      <c r="I43" s="104"/>
+      <c r="J43" s="105"/>
+      <c r="K43" s="105"/>
+      <c r="L43" s="106"/>
+      <c r="M43" s="103"/>
+      <c r="N43" s="103"/>
+      <c r="O43" s="103"/>
+      <c r="P43" s="103"/>
+      <c r="Q43" s="103"/>
+      <c r="R43" s="103"/>
+      <c r="S43" s="103"/>
+      <c r="T43" s="103"/>
+      <c r="U43" s="103"/>
+      <c r="V43" s="103"/>
+      <c r="W43" s="103"/>
+      <c r="X43" s="103"/>
     </row>
     <row r="44" spans="1:24">
       <c r="A44" s="3"/>
-      <c r="B44" s="83"/>
-      <c r="C44" s="83"/>
-      <c r="D44" s="83"/>
-      <c r="E44" s="83"/>
-      <c r="F44" s="83"/>
-      <c r="G44" s="83"/>
-      <c r="H44" s="83"/>
-      <c r="I44" s="85"/>
-      <c r="J44" s="86"/>
-      <c r="K44" s="86"/>
-      <c r="L44" s="87"/>
-      <c r="M44" s="83"/>
-      <c r="N44" s="83"/>
-      <c r="O44" s="83"/>
-      <c r="P44" s="83"/>
-      <c r="Q44" s="83"/>
-      <c r="R44" s="83"/>
-      <c r="S44" s="83"/>
-      <c r="T44" s="83"/>
-      <c r="U44" s="83"/>
-      <c r="V44" s="83"/>
-      <c r="W44" s="83"/>
-      <c r="X44" s="83"/>
+      <c r="B44" s="103"/>
+      <c r="C44" s="103"/>
+      <c r="D44" s="103"/>
+      <c r="E44" s="103"/>
+      <c r="F44" s="103"/>
+      <c r="G44" s="103"/>
+      <c r="H44" s="103"/>
+      <c r="I44" s="104"/>
+      <c r="J44" s="105"/>
+      <c r="K44" s="105"/>
+      <c r="L44" s="106"/>
+      <c r="M44" s="103"/>
+      <c r="N44" s="103"/>
+      <c r="O44" s="103"/>
+      <c r="P44" s="103"/>
+      <c r="Q44" s="103"/>
+      <c r="R44" s="103"/>
+      <c r="S44" s="103"/>
+      <c r="T44" s="103"/>
+      <c r="U44" s="103"/>
+      <c r="V44" s="103"/>
+      <c r="W44" s="103"/>
+      <c r="X44" s="103"/>
     </row>
     <row r="45" spans="1:24">
       <c r="A45" s="3"/>
-      <c r="B45" s="83"/>
-      <c r="C45" s="83"/>
-      <c r="D45" s="83"/>
-      <c r="E45" s="83"/>
-      <c r="F45" s="83"/>
-      <c r="G45" s="83"/>
-      <c r="H45" s="83"/>
-      <c r="I45" s="85"/>
-      <c r="J45" s="86"/>
-      <c r="K45" s="86"/>
-      <c r="L45" s="87"/>
-      <c r="M45" s="83"/>
-      <c r="N45" s="83"/>
-      <c r="O45" s="83"/>
-      <c r="P45" s="83"/>
-      <c r="Q45" s="83"/>
-      <c r="R45" s="83"/>
-      <c r="S45" s="83"/>
-      <c r="T45" s="83"/>
-      <c r="U45" s="83"/>
-      <c r="V45" s="83"/>
-      <c r="W45" s="83"/>
-      <c r="X45" s="83"/>
+      <c r="B45" s="103"/>
+      <c r="C45" s="103"/>
+      <c r="D45" s="103"/>
+      <c r="E45" s="103"/>
+      <c r="F45" s="103"/>
+      <c r="G45" s="103"/>
+      <c r="H45" s="103"/>
+      <c r="I45" s="104"/>
+      <c r="J45" s="105"/>
+      <c r="K45" s="105"/>
+      <c r="L45" s="106"/>
+      <c r="M45" s="103"/>
+      <c r="N45" s="103"/>
+      <c r="O45" s="103"/>
+      <c r="P45" s="103"/>
+      <c r="Q45" s="103"/>
+      <c r="R45" s="103"/>
+      <c r="S45" s="103"/>
+      <c r="T45" s="103"/>
+      <c r="U45" s="103"/>
+      <c r="V45" s="103"/>
+      <c r="W45" s="103"/>
+      <c r="X45" s="103"/>
     </row>
     <row r="46" spans="1:24">
       <c r="A46" s="3"/>
-      <c r="B46" s="83"/>
-      <c r="C46" s="83"/>
-      <c r="D46" s="83"/>
-      <c r="E46" s="83"/>
-      <c r="F46" s="83"/>
-      <c r="G46" s="83"/>
-      <c r="H46" s="83"/>
-      <c r="I46" s="85"/>
-      <c r="J46" s="86"/>
-      <c r="K46" s="86"/>
-      <c r="L46" s="87"/>
-      <c r="M46" s="83"/>
-      <c r="N46" s="83"/>
-      <c r="O46" s="83"/>
-      <c r="P46" s="83"/>
-      <c r="Q46" s="83"/>
-      <c r="R46" s="83"/>
-      <c r="S46" s="83"/>
-      <c r="T46" s="83"/>
-      <c r="U46" s="83"/>
-      <c r="V46" s="83"/>
-      <c r="W46" s="83"/>
-      <c r="X46" s="83"/>
+      <c r="B46" s="103"/>
+      <c r="C46" s="103"/>
+      <c r="D46" s="103"/>
+      <c r="E46" s="103"/>
+      <c r="F46" s="103"/>
+      <c r="G46" s="103"/>
+      <c r="H46" s="103"/>
+      <c r="I46" s="104"/>
+      <c r="J46" s="105"/>
+      <c r="K46" s="105"/>
+      <c r="L46" s="106"/>
+      <c r="M46" s="103"/>
+      <c r="N46" s="103"/>
+      <c r="O46" s="103"/>
+      <c r="P46" s="103"/>
+      <c r="Q46" s="103"/>
+      <c r="R46" s="103"/>
+      <c r="S46" s="103"/>
+      <c r="T46" s="103"/>
+      <c r="U46" s="103"/>
+      <c r="V46" s="103"/>
+      <c r="W46" s="103"/>
+      <c r="X46" s="103"/>
     </row>
     <row r="47" spans="1:24">
       <c r="A47" s="3"/>
-      <c r="B47" s="83"/>
-      <c r="C47" s="83"/>
-      <c r="D47" s="83"/>
-      <c r="E47" s="83"/>
-      <c r="F47" s="83"/>
-      <c r="G47" s="83"/>
-      <c r="H47" s="83"/>
-      <c r="I47" s="85"/>
-      <c r="J47" s="86"/>
-      <c r="K47" s="86"/>
-      <c r="L47" s="87"/>
-      <c r="M47" s="83"/>
-      <c r="N47" s="83"/>
-      <c r="O47" s="83"/>
-      <c r="P47" s="83"/>
-      <c r="Q47" s="83"/>
-      <c r="R47" s="83"/>
-      <c r="S47" s="83"/>
-      <c r="T47" s="83"/>
-      <c r="U47" s="83"/>
-      <c r="V47" s="83"/>
-      <c r="W47" s="83"/>
-      <c r="X47" s="83"/>
+      <c r="B47" s="103"/>
+      <c r="C47" s="103"/>
+      <c r="D47" s="103"/>
+      <c r="E47" s="103"/>
+      <c r="F47" s="103"/>
+      <c r="G47" s="103"/>
+      <c r="H47" s="103"/>
+      <c r="I47" s="104"/>
+      <c r="J47" s="105"/>
+      <c r="K47" s="105"/>
+      <c r="L47" s="106"/>
+      <c r="M47" s="103"/>
+      <c r="N47" s="103"/>
+      <c r="O47" s="103"/>
+      <c r="P47" s="103"/>
+      <c r="Q47" s="103"/>
+      <c r="R47" s="103"/>
+      <c r="S47" s="103"/>
+      <c r="T47" s="103"/>
+      <c r="U47" s="103"/>
+      <c r="V47" s="103"/>
+      <c r="W47" s="103"/>
+      <c r="X47" s="103"/>
     </row>
     <row r="48" spans="1:24">
       <c r="A48" s="3"/>
-      <c r="B48" s="83"/>
-      <c r="C48" s="83"/>
-      <c r="D48" s="83"/>
-      <c r="E48" s="83"/>
-      <c r="F48" s="83"/>
-      <c r="G48" s="83"/>
-      <c r="H48" s="83"/>
-      <c r="I48" s="85"/>
-      <c r="J48" s="86"/>
-      <c r="K48" s="86"/>
-      <c r="L48" s="87"/>
-      <c r="M48" s="83"/>
-      <c r="N48" s="83"/>
-      <c r="O48" s="83"/>
-      <c r="P48" s="83"/>
-      <c r="Q48" s="83"/>
-      <c r="R48" s="83"/>
-      <c r="S48" s="83"/>
-      <c r="T48" s="83"/>
-      <c r="U48" s="83"/>
-      <c r="V48" s="83"/>
-      <c r="W48" s="83"/>
-      <c r="X48" s="83"/>
+      <c r="B48" s="103"/>
+      <c r="C48" s="103"/>
+      <c r="D48" s="103"/>
+      <c r="E48" s="103"/>
+      <c r="F48" s="103"/>
+      <c r="G48" s="103"/>
+      <c r="H48" s="103"/>
+      <c r="I48" s="104"/>
+      <c r="J48" s="105"/>
+      <c r="K48" s="105"/>
+      <c r="L48" s="106"/>
+      <c r="M48" s="103"/>
+      <c r="N48" s="103"/>
+      <c r="O48" s="103"/>
+      <c r="P48" s="103"/>
+      <c r="Q48" s="103"/>
+      <c r="R48" s="103"/>
+      <c r="S48" s="103"/>
+      <c r="T48" s="103"/>
+      <c r="U48" s="103"/>
+      <c r="V48" s="103"/>
+      <c r="W48" s="103"/>
+      <c r="X48" s="103"/>
     </row>
     <row r="49" spans="1:24">
       <c r="A49" s="3"/>
-      <c r="B49" s="83"/>
-      <c r="C49" s="83"/>
-      <c r="D49" s="83"/>
-      <c r="E49" s="83"/>
-      <c r="F49" s="83"/>
-      <c r="G49" s="83"/>
-      <c r="H49" s="83"/>
-      <c r="I49" s="85"/>
-      <c r="J49" s="86"/>
-      <c r="K49" s="86"/>
-      <c r="L49" s="87"/>
-      <c r="M49" s="83"/>
-      <c r="N49" s="83"/>
-      <c r="O49" s="83"/>
-      <c r="P49" s="83"/>
-      <c r="Q49" s="83"/>
-      <c r="R49" s="83"/>
-      <c r="S49" s="83"/>
-      <c r="T49" s="83"/>
-      <c r="U49" s="83"/>
-      <c r="V49" s="83"/>
-      <c r="W49" s="83"/>
-      <c r="X49" s="83"/>
+      <c r="B49" s="103"/>
+      <c r="C49" s="103"/>
+      <c r="D49" s="103"/>
+      <c r="E49" s="103"/>
+      <c r="F49" s="103"/>
+      <c r="G49" s="103"/>
+      <c r="H49" s="103"/>
+      <c r="I49" s="104"/>
+      <c r="J49" s="105"/>
+      <c r="K49" s="105"/>
+      <c r="L49" s="106"/>
+      <c r="M49" s="103"/>
+      <c r="N49" s="103"/>
+      <c r="O49" s="103"/>
+      <c r="P49" s="103"/>
+      <c r="Q49" s="103"/>
+      <c r="R49" s="103"/>
+      <c r="S49" s="103"/>
+      <c r="T49" s="103"/>
+      <c r="U49" s="103"/>
+      <c r="V49" s="103"/>
+      <c r="W49" s="103"/>
+      <c r="X49" s="103"/>
     </row>
     <row r="50" spans="1:24">
       <c r="A50" s="3"/>
-      <c r="B50" s="83"/>
-      <c r="C50" s="83"/>
-      <c r="D50" s="83"/>
-      <c r="E50" s="83"/>
-      <c r="F50" s="83"/>
-      <c r="G50" s="83"/>
-      <c r="H50" s="83"/>
-      <c r="I50" s="85"/>
-      <c r="J50" s="86"/>
-      <c r="K50" s="86"/>
-      <c r="L50" s="87"/>
-      <c r="M50" s="83"/>
-      <c r="N50" s="83"/>
-      <c r="O50" s="83"/>
-      <c r="P50" s="83"/>
-      <c r="Q50" s="83"/>
-      <c r="R50" s="83"/>
-      <c r="S50" s="83"/>
-      <c r="T50" s="83"/>
-      <c r="U50" s="83"/>
-      <c r="V50" s="83"/>
-      <c r="W50" s="83"/>
-      <c r="X50" s="83"/>
+      <c r="B50" s="103"/>
+      <c r="C50" s="103"/>
+      <c r="D50" s="103"/>
+      <c r="E50" s="103"/>
+      <c r="F50" s="103"/>
+      <c r="G50" s="103"/>
+      <c r="H50" s="103"/>
+      <c r="I50" s="104"/>
+      <c r="J50" s="105"/>
+      <c r="K50" s="105"/>
+      <c r="L50" s="106"/>
+      <c r="M50" s="103"/>
+      <c r="N50" s="103"/>
+      <c r="O50" s="103"/>
+      <c r="P50" s="103"/>
+      <c r="Q50" s="103"/>
+      <c r="R50" s="103"/>
+      <c r="S50" s="103"/>
+      <c r="T50" s="103"/>
+      <c r="U50" s="103"/>
+      <c r="V50" s="103"/>
+      <c r="W50" s="103"/>
+      <c r="X50" s="103"/>
     </row>
     <row r="51" spans="1:24">
       <c r="A51" s="3"/>
-      <c r="B51" s="83"/>
-      <c r="C51" s="83"/>
-      <c r="D51" s="83"/>
-      <c r="E51" s="83"/>
-      <c r="F51" s="83"/>
-      <c r="G51" s="83"/>
-      <c r="H51" s="83"/>
-      <c r="I51" s="85"/>
-      <c r="J51" s="86"/>
-      <c r="K51" s="86"/>
-      <c r="L51" s="87"/>
-      <c r="M51" s="83"/>
-      <c r="N51" s="83"/>
-      <c r="O51" s="83"/>
-      <c r="P51" s="83"/>
-      <c r="Q51" s="83"/>
-      <c r="R51" s="83"/>
-      <c r="S51" s="83"/>
-      <c r="T51" s="83"/>
-      <c r="U51" s="83"/>
-      <c r="V51" s="83"/>
-      <c r="W51" s="83"/>
-      <c r="X51" s="83"/>
+      <c r="B51" s="103"/>
+      <c r="C51" s="103"/>
+      <c r="D51" s="103"/>
+      <c r="E51" s="103"/>
+      <c r="F51" s="103"/>
+      <c r="G51" s="103"/>
+      <c r="H51" s="103"/>
+      <c r="I51" s="104"/>
+      <c r="J51" s="105"/>
+      <c r="K51" s="105"/>
+      <c r="L51" s="106"/>
+      <c r="M51" s="103"/>
+      <c r="N51" s="103"/>
+      <c r="O51" s="103"/>
+      <c r="P51" s="103"/>
+      <c r="Q51" s="103"/>
+      <c r="R51" s="103"/>
+      <c r="S51" s="103"/>
+      <c r="T51" s="103"/>
+      <c r="U51" s="103"/>
+      <c r="V51" s="103"/>
+      <c r="W51" s="103"/>
+      <c r="X51" s="103"/>
     </row>
     <row r="52" spans="1:24">
       <c r="A52" s="3"/>
-      <c r="B52" s="83"/>
-      <c r="C52" s="83"/>
-      <c r="D52" s="83"/>
-      <c r="E52" s="83"/>
-      <c r="F52" s="83"/>
-      <c r="G52" s="83"/>
-      <c r="H52" s="83"/>
-      <c r="I52" s="85"/>
-      <c r="J52" s="86"/>
-      <c r="K52" s="86"/>
-      <c r="L52" s="87"/>
-      <c r="M52" s="83"/>
-      <c r="N52" s="83"/>
-      <c r="O52" s="83"/>
-      <c r="P52" s="83"/>
-      <c r="Q52" s="83"/>
-      <c r="R52" s="83"/>
-      <c r="S52" s="83"/>
-      <c r="T52" s="83"/>
-      <c r="U52" s="83"/>
-      <c r="V52" s="83"/>
-      <c r="W52" s="83"/>
-      <c r="X52" s="83"/>
+      <c r="B52" s="103"/>
+      <c r="C52" s="103"/>
+      <c r="D52" s="103"/>
+      <c r="E52" s="103"/>
+      <c r="F52" s="103"/>
+      <c r="G52" s="103"/>
+      <c r="H52" s="103"/>
+      <c r="I52" s="104"/>
+      <c r="J52" s="105"/>
+      <c r="K52" s="105"/>
+      <c r="L52" s="106"/>
+      <c r="M52" s="103"/>
+      <c r="N52" s="103"/>
+      <c r="O52" s="103"/>
+      <c r="P52" s="103"/>
+      <c r="Q52" s="103"/>
+      <c r="R52" s="103"/>
+      <c r="S52" s="103"/>
+      <c r="T52" s="103"/>
+      <c r="U52" s="103"/>
+      <c r="V52" s="103"/>
+      <c r="W52" s="103"/>
+      <c r="X52" s="103"/>
     </row>
     <row r="53" spans="1:24">
       <c r="A53" s="3"/>
-      <c r="B53" s="83"/>
-      <c r="C53" s="83"/>
-      <c r="D53" s="83"/>
-      <c r="E53" s="83"/>
-      <c r="F53" s="83"/>
-      <c r="G53" s="83"/>
-      <c r="H53" s="83"/>
-      <c r="I53" s="83"/>
-      <c r="J53" s="83"/>
-      <c r="K53" s="83"/>
-      <c r="L53" s="83"/>
-      <c r="M53" s="83"/>
-      <c r="N53" s="83"/>
-      <c r="O53" s="83"/>
-      <c r="P53" s="83"/>
-      <c r="Q53" s="83"/>
-      <c r="R53" s="83"/>
-      <c r="S53" s="83"/>
-      <c r="T53" s="83"/>
-      <c r="U53" s="83"/>
-      <c r="V53" s="83"/>
-      <c r="W53" s="83"/>
-      <c r="X53" s="83"/>
+      <c r="B53" s="103"/>
+      <c r="C53" s="103"/>
+      <c r="D53" s="103"/>
+      <c r="E53" s="103"/>
+      <c r="F53" s="103"/>
+      <c r="G53" s="103"/>
+      <c r="H53" s="103"/>
+      <c r="I53" s="103"/>
+      <c r="J53" s="103"/>
+      <c r="K53" s="103"/>
+      <c r="L53" s="103"/>
+      <c r="M53" s="103"/>
+      <c r="N53" s="103"/>
+      <c r="O53" s="103"/>
+      <c r="P53" s="103"/>
+      <c r="Q53" s="103"/>
+      <c r="R53" s="103"/>
+      <c r="S53" s="103"/>
+      <c r="T53" s="103"/>
+      <c r="U53" s="103"/>
+      <c r="V53" s="103"/>
+      <c r="W53" s="103"/>
+      <c r="X53" s="103"/>
     </row>
   </sheetData>
   <mergeCells count="256">
+    <mergeCell ref="F51:H51"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="F53:H53"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="F44:H44"/>
+    <mergeCell ref="F45:H45"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="P50:X50"/>
+    <mergeCell ref="P51:X51"/>
+    <mergeCell ref="P52:X52"/>
+    <mergeCell ref="P53:X53"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="P45:X45"/>
+    <mergeCell ref="P46:X46"/>
+    <mergeCell ref="P47:X47"/>
+    <mergeCell ref="P48:X48"/>
+    <mergeCell ref="P49:X49"/>
+    <mergeCell ref="P40:X40"/>
+    <mergeCell ref="P41:X41"/>
+    <mergeCell ref="P42:X42"/>
+    <mergeCell ref="P35:X35"/>
+    <mergeCell ref="P36:X36"/>
+    <mergeCell ref="P37:X37"/>
+    <mergeCell ref="P38:X38"/>
+    <mergeCell ref="P39:X39"/>
+    <mergeCell ref="P21:X21"/>
+    <mergeCell ref="P22:X22"/>
+    <mergeCell ref="P23:X23"/>
+    <mergeCell ref="P33:X33"/>
+    <mergeCell ref="P34:X34"/>
+    <mergeCell ref="P28:X28"/>
+    <mergeCell ref="P29:X29"/>
+    <mergeCell ref="P32:X32"/>
+    <mergeCell ref="P30:X30"/>
+    <mergeCell ref="P31:X31"/>
+    <mergeCell ref="P24:X24"/>
+    <mergeCell ref="P13:X13"/>
+    <mergeCell ref="P14:X14"/>
+    <mergeCell ref="P15:X15"/>
+    <mergeCell ref="P25:X25"/>
+    <mergeCell ref="P26:X26"/>
+    <mergeCell ref="P27:X27"/>
+    <mergeCell ref="P43:X43"/>
+    <mergeCell ref="I50:L50"/>
+    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="I36:L36"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="I33:L33"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="P44:X44"/>
+    <mergeCell ref="I51:L51"/>
+    <mergeCell ref="I52:L52"/>
+    <mergeCell ref="I53:L53"/>
+    <mergeCell ref="P4:X4"/>
+    <mergeCell ref="P5:X5"/>
+    <mergeCell ref="P6:X6"/>
+    <mergeCell ref="P7:X7"/>
+    <mergeCell ref="P8:X8"/>
+    <mergeCell ref="P9:X9"/>
+    <mergeCell ref="P10:X10"/>
+    <mergeCell ref="P11:X11"/>
+    <mergeCell ref="P17:X17"/>
+    <mergeCell ref="P18:X18"/>
+    <mergeCell ref="P19:X19"/>
+    <mergeCell ref="P20:X20"/>
+    <mergeCell ref="I45:L45"/>
+    <mergeCell ref="I46:L46"/>
+    <mergeCell ref="I47:L47"/>
+    <mergeCell ref="I48:L48"/>
+    <mergeCell ref="I49:L49"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="I41:L41"/>
+    <mergeCell ref="I42:L42"/>
+    <mergeCell ref="I44:L44"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="I43:L43"/>
+    <mergeCell ref="M50:O50"/>
+    <mergeCell ref="M51:O51"/>
+    <mergeCell ref="M52:O52"/>
+    <mergeCell ref="M53:O53"/>
+    <mergeCell ref="I4:L4"/>
+    <mergeCell ref="I5:L5"/>
+    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="I7:L7"/>
+    <mergeCell ref="I8:L8"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="I10:L10"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="M45:O45"/>
+    <mergeCell ref="M46:O46"/>
+    <mergeCell ref="M47:O47"/>
+    <mergeCell ref="M48:O48"/>
+    <mergeCell ref="M49:O49"/>
+    <mergeCell ref="M40:O40"/>
+    <mergeCell ref="M41:O41"/>
+    <mergeCell ref="M42:O42"/>
+    <mergeCell ref="M25:O25"/>
+    <mergeCell ref="M26:O26"/>
+    <mergeCell ref="M27:O27"/>
+    <mergeCell ref="M43:O43"/>
+    <mergeCell ref="P2:X3"/>
+    <mergeCell ref="P16:X16"/>
+    <mergeCell ref="M44:O44"/>
+    <mergeCell ref="M35:O35"/>
+    <mergeCell ref="M36:O36"/>
+    <mergeCell ref="M37:O37"/>
+    <mergeCell ref="M38:O38"/>
+    <mergeCell ref="M39:O39"/>
+    <mergeCell ref="M21:O21"/>
+    <mergeCell ref="M22:O22"/>
+    <mergeCell ref="M23:O23"/>
+    <mergeCell ref="M33:O33"/>
+    <mergeCell ref="M34:O34"/>
+    <mergeCell ref="M28:O28"/>
+    <mergeCell ref="M29:O29"/>
+    <mergeCell ref="M32:O32"/>
+    <mergeCell ref="M30:O30"/>
+    <mergeCell ref="M31:O31"/>
+    <mergeCell ref="M24:O24"/>
+    <mergeCell ref="P12:X12"/>
     <mergeCell ref="I3:L3"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="F3:H3"/>
@@ -9988,238 +11022,6 @@
     <mergeCell ref="M13:O13"/>
     <mergeCell ref="M14:O14"/>
     <mergeCell ref="M15:O15"/>
-    <mergeCell ref="M25:O25"/>
-    <mergeCell ref="M26:O26"/>
-    <mergeCell ref="M27:O27"/>
-    <mergeCell ref="M43:O43"/>
-    <mergeCell ref="P2:X3"/>
-    <mergeCell ref="P16:X16"/>
-    <mergeCell ref="M44:O44"/>
-    <mergeCell ref="M35:O35"/>
-    <mergeCell ref="M36:O36"/>
-    <mergeCell ref="M37:O37"/>
-    <mergeCell ref="M38:O38"/>
-    <mergeCell ref="M39:O39"/>
-    <mergeCell ref="M21:O21"/>
-    <mergeCell ref="M22:O22"/>
-    <mergeCell ref="M23:O23"/>
-    <mergeCell ref="M33:O33"/>
-    <mergeCell ref="M34:O34"/>
-    <mergeCell ref="M28:O28"/>
-    <mergeCell ref="M29:O29"/>
-    <mergeCell ref="M32:O32"/>
-    <mergeCell ref="M30:O30"/>
-    <mergeCell ref="M31:O31"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="P12:X12"/>
-    <mergeCell ref="M50:O50"/>
-    <mergeCell ref="M51:O51"/>
-    <mergeCell ref="M52:O52"/>
-    <mergeCell ref="M53:O53"/>
-    <mergeCell ref="I4:L4"/>
-    <mergeCell ref="I5:L5"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="I7:L7"/>
-    <mergeCell ref="I8:L8"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="M45:O45"/>
-    <mergeCell ref="M46:O46"/>
-    <mergeCell ref="M47:O47"/>
-    <mergeCell ref="M48:O48"/>
-    <mergeCell ref="M49:O49"/>
-    <mergeCell ref="M40:O40"/>
-    <mergeCell ref="M41:O41"/>
-    <mergeCell ref="M42:O42"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="I27:L27"/>
-    <mergeCell ref="I43:L43"/>
-    <mergeCell ref="I51:L51"/>
-    <mergeCell ref="I52:L52"/>
-    <mergeCell ref="I53:L53"/>
-    <mergeCell ref="P4:X4"/>
-    <mergeCell ref="P5:X5"/>
-    <mergeCell ref="P6:X6"/>
-    <mergeCell ref="P7:X7"/>
-    <mergeCell ref="P8:X8"/>
-    <mergeCell ref="P9:X9"/>
-    <mergeCell ref="P10:X10"/>
-    <mergeCell ref="P11:X11"/>
-    <mergeCell ref="P17:X17"/>
-    <mergeCell ref="P18:X18"/>
-    <mergeCell ref="P19:X19"/>
-    <mergeCell ref="P20:X20"/>
-    <mergeCell ref="I45:L45"/>
-    <mergeCell ref="I46:L46"/>
-    <mergeCell ref="I47:L47"/>
-    <mergeCell ref="I48:L48"/>
-    <mergeCell ref="I49:L49"/>
-    <mergeCell ref="I40:L40"/>
-    <mergeCell ref="I41:L41"/>
-    <mergeCell ref="I42:L42"/>
-    <mergeCell ref="I44:L44"/>
-    <mergeCell ref="P13:X13"/>
-    <mergeCell ref="P14:X14"/>
-    <mergeCell ref="P15:X15"/>
-    <mergeCell ref="P25:X25"/>
-    <mergeCell ref="P26:X26"/>
-    <mergeCell ref="P27:X27"/>
-    <mergeCell ref="P43:X43"/>
-    <mergeCell ref="I50:L50"/>
-    <mergeCell ref="I35:L35"/>
-    <mergeCell ref="I36:L36"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="I33:L33"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="P44:X44"/>
-    <mergeCell ref="P35:X35"/>
-    <mergeCell ref="P36:X36"/>
-    <mergeCell ref="P37:X37"/>
-    <mergeCell ref="P38:X38"/>
-    <mergeCell ref="P39:X39"/>
-    <mergeCell ref="P21:X21"/>
-    <mergeCell ref="P22:X22"/>
-    <mergeCell ref="P23:X23"/>
-    <mergeCell ref="P33:X33"/>
-    <mergeCell ref="P34:X34"/>
-    <mergeCell ref="P28:X28"/>
-    <mergeCell ref="P29:X29"/>
-    <mergeCell ref="P32:X32"/>
-    <mergeCell ref="P30:X30"/>
-    <mergeCell ref="P31:X31"/>
-    <mergeCell ref="P24:X24"/>
-    <mergeCell ref="P50:X50"/>
-    <mergeCell ref="P51:X51"/>
-    <mergeCell ref="P52:X52"/>
-    <mergeCell ref="P53:X53"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="P45:X45"/>
-    <mergeCell ref="P46:X46"/>
-    <mergeCell ref="P47:X47"/>
-    <mergeCell ref="P48:X48"/>
-    <mergeCell ref="P49:X49"/>
-    <mergeCell ref="P40:X40"/>
-    <mergeCell ref="P41:X41"/>
-    <mergeCell ref="P42:X42"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="F44:H44"/>
-    <mergeCell ref="F45:H45"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="F51:H51"/>
-    <mergeCell ref="F52:H52"/>
-    <mergeCell ref="F53:H53"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="F50:H50"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="F43:H43"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10230,7 +11032,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B96454FA-A95E-4D58-81B9-E68FAAFA79D0}">
-  <dimension ref="A1:W199"/>
+  <dimension ref="A1:Z219"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -10265,102 +11067,102 @@
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="B8" s="88" t="s">
+      <c r="B8" s="113" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="86"/>
-      <c r="D8" s="86"/>
-      <c r="E8" s="86"/>
-      <c r="F8" s="86"/>
-      <c r="G8" s="87"/>
+      <c r="C8" s="105"/>
+      <c r="D8" s="105"/>
+      <c r="E8" s="105"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="106"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="B9" s="105"/>
-      <c r="C9" s="106"/>
-      <c r="D9" s="106"/>
-      <c r="E9" s="106"/>
-      <c r="F9" s="106"/>
-      <c r="G9" s="107"/>
+      <c r="B9" s="116"/>
+      <c r="C9" s="117"/>
+      <c r="D9" s="117"/>
+      <c r="E9" s="117"/>
+      <c r="F9" s="117"/>
+      <c r="G9" s="118"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="B10" s="105"/>
-      <c r="C10" s="106"/>
-      <c r="D10" s="106"/>
-      <c r="E10" s="106"/>
-      <c r="F10" s="106"/>
-      <c r="G10" s="107"/>
+      <c r="B10" s="116"/>
+      <c r="C10" s="117"/>
+      <c r="D10" s="117"/>
+      <c r="E10" s="117"/>
+      <c r="F10" s="117"/>
+      <c r="G10" s="118"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="B11" s="105"/>
-      <c r="C11" s="106"/>
-      <c r="D11" s="106"/>
-      <c r="E11" s="106"/>
-      <c r="F11" s="106"/>
-      <c r="G11" s="107"/>
+      <c r="B11" s="116"/>
+      <c r="C11" s="117"/>
+      <c r="D11" s="117"/>
+      <c r="E11" s="117"/>
+      <c r="F11" s="117"/>
+      <c r="G11" s="118"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="B12" s="105"/>
-      <c r="C12" s="106"/>
-      <c r="D12" s="106"/>
-      <c r="E12" s="106"/>
-      <c r="F12" s="106"/>
-      <c r="G12" s="107"/>
+      <c r="B12" s="116"/>
+      <c r="C12" s="117"/>
+      <c r="D12" s="117"/>
+      <c r="E12" s="117"/>
+      <c r="F12" s="117"/>
+      <c r="G12" s="118"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="B13" s="105"/>
-      <c r="C13" s="106"/>
-      <c r="D13" s="106"/>
-      <c r="E13" s="106"/>
-      <c r="F13" s="106"/>
-      <c r="G13" s="107"/>
+      <c r="B13" s="116"/>
+      <c r="C13" s="117"/>
+      <c r="D13" s="117"/>
+      <c r="E13" s="117"/>
+      <c r="F13" s="117"/>
+      <c r="G13" s="118"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="B14" s="105"/>
-      <c r="C14" s="106"/>
-      <c r="D14" s="106"/>
-      <c r="E14" s="106"/>
-      <c r="F14" s="106"/>
-      <c r="G14" s="107"/>
+      <c r="B14" s="116"/>
+      <c r="C14" s="117"/>
+      <c r="D14" s="117"/>
+      <c r="E14" s="117"/>
+      <c r="F14" s="117"/>
+      <c r="G14" s="118"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="B15" s="105"/>
-      <c r="C15" s="106"/>
-      <c r="D15" s="106"/>
-      <c r="E15" s="106"/>
-      <c r="F15" s="106"/>
-      <c r="G15" s="107"/>
+      <c r="B15" s="116"/>
+      <c r="C15" s="117"/>
+      <c r="D15" s="117"/>
+      <c r="E15" s="117"/>
+      <c r="F15" s="117"/>
+      <c r="G15" s="118"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="B16" s="108"/>
-      <c r="C16" s="106"/>
-      <c r="D16" s="106"/>
-      <c r="E16" s="106"/>
-      <c r="F16" s="106"/>
-      <c r="G16" s="107"/>
+      <c r="B16" s="119"/>
+      <c r="C16" s="117"/>
+      <c r="D16" s="117"/>
+      <c r="E16" s="117"/>
+      <c r="F16" s="117"/>
+      <c r="G16" s="118"/>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="108"/>
-      <c r="C17" s="106"/>
-      <c r="D17" s="106"/>
-      <c r="E17" s="106"/>
-      <c r="F17" s="106"/>
-      <c r="G17" s="107"/>
+      <c r="B17" s="119"/>
+      <c r="C17" s="117"/>
+      <c r="D17" s="117"/>
+      <c r="E17" s="117"/>
+      <c r="F17" s="117"/>
+      <c r="G17" s="118"/>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="108"/>
-      <c r="C18" s="106"/>
-      <c r="D18" s="106"/>
-      <c r="E18" s="106"/>
-      <c r="F18" s="106"/>
-      <c r="G18" s="107"/>
+      <c r="B18" s="119"/>
+      <c r="C18" s="117"/>
+      <c r="D18" s="117"/>
+      <c r="E18" s="117"/>
+      <c r="F18" s="117"/>
+      <c r="G18" s="118"/>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="109"/>
-      <c r="C19" s="110"/>
-      <c r="D19" s="110"/>
-      <c r="E19" s="110"/>
-      <c r="F19" s="110"/>
-      <c r="G19" s="111"/>
+      <c r="B19" s="120"/>
+      <c r="C19" s="121"/>
+      <c r="D19" s="121"/>
+      <c r="E19" s="121"/>
+      <c r="F19" s="121"/>
+      <c r="G19" s="122"/>
     </row>
     <row r="21" spans="2:7">
       <c r="B21" s="10" t="s">
@@ -10399,97 +11201,97 @@
     </row>
     <row r="110" spans="1:3" ht="20.25">
       <c r="A110" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="B111" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="112" spans="1:3">
       <c r="C112" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="113" spans="2:16">
       <c r="B113" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="114" spans="2:16" ht="15.75">
       <c r="C114" s="42" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="115" spans="2:16">
       <c r="B115" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="116" spans="2:16">
       <c r="B116" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="117" spans="2:16">
       <c r="B117" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="118" spans="2:16">
       <c r="B118" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="119" spans="2:16">
       <c r="B119" s="41" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="120" spans="2:16">
       <c r="B120" s="41" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="121" spans="2:16">
       <c r="C121" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="122" spans="2:16">
       <c r="C122" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="123" spans="2:16">
       <c r="C123" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="124" spans="2:16">
       <c r="C124" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="125" spans="2:16">
       <c r="C125" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="126" spans="2:16" ht="15.75">
       <c r="D126" s="43" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E126" s="40"/>
       <c r="F126" s="40"/>
       <c r="G126" s="40"/>
       <c r="H126" s="40"/>
       <c r="J126" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K126" s="43" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L126" s="43"/>
       <c r="M126" s="43"/>
@@ -10499,22 +11301,22 @@
     </row>
     <row r="127" spans="2:16" ht="15.75">
       <c r="C127" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D127" s="42"/>
       <c r="I127" s="44" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="128" spans="2:16" ht="15.75">
       <c r="C128" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D128" s="42"/>
     </row>
     <row r="129" spans="3:23" ht="15.75">
       <c r="D129" s="43" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E129" s="40"/>
       <c r="F129" s="40"/>
@@ -10527,17 +11329,17 @@
       <c r="M129" s="40"/>
       <c r="N129" s="40"/>
       <c r="P129" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Q129" s="43" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="R129" s="40"/>
       <c r="S129" s="40"/>
     </row>
     <row r="130" spans="3:23" ht="15.75">
       <c r="C130" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D130" s="45"/>
       <c r="E130" s="46"/>
@@ -10558,71 +11360,59 @@
     </row>
     <row r="131" spans="3:23">
       <c r="D131" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="132" spans="3:23">
       <c r="D132" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="133" spans="3:23" ht="15">
-      <c r="C133" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="133" spans="3:23">
+      <c r="D133" s="40" t="s">
+        <v>338</v>
+      </c>
+      <c r="E133" s="40"/>
+      <c r="F133" s="40"/>
+      <c r="G133" s="40"/>
+      <c r="H133" s="40"/>
+      <c r="I133" s="40"/>
+      <c r="J133" s="40"/>
+      <c r="K133" s="40"/>
+      <c r="L133" s="40"/>
+      <c r="M133" s="40"/>
+      <c r="N133" s="40"/>
+    </row>
+    <row r="134" spans="3:23" ht="15">
+      <c r="C134" t="s">
+        <v>361</v>
+      </c>
+      <c r="K134" s="54" t="s">
         <v>261</v>
       </c>
-      <c r="K133" s="54" t="s">
-        <v>263</v>
-      </c>
-      <c r="L133" s="62"/>
-      <c r="M133" s="62"/>
-      <c r="N133" s="13"/>
-      <c r="O133" s="13"/>
-      <c r="P133" s="13"/>
-      <c r="Q133" s="13"/>
-      <c r="R133" s="13"/>
-      <c r="S133" s="13"/>
-      <c r="T133" s="13"/>
-      <c r="U133" s="13"/>
-      <c r="V133" s="13"/>
-      <c r="W133" s="15"/>
-    </row>
-    <row r="134" spans="3:23" ht="15">
-      <c r="D134" s="49" t="s">
-        <v>258</v>
-      </c>
-      <c r="E134" s="13"/>
-      <c r="F134" s="13"/>
-      <c r="G134" s="13"/>
-      <c r="H134" s="15"/>
-      <c r="K134" s="55" t="s">
-        <v>264</v>
-      </c>
-      <c r="L134" s="57"/>
-      <c r="M134" s="57"/>
-      <c r="N134" s="14"/>
-      <c r="O134" s="14"/>
-      <c r="P134" s="14"/>
-      <c r="Q134" s="14"/>
-      <c r="R134" s="14"/>
-      <c r="S134" s="14"/>
-      <c r="T134" s="14"/>
-      <c r="U134" s="14"/>
-      <c r="V134" s="14"/>
-      <c r="W134" s="16"/>
+      <c r="L134" s="62"/>
+      <c r="M134" s="62"/>
+      <c r="N134" s="13"/>
+      <c r="O134" s="13"/>
+      <c r="P134" s="13"/>
+      <c r="Q134" s="13"/>
+      <c r="R134" s="13"/>
+      <c r="S134" s="13"/>
+      <c r="T134" s="13"/>
+      <c r="U134" s="13"/>
+      <c r="V134" s="13"/>
+      <c r="W134" s="15"/>
     </row>
     <row r="135" spans="3:23" ht="15">
-      <c r="D135" s="50" t="s">
+      <c r="D135" s="49" t="s">
+        <v>257</v>
+      </c>
+      <c r="E135" s="13"/>
+      <c r="F135" s="13"/>
+      <c r="G135" s="13"/>
+      <c r="H135" s="15"/>
+      <c r="K135" s="55" t="s">
         <v>262</v>
-      </c>
-      <c r="E135" s="14"/>
-      <c r="F135" s="14"/>
-      <c r="G135" s="14"/>
-      <c r="H135" s="16"/>
-      <c r="J135" t="s">
-        <v>268</v>
-      </c>
-      <c r="K135" s="55" t="s">
-        <v>265</v>
       </c>
       <c r="L135" s="57"/>
       <c r="M135" s="57"/>
@@ -10638,15 +11428,18 @@
       <c r="W135" s="16"/>
     </row>
     <row r="136" spans="3:23" ht="15">
-      <c r="D136" s="51" t="s">
+      <c r="D136" s="50" t="s">
         <v>260</v>
       </c>
-      <c r="E136" s="18"/>
-      <c r="F136" s="18"/>
-      <c r="G136" s="18"/>
-      <c r="H136" s="19"/>
+      <c r="E136" s="14"/>
+      <c r="F136" s="14"/>
+      <c r="G136" s="14"/>
+      <c r="H136" s="16"/>
+      <c r="J136" t="s">
+        <v>266</v>
+      </c>
       <c r="K136" s="55" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="L136" s="57"/>
       <c r="M136" s="57"/>
@@ -10662,43 +11455,49 @@
       <c r="W136" s="16"/>
     </row>
     <row r="137" spans="3:23" ht="15">
-      <c r="K137" s="56" t="s">
+      <c r="D137" s="51" t="s">
+        <v>259</v>
+      </c>
+      <c r="E137" s="18"/>
+      <c r="F137" s="18"/>
+      <c r="G137" s="18"/>
+      <c r="H137" s="19"/>
+      <c r="K137" s="55" t="s">
+        <v>264</v>
+      </c>
+      <c r="L137" s="57"/>
+      <c r="M137" s="57"/>
+      <c r="N137" s="14"/>
+      <c r="O137" s="14"/>
+      <c r="P137" s="14"/>
+      <c r="Q137" s="14"/>
+      <c r="R137" s="14"/>
+      <c r="S137" s="14"/>
+      <c r="T137" s="14"/>
+      <c r="U137" s="14"/>
+      <c r="V137" s="14"/>
+      <c r="W137" s="16"/>
+    </row>
+    <row r="138" spans="3:23" ht="15">
+      <c r="K138" s="56" t="s">
+        <v>265</v>
+      </c>
+      <c r="L138" s="63"/>
+      <c r="M138" s="63"/>
+      <c r="N138" s="18"/>
+      <c r="O138" s="18"/>
+      <c r="P138" s="18"/>
+      <c r="Q138" s="18"/>
+      <c r="R138" s="18"/>
+      <c r="S138" s="18"/>
+      <c r="T138" s="18"/>
+      <c r="U138" s="18"/>
+      <c r="V138" s="18"/>
+      <c r="W138" s="19"/>
+    </row>
+    <row r="139" spans="3:23" ht="15">
+      <c r="C139" t="s">
         <v>267</v>
-      </c>
-      <c r="L137" s="63"/>
-      <c r="M137" s="63"/>
-      <c r="N137" s="18"/>
-      <c r="O137" s="18"/>
-      <c r="P137" s="18"/>
-      <c r="Q137" s="18"/>
-      <c r="R137" s="18"/>
-      <c r="S137" s="18"/>
-      <c r="T137" s="18"/>
-      <c r="U137" s="18"/>
-      <c r="V137" s="18"/>
-      <c r="W137" s="19"/>
-    </row>
-    <row r="138" spans="3:23" ht="15">
-      <c r="C138" t="s">
-        <v>269</v>
-      </c>
-      <c r="K138" s="57"/>
-      <c r="L138" s="57"/>
-      <c r="M138" s="57"/>
-      <c r="N138" s="14"/>
-      <c r="O138" s="14"/>
-      <c r="P138" s="14"/>
-      <c r="Q138" s="14"/>
-      <c r="R138" s="14"/>
-      <c r="S138" s="14"/>
-      <c r="T138" s="14"/>
-      <c r="U138" s="14"/>
-      <c r="V138" s="14"/>
-      <c r="W138" s="14"/>
-    </row>
-    <row r="139" spans="3:23" ht="17.25">
-      <c r="D139" s="59" t="s">
-        <v>272</v>
       </c>
       <c r="K139" s="57"/>
       <c r="L139" s="57"/>
@@ -10715,7 +11514,7 @@
       <c r="W139" s="14"/>
     </row>
     <row r="140" spans="3:23" ht="17.25">
-      <c r="D140" s="60" t="s">
+      <c r="D140" s="59" t="s">
         <v>270</v>
       </c>
       <c r="K140" s="57"/>
@@ -10734,7 +11533,7 @@
     </row>
     <row r="141" spans="3:23" ht="17.25">
       <c r="D141" s="60" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="K141" s="57"/>
       <c r="L141" s="57"/>
@@ -10751,10 +11550,9 @@
       <c r="W141" s="14"/>
     </row>
     <row r="142" spans="3:23" ht="17.25">
-      <c r="C142" t="s">
-        <v>298</v>
-      </c>
-      <c r="D142" s="60"/>
+      <c r="D142" s="60" t="s">
+        <v>269</v>
+      </c>
       <c r="K142" s="57"/>
       <c r="L142" s="57"/>
       <c r="M142" s="57"/>
@@ -10769,64 +11567,64 @@
       <c r="V142" s="14"/>
       <c r="W142" s="14"/>
     </row>
-    <row r="143" spans="3:23" ht="15.75">
-      <c r="D143" s="76" t="s">
+    <row r="143" spans="3:23" ht="17.25">
+      <c r="C143" t="s">
+        <v>296</v>
+      </c>
+      <c r="D143" s="60"/>
+      <c r="K143" s="57"/>
+      <c r="L143" s="57"/>
+      <c r="M143" s="57"/>
+      <c r="N143" s="14"/>
+      <c r="O143" s="14"/>
+      <c r="P143" s="14"/>
+      <c r="Q143" s="14"/>
+      <c r="R143" s="14"/>
+      <c r="S143" s="14"/>
+      <c r="T143" s="14"/>
+      <c r="U143" s="14"/>
+      <c r="V143" s="14"/>
+      <c r="W143" s="14"/>
+    </row>
+    <row r="144" spans="3:23" ht="15.75">
+      <c r="D144" s="76" t="s">
+        <v>306</v>
+      </c>
+      <c r="E144" s="13"/>
+      <c r="F144" s="13"/>
+      <c r="G144" s="13"/>
+      <c r="H144" s="13"/>
+      <c r="I144" s="13"/>
+      <c r="J144" s="15"/>
+      <c r="M144" s="33" t="s">
+        <v>311</v>
+      </c>
+      <c r="N144" s="13"/>
+      <c r="O144" s="13"/>
+      <c r="P144" s="13"/>
+      <c r="Q144" s="15"/>
+    </row>
+    <row r="145" spans="3:26" ht="15.75">
+      <c r="D145" s="56" t="s">
+        <v>307</v>
+      </c>
+      <c r="E145" s="18"/>
+      <c r="F145" s="18"/>
+      <c r="G145" s="18"/>
+      <c r="H145" s="18"/>
+      <c r="I145" s="18"/>
+      <c r="J145" s="19"/>
+      <c r="M145" s="31" t="s">
+        <v>354</v>
+      </c>
+      <c r="N145" s="18"/>
+      <c r="O145" s="18"/>
+      <c r="P145" s="18"/>
+      <c r="Q145" s="19"/>
+    </row>
+    <row r="146" spans="3:26" ht="17.25">
+      <c r="C146" t="s">
         <v>309</v>
-      </c>
-      <c r="E143" s="13"/>
-      <c r="F143" s="13"/>
-      <c r="G143" s="13"/>
-      <c r="H143" s="13"/>
-      <c r="I143" s="13"/>
-      <c r="J143" s="15"/>
-      <c r="M143" s="33" t="s">
-        <v>314</v>
-      </c>
-      <c r="N143" s="13"/>
-      <c r="O143" s="13"/>
-      <c r="P143" s="13"/>
-      <c r="Q143" s="15"/>
-    </row>
-    <row r="144" spans="3:23" ht="15.75">
-      <c r="D144" s="56" t="s">
-        <v>310</v>
-      </c>
-      <c r="E144" s="18"/>
-      <c r="F144" s="18"/>
-      <c r="G144" s="18"/>
-      <c r="H144" s="18"/>
-      <c r="I144" s="18"/>
-      <c r="J144" s="19"/>
-      <c r="M144" s="31" t="s">
-        <v>299</v>
-      </c>
-      <c r="N144" s="18"/>
-      <c r="O144" s="18"/>
-      <c r="P144" s="18"/>
-      <c r="Q144" s="19"/>
-    </row>
-    <row r="145" spans="2:23" ht="17.25">
-      <c r="C145" t="s">
-        <v>312</v>
-      </c>
-      <c r="D145" s="60"/>
-      <c r="K145" s="57"/>
-      <c r="L145" s="57"/>
-      <c r="M145" s="57"/>
-      <c r="N145" s="14"/>
-      <c r="O145" s="14"/>
-      <c r="P145" s="14"/>
-      <c r="Q145" s="14"/>
-      <c r="R145" s="14"/>
-      <c r="S145" s="14"/>
-      <c r="T145" s="14"/>
-      <c r="U145" s="14"/>
-      <c r="V145" s="14"/>
-      <c r="W145" s="14"/>
-    </row>
-    <row r="146" spans="2:23" ht="17.25">
-      <c r="C146" t="s">
-        <v>316</v>
       </c>
       <c r="D146" s="60"/>
       <c r="K146" s="57"/>
@@ -10843,14 +11641,13 @@
       <c r="V146" s="14"/>
       <c r="W146" s="14"/>
     </row>
-    <row r="147" spans="2:23" ht="20.25">
-      <c r="D147" s="78" t="s">
-        <v>315</v>
-      </c>
+    <row r="147" spans="3:26" ht="17.25">
+      <c r="C147" t="s">
+        <v>313</v>
+      </c>
+      <c r="D147" s="60"/>
       <c r="K147" s="57"/>
-      <c r="L147" s="77" t="s">
-        <v>317</v>
-      </c>
+      <c r="L147" s="57"/>
       <c r="M147" s="57"/>
       <c r="N147" s="14"/>
       <c r="O147" s="14"/>
@@ -10863,16 +11660,14 @@
       <c r="V147" s="14"/>
       <c r="W147" s="14"/>
     </row>
-    <row r="148" spans="2:23" ht="20.25">
-      <c r="C148" t="s">
-        <v>337</v>
-      </c>
-      <c r="D148" s="78"/>
-      <c r="I148" t="s">
-        <v>320</v>
+    <row r="148" spans="3:26" ht="20.25">
+      <c r="D148" s="78" t="s">
+        <v>312</v>
       </c>
       <c r="K148" s="57"/>
-      <c r="L148" s="77"/>
+      <c r="L148" s="77" t="s">
+        <v>314</v>
+      </c>
       <c r="M148" s="57"/>
       <c r="N148" s="14"/>
       <c r="O148" s="14"/>
@@ -10885,203 +11680,543 @@
       <c r="V148" s="14"/>
       <c r="W148" s="14"/>
     </row>
-    <row r="149" spans="2:23" ht="18.75" customHeight="1">
-      <c r="D149" s="82" t="s">
-        <v>318</v>
-      </c>
-      <c r="E149" s="11"/>
-      <c r="F149" s="11"/>
-      <c r="G149" s="11"/>
-      <c r="H149" s="11"/>
-      <c r="I149" s="12"/>
+    <row r="149" spans="3:26" ht="20.25">
+      <c r="C149" t="s">
+        <v>331</v>
+      </c>
+      <c r="D149" s="78"/>
+      <c r="I149" t="s">
+        <v>317</v>
+      </c>
       <c r="K149" s="57"/>
-      <c r="L149" s="81" t="s">
-        <v>319</v>
-      </c>
-      <c r="M149" s="79"/>
-      <c r="N149" s="79"/>
-      <c r="O149" s="79"/>
-      <c r="P149" s="79"/>
-      <c r="Q149" s="79"/>
-      <c r="R149" s="79"/>
-      <c r="S149" s="80"/>
+      <c r="L149" s="77"/>
+      <c r="M149" s="57"/>
+      <c r="N149" s="14"/>
+      <c r="O149" s="14"/>
+      <c r="P149" s="14"/>
+      <c r="Q149" s="14"/>
+      <c r="R149" s="14"/>
+      <c r="S149" s="14"/>
       <c r="T149" s="14"/>
       <c r="U149" s="14"/>
       <c r="V149" s="14"/>
       <c r="W149" s="14"/>
     </row>
-    <row r="155" spans="2:23">
-      <c r="C155" t="s">
+    <row r="150" spans="3:26" ht="18.75" customHeight="1">
+      <c r="D150" s="81" t="s">
+        <v>315</v>
+      </c>
+      <c r="E150" s="11"/>
+      <c r="F150" s="11"/>
+      <c r="G150" s="11"/>
+      <c r="H150" s="11"/>
+      <c r="I150" s="12"/>
+      <c r="K150" s="57"/>
+      <c r="L150" s="89" t="s">
+        <v>316</v>
+      </c>
+      <c r="M150" s="79"/>
+      <c r="N150" s="79"/>
+      <c r="O150" s="79"/>
+      <c r="P150" s="79"/>
+      <c r="Q150" s="79"/>
+      <c r="R150" s="79"/>
+      <c r="S150" s="80"/>
+      <c r="T150" s="14"/>
+      <c r="U150" s="14"/>
+      <c r="V150" s="14"/>
+      <c r="W150" s="14"/>
+    </row>
+    <row r="151" spans="3:26">
+      <c r="C151" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="152" spans="3:26" ht="15.75">
+      <c r="C152" t="s">
+        <v>336</v>
+      </c>
+      <c r="N152" s="91" t="s">
+        <v>335</v>
+      </c>
+      <c r="O152" s="13"/>
+      <c r="P152" s="13"/>
+      <c r="Q152" s="13"/>
+      <c r="R152" s="13"/>
+      <c r="S152" s="13"/>
+      <c r="T152" s="13"/>
+      <c r="U152" s="13"/>
+      <c r="V152" s="13"/>
+      <c r="W152" s="13"/>
+      <c r="X152" s="13"/>
+      <c r="Y152" s="13"/>
+      <c r="Z152" s="15"/>
+    </row>
+    <row r="153" spans="3:26" ht="15">
+      <c r="D153" t="s">
+        <v>333</v>
+      </c>
+      <c r="N153" s="92" t="s">
+        <v>334</v>
+      </c>
+      <c r="O153" s="18"/>
+      <c r="P153" s="18"/>
+      <c r="Q153" s="18"/>
+      <c r="R153" s="18"/>
+      <c r="S153" s="18"/>
+      <c r="T153" s="18"/>
+      <c r="U153" s="18"/>
+      <c r="V153" s="18"/>
+      <c r="W153" s="18"/>
+      <c r="X153" s="18"/>
+      <c r="Y153" s="18"/>
+      <c r="Z153" s="19"/>
+    </row>
+    <row r="154" spans="3:26" ht="15">
+      <c r="D154" t="s">
+        <v>362</v>
+      </c>
+      <c r="N154" s="88"/>
+    </row>
+    <row r="155" spans="3:26">
+      <c r="D155" s="113" t="s">
+        <v>365</v>
+      </c>
+      <c r="E155" s="105"/>
+      <c r="F155" s="105"/>
+      <c r="G155" s="105"/>
+      <c r="H155" s="105"/>
+      <c r="I155" s="106"/>
+      <c r="L155" s="113" t="s">
+        <v>366</v>
+      </c>
+      <c r="M155" s="105"/>
+      <c r="N155" s="105"/>
+      <c r="O155" s="105"/>
+      <c r="P155" s="105"/>
+      <c r="Q155" s="106"/>
+      <c r="S155" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="156" spans="3:26">
+      <c r="D156" s="119"/>
+      <c r="E156" s="126"/>
+      <c r="F156" s="126"/>
+      <c r="G156" s="126"/>
+      <c r="H156" s="126"/>
+      <c r="I156" s="118"/>
+      <c r="K156" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="156" spans="2:23" ht="18.75">
-      <c r="B156" t="s">
-        <v>254</v>
-      </c>
-      <c r="K156" s="52"/>
-      <c r="L156" s="52"/>
-      <c r="M156" s="52"/>
-    </row>
-    <row r="157" spans="2:23" ht="18.75">
-      <c r="B157" t="s">
+      <c r="L156" s="119"/>
+      <c r="M156" s="126"/>
+      <c r="N156" s="126"/>
+      <c r="O156" s="126"/>
+      <c r="P156" s="126"/>
+      <c r="Q156" s="118"/>
+      <c r="S156" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="157" spans="3:26">
+      <c r="D157" s="120"/>
+      <c r="E157" s="121"/>
+      <c r="F157" s="121"/>
+      <c r="G157" s="121"/>
+      <c r="H157" s="121"/>
+      <c r="I157" s="122"/>
+      <c r="L157" s="120"/>
+      <c r="M157" s="121"/>
+      <c r="N157" s="121"/>
+      <c r="O157" s="121"/>
+      <c r="P157" s="121"/>
+      <c r="Q157" s="122"/>
+    </row>
+    <row r="158" spans="3:26">
+      <c r="C158" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="159" spans="3:26">
+      <c r="C159" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="160" spans="3:26">
+      <c r="D160" s="123" t="s">
+        <v>344</v>
+      </c>
+      <c r="E160" s="124"/>
+      <c r="F160" s="124"/>
+      <c r="G160" s="124"/>
+      <c r="H160" s="124"/>
+      <c r="I160" s="125"/>
+      <c r="K160" t="s">
+        <v>244</v>
+      </c>
+      <c r="L160" s="123"/>
+      <c r="M160" s="124"/>
+      <c r="N160" s="124"/>
+      <c r="O160" s="124"/>
+      <c r="P160" s="124"/>
+      <c r="Q160" s="125"/>
+    </row>
+    <row r="161" spans="3:17" ht="15.75">
+      <c r="D161" s="42" t="s">
+        <v>345</v>
+      </c>
+      <c r="L161" s="42" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="162" spans="3:17" ht="15.75">
+      <c r="C162" t="s">
+        <v>351</v>
+      </c>
+      <c r="L162" s="42" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="163" spans="3:17" ht="14.25" customHeight="1">
+      <c r="D163" s="113" t="s">
+        <v>352</v>
+      </c>
+      <c r="E163" s="114"/>
+      <c r="F163" s="114"/>
+      <c r="G163" s="114"/>
+      <c r="H163" s="114"/>
+      <c r="I163" s="115"/>
+      <c r="K163" t="s">
+        <v>244</v>
+      </c>
+      <c r="L163" s="113" t="s">
+        <v>353</v>
+      </c>
+      <c r="M163" s="114"/>
+      <c r="N163" s="114"/>
+      <c r="O163" s="114"/>
+      <c r="P163" s="114"/>
+      <c r="Q163" s="115"/>
+    </row>
+    <row r="164" spans="3:17">
+      <c r="D164" s="133"/>
+      <c r="E164" s="134"/>
+      <c r="F164" s="134"/>
+      <c r="G164" s="134"/>
+      <c r="H164" s="134"/>
+      <c r="I164" s="135"/>
+      <c r="L164" s="133"/>
+      <c r="M164" s="134"/>
+      <c r="N164" s="134"/>
+      <c r="O164" s="134"/>
+      <c r="P164" s="134"/>
+      <c r="Q164" s="135"/>
+    </row>
+    <row r="165" spans="3:17">
+      <c r="C165" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="166" spans="3:17">
+      <c r="D166" s="127" t="s">
+        <v>355</v>
+      </c>
+      <c r="E166" s="128"/>
+      <c r="F166" s="128"/>
+      <c r="G166" s="128"/>
+      <c r="H166" s="128"/>
+      <c r="I166" s="129"/>
+      <c r="L166" s="127" t="s">
+        <v>356</v>
+      </c>
+      <c r="M166" s="128"/>
+      <c r="N166" s="128"/>
+      <c r="O166" s="128"/>
+      <c r="P166" s="128"/>
+      <c r="Q166" s="129"/>
+    </row>
+    <row r="167" spans="3:17">
+      <c r="D167" s="130"/>
+      <c r="E167" s="131"/>
+      <c r="F167" s="131"/>
+      <c r="G167" s="131"/>
+      <c r="H167" s="131"/>
+      <c r="I167" s="132"/>
+      <c r="L167" s="130"/>
+      <c r="M167" s="131"/>
+      <c r="N167" s="131"/>
+      <c r="O167" s="131"/>
+      <c r="P167" s="131"/>
+      <c r="Q167" s="132"/>
+    </row>
+    <row r="168" spans="3:17">
+      <c r="C168" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="169" spans="3:17">
+      <c r="D169" s="93" t="s">
+        <v>367</v>
+      </c>
+      <c r="E169" s="11"/>
+      <c r="F169" s="11"/>
+      <c r="G169" s="11"/>
+      <c r="H169" s="11"/>
+      <c r="I169" s="12"/>
+    </row>
+    <row r="178" spans="2:13">
+      <c r="C178" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="179" spans="2:13" ht="18.75">
+      <c r="B179" t="s">
         <v>253</v>
       </c>
-      <c r="K157" s="52"/>
-      <c r="L157" s="52"/>
-      <c r="M157" s="52"/>
-    </row>
-    <row r="158" spans="2:23" ht="18.75">
-      <c r="B158" t="s">
+      <c r="K179" s="52"/>
+      <c r="L179" s="52"/>
+      <c r="M179" s="52"/>
+    </row>
+    <row r="180" spans="2:13" ht="18.75">
+      <c r="B180" t="s">
+        <v>252</v>
+      </c>
+      <c r="K180" s="52"/>
+      <c r="L180" s="52"/>
+      <c r="M180" s="52"/>
+    </row>
+    <row r="181" spans="2:13" ht="18.75">
+      <c r="B181" t="s">
         <v>138</v>
       </c>
-      <c r="K158" s="53"/>
-      <c r="L158" s="53"/>
-      <c r="M158" s="53"/>
-    </row>
-    <row r="159" spans="2:23" ht="18.75">
-      <c r="C159" t="s">
-        <v>225</v>
-      </c>
-      <c r="K159" s="52"/>
-      <c r="L159" s="52"/>
-      <c r="M159" s="52"/>
-    </row>
-    <row r="160" spans="2:23" ht="18.75">
-      <c r="C160" t="s">
+      <c r="K181" s="53"/>
+      <c r="L181" s="53"/>
+      <c r="M181" s="53"/>
+    </row>
+    <row r="182" spans="2:13" ht="18.75">
+      <c r="C182" t="s">
+        <v>224</v>
+      </c>
+      <c r="K182" s="52"/>
+      <c r="L182" s="52"/>
+      <c r="M182" s="52"/>
+    </row>
+    <row r="183" spans="2:13" ht="18.75">
+      <c r="C183" t="s">
+        <v>227</v>
+      </c>
+      <c r="K183" s="52"/>
+      <c r="L183" s="52"/>
+      <c r="M183" s="52"/>
+    </row>
+    <row r="184" spans="2:13" ht="18.75">
+      <c r="C184" t="s">
         <v>228</v>
       </c>
-      <c r="K160" s="52"/>
-      <c r="L160" s="52"/>
-      <c r="M160" s="52"/>
-    </row>
-    <row r="161" spans="1:14" ht="18.75">
-      <c r="C161" t="s">
-        <v>229</v>
-      </c>
-      <c r="K161" s="52"/>
-      <c r="L161" s="52"/>
-      <c r="M161" s="52"/>
-    </row>
-    <row r="162" spans="1:14">
-      <c r="C162" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="163" spans="1:14">
-      <c r="C163" t="s">
+      <c r="K184" s="52"/>
+      <c r="L184" s="52"/>
+      <c r="M184" s="52"/>
+    </row>
+    <row r="185" spans="2:13">
+      <c r="C185" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="186" spans="2:13">
+      <c r="C186" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="187" spans="2:13">
+      <c r="E187" s="47" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="164" spans="1:14">
-      <c r="E164" s="47" t="s">
-        <v>252</v>
-      </c>
-      <c r="F164" s="48"/>
-      <c r="G164" s="48"/>
-      <c r="H164" s="48"/>
-      <c r="I164" s="48"/>
-    </row>
-    <row r="165" spans="1:14">
-      <c r="C165" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="167" spans="1:14">
-      <c r="C167" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="169" spans="1:14">
-      <c r="C169" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="172" spans="1:14" ht="20.25">
-      <c r="A172" s="61" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="173" spans="1:14" ht="17.25">
-      <c r="B173" s="58" t="s">
+      <c r="F187" s="48"/>
+      <c r="G187" s="48"/>
+      <c r="H187" s="48"/>
+      <c r="I187" s="48"/>
+    </row>
+    <row r="188" spans="2:13">
+      <c r="C188" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="190" spans="2:13">
+      <c r="C190" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="192" spans="2:13">
+      <c r="C192" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="195" spans="1:14" ht="20.25">
+      <c r="A195" s="61" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="196" spans="1:14" ht="17.25">
+      <c r="B196" s="58" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="197" spans="1:14" ht="17.25">
+      <c r="B197" s="66" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="174" spans="1:14" ht="17.25">
-      <c r="B174" s="66" t="s">
+      <c r="C197" s="14"/>
+      <c r="D197" s="14"/>
+      <c r="G197" t="s">
+        <v>244</v>
+      </c>
+      <c r="H197" s="64" t="s">
+        <v>274</v>
+      </c>
+      <c r="I197" s="14"/>
+      <c r="J197" s="14"/>
+      <c r="K197" s="14"/>
+      <c r="L197" s="14"/>
+      <c r="M197" s="14"/>
+      <c r="N197" s="14"/>
+    </row>
+    <row r="198" spans="1:14">
+      <c r="G198" t="s">
+        <v>272</v>
+      </c>
+      <c r="H198" s="65" t="s">
         <v>275</v>
       </c>
-      <c r="C174" s="14"/>
-      <c r="D174" s="14"/>
-      <c r="G174" t="s">
-        <v>245</v>
-      </c>
-      <c r="H174" s="64" t="s">
+      <c r="I198" s="14"/>
+      <c r="J198" s="14"/>
+      <c r="K198" s="14"/>
+      <c r="L198" s="14"/>
+      <c r="M198" s="14"/>
+      <c r="N198" s="14"/>
+    </row>
+    <row r="199" spans="1:14">
+      <c r="G199" t="s">
+        <v>272</v>
+      </c>
+      <c r="H199" t="s">
         <v>276</v>
       </c>
-      <c r="I174" s="14"/>
-      <c r="J174" s="14"/>
-      <c r="K174" s="14"/>
-      <c r="L174" s="14"/>
-      <c r="M174" s="14"/>
-      <c r="N174" s="14"/>
-    </row>
-    <row r="175" spans="1:14">
-      <c r="G175" t="s">
-        <v>274</v>
-      </c>
-      <c r="H175" s="65" t="s">
+      <c r="M199" t="s">
         <v>277</v>
       </c>
-      <c r="I175" s="14"/>
-      <c r="J175" s="14"/>
-      <c r="K175" s="14"/>
-      <c r="L175" s="14"/>
-      <c r="M175" s="14"/>
-      <c r="N175" s="14"/>
-    </row>
-    <row r="176" spans="1:14">
-      <c r="G176" t="s">
-        <v>274</v>
-      </c>
-      <c r="H176" t="s">
-        <v>278</v>
-      </c>
-      <c r="M176" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6" ht="18">
-      <c r="A185" s="23" t="s">
-        <v>295</v>
-      </c>
-      <c r="F185" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6">
-      <c r="B186" t="s">
+    </row>
+    <row r="208" spans="1:14" ht="18">
+      <c r="A208" s="23" t="s">
+        <v>293</v>
+      </c>
+      <c r="F208" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="209" spans="1:10">
+      <c r="B209" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="210" spans="1:10">
+      <c r="B210" s="71" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
-      <c r="B187" s="71" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6">
-      <c r="B188" s="71" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="195" customFormat="1"/>
-    <row r="196" customFormat="1"/>
-    <row r="197" customFormat="1"/>
-    <row r="198" customFormat="1"/>
-    <row r="199" customFormat="1"/>
+    <row r="211" spans="1:10">
+      <c r="B211" s="71" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="213" spans="1:10" ht="18">
+      <c r="A213" s="23" t="s">
+        <v>358</v>
+      </c>
+      <c r="E213" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="214" spans="1:10">
+      <c r="B214" s="113" t="s">
+        <v>360</v>
+      </c>
+      <c r="C214" s="105"/>
+      <c r="D214" s="105"/>
+      <c r="E214" s="105"/>
+      <c r="F214" s="105"/>
+      <c r="G214" s="105"/>
+      <c r="H214" s="105"/>
+      <c r="I214" s="105"/>
+      <c r="J214" s="106"/>
+    </row>
+    <row r="215" spans="1:10">
+      <c r="B215" s="119"/>
+      <c r="C215" s="126"/>
+      <c r="D215" s="126"/>
+      <c r="E215" s="126"/>
+      <c r="F215" s="126"/>
+      <c r="G215" s="126"/>
+      <c r="H215" s="126"/>
+      <c r="I215" s="126"/>
+      <c r="J215" s="118"/>
+    </row>
+    <row r="216" spans="1:10">
+      <c r="B216" s="119"/>
+      <c r="C216" s="126"/>
+      <c r="D216" s="126"/>
+      <c r="E216" s="126"/>
+      <c r="F216" s="126"/>
+      <c r="G216" s="126"/>
+      <c r="H216" s="126"/>
+      <c r="I216" s="126"/>
+      <c r="J216" s="118"/>
+    </row>
+    <row r="217" spans="1:10">
+      <c r="B217" s="119"/>
+      <c r="C217" s="126"/>
+      <c r="D217" s="126"/>
+      <c r="E217" s="126"/>
+      <c r="F217" s="126"/>
+      <c r="G217" s="126"/>
+      <c r="H217" s="126"/>
+      <c r="I217" s="126"/>
+      <c r="J217" s="118"/>
+    </row>
+    <row r="218" spans="1:10">
+      <c r="B218" s="119"/>
+      <c r="C218" s="126"/>
+      <c r="D218" s="126"/>
+      <c r="E218" s="126"/>
+      <c r="F218" s="126"/>
+      <c r="G218" s="126"/>
+      <c r="H218" s="126"/>
+      <c r="I218" s="126"/>
+      <c r="J218" s="118"/>
+    </row>
+    <row r="219" spans="1:10">
+      <c r="B219" s="120"/>
+      <c r="C219" s="121"/>
+      <c r="D219" s="121"/>
+      <c r="E219" s="121"/>
+      <c r="F219" s="121"/>
+      <c r="G219" s="121"/>
+      <c r="H219" s="121"/>
+      <c r="I219" s="121"/>
+      <c r="J219" s="122"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="10">
     <mergeCell ref="B8:G19"/>
+    <mergeCell ref="D160:I160"/>
+    <mergeCell ref="L160:Q160"/>
+    <mergeCell ref="B214:J219"/>
+    <mergeCell ref="D166:I167"/>
+    <mergeCell ref="L166:Q167"/>
+    <mergeCell ref="D163:I164"/>
+    <mergeCell ref="L163:Q164"/>
+    <mergeCell ref="D155:I157"/>
+    <mergeCell ref="L155:Q157"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11147,47 +12282,57 @@
     </row>
     <row r="14" spans="1:11" ht="18">
       <c r="A14" s="23" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="B15" t="s">
-        <v>202</v>
+        <v>340</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="18">
+      <c r="A16" s="23" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="20.25">
+      <c r="B17" s="90" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.75">
       <c r="A18" s="22" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="B19" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="B20" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="B21" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="B22" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="15.75">
       <c r="A24" s="22" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="B25" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -11371,12 +12516,12 @@
     </row>
     <row r="36" spans="1:13" ht="20.25">
       <c r="A36" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="37" spans="1:13">
       <c r="B37" s="39" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C37" s="40"/>
       <c r="D37" s="40"/>
@@ -11386,22 +12531,22 @@
     </row>
     <row r="40" spans="1:13" ht="20.25">
       <c r="A40" s="9" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="41" spans="1:13">
       <c r="B41" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="45" spans="1:13" ht="20.25">
       <c r="A45" s="9" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="20.25">
       <c r="B46" s="72" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C46" s="13"/>
       <c r="D46" s="13"/>
@@ -11417,7 +12562,7 @@
     </row>
     <row r="47" spans="1:13" ht="20.25">
       <c r="B47" s="73" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C47" s="14"/>
       <c r="D47" s="14"/>
@@ -11433,7 +12578,7 @@
     </row>
     <row r="48" spans="1:13" ht="20.25">
       <c r="B48" s="73" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C48" s="14"/>
       <c r="D48" s="14"/>
@@ -11449,7 +12594,7 @@
     </row>
     <row r="49" spans="2:13" ht="20.25">
       <c r="B49" s="73" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C49" s="14"/>
       <c r="D49" s="14"/>
@@ -11465,7 +12610,7 @@
     </row>
     <row r="50" spans="2:13" ht="20.25">
       <c r="B50" s="73" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C50" s="14"/>
       <c r="D50" s="14"/>
@@ -11497,7 +12642,7 @@
     </row>
     <row r="52" spans="2:13" ht="20.25">
       <c r="B52" s="74" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C52" s="14"/>
       <c r="D52" s="14"/>
@@ -11513,7 +12658,7 @@
     </row>
     <row r="53" spans="2:13" ht="20.25">
       <c r="B53" s="74" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C53" s="14"/>
       <c r="D53" s="14"/>
@@ -11529,7 +12674,7 @@
     </row>
     <row r="54" spans="2:13" ht="20.25">
       <c r="B54" s="75" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C54" s="18"/>
       <c r="D54" s="18"/>
@@ -11558,95 +12703,95 @@
   <sheetData>
     <row r="1" spans="1:4" ht="23.25">
       <c r="A1" s="67" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15.75">
+      <c r="B2" s="86" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.75">
+      <c r="B3" s="82" t="s">
+        <v>322</v>
+      </c>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
+    </row>
+    <row r="4" spans="1:4" ht="15.75">
+      <c r="B4" s="84" t="s">
+        <v>319</v>
+      </c>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
+    </row>
+    <row r="5" spans="1:4" ht="15.75">
+      <c r="B5" s="82" t="s">
+        <v>323</v>
+      </c>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
+    </row>
+    <row r="6" spans="1:4" ht="15.75">
+      <c r="B6" s="82" t="s">
+        <v>324</v>
+      </c>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+    </row>
+    <row r="7" spans="1:4" ht="15.75">
+      <c r="B7" s="82" t="s">
+        <v>325</v>
+      </c>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
+    </row>
+    <row r="8" spans="1:4" ht="15.75">
+      <c r="B8" s="85"/>
+      <c r="C8" s="83"/>
+      <c r="D8" s="83"/>
+    </row>
+    <row r="9" spans="1:4" ht="15.75">
+      <c r="B9" s="86" t="s">
+        <v>320</v>
+      </c>
+      <c r="C9" s="83"/>
+      <c r="D9" s="83"/>
+    </row>
+    <row r="10" spans="1:4" ht="15.75">
+      <c r="B10" s="82" t="s">
+        <v>326</v>
+      </c>
+      <c r="C10" s="83"/>
+      <c r="D10" s="83"/>
+    </row>
+    <row r="11" spans="1:4" ht="15.75">
+      <c r="B11" s="87" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="15.75">
-      <c r="B2" s="117" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.75">
-      <c r="B3" s="113" t="s">
+      <c r="C11" s="83"/>
+      <c r="D11" s="83"/>
+    </row>
+    <row r="12" spans="1:4" ht="15.75">
+      <c r="B12" s="82" t="s">
         <v>328</v>
       </c>
-      <c r="C3" s="114"/>
-      <c r="D3" s="114"/>
-    </row>
-    <row r="4" spans="1:4" ht="15.75">
-      <c r="B4" s="115" t="s">
-        <v>325</v>
-      </c>
-      <c r="C4" s="114"/>
-      <c r="D4" s="114"/>
-    </row>
-    <row r="5" spans="1:4" ht="15.75">
-      <c r="B5" s="113" t="s">
+      <c r="C12" s="83"/>
+      <c r="D12" s="83"/>
+    </row>
+    <row r="13" spans="1:4" ht="15.75">
+      <c r="B13" s="82" t="s">
         <v>329</v>
       </c>
-      <c r="C5" s="114"/>
-      <c r="D5" s="114"/>
-    </row>
-    <row r="6" spans="1:4" ht="15.75">
-      <c r="B6" s="113" t="s">
+      <c r="C13" s="83"/>
+      <c r="D13" s="83"/>
+    </row>
+    <row r="14" spans="1:4" ht="15.75">
+      <c r="B14" s="82" t="s">
         <v>330</v>
       </c>
-      <c r="C6" s="114"/>
-      <c r="D6" s="114"/>
-    </row>
-    <row r="7" spans="1:4" ht="15.75">
-      <c r="B7" s="113" t="s">
-        <v>331</v>
-      </c>
-      <c r="C7" s="114"/>
-      <c r="D7" s="114"/>
-    </row>
-    <row r="8" spans="1:4" ht="15.75">
-      <c r="B8" s="116"/>
-      <c r="C8" s="114"/>
-      <c r="D8" s="114"/>
-    </row>
-    <row r="9" spans="1:4" ht="15.75">
-      <c r="B9" s="117" t="s">
-        <v>326</v>
-      </c>
-      <c r="C9" s="114"/>
-      <c r="D9" s="114"/>
-    </row>
-    <row r="10" spans="1:4" ht="15.75">
-      <c r="B10" s="113" t="s">
-        <v>332</v>
-      </c>
-      <c r="C10" s="114"/>
-      <c r="D10" s="114"/>
-    </row>
-    <row r="11" spans="1:4" ht="15.75">
-      <c r="B11" s="118" t="s">
-        <v>333</v>
-      </c>
-      <c r="C11" s="114"/>
-      <c r="D11" s="114"/>
-    </row>
-    <row r="12" spans="1:4" ht="15.75">
-      <c r="B12" s="113" t="s">
-        <v>334</v>
-      </c>
-      <c r="C12" s="114"/>
-      <c r="D12" s="114"/>
-    </row>
-    <row r="13" spans="1:4" ht="15.75">
-      <c r="B13" s="113" t="s">
-        <v>335</v>
-      </c>
-      <c r="C13" s="114"/>
-      <c r="D13" s="114"/>
-    </row>
-    <row r="14" spans="1:4" ht="15.75">
-      <c r="B14" s="113" t="s">
-        <v>336</v>
-      </c>
-      <c r="C14" s="114"/>
-      <c r="D14" s="114"/>
+      <c r="C14" s="83"/>
+      <c r="D14" s="83"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -12071,7 +13216,10 @@
         <v>181</v>
       </c>
       <c r="M1" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
+      </c>
+      <c r="P1" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="15.75">
@@ -12086,15 +13234,15 @@
       <c r="H2" s="13"/>
       <c r="I2" s="13"/>
       <c r="J2" s="15"/>
-      <c r="N2" s="88" t="s">
-        <v>321</v>
-      </c>
-      <c r="O2" s="86"/>
-      <c r="P2" s="86"/>
-      <c r="Q2" s="86"/>
-      <c r="R2" s="86"/>
-      <c r="S2" s="86"/>
-      <c r="T2" s="87"/>
+      <c r="N2" s="113" t="s">
+        <v>348</v>
+      </c>
+      <c r="O2" s="105"/>
+      <c r="P2" s="105"/>
+      <c r="Q2" s="105"/>
+      <c r="R2" s="105"/>
+      <c r="S2" s="105"/>
+      <c r="T2" s="106"/>
     </row>
     <row r="3" spans="1:20" ht="15.75">
       <c r="B3" s="26" t="s">
@@ -12108,13 +13256,13 @@
       <c r="H3" s="14"/>
       <c r="I3" s="14"/>
       <c r="J3" s="16"/>
-      <c r="N3" s="108"/>
-      <c r="O3" s="112"/>
-      <c r="P3" s="112"/>
-      <c r="Q3" s="112"/>
-      <c r="R3" s="112"/>
-      <c r="S3" s="112"/>
-      <c r="T3" s="107"/>
+      <c r="N3" s="119"/>
+      <c r="O3" s="126"/>
+      <c r="P3" s="126"/>
+      <c r="Q3" s="126"/>
+      <c r="R3" s="126"/>
+      <c r="S3" s="126"/>
+      <c r="T3" s="118"/>
     </row>
     <row r="4" spans="1:20" ht="15.75">
       <c r="B4" s="26" t="s">
@@ -12128,13 +13276,13 @@
       <c r="H4" s="14"/>
       <c r="I4" s="14"/>
       <c r="J4" s="16"/>
-      <c r="N4" s="108"/>
-      <c r="O4" s="112"/>
-      <c r="P4" s="112"/>
-      <c r="Q4" s="112"/>
-      <c r="R4" s="112"/>
-      <c r="S4" s="112"/>
-      <c r="T4" s="107"/>
+      <c r="N4" s="119"/>
+      <c r="O4" s="126"/>
+      <c r="P4" s="126"/>
+      <c r="Q4" s="126"/>
+      <c r="R4" s="126"/>
+      <c r="S4" s="126"/>
+      <c r="T4" s="118"/>
     </row>
     <row r="5" spans="1:20" ht="15.75">
       <c r="B5" s="26" t="s">
@@ -12148,13 +13296,13 @@
       <c r="H5" s="14"/>
       <c r="I5" s="14"/>
       <c r="J5" s="16"/>
-      <c r="N5" s="108"/>
-      <c r="O5" s="112"/>
-      <c r="P5" s="112"/>
-      <c r="Q5" s="112"/>
-      <c r="R5" s="112"/>
-      <c r="S5" s="112"/>
-      <c r="T5" s="107"/>
+      <c r="N5" s="119"/>
+      <c r="O5" s="126"/>
+      <c r="P5" s="126"/>
+      <c r="Q5" s="126"/>
+      <c r="R5" s="126"/>
+      <c r="S5" s="126"/>
+      <c r="T5" s="118"/>
     </row>
     <row r="6" spans="1:20" ht="15.75">
       <c r="B6" s="27" t="s">
@@ -12168,13 +13316,13 @@
       <c r="H6" s="14"/>
       <c r="I6" s="14"/>
       <c r="J6" s="16"/>
-      <c r="N6" s="108"/>
-      <c r="O6" s="112"/>
-      <c r="P6" s="112"/>
-      <c r="Q6" s="112"/>
-      <c r="R6" s="112"/>
-      <c r="S6" s="112"/>
-      <c r="T6" s="107"/>
+      <c r="N6" s="119"/>
+      <c r="O6" s="126"/>
+      <c r="P6" s="126"/>
+      <c r="Q6" s="126"/>
+      <c r="R6" s="126"/>
+      <c r="S6" s="126"/>
+      <c r="T6" s="118"/>
     </row>
     <row r="7" spans="1:20" ht="15.75">
       <c r="B7" s="27" t="s">
@@ -12188,13 +13336,13 @@
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
       <c r="J7" s="16"/>
-      <c r="N7" s="108"/>
-      <c r="O7" s="112"/>
-      <c r="P7" s="112"/>
-      <c r="Q7" s="112"/>
-      <c r="R7" s="112"/>
-      <c r="S7" s="112"/>
-      <c r="T7" s="107"/>
+      <c r="N7" s="119"/>
+      <c r="O7" s="126"/>
+      <c r="P7" s="126"/>
+      <c r="Q7" s="126"/>
+      <c r="R7" s="126"/>
+      <c r="S7" s="126"/>
+      <c r="T7" s="118"/>
     </row>
     <row r="8" spans="1:20" ht="15.75">
       <c r="B8" s="27" t="s">
@@ -12208,13 +13356,13 @@
       <c r="H8" s="14"/>
       <c r="I8" s="14"/>
       <c r="J8" s="16"/>
-      <c r="N8" s="108"/>
-      <c r="O8" s="112"/>
-      <c r="P8" s="112"/>
-      <c r="Q8" s="112"/>
-      <c r="R8" s="112"/>
-      <c r="S8" s="112"/>
-      <c r="T8" s="107"/>
+      <c r="N8" s="119"/>
+      <c r="O8" s="126"/>
+      <c r="P8" s="126"/>
+      <c r="Q8" s="126"/>
+      <c r="R8" s="126"/>
+      <c r="S8" s="126"/>
+      <c r="T8" s="118"/>
     </row>
     <row r="9" spans="1:20" ht="15.75">
       <c r="B9" s="27" t="s">
@@ -12228,13 +13376,13 @@
       <c r="H9" s="14"/>
       <c r="I9" s="14"/>
       <c r="J9" s="16"/>
-      <c r="N9" s="109"/>
-      <c r="O9" s="110"/>
-      <c r="P9" s="110"/>
-      <c r="Q9" s="110"/>
-      <c r="R9" s="110"/>
-      <c r="S9" s="110"/>
-      <c r="T9" s="111"/>
+      <c r="N9" s="120"/>
+      <c r="O9" s="121"/>
+      <c r="P9" s="121"/>
+      <c r="Q9" s="121"/>
+      <c r="R9" s="121"/>
+      <c r="S9" s="121"/>
+      <c r="T9" s="122"/>
     </row>
     <row r="10" spans="1:20" ht="15.75">
       <c r="B10" s="27" t="s">
@@ -12249,7 +13397,7 @@
       <c r="I10" s="14"/>
       <c r="J10" s="16"/>
       <c r="M10" s="10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="15.75">
@@ -12264,15 +13412,15 @@
       <c r="H11" s="14"/>
       <c r="I11" s="14"/>
       <c r="J11" s="16"/>
-      <c r="N11" s="88" t="s">
-        <v>322</v>
-      </c>
-      <c r="O11" s="86"/>
-      <c r="P11" s="86"/>
-      <c r="Q11" s="86"/>
-      <c r="R11" s="86"/>
-      <c r="S11" s="86"/>
-      <c r="T11" s="87"/>
+      <c r="N11" s="113" t="s">
+        <v>349</v>
+      </c>
+      <c r="O11" s="105"/>
+      <c r="P11" s="105"/>
+      <c r="Q11" s="105"/>
+      <c r="R11" s="105"/>
+      <c r="S11" s="105"/>
+      <c r="T11" s="106"/>
     </row>
     <row r="12" spans="1:20" ht="15.75">
       <c r="B12" s="26" t="s">
@@ -12286,13 +13434,13 @@
       <c r="H12" s="14"/>
       <c r="I12" s="14"/>
       <c r="J12" s="16"/>
-      <c r="N12" s="108"/>
-      <c r="O12" s="112"/>
-      <c r="P12" s="112"/>
-      <c r="Q12" s="112"/>
-      <c r="R12" s="112"/>
-      <c r="S12" s="112"/>
-      <c r="T12" s="107"/>
+      <c r="N12" s="119"/>
+      <c r="O12" s="126"/>
+      <c r="P12" s="126"/>
+      <c r="Q12" s="126"/>
+      <c r="R12" s="126"/>
+      <c r="S12" s="126"/>
+      <c r="T12" s="118"/>
     </row>
     <row r="13" spans="1:20" ht="15.75">
       <c r="B13" s="27" t="s">
@@ -12306,13 +13454,13 @@
       <c r="H13" s="14"/>
       <c r="I13" s="14"/>
       <c r="J13" s="16"/>
-      <c r="N13" s="108"/>
-      <c r="O13" s="112"/>
-      <c r="P13" s="112"/>
-      <c r="Q13" s="112"/>
-      <c r="R13" s="112"/>
-      <c r="S13" s="112"/>
-      <c r="T13" s="107"/>
+      <c r="N13" s="119"/>
+      <c r="O13" s="126"/>
+      <c r="P13" s="126"/>
+      <c r="Q13" s="126"/>
+      <c r="R13" s="126"/>
+      <c r="S13" s="126"/>
+      <c r="T13" s="118"/>
     </row>
     <row r="14" spans="1:20" ht="15.75">
       <c r="B14" s="28" t="s">
@@ -12326,13 +13474,13 @@
       <c r="H14" s="14"/>
       <c r="I14" s="14"/>
       <c r="J14" s="16"/>
-      <c r="N14" s="108"/>
-      <c r="O14" s="112"/>
-      <c r="P14" s="112"/>
-      <c r="Q14" s="112"/>
-      <c r="R14" s="112"/>
-      <c r="S14" s="112"/>
-      <c r="T14" s="107"/>
+      <c r="N14" s="119"/>
+      <c r="O14" s="126"/>
+      <c r="P14" s="126"/>
+      <c r="Q14" s="126"/>
+      <c r="R14" s="126"/>
+      <c r="S14" s="126"/>
+      <c r="T14" s="118"/>
     </row>
     <row r="15" spans="1:20" ht="15.75">
       <c r="B15" s="28" t="s">
@@ -12346,13 +13494,13 @@
       <c r="H15" s="14"/>
       <c r="I15" s="14"/>
       <c r="J15" s="16"/>
-      <c r="N15" s="108"/>
-      <c r="O15" s="112"/>
-      <c r="P15" s="112"/>
-      <c r="Q15" s="112"/>
-      <c r="R15" s="112"/>
-      <c r="S15" s="112"/>
-      <c r="T15" s="107"/>
+      <c r="N15" s="119"/>
+      <c r="O15" s="126"/>
+      <c r="P15" s="126"/>
+      <c r="Q15" s="126"/>
+      <c r="R15" s="126"/>
+      <c r="S15" s="126"/>
+      <c r="T15" s="118"/>
     </row>
     <row r="16" spans="1:20" ht="15.75">
       <c r="B16" s="28" t="s">
@@ -12366,13 +13514,13 @@
       <c r="H16" s="14"/>
       <c r="I16" s="14"/>
       <c r="J16" s="16"/>
-      <c r="N16" s="108"/>
-      <c r="O16" s="112"/>
-      <c r="P16" s="112"/>
-      <c r="Q16" s="112"/>
-      <c r="R16" s="112"/>
-      <c r="S16" s="112"/>
-      <c r="T16" s="107"/>
+      <c r="N16" s="119"/>
+      <c r="O16" s="126"/>
+      <c r="P16" s="126"/>
+      <c r="Q16" s="126"/>
+      <c r="R16" s="126"/>
+      <c r="S16" s="126"/>
+      <c r="T16" s="118"/>
     </row>
     <row r="17" spans="2:20" ht="15.75">
       <c r="B17" s="27" t="s">
@@ -12386,13 +13534,13 @@
       <c r="H17" s="14"/>
       <c r="I17" s="14"/>
       <c r="J17" s="16"/>
-      <c r="N17" s="108"/>
-      <c r="O17" s="112"/>
-      <c r="P17" s="112"/>
-      <c r="Q17" s="112"/>
-      <c r="R17" s="112"/>
-      <c r="S17" s="112"/>
-      <c r="T17" s="107"/>
+      <c r="N17" s="119"/>
+      <c r="O17" s="126"/>
+      <c r="P17" s="126"/>
+      <c r="Q17" s="126"/>
+      <c r="R17" s="126"/>
+      <c r="S17" s="126"/>
+      <c r="T17" s="118"/>
     </row>
     <row r="18" spans="2:20" ht="15.75">
       <c r="B18" s="27" t="s">
@@ -12406,13 +13554,13 @@
       <c r="H18" s="14"/>
       <c r="I18" s="14"/>
       <c r="J18" s="16"/>
-      <c r="N18" s="109"/>
-      <c r="O18" s="110"/>
-      <c r="P18" s="110"/>
-      <c r="Q18" s="110"/>
-      <c r="R18" s="110"/>
-      <c r="S18" s="110"/>
-      <c r="T18" s="111"/>
+      <c r="N18" s="120"/>
+      <c r="O18" s="121"/>
+      <c r="P18" s="121"/>
+      <c r="Q18" s="121"/>
+      <c r="R18" s="121"/>
+      <c r="S18" s="121"/>
+      <c r="T18" s="122"/>
     </row>
     <row r="19" spans="2:20" ht="15.75">
       <c r="B19" s="27" t="s">
@@ -12427,7 +13575,7 @@
       <c r="I19" s="14"/>
       <c r="J19" s="16"/>
       <c r="M19" s="10" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="2:20" ht="15.75" customHeight="1">
@@ -12442,15 +13590,15 @@
       <c r="H20" s="14"/>
       <c r="I20" s="14"/>
       <c r="J20" s="16"/>
-      <c r="N20" s="88" t="s">
-        <v>323</v>
-      </c>
-      <c r="O20" s="86"/>
-      <c r="P20" s="86"/>
-      <c r="Q20" s="86"/>
-      <c r="R20" s="86"/>
-      <c r="S20" s="86"/>
-      <c r="T20" s="87"/>
+      <c r="N20" s="113" t="s">
+        <v>350</v>
+      </c>
+      <c r="O20" s="105"/>
+      <c r="P20" s="105"/>
+      <c r="Q20" s="105"/>
+      <c r="R20" s="105"/>
+      <c r="S20" s="105"/>
+      <c r="T20" s="106"/>
     </row>
     <row r="21" spans="2:20" ht="15.75">
       <c r="B21" s="27" t="s">
@@ -12464,13 +13612,13 @@
       <c r="H21" s="14"/>
       <c r="I21" s="14"/>
       <c r="J21" s="16"/>
-      <c r="N21" s="108"/>
-      <c r="O21" s="112"/>
-      <c r="P21" s="112"/>
-      <c r="Q21" s="112"/>
-      <c r="R21" s="112"/>
-      <c r="S21" s="112"/>
-      <c r="T21" s="107"/>
+      <c r="N21" s="119"/>
+      <c r="O21" s="126"/>
+      <c r="P21" s="126"/>
+      <c r="Q21" s="126"/>
+      <c r="R21" s="126"/>
+      <c r="S21" s="126"/>
+      <c r="T21" s="118"/>
     </row>
     <row r="22" spans="2:20" ht="15.75">
       <c r="B22" s="29" t="s">
@@ -12484,17 +13632,17 @@
       <c r="H22" s="14"/>
       <c r="I22" s="14"/>
       <c r="J22" s="16"/>
-      <c r="N22" s="108"/>
-      <c r="O22" s="112"/>
-      <c r="P22" s="112"/>
-      <c r="Q22" s="112"/>
-      <c r="R22" s="112"/>
-      <c r="S22" s="112"/>
-      <c r="T22" s="107"/>
+      <c r="N22" s="119"/>
+      <c r="O22" s="126"/>
+      <c r="P22" s="126"/>
+      <c r="Q22" s="126"/>
+      <c r="R22" s="126"/>
+      <c r="S22" s="126"/>
+      <c r="T22" s="118"/>
     </row>
     <row r="23" spans="2:20" ht="15.75">
       <c r="B23" s="26" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C23" s="14"/>
       <c r="D23" s="14"/>
@@ -12504,13 +13652,13 @@
       <c r="H23" s="14"/>
       <c r="I23" s="14"/>
       <c r="J23" s="16"/>
-      <c r="N23" s="108"/>
-      <c r="O23" s="112"/>
-      <c r="P23" s="112"/>
-      <c r="Q23" s="112"/>
-      <c r="R23" s="112"/>
-      <c r="S23" s="112"/>
-      <c r="T23" s="107"/>
+      <c r="N23" s="119"/>
+      <c r="O23" s="126"/>
+      <c r="P23" s="126"/>
+      <c r="Q23" s="126"/>
+      <c r="R23" s="126"/>
+      <c r="S23" s="126"/>
+      <c r="T23" s="118"/>
     </row>
     <row r="24" spans="2:20" ht="15.75">
       <c r="B24" s="26" t="s">
@@ -12524,13 +13672,13 @@
       <c r="H24" s="14"/>
       <c r="I24" s="14"/>
       <c r="J24" s="16"/>
-      <c r="N24" s="108"/>
-      <c r="O24" s="112"/>
-      <c r="P24" s="112"/>
-      <c r="Q24" s="112"/>
-      <c r="R24" s="112"/>
-      <c r="S24" s="112"/>
-      <c r="T24" s="107"/>
+      <c r="N24" s="119"/>
+      <c r="O24" s="126"/>
+      <c r="P24" s="126"/>
+      <c r="Q24" s="126"/>
+      <c r="R24" s="126"/>
+      <c r="S24" s="126"/>
+      <c r="T24" s="118"/>
     </row>
     <row r="25" spans="2:20" ht="15.75">
       <c r="B25" s="26" t="s">
@@ -12544,13 +13692,13 @@
       <c r="H25" s="14"/>
       <c r="I25" s="14"/>
       <c r="J25" s="16"/>
-      <c r="N25" s="108"/>
-      <c r="O25" s="112"/>
-      <c r="P25" s="112"/>
-      <c r="Q25" s="112"/>
-      <c r="R25" s="112"/>
-      <c r="S25" s="112"/>
-      <c r="T25" s="107"/>
+      <c r="N25" s="119"/>
+      <c r="O25" s="126"/>
+      <c r="P25" s="126"/>
+      <c r="Q25" s="126"/>
+      <c r="R25" s="126"/>
+      <c r="S25" s="126"/>
+      <c r="T25" s="118"/>
     </row>
     <row r="26" spans="2:20" ht="15.75">
       <c r="B26" s="29" t="s">
@@ -12564,13 +13712,13 @@
       <c r="H26" s="14"/>
       <c r="I26" s="14"/>
       <c r="J26" s="16"/>
-      <c r="N26" s="108"/>
-      <c r="O26" s="112"/>
-      <c r="P26" s="112"/>
-      <c r="Q26" s="112"/>
-      <c r="R26" s="112"/>
-      <c r="S26" s="112"/>
-      <c r="T26" s="107"/>
+      <c r="N26" s="119"/>
+      <c r="O26" s="126"/>
+      <c r="P26" s="126"/>
+      <c r="Q26" s="126"/>
+      <c r="R26" s="126"/>
+      <c r="S26" s="126"/>
+      <c r="T26" s="118"/>
     </row>
     <row r="27" spans="2:20" ht="15.75">
       <c r="B27" s="26" t="s">
@@ -12584,13 +13732,13 @@
       <c r="H27" s="14"/>
       <c r="I27" s="14"/>
       <c r="J27" s="16"/>
-      <c r="N27" s="109"/>
-      <c r="O27" s="110"/>
-      <c r="P27" s="110"/>
-      <c r="Q27" s="110"/>
-      <c r="R27" s="110"/>
-      <c r="S27" s="110"/>
-      <c r="T27" s="111"/>
+      <c r="N27" s="120"/>
+      <c r="O27" s="121"/>
+      <c r="P27" s="121"/>
+      <c r="Q27" s="121"/>
+      <c r="R27" s="121"/>
+      <c r="S27" s="121"/>
+      <c r="T27" s="122"/>
     </row>
     <row r="28" spans="2:20" ht="15.75">
       <c r="B28" s="26" t="s">
@@ -12728,182 +13876,182 @@
       </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="B40" s="88" t="s">
+      <c r="B40" s="113" t="s">
         <v>182</v>
       </c>
-      <c r="C40" s="86"/>
-      <c r="D40" s="86"/>
-      <c r="E40" s="86"/>
-      <c r="F40" s="86"/>
-      <c r="G40" s="86"/>
-      <c r="H40" s="86"/>
-      <c r="I40" s="86"/>
-      <c r="J40" s="87"/>
+      <c r="C40" s="105"/>
+      <c r="D40" s="105"/>
+      <c r="E40" s="105"/>
+      <c r="F40" s="105"/>
+      <c r="G40" s="105"/>
+      <c r="H40" s="105"/>
+      <c r="I40" s="105"/>
+      <c r="J40" s="106"/>
     </row>
     <row r="41" spans="1:10">
-      <c r="B41" s="108"/>
-      <c r="C41" s="112"/>
-      <c r="D41" s="112"/>
-      <c r="E41" s="112"/>
-      <c r="F41" s="112"/>
-      <c r="G41" s="112"/>
-      <c r="H41" s="112"/>
-      <c r="I41" s="112"/>
-      <c r="J41" s="107"/>
+      <c r="B41" s="119"/>
+      <c r="C41" s="126"/>
+      <c r="D41" s="126"/>
+      <c r="E41" s="126"/>
+      <c r="F41" s="126"/>
+      <c r="G41" s="126"/>
+      <c r="H41" s="126"/>
+      <c r="I41" s="126"/>
+      <c r="J41" s="118"/>
     </row>
     <row r="42" spans="1:10">
-      <c r="B42" s="108"/>
-      <c r="C42" s="112"/>
-      <c r="D42" s="112"/>
-      <c r="E42" s="112"/>
-      <c r="F42" s="112"/>
-      <c r="G42" s="112"/>
-      <c r="H42" s="112"/>
-      <c r="I42" s="112"/>
-      <c r="J42" s="107"/>
+      <c r="B42" s="119"/>
+      <c r="C42" s="126"/>
+      <c r="D42" s="126"/>
+      <c r="E42" s="126"/>
+      <c r="F42" s="126"/>
+      <c r="G42" s="126"/>
+      <c r="H42" s="126"/>
+      <c r="I42" s="126"/>
+      <c r="J42" s="118"/>
     </row>
     <row r="43" spans="1:10">
-      <c r="B43" s="108"/>
-      <c r="C43" s="112"/>
-      <c r="D43" s="112"/>
-      <c r="E43" s="112"/>
-      <c r="F43" s="112"/>
-      <c r="G43" s="112"/>
-      <c r="H43" s="112"/>
-      <c r="I43" s="112"/>
-      <c r="J43" s="107"/>
+      <c r="B43" s="119"/>
+      <c r="C43" s="126"/>
+      <c r="D43" s="126"/>
+      <c r="E43" s="126"/>
+      <c r="F43" s="126"/>
+      <c r="G43" s="126"/>
+      <c r="H43" s="126"/>
+      <c r="I43" s="126"/>
+      <c r="J43" s="118"/>
     </row>
     <row r="44" spans="1:10">
-      <c r="B44" s="108"/>
-      <c r="C44" s="112"/>
-      <c r="D44" s="112"/>
-      <c r="E44" s="112"/>
-      <c r="F44" s="112"/>
-      <c r="G44" s="112"/>
-      <c r="H44" s="112"/>
-      <c r="I44" s="112"/>
-      <c r="J44" s="107"/>
+      <c r="B44" s="119"/>
+      <c r="C44" s="126"/>
+      <c r="D44" s="126"/>
+      <c r="E44" s="126"/>
+      <c r="F44" s="126"/>
+      <c r="G44" s="126"/>
+      <c r="H44" s="126"/>
+      <c r="I44" s="126"/>
+      <c r="J44" s="118"/>
     </row>
     <row r="45" spans="1:10">
-      <c r="B45" s="108"/>
-      <c r="C45" s="112"/>
-      <c r="D45" s="112"/>
-      <c r="E45" s="112"/>
-      <c r="F45" s="112"/>
-      <c r="G45" s="112"/>
-      <c r="H45" s="112"/>
-      <c r="I45" s="112"/>
-      <c r="J45" s="107"/>
+      <c r="B45" s="119"/>
+      <c r="C45" s="126"/>
+      <c r="D45" s="126"/>
+      <c r="E45" s="126"/>
+      <c r="F45" s="126"/>
+      <c r="G45" s="126"/>
+      <c r="H45" s="126"/>
+      <c r="I45" s="126"/>
+      <c r="J45" s="118"/>
     </row>
     <row r="46" spans="1:10">
-      <c r="B46" s="108"/>
-      <c r="C46" s="112"/>
-      <c r="D46" s="112"/>
-      <c r="E46" s="112"/>
-      <c r="F46" s="112"/>
-      <c r="G46" s="112"/>
-      <c r="H46" s="112"/>
-      <c r="I46" s="112"/>
-      <c r="J46" s="107"/>
+      <c r="B46" s="119"/>
+      <c r="C46" s="126"/>
+      <c r="D46" s="126"/>
+      <c r="E46" s="126"/>
+      <c r="F46" s="126"/>
+      <c r="G46" s="126"/>
+      <c r="H46" s="126"/>
+      <c r="I46" s="126"/>
+      <c r="J46" s="118"/>
     </row>
     <row r="47" spans="1:10">
-      <c r="B47" s="108"/>
-      <c r="C47" s="112"/>
-      <c r="D47" s="112"/>
-      <c r="E47" s="112"/>
-      <c r="F47" s="112"/>
-      <c r="G47" s="112"/>
-      <c r="H47" s="112"/>
-      <c r="I47" s="112"/>
-      <c r="J47" s="107"/>
+      <c r="B47" s="119"/>
+      <c r="C47" s="126"/>
+      <c r="D47" s="126"/>
+      <c r="E47" s="126"/>
+      <c r="F47" s="126"/>
+      <c r="G47" s="126"/>
+      <c r="H47" s="126"/>
+      <c r="I47" s="126"/>
+      <c r="J47" s="118"/>
     </row>
     <row r="48" spans="1:10">
-      <c r="B48" s="108"/>
-      <c r="C48" s="112"/>
-      <c r="D48" s="112"/>
-      <c r="E48" s="112"/>
-      <c r="F48" s="112"/>
-      <c r="G48" s="112"/>
-      <c r="H48" s="112"/>
-      <c r="I48" s="112"/>
-      <c r="J48" s="107"/>
+      <c r="B48" s="119"/>
+      <c r="C48" s="126"/>
+      <c r="D48" s="126"/>
+      <c r="E48" s="126"/>
+      <c r="F48" s="126"/>
+      <c r="G48" s="126"/>
+      <c r="H48" s="126"/>
+      <c r="I48" s="126"/>
+      <c r="J48" s="118"/>
     </row>
     <row r="49" spans="2:10">
-      <c r="B49" s="108"/>
-      <c r="C49" s="112"/>
-      <c r="D49" s="112"/>
-      <c r="E49" s="112"/>
-      <c r="F49" s="112"/>
-      <c r="G49" s="112"/>
-      <c r="H49" s="112"/>
-      <c r="I49" s="112"/>
-      <c r="J49" s="107"/>
+      <c r="B49" s="119"/>
+      <c r="C49" s="126"/>
+      <c r="D49" s="126"/>
+      <c r="E49" s="126"/>
+      <c r="F49" s="126"/>
+      <c r="G49" s="126"/>
+      <c r="H49" s="126"/>
+      <c r="I49" s="126"/>
+      <c r="J49" s="118"/>
     </row>
     <row r="50" spans="2:10">
-      <c r="B50" s="108"/>
-      <c r="C50" s="112"/>
-      <c r="D50" s="112"/>
-      <c r="E50" s="112"/>
-      <c r="F50" s="112"/>
-      <c r="G50" s="112"/>
-      <c r="H50" s="112"/>
-      <c r="I50" s="112"/>
-      <c r="J50" s="107"/>
+      <c r="B50" s="119"/>
+      <c r="C50" s="126"/>
+      <c r="D50" s="126"/>
+      <c r="E50" s="126"/>
+      <c r="F50" s="126"/>
+      <c r="G50" s="126"/>
+      <c r="H50" s="126"/>
+      <c r="I50" s="126"/>
+      <c r="J50" s="118"/>
     </row>
     <row r="51" spans="2:10">
-      <c r="B51" s="108"/>
-      <c r="C51" s="112"/>
-      <c r="D51" s="112"/>
-      <c r="E51" s="112"/>
-      <c r="F51" s="112"/>
-      <c r="G51" s="112"/>
-      <c r="H51" s="112"/>
-      <c r="I51" s="112"/>
-      <c r="J51" s="107"/>
+      <c r="B51" s="119"/>
+      <c r="C51" s="126"/>
+      <c r="D51" s="126"/>
+      <c r="E51" s="126"/>
+      <c r="F51" s="126"/>
+      <c r="G51" s="126"/>
+      <c r="H51" s="126"/>
+      <c r="I51" s="126"/>
+      <c r="J51" s="118"/>
     </row>
     <row r="52" spans="2:10">
-      <c r="B52" s="108"/>
-      <c r="C52" s="112"/>
-      <c r="D52" s="112"/>
-      <c r="E52" s="112"/>
-      <c r="F52" s="112"/>
-      <c r="G52" s="112"/>
-      <c r="H52" s="112"/>
-      <c r="I52" s="112"/>
-      <c r="J52" s="107"/>
+      <c r="B52" s="119"/>
+      <c r="C52" s="126"/>
+      <c r="D52" s="126"/>
+      <c r="E52" s="126"/>
+      <c r="F52" s="126"/>
+      <c r="G52" s="126"/>
+      <c r="H52" s="126"/>
+      <c r="I52" s="126"/>
+      <c r="J52" s="118"/>
     </row>
     <row r="53" spans="2:10">
-      <c r="B53" s="108"/>
-      <c r="C53" s="112"/>
-      <c r="D53" s="112"/>
-      <c r="E53" s="112"/>
-      <c r="F53" s="112"/>
-      <c r="G53" s="112"/>
-      <c r="H53" s="112"/>
-      <c r="I53" s="112"/>
-      <c r="J53" s="107"/>
+      <c r="B53" s="119"/>
+      <c r="C53" s="126"/>
+      <c r="D53" s="126"/>
+      <c r="E53" s="126"/>
+      <c r="F53" s="126"/>
+      <c r="G53" s="126"/>
+      <c r="H53" s="126"/>
+      <c r="I53" s="126"/>
+      <c r="J53" s="118"/>
     </row>
     <row r="54" spans="2:10">
-      <c r="B54" s="108"/>
-      <c r="C54" s="112"/>
-      <c r="D54" s="112"/>
-      <c r="E54" s="112"/>
-      <c r="F54" s="112"/>
-      <c r="G54" s="112"/>
-      <c r="H54" s="112"/>
-      <c r="I54" s="112"/>
-      <c r="J54" s="107"/>
+      <c r="B54" s="119"/>
+      <c r="C54" s="126"/>
+      <c r="D54" s="126"/>
+      <c r="E54" s="126"/>
+      <c r="F54" s="126"/>
+      <c r="G54" s="126"/>
+      <c r="H54" s="126"/>
+      <c r="I54" s="126"/>
+      <c r="J54" s="118"/>
     </row>
     <row r="55" spans="2:10">
-      <c r="B55" s="109"/>
-      <c r="C55" s="110"/>
-      <c r="D55" s="110"/>
-      <c r="E55" s="110"/>
-      <c r="F55" s="110"/>
-      <c r="G55" s="110"/>
-      <c r="H55" s="110"/>
-      <c r="I55" s="110"/>
-      <c r="J55" s="111"/>
+      <c r="B55" s="120"/>
+      <c r="C55" s="121"/>
+      <c r="D55" s="121"/>
+      <c r="E55" s="121"/>
+      <c r="F55" s="121"/>
+      <c r="G55" s="121"/>
+      <c r="H55" s="121"/>
+      <c r="I55" s="121"/>
+      <c r="J55" s="122"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/40_数据库/学习笔记_RDBMS_GaussDB.xlsx
+++ b/40_数据库/学习笔记_RDBMS_GaussDB.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8117F442-9E4A-4E00-973B-2BBDE7A9F337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A672A2-5A93-4722-A28F-33564A395253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="概述" sheetId="1" r:id="rId1"/>
@@ -8001,6 +8001,48 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -8024,48 +8066,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -9133,7 +9133,7 @@
       </c>
     </row>
     <row r="2" spans="1:24" ht="18">
-      <c r="A2" s="100" t="s">
+      <c r="A2" s="114" t="s">
         <v>41</v>
       </c>
       <c r="B2" s="17" t="s">
@@ -9154,1618 +9154,1850 @@
       <c r="M2" s="11"/>
       <c r="N2" s="11"/>
       <c r="O2" s="12"/>
-      <c r="P2" s="107" t="s">
+      <c r="P2" s="102" t="s">
         <v>32</v>
       </c>
-      <c r="Q2" s="108"/>
-      <c r="R2" s="108"/>
-      <c r="S2" s="108"/>
-      <c r="T2" s="108"/>
-      <c r="U2" s="108"/>
-      <c r="V2" s="108"/>
-      <c r="W2" s="108"/>
-      <c r="X2" s="109"/>
+      <c r="Q2" s="103"/>
+      <c r="R2" s="103"/>
+      <c r="S2" s="103"/>
+      <c r="T2" s="103"/>
+      <c r="U2" s="103"/>
+      <c r="V2" s="103"/>
+      <c r="W2" s="103"/>
+      <c r="X2" s="104"/>
     </row>
     <row r="3" spans="1:24" ht="18">
-      <c r="A3" s="101"/>
-      <c r="B3" s="94" t="s">
+      <c r="A3" s="115"/>
+      <c r="B3" s="108" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="95"/>
-      <c r="D3" s="95"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="96" t="s">
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="110" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="97"/>
-      <c r="H3" s="98"/>
-      <c r="I3" s="94" t="s">
+      <c r="G3" s="111"/>
+      <c r="H3" s="112"/>
+      <c r="I3" s="108" t="s">
         <v>34</v>
       </c>
-      <c r="J3" s="95"/>
-      <c r="K3" s="95"/>
-      <c r="L3" s="95"/>
-      <c r="M3" s="96" t="s">
+      <c r="J3" s="109"/>
+      <c r="K3" s="109"/>
+      <c r="L3" s="109"/>
+      <c r="M3" s="110" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="97"/>
-      <c r="O3" s="98"/>
-      <c r="P3" s="110"/>
-      <c r="Q3" s="111"/>
-      <c r="R3" s="111"/>
-      <c r="S3" s="111"/>
-      <c r="T3" s="111"/>
-      <c r="U3" s="111"/>
-      <c r="V3" s="111"/>
-      <c r="W3" s="111"/>
-      <c r="X3" s="112"/>
+      <c r="N3" s="111"/>
+      <c r="O3" s="112"/>
+      <c r="P3" s="105"/>
+      <c r="Q3" s="106"/>
+      <c r="R3" s="106"/>
+      <c r="S3" s="106"/>
+      <c r="T3" s="106"/>
+      <c r="U3" s="106"/>
+      <c r="V3" s="106"/>
+      <c r="W3" s="106"/>
+      <c r="X3" s="107"/>
     </row>
     <row r="4" spans="1:24">
       <c r="A4" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="103" t="s">
+      <c r="B4" s="94" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="103"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="103"/>
-      <c r="H4" s="103"/>
-      <c r="I4" s="104" t="s">
+      <c r="C4" s="94"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="94"/>
+      <c r="I4" s="96" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="105"/>
-      <c r="K4" s="105"/>
-      <c r="L4" s="106"/>
-      <c r="M4" s="103"/>
-      <c r="N4" s="103"/>
-      <c r="O4" s="103"/>
-      <c r="P4" s="103"/>
-      <c r="Q4" s="103"/>
-      <c r="R4" s="103"/>
-      <c r="S4" s="103"/>
-      <c r="T4" s="103"/>
-      <c r="U4" s="103"/>
-      <c r="V4" s="103"/>
-      <c r="W4" s="103"/>
-      <c r="X4" s="103"/>
+      <c r="J4" s="97"/>
+      <c r="K4" s="97"/>
+      <c r="L4" s="98"/>
+      <c r="M4" s="94"/>
+      <c r="N4" s="94"/>
+      <c r="O4" s="94"/>
+      <c r="P4" s="94"/>
+      <c r="Q4" s="94"/>
+      <c r="R4" s="94"/>
+      <c r="S4" s="94"/>
+      <c r="T4" s="94"/>
+      <c r="U4" s="94"/>
+      <c r="V4" s="94"/>
+      <c r="W4" s="94"/>
+      <c r="X4" s="94"/>
     </row>
     <row r="5" spans="1:24">
       <c r="A5" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="103" t="s">
+      <c r="B5" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="103"/>
-      <c r="D5" s="103"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="103" t="s">
+      <c r="C5" s="94"/>
+      <c r="D5" s="94"/>
+      <c r="E5" s="94"/>
+      <c r="F5" s="94" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="103"/>
-      <c r="H5" s="103"/>
-      <c r="I5" s="104" t="s">
+      <c r="G5" s="94"/>
+      <c r="H5" s="94"/>
+      <c r="I5" s="96" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="105"/>
-      <c r="K5" s="105"/>
-      <c r="L5" s="106"/>
-      <c r="M5" s="103" t="s">
+      <c r="J5" s="97"/>
+      <c r="K5" s="97"/>
+      <c r="L5" s="98"/>
+      <c r="M5" s="94" t="s">
         <v>36</v>
       </c>
-      <c r="N5" s="103"/>
-      <c r="O5" s="103"/>
-      <c r="P5" s="103" t="s">
+      <c r="N5" s="94"/>
+      <c r="O5" s="94"/>
+      <c r="P5" s="94" t="s">
         <v>33</v>
       </c>
-      <c r="Q5" s="103"/>
-      <c r="R5" s="103"/>
-      <c r="S5" s="103"/>
-      <c r="T5" s="103"/>
-      <c r="U5" s="103"/>
-      <c r="V5" s="103"/>
-      <c r="W5" s="103"/>
-      <c r="X5" s="103"/>
+      <c r="Q5" s="94"/>
+      <c r="R5" s="94"/>
+      <c r="S5" s="94"/>
+      <c r="T5" s="94"/>
+      <c r="U5" s="94"/>
+      <c r="V5" s="94"/>
+      <c r="W5" s="94"/>
+      <c r="X5" s="94"/>
     </row>
     <row r="6" spans="1:24">
       <c r="A6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="103" t="s">
+      <c r="B6" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="103"/>
-      <c r="D6" s="103"/>
-      <c r="E6" s="103"/>
-      <c r="F6" s="103" t="s">
+      <c r="C6" s="94"/>
+      <c r="D6" s="94"/>
+      <c r="E6" s="94"/>
+      <c r="F6" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="103"/>
-      <c r="H6" s="103"/>
-      <c r="I6" s="104" t="s">
+      <c r="G6" s="94"/>
+      <c r="H6" s="94"/>
+      <c r="I6" s="96" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="105"/>
-      <c r="K6" s="105"/>
-      <c r="L6" s="106"/>
-      <c r="M6" s="103" t="s">
+      <c r="J6" s="97"/>
+      <c r="K6" s="97"/>
+      <c r="L6" s="98"/>
+      <c r="M6" s="94" t="s">
         <v>24</v>
       </c>
-      <c r="N6" s="103"/>
-      <c r="O6" s="103"/>
-      <c r="P6" s="103"/>
-      <c r="Q6" s="103"/>
-      <c r="R6" s="103"/>
-      <c r="S6" s="103"/>
-      <c r="T6" s="103"/>
-      <c r="U6" s="103"/>
-      <c r="V6" s="103"/>
-      <c r="W6" s="103"/>
-      <c r="X6" s="103"/>
+      <c r="N6" s="94"/>
+      <c r="O6" s="94"/>
+      <c r="P6" s="94"/>
+      <c r="Q6" s="94"/>
+      <c r="R6" s="94"/>
+      <c r="S6" s="94"/>
+      <c r="T6" s="94"/>
+      <c r="U6" s="94"/>
+      <c r="V6" s="94"/>
+      <c r="W6" s="94"/>
+      <c r="X6" s="94"/>
     </row>
     <row r="7" spans="1:24">
       <c r="A7" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B7" s="103" t="s">
+      <c r="B7" s="94" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="103"/>
-      <c r="D7" s="103"/>
-      <c r="E7" s="103"/>
-      <c r="F7" s="103"/>
-      <c r="G7" s="103"/>
-      <c r="H7" s="103"/>
-      <c r="I7" s="104" t="s">
+      <c r="C7" s="94"/>
+      <c r="D7" s="94"/>
+      <c r="E7" s="94"/>
+      <c r="F7" s="94"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="94"/>
+      <c r="I7" s="96" t="s">
         <v>107</v>
       </c>
-      <c r="J7" s="105"/>
-      <c r="K7" s="105"/>
-      <c r="L7" s="106"/>
-      <c r="M7" s="103"/>
-      <c r="N7" s="103"/>
-      <c r="O7" s="103"/>
-      <c r="P7" s="103"/>
-      <c r="Q7" s="103"/>
-      <c r="R7" s="103"/>
-      <c r="S7" s="103"/>
-      <c r="T7" s="103"/>
-      <c r="U7" s="103"/>
-      <c r="V7" s="103"/>
-      <c r="W7" s="103"/>
-      <c r="X7" s="103"/>
+      <c r="J7" s="97"/>
+      <c r="K7" s="97"/>
+      <c r="L7" s="98"/>
+      <c r="M7" s="94"/>
+      <c r="N7" s="94"/>
+      <c r="O7" s="94"/>
+      <c r="P7" s="94"/>
+      <c r="Q7" s="94"/>
+      <c r="R7" s="94"/>
+      <c r="S7" s="94"/>
+      <c r="T7" s="94"/>
+      <c r="U7" s="94"/>
+      <c r="V7" s="94"/>
+      <c r="W7" s="94"/>
+      <c r="X7" s="94"/>
     </row>
     <row r="8" spans="1:24">
       <c r="A8" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="103" t="s">
+      <c r="B8" s="94" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="103"/>
-      <c r="D8" s="103"/>
-      <c r="E8" s="103"/>
-      <c r="F8" s="103" t="s">
+      <c r="C8" s="94"/>
+      <c r="D8" s="94"/>
+      <c r="E8" s="94"/>
+      <c r="F8" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="G8" s="103"/>
-      <c r="H8" s="103"/>
-      <c r="I8" s="104" t="s">
+      <c r="G8" s="94"/>
+      <c r="H8" s="94"/>
+      <c r="I8" s="96" t="s">
         <v>27</v>
       </c>
-      <c r="J8" s="105"/>
-      <c r="K8" s="105"/>
-      <c r="L8" s="106"/>
-      <c r="M8" s="103" t="s">
+      <c r="J8" s="97"/>
+      <c r="K8" s="97"/>
+      <c r="L8" s="98"/>
+      <c r="M8" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="N8" s="103"/>
-      <c r="O8" s="103"/>
-      <c r="P8" s="103" t="s">
+      <c r="N8" s="94"/>
+      <c r="O8" s="94"/>
+      <c r="P8" s="94" t="s">
         <v>37</v>
       </c>
-      <c r="Q8" s="103"/>
-      <c r="R8" s="103"/>
-      <c r="S8" s="103"/>
-      <c r="T8" s="103"/>
-      <c r="U8" s="103"/>
-      <c r="V8" s="103"/>
-      <c r="W8" s="103"/>
-      <c r="X8" s="103"/>
+      <c r="Q8" s="94"/>
+      <c r="R8" s="94"/>
+      <c r="S8" s="94"/>
+      <c r="T8" s="94"/>
+      <c r="U8" s="94"/>
+      <c r="V8" s="94"/>
+      <c r="W8" s="94"/>
+      <c r="X8" s="94"/>
     </row>
     <row r="9" spans="1:24">
       <c r="A9" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="103" t="s">
+      <c r="B9" s="94" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="103"/>
-      <c r="D9" s="103"/>
-      <c r="E9" s="103"/>
-      <c r="F9" s="103"/>
-      <c r="G9" s="103"/>
-      <c r="H9" s="103"/>
-      <c r="I9" s="104" t="s">
+      <c r="C9" s="94"/>
+      <c r="D9" s="94"/>
+      <c r="E9" s="94"/>
+      <c r="F9" s="94"/>
+      <c r="G9" s="94"/>
+      <c r="H9" s="94"/>
+      <c r="I9" s="96" t="s">
         <v>29</v>
       </c>
-      <c r="J9" s="105"/>
-      <c r="K9" s="105"/>
-      <c r="L9" s="106"/>
-      <c r="M9" s="103"/>
-      <c r="N9" s="103"/>
-      <c r="O9" s="103"/>
-      <c r="P9" s="103"/>
-      <c r="Q9" s="103"/>
-      <c r="R9" s="103"/>
-      <c r="S9" s="103"/>
-      <c r="T9" s="103"/>
-      <c r="U9" s="103"/>
-      <c r="V9" s="103"/>
-      <c r="W9" s="103"/>
-      <c r="X9" s="103"/>
+      <c r="J9" s="97"/>
+      <c r="K9" s="97"/>
+      <c r="L9" s="98"/>
+      <c r="M9" s="94"/>
+      <c r="N9" s="94"/>
+      <c r="O9" s="94"/>
+      <c r="P9" s="94"/>
+      <c r="Q9" s="94"/>
+      <c r="R9" s="94"/>
+      <c r="S9" s="94"/>
+      <c r="T9" s="94"/>
+      <c r="U9" s="94"/>
+      <c r="V9" s="94"/>
+      <c r="W9" s="94"/>
+      <c r="X9" s="94"/>
     </row>
     <row r="10" spans="1:24">
       <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="103" t="s">
+      <c r="B10" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="103"/>
-      <c r="D10" s="103"/>
-      <c r="E10" s="103"/>
-      <c r="F10" s="103" t="s">
+      <c r="C10" s="94"/>
+      <c r="D10" s="94"/>
+      <c r="E10" s="94"/>
+      <c r="F10" s="94" t="s">
         <v>38</v>
       </c>
-      <c r="G10" s="103"/>
-      <c r="H10" s="103"/>
-      <c r="I10" s="104" t="s">
+      <c r="G10" s="94"/>
+      <c r="H10" s="94"/>
+      <c r="I10" s="96" t="s">
         <v>43</v>
       </c>
-      <c r="J10" s="105"/>
-      <c r="K10" s="105"/>
-      <c r="L10" s="106"/>
-      <c r="M10" s="103" t="s">
+      <c r="J10" s="97"/>
+      <c r="K10" s="97"/>
+      <c r="L10" s="98"/>
+      <c r="M10" s="94" t="s">
         <v>39</v>
       </c>
-      <c r="N10" s="103"/>
-      <c r="O10" s="103"/>
-      <c r="P10" s="103"/>
-      <c r="Q10" s="103"/>
-      <c r="R10" s="103"/>
-      <c r="S10" s="103"/>
-      <c r="T10" s="103"/>
-      <c r="U10" s="103"/>
-      <c r="V10" s="103"/>
-      <c r="W10" s="103"/>
-      <c r="X10" s="103"/>
+      <c r="N10" s="94"/>
+      <c r="O10" s="94"/>
+      <c r="P10" s="94"/>
+      <c r="Q10" s="94"/>
+      <c r="R10" s="94"/>
+      <c r="S10" s="94"/>
+      <c r="T10" s="94"/>
+      <c r="U10" s="94"/>
+      <c r="V10" s="94"/>
+      <c r="W10" s="94"/>
+      <c r="X10" s="94"/>
     </row>
     <row r="11" spans="1:24">
       <c r="A11" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="103" t="s">
+      <c r="B11" s="94" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="103"/>
-      <c r="D11" s="103"/>
-      <c r="E11" s="103"/>
-      <c r="F11" s="103"/>
-      <c r="G11" s="103"/>
-      <c r="H11" s="103"/>
-      <c r="I11" s="104" t="s">
+      <c r="C11" s="94"/>
+      <c r="D11" s="94"/>
+      <c r="E11" s="94"/>
+      <c r="F11" s="94"/>
+      <c r="G11" s="94"/>
+      <c r="H11" s="94"/>
+      <c r="I11" s="96" t="s">
         <v>52</v>
       </c>
-      <c r="J11" s="105"/>
-      <c r="K11" s="105"/>
-      <c r="L11" s="106"/>
-      <c r="M11" s="103"/>
-      <c r="N11" s="103"/>
-      <c r="O11" s="103"/>
-      <c r="P11" s="103" t="s">
+      <c r="J11" s="97"/>
+      <c r="K11" s="97"/>
+      <c r="L11" s="98"/>
+      <c r="M11" s="94"/>
+      <c r="N11" s="94"/>
+      <c r="O11" s="94"/>
+      <c r="P11" s="94" t="s">
         <v>53</v>
       </c>
-      <c r="Q11" s="103"/>
-      <c r="R11" s="103"/>
-      <c r="S11" s="103"/>
-      <c r="T11" s="103"/>
-      <c r="U11" s="103"/>
-      <c r="V11" s="103"/>
-      <c r="W11" s="103"/>
-      <c r="X11" s="103"/>
+      <c r="Q11" s="94"/>
+      <c r="R11" s="94"/>
+      <c r="S11" s="94"/>
+      <c r="T11" s="94"/>
+      <c r="U11" s="94"/>
+      <c r="V11" s="94"/>
+      <c r="W11" s="94"/>
+      <c r="X11" s="94"/>
     </row>
     <row r="12" spans="1:24" ht="34.5" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B12" s="103" t="s">
+      <c r="B12" s="94" t="s">
         <v>92</v>
       </c>
-      <c r="C12" s="103"/>
-      <c r="D12" s="103"/>
-      <c r="E12" s="103"/>
-      <c r="F12" s="103" t="s">
+      <c r="C12" s="94"/>
+      <c r="D12" s="94"/>
+      <c r="E12" s="94"/>
+      <c r="F12" s="94" t="s">
         <v>97</v>
       </c>
-      <c r="G12" s="103"/>
-      <c r="H12" s="103"/>
-      <c r="I12" s="104" t="s">
+      <c r="G12" s="94"/>
+      <c r="H12" s="94"/>
+      <c r="I12" s="96" t="s">
         <v>98</v>
       </c>
-      <c r="J12" s="105"/>
-      <c r="K12" s="105"/>
-      <c r="L12" s="106"/>
-      <c r="M12" s="102" t="s">
+      <c r="J12" s="97"/>
+      <c r="K12" s="97"/>
+      <c r="L12" s="98"/>
+      <c r="M12" s="95" t="s">
         <v>99</v>
       </c>
-      <c r="N12" s="103"/>
-      <c r="O12" s="103"/>
-      <c r="P12" s="103"/>
-      <c r="Q12" s="103"/>
-      <c r="R12" s="103"/>
-      <c r="S12" s="103"/>
-      <c r="T12" s="103"/>
-      <c r="U12" s="103"/>
-      <c r="V12" s="103"/>
-      <c r="W12" s="103"/>
-      <c r="X12" s="103"/>
+      <c r="N12" s="94"/>
+      <c r="O12" s="94"/>
+      <c r="P12" s="94"/>
+      <c r="Q12" s="94"/>
+      <c r="R12" s="94"/>
+      <c r="S12" s="94"/>
+      <c r="T12" s="94"/>
+      <c r="U12" s="94"/>
+      <c r="V12" s="94"/>
+      <c r="W12" s="94"/>
+      <c r="X12" s="94"/>
     </row>
     <row r="13" spans="1:24">
       <c r="A13" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B13" s="103"/>
-      <c r="C13" s="103"/>
-      <c r="D13" s="103"/>
-      <c r="E13" s="103"/>
-      <c r="F13" s="103" t="s">
+      <c r="B13" s="94"/>
+      <c r="C13" s="94"/>
+      <c r="D13" s="94"/>
+      <c r="E13" s="94"/>
+      <c r="F13" s="94" t="s">
         <v>100</v>
       </c>
-      <c r="G13" s="103"/>
-      <c r="H13" s="103"/>
-      <c r="I13" s="104"/>
-      <c r="J13" s="105"/>
-      <c r="K13" s="105"/>
-      <c r="L13" s="106"/>
-      <c r="M13" s="102" t="s">
+      <c r="G13" s="94"/>
+      <c r="H13" s="94"/>
+      <c r="I13" s="96"/>
+      <c r="J13" s="97"/>
+      <c r="K13" s="97"/>
+      <c r="L13" s="98"/>
+      <c r="M13" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="N13" s="103"/>
-      <c r="O13" s="103"/>
-      <c r="P13" s="103"/>
-      <c r="Q13" s="103"/>
-      <c r="R13" s="103"/>
-      <c r="S13" s="103"/>
-      <c r="T13" s="103"/>
-      <c r="U13" s="103"/>
-      <c r="V13" s="103"/>
-      <c r="W13" s="103"/>
-      <c r="X13" s="103"/>
+      <c r="N13" s="94"/>
+      <c r="O13" s="94"/>
+      <c r="P13" s="94"/>
+      <c r="Q13" s="94"/>
+      <c r="R13" s="94"/>
+      <c r="S13" s="94"/>
+      <c r="T13" s="94"/>
+      <c r="U13" s="94"/>
+      <c r="V13" s="94"/>
+      <c r="W13" s="94"/>
+      <c r="X13" s="94"/>
     </row>
     <row r="14" spans="1:24">
       <c r="A14" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B14" s="103"/>
-      <c r="C14" s="103"/>
-      <c r="D14" s="103"/>
-      <c r="E14" s="103"/>
-      <c r="F14" s="103" t="s">
+      <c r="B14" s="94"/>
+      <c r="C14" s="94"/>
+      <c r="D14" s="94"/>
+      <c r="E14" s="94"/>
+      <c r="F14" s="94" t="s">
         <v>100</v>
       </c>
-      <c r="G14" s="103"/>
-      <c r="H14" s="103"/>
-      <c r="I14" s="104"/>
-      <c r="J14" s="105"/>
-      <c r="K14" s="105"/>
-      <c r="L14" s="106"/>
-      <c r="M14" s="102" t="s">
+      <c r="G14" s="94"/>
+      <c r="H14" s="94"/>
+      <c r="I14" s="96"/>
+      <c r="J14" s="97"/>
+      <c r="K14" s="97"/>
+      <c r="L14" s="98"/>
+      <c r="M14" s="95" t="s">
         <v>103</v>
       </c>
-      <c r="N14" s="103"/>
-      <c r="O14" s="103"/>
-      <c r="P14" s="103"/>
-      <c r="Q14" s="103"/>
-      <c r="R14" s="103"/>
-      <c r="S14" s="103"/>
-      <c r="T14" s="103"/>
-      <c r="U14" s="103"/>
-      <c r="V14" s="103"/>
-      <c r="W14" s="103"/>
-      <c r="X14" s="103"/>
+      <c r="N14" s="94"/>
+      <c r="O14" s="94"/>
+      <c r="P14" s="94"/>
+      <c r="Q14" s="94"/>
+      <c r="R14" s="94"/>
+      <c r="S14" s="94"/>
+      <c r="T14" s="94"/>
+      <c r="U14" s="94"/>
+      <c r="V14" s="94"/>
+      <c r="W14" s="94"/>
+      <c r="X14" s="94"/>
     </row>
     <row r="15" spans="1:24">
       <c r="A15" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B15" s="103"/>
-      <c r="C15" s="103"/>
-      <c r="D15" s="103"/>
-      <c r="E15" s="103"/>
-      <c r="F15" s="103" t="s">
+      <c r="B15" s="94"/>
+      <c r="C15" s="94"/>
+      <c r="D15" s="94"/>
+      <c r="E15" s="94"/>
+      <c r="F15" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="G15" s="103"/>
-      <c r="H15" s="103"/>
-      <c r="I15" s="104"/>
-      <c r="J15" s="105"/>
-      <c r="K15" s="105"/>
-      <c r="L15" s="106"/>
-      <c r="M15" s="102" t="s">
+      <c r="G15" s="94"/>
+      <c r="H15" s="94"/>
+      <c r="I15" s="96"/>
+      <c r="J15" s="97"/>
+      <c r="K15" s="97"/>
+      <c r="L15" s="98"/>
+      <c r="M15" s="95" t="s">
         <v>104</v>
       </c>
-      <c r="N15" s="103"/>
-      <c r="O15" s="103"/>
-      <c r="P15" s="103"/>
-      <c r="Q15" s="103"/>
-      <c r="R15" s="103"/>
-      <c r="S15" s="103"/>
-      <c r="T15" s="103"/>
-      <c r="U15" s="103"/>
-      <c r="V15" s="103"/>
-      <c r="W15" s="103"/>
-      <c r="X15" s="103"/>
+      <c r="N15" s="94"/>
+      <c r="O15" s="94"/>
+      <c r="P15" s="94"/>
+      <c r="Q15" s="94"/>
+      <c r="R15" s="94"/>
+      <c r="S15" s="94"/>
+      <c r="T15" s="94"/>
+      <c r="U15" s="94"/>
+      <c r="V15" s="94"/>
+      <c r="W15" s="94"/>
+      <c r="X15" s="94"/>
     </row>
     <row r="16" spans="1:24">
       <c r="A16" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B16" s="103" t="s">
+      <c r="B16" s="94" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="103"/>
-      <c r="D16" s="103"/>
-      <c r="E16" s="103"/>
-      <c r="F16" s="103" t="s">
+      <c r="C16" s="94"/>
+      <c r="D16" s="94"/>
+      <c r="E16" s="94"/>
+      <c r="F16" s="94" t="s">
         <v>105</v>
       </c>
-      <c r="G16" s="103"/>
-      <c r="H16" s="103"/>
-      <c r="I16" s="104" t="s">
+      <c r="G16" s="94"/>
+      <c r="H16" s="94"/>
+      <c r="I16" s="96" t="s">
         <v>86</v>
       </c>
-      <c r="J16" s="105"/>
-      <c r="K16" s="105"/>
-      <c r="L16" s="106"/>
-      <c r="M16" s="103"/>
-      <c r="N16" s="103"/>
-      <c r="O16" s="103"/>
-      <c r="P16" s="103" t="s">
+      <c r="J16" s="97"/>
+      <c r="K16" s="97"/>
+      <c r="L16" s="98"/>
+      <c r="M16" s="94"/>
+      <c r="N16" s="94"/>
+      <c r="O16" s="94"/>
+      <c r="P16" s="94" t="s">
         <v>89</v>
       </c>
-      <c r="Q16" s="103"/>
-      <c r="R16" s="103"/>
-      <c r="S16" s="103"/>
-      <c r="T16" s="103"/>
-      <c r="U16" s="103"/>
-      <c r="V16" s="103"/>
-      <c r="W16" s="103"/>
-      <c r="X16" s="103"/>
+      <c r="Q16" s="94"/>
+      <c r="R16" s="94"/>
+      <c r="S16" s="94"/>
+      <c r="T16" s="94"/>
+      <c r="U16" s="94"/>
+      <c r="V16" s="94"/>
+      <c r="W16" s="94"/>
+      <c r="X16" s="94"/>
     </row>
     <row r="17" spans="1:24">
       <c r="A17" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="103" t="s">
+      <c r="B17" s="94" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="103"/>
-      <c r="D17" s="103"/>
-      <c r="E17" s="103"/>
-      <c r="F17" s="103"/>
-      <c r="G17" s="103"/>
-      <c r="H17" s="103"/>
-      <c r="I17" s="104" t="s">
+      <c r="C17" s="94"/>
+      <c r="D17" s="94"/>
+      <c r="E17" s="94"/>
+      <c r="F17" s="94"/>
+      <c r="G17" s="94"/>
+      <c r="H17" s="94"/>
+      <c r="I17" s="96" t="s">
         <v>55</v>
       </c>
-      <c r="J17" s="105"/>
-      <c r="K17" s="105"/>
-      <c r="L17" s="106"/>
-      <c r="M17" s="103"/>
-      <c r="N17" s="103"/>
-      <c r="O17" s="103"/>
-      <c r="P17" s="103" t="s">
+      <c r="J17" s="97"/>
+      <c r="K17" s="97"/>
+      <c r="L17" s="98"/>
+      <c r="M17" s="94"/>
+      <c r="N17" s="94"/>
+      <c r="O17" s="94"/>
+      <c r="P17" s="94" t="s">
         <v>56</v>
       </c>
-      <c r="Q17" s="103"/>
-      <c r="R17" s="103"/>
-      <c r="S17" s="103"/>
-      <c r="T17" s="103"/>
-      <c r="U17" s="103"/>
-      <c r="V17" s="103"/>
-      <c r="W17" s="103"/>
-      <c r="X17" s="103"/>
+      <c r="Q17" s="94"/>
+      <c r="R17" s="94"/>
+      <c r="S17" s="94"/>
+      <c r="T17" s="94"/>
+      <c r="U17" s="94"/>
+      <c r="V17" s="94"/>
+      <c r="W17" s="94"/>
+      <c r="X17" s="94"/>
     </row>
     <row r="18" spans="1:24">
       <c r="A18" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B18" s="103" t="s">
+      <c r="B18" s="94" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="103"/>
-      <c r="D18" s="103"/>
-      <c r="E18" s="103"/>
-      <c r="F18" s="103"/>
-      <c r="G18" s="103"/>
-      <c r="H18" s="103"/>
-      <c r="I18" s="104" t="s">
+      <c r="C18" s="94"/>
+      <c r="D18" s="94"/>
+      <c r="E18" s="94"/>
+      <c r="F18" s="94"/>
+      <c r="G18" s="94"/>
+      <c r="H18" s="94"/>
+      <c r="I18" s="96" t="s">
         <v>210</v>
       </c>
-      <c r="J18" s="105"/>
-      <c r="K18" s="105"/>
-      <c r="L18" s="106"/>
-      <c r="M18" s="103"/>
-      <c r="N18" s="103"/>
-      <c r="O18" s="103"/>
-      <c r="P18" s="103" t="s">
+      <c r="J18" s="97"/>
+      <c r="K18" s="97"/>
+      <c r="L18" s="98"/>
+      <c r="M18" s="94"/>
+      <c r="N18" s="94"/>
+      <c r="O18" s="94"/>
+      <c r="P18" s="94" t="s">
         <v>60</v>
       </c>
-      <c r="Q18" s="103"/>
-      <c r="R18" s="103"/>
-      <c r="S18" s="103"/>
-      <c r="T18" s="103"/>
-      <c r="U18" s="103"/>
-      <c r="V18" s="103"/>
-      <c r="W18" s="103"/>
-      <c r="X18" s="103"/>
+      <c r="Q18" s="94"/>
+      <c r="R18" s="94"/>
+      <c r="S18" s="94"/>
+      <c r="T18" s="94"/>
+      <c r="U18" s="94"/>
+      <c r="V18" s="94"/>
+      <c r="W18" s="94"/>
+      <c r="X18" s="94"/>
     </row>
     <row r="19" spans="1:24">
       <c r="A19" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B19" s="103" t="s">
+      <c r="B19" s="94" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="103"/>
-      <c r="D19" s="103"/>
-      <c r="E19" s="103"/>
-      <c r="F19" s="103"/>
-      <c r="G19" s="103"/>
-      <c r="H19" s="103"/>
-      <c r="I19" s="104" t="s">
+      <c r="C19" s="94"/>
+      <c r="D19" s="94"/>
+      <c r="E19" s="94"/>
+      <c r="F19" s="94"/>
+      <c r="G19" s="94"/>
+      <c r="H19" s="94"/>
+      <c r="I19" s="96" t="s">
         <v>62</v>
       </c>
-      <c r="J19" s="105"/>
-      <c r="K19" s="105"/>
-      <c r="L19" s="106"/>
-      <c r="M19" s="103"/>
-      <c r="N19" s="103"/>
-      <c r="O19" s="103"/>
-      <c r="P19" s="103" t="s">
+      <c r="J19" s="97"/>
+      <c r="K19" s="97"/>
+      <c r="L19" s="98"/>
+      <c r="M19" s="94"/>
+      <c r="N19" s="94"/>
+      <c r="O19" s="94"/>
+      <c r="P19" s="94" t="s">
         <v>61</v>
       </c>
-      <c r="Q19" s="103"/>
-      <c r="R19" s="103"/>
-      <c r="S19" s="103"/>
-      <c r="T19" s="103"/>
-      <c r="U19" s="103"/>
-      <c r="V19" s="103"/>
-      <c r="W19" s="103"/>
-      <c r="X19" s="103"/>
+      <c r="Q19" s="94"/>
+      <c r="R19" s="94"/>
+      <c r="S19" s="94"/>
+      <c r="T19" s="94"/>
+      <c r="U19" s="94"/>
+      <c r="V19" s="94"/>
+      <c r="W19" s="94"/>
+      <c r="X19" s="94"/>
     </row>
     <row r="20" spans="1:24" ht="45" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B20" s="103" t="s">
+      <c r="B20" s="94" t="s">
         <v>69</v>
       </c>
-      <c r="C20" s="103"/>
-      <c r="D20" s="103"/>
-      <c r="E20" s="103"/>
-      <c r="F20" s="102" t="s">
+      <c r="C20" s="94"/>
+      <c r="D20" s="94"/>
+      <c r="E20" s="94"/>
+      <c r="F20" s="95" t="s">
         <v>71</v>
       </c>
-      <c r="G20" s="103"/>
-      <c r="H20" s="103"/>
-      <c r="I20" s="113" t="s">
+      <c r="G20" s="94"/>
+      <c r="H20" s="94"/>
+      <c r="I20" s="99" t="s">
         <v>73</v>
       </c>
-      <c r="J20" s="114"/>
-      <c r="K20" s="114"/>
-      <c r="L20" s="115"/>
-      <c r="M20" s="102" t="s">
+      <c r="J20" s="100"/>
+      <c r="K20" s="100"/>
+      <c r="L20" s="101"/>
+      <c r="M20" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="N20" s="103"/>
-      <c r="O20" s="103"/>
-      <c r="P20" s="103"/>
-      <c r="Q20" s="103"/>
-      <c r="R20" s="103"/>
-      <c r="S20" s="103"/>
-      <c r="T20" s="103"/>
-      <c r="U20" s="103"/>
-      <c r="V20" s="103"/>
-      <c r="W20" s="103"/>
-      <c r="X20" s="103"/>
+      <c r="N20" s="94"/>
+      <c r="O20" s="94"/>
+      <c r="P20" s="94"/>
+      <c r="Q20" s="94"/>
+      <c r="R20" s="94"/>
+      <c r="S20" s="94"/>
+      <c r="T20" s="94"/>
+      <c r="U20" s="94"/>
+      <c r="V20" s="94"/>
+      <c r="W20" s="94"/>
+      <c r="X20" s="94"/>
     </row>
     <row r="21" spans="1:24" ht="61.5" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B21" s="102" t="s">
+      <c r="B21" s="95" t="s">
         <v>76</v>
       </c>
-      <c r="C21" s="103"/>
-      <c r="D21" s="103"/>
-      <c r="E21" s="103"/>
-      <c r="F21" s="103"/>
-      <c r="G21" s="103"/>
-      <c r="H21" s="103"/>
-      <c r="I21" s="104" t="s">
+      <c r="C21" s="94"/>
+      <c r="D21" s="94"/>
+      <c r="E21" s="94"/>
+      <c r="F21" s="94"/>
+      <c r="G21" s="94"/>
+      <c r="H21" s="94"/>
+      <c r="I21" s="96" t="s">
         <v>78</v>
       </c>
-      <c r="J21" s="105"/>
-      <c r="K21" s="105"/>
-      <c r="L21" s="106"/>
-      <c r="M21" s="102" t="s">
+      <c r="J21" s="97"/>
+      <c r="K21" s="97"/>
+      <c r="L21" s="98"/>
+      <c r="M21" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="N21" s="103"/>
-      <c r="O21" s="103"/>
-      <c r="P21" s="103" t="s">
+      <c r="N21" s="94"/>
+      <c r="O21" s="94"/>
+      <c r="P21" s="94" t="s">
         <v>75</v>
       </c>
-      <c r="Q21" s="103"/>
-      <c r="R21" s="103"/>
-      <c r="S21" s="103"/>
-      <c r="T21" s="103"/>
-      <c r="U21" s="103"/>
-      <c r="V21" s="103"/>
-      <c r="W21" s="103"/>
-      <c r="X21" s="103"/>
+      <c r="Q21" s="94"/>
+      <c r="R21" s="94"/>
+      <c r="S21" s="94"/>
+      <c r="T21" s="94"/>
+      <c r="U21" s="94"/>
+      <c r="V21" s="94"/>
+      <c r="W21" s="94"/>
+      <c r="X21" s="94"/>
     </row>
     <row r="22" spans="1:24">
       <c r="A22" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B22" s="103" t="s">
+      <c r="B22" s="94" t="s">
         <v>81</v>
       </c>
-      <c r="C22" s="103"/>
-      <c r="D22" s="103"/>
-      <c r="E22" s="103"/>
-      <c r="F22" s="103" t="s">
+      <c r="C22" s="94"/>
+      <c r="D22" s="94"/>
+      <c r="E22" s="94"/>
+      <c r="F22" s="94" t="s">
         <v>82</v>
       </c>
-      <c r="G22" s="103"/>
-      <c r="H22" s="103"/>
-      <c r="I22" s="104" t="s">
+      <c r="G22" s="94"/>
+      <c r="H22" s="94"/>
+      <c r="I22" s="96" t="s">
         <v>80</v>
       </c>
-      <c r="J22" s="105"/>
-      <c r="K22" s="105"/>
-      <c r="L22" s="106"/>
-      <c r="M22" s="103" t="s">
+      <c r="J22" s="97"/>
+      <c r="K22" s="97"/>
+      <c r="L22" s="98"/>
+      <c r="M22" s="94" t="s">
         <v>83</v>
       </c>
-      <c r="N22" s="103"/>
-      <c r="O22" s="103"/>
-      <c r="P22" s="103" t="s">
+      <c r="N22" s="94"/>
+      <c r="O22" s="94"/>
+      <c r="P22" s="94" t="s">
         <v>89</v>
       </c>
-      <c r="Q22" s="103"/>
-      <c r="R22" s="103"/>
-      <c r="S22" s="103"/>
-      <c r="T22" s="103"/>
-      <c r="U22" s="103"/>
-      <c r="V22" s="103"/>
-      <c r="W22" s="103"/>
-      <c r="X22" s="103"/>
+      <c r="Q22" s="94"/>
+      <c r="R22" s="94"/>
+      <c r="S22" s="94"/>
+      <c r="T22" s="94"/>
+      <c r="U22" s="94"/>
+      <c r="V22" s="94"/>
+      <c r="W22" s="94"/>
+      <c r="X22" s="94"/>
     </row>
     <row r="23" spans="1:24">
       <c r="A23" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B23" s="103" t="s">
+      <c r="B23" s="94" t="s">
         <v>88</v>
       </c>
-      <c r="C23" s="103"/>
-      <c r="D23" s="103"/>
-      <c r="E23" s="103"/>
-      <c r="F23" s="103"/>
-      <c r="G23" s="103"/>
-      <c r="H23" s="103"/>
-      <c r="I23" s="104" t="s">
+      <c r="C23" s="94"/>
+      <c r="D23" s="94"/>
+      <c r="E23" s="94"/>
+      <c r="F23" s="94"/>
+      <c r="G23" s="94"/>
+      <c r="H23" s="94"/>
+      <c r="I23" s="96" t="s">
         <v>84</v>
       </c>
-      <c r="J23" s="105"/>
-      <c r="K23" s="105"/>
-      <c r="L23" s="106"/>
-      <c r="M23" s="103"/>
-      <c r="N23" s="103"/>
-      <c r="O23" s="103"/>
-      <c r="P23" s="103" t="s">
+      <c r="J23" s="97"/>
+      <c r="K23" s="97"/>
+      <c r="L23" s="98"/>
+      <c r="M23" s="94"/>
+      <c r="N23" s="94"/>
+      <c r="O23" s="94"/>
+      <c r="P23" s="94" t="s">
         <v>89</v>
       </c>
-      <c r="Q23" s="103"/>
-      <c r="R23" s="103"/>
-      <c r="S23" s="103"/>
-      <c r="T23" s="103"/>
-      <c r="U23" s="103"/>
-      <c r="V23" s="103"/>
-      <c r="W23" s="103"/>
-      <c r="X23" s="103"/>
+      <c r="Q23" s="94"/>
+      <c r="R23" s="94"/>
+      <c r="S23" s="94"/>
+      <c r="T23" s="94"/>
+      <c r="U23" s="94"/>
+      <c r="V23" s="94"/>
+      <c r="W23" s="94"/>
+      <c r="X23" s="94"/>
     </row>
     <row r="24" spans="1:24">
       <c r="A24" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B24" s="103"/>
-      <c r="C24" s="103"/>
-      <c r="D24" s="103"/>
-      <c r="E24" s="103"/>
-      <c r="F24" s="103"/>
-      <c r="G24" s="103"/>
-      <c r="H24" s="103"/>
-      <c r="I24" s="104" t="s">
+      <c r="B24" s="94"/>
+      <c r="C24" s="94"/>
+      <c r="D24" s="94"/>
+      <c r="E24" s="94"/>
+      <c r="F24" s="94"/>
+      <c r="G24" s="94"/>
+      <c r="H24" s="94"/>
+      <c r="I24" s="96" t="s">
         <v>90</v>
       </c>
-      <c r="J24" s="105"/>
-      <c r="K24" s="105"/>
-      <c r="L24" s="106"/>
-      <c r="M24" s="103"/>
-      <c r="N24" s="103"/>
-      <c r="O24" s="103"/>
-      <c r="P24" s="103"/>
-      <c r="Q24" s="103"/>
-      <c r="R24" s="103"/>
-      <c r="S24" s="103"/>
-      <c r="T24" s="103"/>
-      <c r="U24" s="103"/>
-      <c r="V24" s="103"/>
-      <c r="W24" s="103"/>
-      <c r="X24" s="103"/>
+      <c r="J24" s="97"/>
+      <c r="K24" s="97"/>
+      <c r="L24" s="98"/>
+      <c r="M24" s="94"/>
+      <c r="N24" s="94"/>
+      <c r="O24" s="94"/>
+      <c r="P24" s="94"/>
+      <c r="Q24" s="94"/>
+      <c r="R24" s="94"/>
+      <c r="S24" s="94"/>
+      <c r="T24" s="94"/>
+      <c r="U24" s="94"/>
+      <c r="V24" s="94"/>
+      <c r="W24" s="94"/>
+      <c r="X24" s="94"/>
     </row>
     <row r="25" spans="1:24">
       <c r="A25" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B25" s="103"/>
-      <c r="C25" s="103"/>
-      <c r="D25" s="103"/>
-      <c r="E25" s="103"/>
-      <c r="F25" s="103" t="s">
+      <c r="B25" s="94"/>
+      <c r="C25" s="94"/>
+      <c r="D25" s="94"/>
+      <c r="E25" s="94"/>
+      <c r="F25" s="94" t="s">
         <v>109</v>
       </c>
-      <c r="G25" s="103"/>
-      <c r="H25" s="103"/>
-      <c r="I25" s="104" t="s">
+      <c r="G25" s="94"/>
+      <c r="H25" s="94"/>
+      <c r="I25" s="96" t="s">
         <v>112</v>
       </c>
-      <c r="J25" s="105"/>
-      <c r="K25" s="105"/>
-      <c r="L25" s="106"/>
-      <c r="M25" s="102" t="s">
+      <c r="J25" s="97"/>
+      <c r="K25" s="97"/>
+      <c r="L25" s="98"/>
+      <c r="M25" s="95" t="s">
         <v>110</v>
       </c>
-      <c r="N25" s="103"/>
-      <c r="O25" s="103"/>
-      <c r="P25" s="103" t="s">
+      <c r="N25" s="94"/>
+      <c r="O25" s="94"/>
+      <c r="P25" s="94" t="s">
         <v>111</v>
       </c>
-      <c r="Q25" s="103"/>
-      <c r="R25" s="103"/>
-      <c r="S25" s="103"/>
-      <c r="T25" s="103"/>
-      <c r="U25" s="103"/>
-      <c r="V25" s="103"/>
-      <c r="W25" s="103"/>
-      <c r="X25" s="103"/>
+      <c r="Q25" s="94"/>
+      <c r="R25" s="94"/>
+      <c r="S25" s="94"/>
+      <c r="T25" s="94"/>
+      <c r="U25" s="94"/>
+      <c r="V25" s="94"/>
+      <c r="W25" s="94"/>
+      <c r="X25" s="94"/>
     </row>
     <row r="26" spans="1:24" ht="45.75" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B26" s="103" t="s">
+      <c r="B26" s="94" t="s">
         <v>114</v>
       </c>
-      <c r="C26" s="103"/>
-      <c r="D26" s="103"/>
-      <c r="E26" s="103"/>
-      <c r="F26" s="102" t="s">
+      <c r="C26" s="94"/>
+      <c r="D26" s="94"/>
+      <c r="E26" s="94"/>
+      <c r="F26" s="95" t="s">
         <v>132</v>
       </c>
-      <c r="G26" s="103"/>
-      <c r="H26" s="103"/>
-      <c r="I26" s="104" t="s">
+      <c r="G26" s="94"/>
+      <c r="H26" s="94"/>
+      <c r="I26" s="96" t="s">
         <v>113</v>
       </c>
-      <c r="J26" s="105"/>
-      <c r="K26" s="105"/>
-      <c r="L26" s="106"/>
-      <c r="M26" s="102" t="s">
+      <c r="J26" s="97"/>
+      <c r="K26" s="97"/>
+      <c r="L26" s="98"/>
+      <c r="M26" s="95" t="s">
         <v>133</v>
       </c>
-      <c r="N26" s="103"/>
-      <c r="O26" s="103"/>
-      <c r="P26" s="102" t="s">
+      <c r="N26" s="94"/>
+      <c r="O26" s="94"/>
+      <c r="P26" s="95" t="s">
         <v>126</v>
       </c>
-      <c r="Q26" s="102"/>
-      <c r="R26" s="102"/>
-      <c r="S26" s="102"/>
-      <c r="T26" s="102"/>
-      <c r="U26" s="102"/>
-      <c r="V26" s="102"/>
-      <c r="W26" s="102"/>
-      <c r="X26" s="102"/>
+      <c r="Q26" s="95"/>
+      <c r="R26" s="95"/>
+      <c r="S26" s="95"/>
+      <c r="T26" s="95"/>
+      <c r="U26" s="95"/>
+      <c r="V26" s="95"/>
+      <c r="W26" s="95"/>
+      <c r="X26" s="95"/>
     </row>
     <row r="27" spans="1:24">
       <c r="A27" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B27" s="103"/>
-      <c r="C27" s="103"/>
-      <c r="D27" s="103"/>
-      <c r="E27" s="103"/>
-      <c r="F27" s="103"/>
-      <c r="G27" s="103"/>
-      <c r="H27" s="103"/>
-      <c r="I27" s="104" t="s">
+      <c r="B27" s="94"/>
+      <c r="C27" s="94"/>
+      <c r="D27" s="94"/>
+      <c r="E27" s="94"/>
+      <c r="F27" s="94"/>
+      <c r="G27" s="94"/>
+      <c r="H27" s="94"/>
+      <c r="I27" s="96" t="s">
         <v>117</v>
       </c>
-      <c r="J27" s="105"/>
-      <c r="K27" s="105"/>
-      <c r="L27" s="106"/>
-      <c r="M27" s="103"/>
-      <c r="N27" s="103"/>
-      <c r="O27" s="103"/>
-      <c r="P27" s="103"/>
-      <c r="Q27" s="103"/>
-      <c r="R27" s="103"/>
-      <c r="S27" s="103"/>
-      <c r="T27" s="103"/>
-      <c r="U27" s="103"/>
-      <c r="V27" s="103"/>
-      <c r="W27" s="103"/>
-      <c r="X27" s="103"/>
+      <c r="J27" s="97"/>
+      <c r="K27" s="97"/>
+      <c r="L27" s="98"/>
+      <c r="M27" s="94"/>
+      <c r="N27" s="94"/>
+      <c r="O27" s="94"/>
+      <c r="P27" s="94"/>
+      <c r="Q27" s="94"/>
+      <c r="R27" s="94"/>
+      <c r="S27" s="94"/>
+      <c r="T27" s="94"/>
+      <c r="U27" s="94"/>
+      <c r="V27" s="94"/>
+      <c r="W27" s="94"/>
+      <c r="X27" s="94"/>
     </row>
     <row r="28" spans="1:24">
       <c r="A28" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B28" s="103"/>
-      <c r="C28" s="103"/>
-      <c r="D28" s="103"/>
-      <c r="E28" s="103"/>
-      <c r="F28" s="103"/>
-      <c r="G28" s="103"/>
-      <c r="H28" s="103"/>
-      <c r="I28" s="104" t="s">
+      <c r="B28" s="94"/>
+      <c r="C28" s="94"/>
+      <c r="D28" s="94"/>
+      <c r="E28" s="94"/>
+      <c r="F28" s="94"/>
+      <c r="G28" s="94"/>
+      <c r="H28" s="94"/>
+      <c r="I28" s="96" t="s">
         <v>119</v>
       </c>
-      <c r="J28" s="105"/>
-      <c r="K28" s="105"/>
-      <c r="L28" s="106"/>
-      <c r="M28" s="103"/>
-      <c r="N28" s="103"/>
-      <c r="O28" s="103"/>
-      <c r="P28" s="103"/>
-      <c r="Q28" s="103"/>
-      <c r="R28" s="103"/>
-      <c r="S28" s="103"/>
-      <c r="T28" s="103"/>
-      <c r="U28" s="103"/>
-      <c r="V28" s="103"/>
-      <c r="W28" s="103"/>
-      <c r="X28" s="103"/>
+      <c r="J28" s="97"/>
+      <c r="K28" s="97"/>
+      <c r="L28" s="98"/>
+      <c r="M28" s="94"/>
+      <c r="N28" s="94"/>
+      <c r="O28" s="94"/>
+      <c r="P28" s="94"/>
+      <c r="Q28" s="94"/>
+      <c r="R28" s="94"/>
+      <c r="S28" s="94"/>
+      <c r="T28" s="94"/>
+      <c r="U28" s="94"/>
+      <c r="V28" s="94"/>
+      <c r="W28" s="94"/>
+      <c r="X28" s="94"/>
     </row>
     <row r="29" spans="1:24" ht="56.25" customHeight="1">
       <c r="A29" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B29" s="102" t="s">
+      <c r="B29" s="95" t="s">
         <v>125</v>
       </c>
-      <c r="C29" s="102"/>
-      <c r="D29" s="102"/>
-      <c r="E29" s="102"/>
-      <c r="F29" s="102" t="s">
+      <c r="C29" s="95"/>
+      <c r="D29" s="95"/>
+      <c r="E29" s="95"/>
+      <c r="F29" s="95" t="s">
         <v>120</v>
       </c>
-      <c r="G29" s="103"/>
-      <c r="H29" s="103"/>
-      <c r="I29" s="104" t="s">
+      <c r="G29" s="94"/>
+      <c r="H29" s="94"/>
+      <c r="I29" s="96" t="s">
         <v>122</v>
       </c>
-      <c r="J29" s="105"/>
-      <c r="K29" s="105"/>
-      <c r="L29" s="106"/>
-      <c r="M29" s="102" t="s">
+      <c r="J29" s="97"/>
+      <c r="K29" s="97"/>
+      <c r="L29" s="98"/>
+      <c r="M29" s="95" t="s">
         <v>123</v>
       </c>
-      <c r="N29" s="103"/>
-      <c r="O29" s="103"/>
-      <c r="P29" s="102" t="s">
+      <c r="N29" s="94"/>
+      <c r="O29" s="94"/>
+      <c r="P29" s="95" t="s">
         <v>124</v>
       </c>
-      <c r="Q29" s="102"/>
-      <c r="R29" s="102"/>
-      <c r="S29" s="102"/>
-      <c r="T29" s="102"/>
-      <c r="U29" s="102"/>
-      <c r="V29" s="102"/>
-      <c r="W29" s="102"/>
-      <c r="X29" s="102"/>
+      <c r="Q29" s="95"/>
+      <c r="R29" s="95"/>
+      <c r="S29" s="95"/>
+      <c r="T29" s="95"/>
+      <c r="U29" s="95"/>
+      <c r="V29" s="95"/>
+      <c r="W29" s="95"/>
+      <c r="X29" s="95"/>
     </row>
     <row r="30" spans="1:24">
       <c r="A30" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B30" s="103"/>
-      <c r="C30" s="103"/>
-      <c r="D30" s="103"/>
-      <c r="E30" s="103"/>
-      <c r="F30" s="103" t="s">
+      <c r="B30" s="94"/>
+      <c r="C30" s="94"/>
+      <c r="D30" s="94"/>
+      <c r="E30" s="94"/>
+      <c r="F30" s="94" t="s">
         <v>136</v>
       </c>
-      <c r="G30" s="103"/>
-      <c r="H30" s="103"/>
-      <c r="I30" s="104" t="s">
+      <c r="G30" s="94"/>
+      <c r="H30" s="94"/>
+      <c r="I30" s="96" t="s">
         <v>135</v>
       </c>
-      <c r="J30" s="105"/>
-      <c r="K30" s="105"/>
-      <c r="L30" s="106"/>
-      <c r="M30" s="103" t="s">
+      <c r="J30" s="97"/>
+      <c r="K30" s="97"/>
+      <c r="L30" s="98"/>
+      <c r="M30" s="94" t="s">
         <v>137</v>
       </c>
-      <c r="N30" s="103"/>
-      <c r="O30" s="103"/>
-      <c r="P30" s="103"/>
-      <c r="Q30" s="103"/>
-      <c r="R30" s="103"/>
-      <c r="S30" s="103"/>
-      <c r="T30" s="103"/>
-      <c r="U30" s="103"/>
-      <c r="V30" s="103"/>
-      <c r="W30" s="103"/>
-      <c r="X30" s="103"/>
+      <c r="N30" s="94"/>
+      <c r="O30" s="94"/>
+      <c r="P30" s="94"/>
+      <c r="Q30" s="94"/>
+      <c r="R30" s="94"/>
+      <c r="S30" s="94"/>
+      <c r="T30" s="94"/>
+      <c r="U30" s="94"/>
+      <c r="V30" s="94"/>
+      <c r="W30" s="94"/>
+      <c r="X30" s="94"/>
     </row>
     <row r="31" spans="1:24">
       <c r="A31" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B31" s="103" t="s">
+      <c r="B31" s="94" t="s">
         <v>144</v>
       </c>
-      <c r="C31" s="103"/>
-      <c r="D31" s="103"/>
-      <c r="E31" s="103"/>
-      <c r="F31" s="102" t="s">
+      <c r="C31" s="94"/>
+      <c r="D31" s="94"/>
+      <c r="E31" s="94"/>
+      <c r="F31" s="95" t="s">
         <v>143</v>
       </c>
-      <c r="G31" s="103"/>
-      <c r="H31" s="103"/>
-      <c r="I31" s="104" t="s">
+      <c r="G31" s="94"/>
+      <c r="H31" s="94"/>
+      <c r="I31" s="96" t="s">
         <v>145</v>
       </c>
-      <c r="J31" s="105"/>
-      <c r="K31" s="105"/>
-      <c r="L31" s="106"/>
-      <c r="M31" s="102" t="s">
+      <c r="J31" s="97"/>
+      <c r="K31" s="97"/>
+      <c r="L31" s="98"/>
+      <c r="M31" s="95" t="s">
         <v>146</v>
       </c>
-      <c r="N31" s="103"/>
-      <c r="O31" s="103"/>
-      <c r="P31" s="103"/>
-      <c r="Q31" s="103"/>
-      <c r="R31" s="103"/>
-      <c r="S31" s="103"/>
-      <c r="T31" s="103"/>
-      <c r="U31" s="103"/>
-      <c r="V31" s="103"/>
-      <c r="W31" s="103"/>
-      <c r="X31" s="103"/>
+      <c r="N31" s="94"/>
+      <c r="O31" s="94"/>
+      <c r="P31" s="94"/>
+      <c r="Q31" s="94"/>
+      <c r="R31" s="94"/>
+      <c r="S31" s="94"/>
+      <c r="T31" s="94"/>
+      <c r="U31" s="94"/>
+      <c r="V31" s="94"/>
+      <c r="W31" s="94"/>
+      <c r="X31" s="94"/>
     </row>
     <row r="32" spans="1:24">
       <c r="A32" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="B32" s="103"/>
-      <c r="C32" s="103"/>
-      <c r="D32" s="103"/>
-      <c r="E32" s="103"/>
-      <c r="F32" s="102" t="s">
+      <c r="B32" s="94"/>
+      <c r="C32" s="94"/>
+      <c r="D32" s="94"/>
+      <c r="E32" s="94"/>
+      <c r="F32" s="95" t="s">
         <v>203</v>
       </c>
-      <c r="G32" s="103"/>
-      <c r="H32" s="103"/>
-      <c r="I32" s="104"/>
-      <c r="J32" s="105"/>
-      <c r="K32" s="105"/>
-      <c r="L32" s="106"/>
-      <c r="M32" s="102" t="s">
+      <c r="G32" s="94"/>
+      <c r="H32" s="94"/>
+      <c r="I32" s="96"/>
+      <c r="J32" s="97"/>
+      <c r="K32" s="97"/>
+      <c r="L32" s="98"/>
+      <c r="M32" s="95" t="s">
         <v>204</v>
       </c>
-      <c r="N32" s="103"/>
-      <c r="O32" s="103"/>
-      <c r="P32" s="103" t="s">
+      <c r="N32" s="94"/>
+      <c r="O32" s="94"/>
+      <c r="P32" s="94" t="s">
         <v>209</v>
       </c>
-      <c r="Q32" s="103"/>
-      <c r="R32" s="103"/>
-      <c r="S32" s="103"/>
-      <c r="T32" s="103"/>
-      <c r="U32" s="103"/>
-      <c r="V32" s="103"/>
-      <c r="W32" s="103"/>
-      <c r="X32" s="103"/>
+      <c r="Q32" s="94"/>
+      <c r="R32" s="94"/>
+      <c r="S32" s="94"/>
+      <c r="T32" s="94"/>
+      <c r="U32" s="94"/>
+      <c r="V32" s="94"/>
+      <c r="W32" s="94"/>
+      <c r="X32" s="94"/>
     </row>
     <row r="33" spans="1:24">
       <c r="A33" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="B33" s="103"/>
-      <c r="C33" s="103"/>
-      <c r="D33" s="103"/>
-      <c r="E33" s="103"/>
-      <c r="F33" s="103" t="s">
+      <c r="B33" s="94"/>
+      <c r="C33" s="94"/>
+      <c r="D33" s="94"/>
+      <c r="E33" s="94"/>
+      <c r="F33" s="94" t="s">
         <v>206</v>
       </c>
-      <c r="G33" s="103"/>
-      <c r="H33" s="103"/>
-      <c r="I33" s="104"/>
-      <c r="J33" s="105"/>
-      <c r="K33" s="105"/>
-      <c r="L33" s="106"/>
-      <c r="M33" s="103" t="s">
+      <c r="G33" s="94"/>
+      <c r="H33" s="94"/>
+      <c r="I33" s="96"/>
+      <c r="J33" s="97"/>
+      <c r="K33" s="97"/>
+      <c r="L33" s="98"/>
+      <c r="M33" s="94" t="s">
         <v>205</v>
       </c>
-      <c r="N33" s="103"/>
-      <c r="O33" s="103"/>
-      <c r="P33" s="103"/>
-      <c r="Q33" s="103"/>
-      <c r="R33" s="103"/>
-      <c r="S33" s="103"/>
-      <c r="T33" s="103"/>
-      <c r="U33" s="103"/>
-      <c r="V33" s="103"/>
-      <c r="W33" s="103"/>
-      <c r="X33" s="103"/>
+      <c r="N33" s="94"/>
+      <c r="O33" s="94"/>
+      <c r="P33" s="94"/>
+      <c r="Q33" s="94"/>
+      <c r="R33" s="94"/>
+      <c r="S33" s="94"/>
+      <c r="T33" s="94"/>
+      <c r="U33" s="94"/>
+      <c r="V33" s="94"/>
+      <c r="W33" s="94"/>
+      <c r="X33" s="94"/>
     </row>
     <row r="34" spans="1:24">
       <c r="A34" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="B34" s="103" t="s">
+      <c r="B34" s="94" t="s">
         <v>370</v>
       </c>
-      <c r="C34" s="103"/>
-      <c r="D34" s="103"/>
-      <c r="E34" s="103"/>
-      <c r="F34" s="103"/>
-      <c r="G34" s="103"/>
-      <c r="H34" s="103"/>
-      <c r="I34" s="104" t="s">
+      <c r="C34" s="94"/>
+      <c r="D34" s="94"/>
+      <c r="E34" s="94"/>
+      <c r="F34" s="94"/>
+      <c r="G34" s="94"/>
+      <c r="H34" s="94"/>
+      <c r="I34" s="96" t="s">
         <v>369</v>
       </c>
-      <c r="J34" s="105"/>
-      <c r="K34" s="105"/>
-      <c r="L34" s="106"/>
-      <c r="M34" s="103"/>
-      <c r="N34" s="103"/>
-      <c r="O34" s="103"/>
-      <c r="P34" s="103"/>
-      <c r="Q34" s="103"/>
-      <c r="R34" s="103"/>
-      <c r="S34" s="103"/>
-      <c r="T34" s="103"/>
-      <c r="U34" s="103"/>
-      <c r="V34" s="103"/>
-      <c r="W34" s="103"/>
-      <c r="X34" s="103"/>
+      <c r="J34" s="97"/>
+      <c r="K34" s="97"/>
+      <c r="L34" s="98"/>
+      <c r="M34" s="94"/>
+      <c r="N34" s="94"/>
+      <c r="O34" s="94"/>
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="94"/>
+      <c r="S34" s="94"/>
+      <c r="T34" s="94"/>
+      <c r="U34" s="94"/>
+      <c r="V34" s="94"/>
+      <c r="W34" s="94"/>
+      <c r="X34" s="94"/>
     </row>
     <row r="35" spans="1:24">
       <c r="A35" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="B35" s="103" t="s">
+      <c r="B35" s="94" t="s">
         <v>372</v>
       </c>
-      <c r="C35" s="103"/>
-      <c r="D35" s="103"/>
-      <c r="E35" s="103"/>
-      <c r="F35" s="103"/>
-      <c r="G35" s="103"/>
-      <c r="H35" s="103"/>
-      <c r="I35" s="104" t="s">
+      <c r="C35" s="94"/>
+      <c r="D35" s="94"/>
+      <c r="E35" s="94"/>
+      <c r="F35" s="94"/>
+      <c r="G35" s="94"/>
+      <c r="H35" s="94"/>
+      <c r="I35" s="96" t="s">
         <v>372</v>
       </c>
-      <c r="J35" s="105"/>
-      <c r="K35" s="105"/>
-      <c r="L35" s="106"/>
-      <c r="M35" s="103"/>
-      <c r="N35" s="103"/>
-      <c r="O35" s="103"/>
-      <c r="P35" s="103" t="s">
+      <c r="J35" s="97"/>
+      <c r="K35" s="97"/>
+      <c r="L35" s="98"/>
+      <c r="M35" s="94"/>
+      <c r="N35" s="94"/>
+      <c r="O35" s="94"/>
+      <c r="P35" s="94" t="s">
         <v>374</v>
       </c>
-      <c r="Q35" s="103"/>
-      <c r="R35" s="103"/>
-      <c r="S35" s="103"/>
-      <c r="T35" s="103"/>
-      <c r="U35" s="103"/>
-      <c r="V35" s="103"/>
-      <c r="W35" s="103"/>
-      <c r="X35" s="103"/>
+      <c r="Q35" s="94"/>
+      <c r="R35" s="94"/>
+      <c r="S35" s="94"/>
+      <c r="T35" s="94"/>
+      <c r="U35" s="94"/>
+      <c r="V35" s="94"/>
+      <c r="W35" s="94"/>
+      <c r="X35" s="94"/>
     </row>
     <row r="36" spans="1:24">
       <c r="A36" s="3"/>
-      <c r="B36" s="103"/>
-      <c r="C36" s="103"/>
-      <c r="D36" s="103"/>
-      <c r="E36" s="103"/>
-      <c r="F36" s="103"/>
-      <c r="G36" s="103"/>
-      <c r="H36" s="103"/>
-      <c r="I36" s="104"/>
-      <c r="J36" s="105"/>
-      <c r="K36" s="105"/>
-      <c r="L36" s="106"/>
-      <c r="M36" s="103"/>
-      <c r="N36" s="103"/>
-      <c r="O36" s="103"/>
-      <c r="P36" s="103"/>
-      <c r="Q36" s="103"/>
-      <c r="R36" s="103"/>
-      <c r="S36" s="103"/>
-      <c r="T36" s="103"/>
-      <c r="U36" s="103"/>
-      <c r="V36" s="103"/>
-      <c r="W36" s="103"/>
-      <c r="X36" s="103"/>
+      <c r="B36" s="94"/>
+      <c r="C36" s="94"/>
+      <c r="D36" s="94"/>
+      <c r="E36" s="94"/>
+      <c r="F36" s="94"/>
+      <c r="G36" s="94"/>
+      <c r="H36" s="94"/>
+      <c r="I36" s="96"/>
+      <c r="J36" s="97"/>
+      <c r="K36" s="97"/>
+      <c r="L36" s="98"/>
+      <c r="M36" s="94"/>
+      <c r="N36" s="94"/>
+      <c r="O36" s="94"/>
+      <c r="P36" s="94"/>
+      <c r="Q36" s="94"/>
+      <c r="R36" s="94"/>
+      <c r="S36" s="94"/>
+      <c r="T36" s="94"/>
+      <c r="U36" s="94"/>
+      <c r="V36" s="94"/>
+      <c r="W36" s="94"/>
+      <c r="X36" s="94"/>
     </row>
     <row r="37" spans="1:24">
       <c r="A37" s="3"/>
-      <c r="B37" s="103"/>
-      <c r="C37" s="103"/>
-      <c r="D37" s="103"/>
-      <c r="E37" s="103"/>
-      <c r="F37" s="103"/>
-      <c r="G37" s="103"/>
-      <c r="H37" s="103"/>
-      <c r="I37" s="104"/>
-      <c r="J37" s="105"/>
-      <c r="K37" s="105"/>
-      <c r="L37" s="106"/>
-      <c r="M37" s="103"/>
-      <c r="N37" s="103"/>
-      <c r="O37" s="103"/>
-      <c r="P37" s="103"/>
-      <c r="Q37" s="103"/>
-      <c r="R37" s="103"/>
-      <c r="S37" s="103"/>
-      <c r="T37" s="103"/>
-      <c r="U37" s="103"/>
-      <c r="V37" s="103"/>
-      <c r="W37" s="103"/>
-      <c r="X37" s="103"/>
+      <c r="B37" s="94"/>
+      <c r="C37" s="94"/>
+      <c r="D37" s="94"/>
+      <c r="E37" s="94"/>
+      <c r="F37" s="94"/>
+      <c r="G37" s="94"/>
+      <c r="H37" s="94"/>
+      <c r="I37" s="96"/>
+      <c r="J37" s="97"/>
+      <c r="K37" s="97"/>
+      <c r="L37" s="98"/>
+      <c r="M37" s="94"/>
+      <c r="N37" s="94"/>
+      <c r="O37" s="94"/>
+      <c r="P37" s="94"/>
+      <c r="Q37" s="94"/>
+      <c r="R37" s="94"/>
+      <c r="S37" s="94"/>
+      <c r="T37" s="94"/>
+      <c r="U37" s="94"/>
+      <c r="V37" s="94"/>
+      <c r="W37" s="94"/>
+      <c r="X37" s="94"/>
     </row>
     <row r="38" spans="1:24">
       <c r="A38" s="3"/>
-      <c r="B38" s="103"/>
-      <c r="C38" s="103"/>
-      <c r="D38" s="103"/>
-      <c r="E38" s="103"/>
-      <c r="F38" s="103"/>
-      <c r="G38" s="103"/>
-      <c r="H38" s="103"/>
-      <c r="I38" s="104"/>
-      <c r="J38" s="105"/>
-      <c r="K38" s="105"/>
-      <c r="L38" s="106"/>
-      <c r="M38" s="103"/>
-      <c r="N38" s="103"/>
-      <c r="O38" s="103"/>
-      <c r="P38" s="103"/>
-      <c r="Q38" s="103"/>
-      <c r="R38" s="103"/>
-      <c r="S38" s="103"/>
-      <c r="T38" s="103"/>
-      <c r="U38" s="103"/>
-      <c r="V38" s="103"/>
-      <c r="W38" s="103"/>
-      <c r="X38" s="103"/>
+      <c r="B38" s="94"/>
+      <c r="C38" s="94"/>
+      <c r="D38" s="94"/>
+      <c r="E38" s="94"/>
+      <c r="F38" s="94"/>
+      <c r="G38" s="94"/>
+      <c r="H38" s="94"/>
+      <c r="I38" s="96"/>
+      <c r="J38" s="97"/>
+      <c r="K38" s="97"/>
+      <c r="L38" s="98"/>
+      <c r="M38" s="94"/>
+      <c r="N38" s="94"/>
+      <c r="O38" s="94"/>
+      <c r="P38" s="94"/>
+      <c r="Q38" s="94"/>
+      <c r="R38" s="94"/>
+      <c r="S38" s="94"/>
+      <c r="T38" s="94"/>
+      <c r="U38" s="94"/>
+      <c r="V38" s="94"/>
+      <c r="W38" s="94"/>
+      <c r="X38" s="94"/>
     </row>
     <row r="39" spans="1:24">
       <c r="A39" s="3"/>
-      <c r="B39" s="103"/>
-      <c r="C39" s="103"/>
-      <c r="D39" s="103"/>
-      <c r="E39" s="103"/>
-      <c r="F39" s="103"/>
-      <c r="G39" s="103"/>
-      <c r="H39" s="103"/>
-      <c r="I39" s="104"/>
-      <c r="J39" s="105"/>
-      <c r="K39" s="105"/>
-      <c r="L39" s="106"/>
-      <c r="M39" s="103"/>
-      <c r="N39" s="103"/>
-      <c r="O39" s="103"/>
-      <c r="P39" s="103"/>
-      <c r="Q39" s="103"/>
-      <c r="R39" s="103"/>
-      <c r="S39" s="103"/>
-      <c r="T39" s="103"/>
-      <c r="U39" s="103"/>
-      <c r="V39" s="103"/>
-      <c r="W39" s="103"/>
-      <c r="X39" s="103"/>
+      <c r="B39" s="94"/>
+      <c r="C39" s="94"/>
+      <c r="D39" s="94"/>
+      <c r="E39" s="94"/>
+      <c r="F39" s="94"/>
+      <c r="G39" s="94"/>
+      <c r="H39" s="94"/>
+      <c r="I39" s="96"/>
+      <c r="J39" s="97"/>
+      <c r="K39" s="97"/>
+      <c r="L39" s="98"/>
+      <c r="M39" s="94"/>
+      <c r="N39" s="94"/>
+      <c r="O39" s="94"/>
+      <c r="P39" s="94"/>
+      <c r="Q39" s="94"/>
+      <c r="R39" s="94"/>
+      <c r="S39" s="94"/>
+      <c r="T39" s="94"/>
+      <c r="U39" s="94"/>
+      <c r="V39" s="94"/>
+      <c r="W39" s="94"/>
+      <c r="X39" s="94"/>
     </row>
     <row r="40" spans="1:24">
       <c r="A40" s="3"/>
-      <c r="B40" s="103"/>
-      <c r="C40" s="103"/>
-      <c r="D40" s="103"/>
-      <c r="E40" s="103"/>
-      <c r="F40" s="103"/>
-      <c r="G40" s="103"/>
-      <c r="H40" s="103"/>
-      <c r="I40" s="104"/>
-      <c r="J40" s="105"/>
-      <c r="K40" s="105"/>
-      <c r="L40" s="106"/>
-      <c r="M40" s="103"/>
-      <c r="N40" s="103"/>
-      <c r="O40" s="103"/>
-      <c r="P40" s="103"/>
-      <c r="Q40" s="103"/>
-      <c r="R40" s="103"/>
-      <c r="S40" s="103"/>
-      <c r="T40" s="103"/>
-      <c r="U40" s="103"/>
-      <c r="V40" s="103"/>
-      <c r="W40" s="103"/>
-      <c r="X40" s="103"/>
+      <c r="B40" s="94"/>
+      <c r="C40" s="94"/>
+      <c r="D40" s="94"/>
+      <c r="E40" s="94"/>
+      <c r="F40" s="94"/>
+      <c r="G40" s="94"/>
+      <c r="H40" s="94"/>
+      <c r="I40" s="96"/>
+      <c r="J40" s="97"/>
+      <c r="K40" s="97"/>
+      <c r="L40" s="98"/>
+      <c r="M40" s="94"/>
+      <c r="N40" s="94"/>
+      <c r="O40" s="94"/>
+      <c r="P40" s="94"/>
+      <c r="Q40" s="94"/>
+      <c r="R40" s="94"/>
+      <c r="S40" s="94"/>
+      <c r="T40" s="94"/>
+      <c r="U40" s="94"/>
+      <c r="V40" s="94"/>
+      <c r="W40" s="94"/>
+      <c r="X40" s="94"/>
     </row>
     <row r="41" spans="1:24">
       <c r="A41" s="3"/>
-      <c r="B41" s="103"/>
-      <c r="C41" s="103"/>
-      <c r="D41" s="103"/>
-      <c r="E41" s="103"/>
-      <c r="F41" s="103"/>
-      <c r="G41" s="103"/>
-      <c r="H41" s="103"/>
-      <c r="I41" s="104"/>
-      <c r="J41" s="105"/>
-      <c r="K41" s="105"/>
-      <c r="L41" s="106"/>
-      <c r="M41" s="103"/>
-      <c r="N41" s="103"/>
-      <c r="O41" s="103"/>
-      <c r="P41" s="103"/>
-      <c r="Q41" s="103"/>
-      <c r="R41" s="103"/>
-      <c r="S41" s="103"/>
-      <c r="T41" s="103"/>
-      <c r="U41" s="103"/>
-      <c r="V41" s="103"/>
-      <c r="W41" s="103"/>
-      <c r="X41" s="103"/>
+      <c r="B41" s="94"/>
+      <c r="C41" s="94"/>
+      <c r="D41" s="94"/>
+      <c r="E41" s="94"/>
+      <c r="F41" s="94"/>
+      <c r="G41" s="94"/>
+      <c r="H41" s="94"/>
+      <c r="I41" s="96"/>
+      <c r="J41" s="97"/>
+      <c r="K41" s="97"/>
+      <c r="L41" s="98"/>
+      <c r="M41" s="94"/>
+      <c r="N41" s="94"/>
+      <c r="O41" s="94"/>
+      <c r="P41" s="94"/>
+      <c r="Q41" s="94"/>
+      <c r="R41" s="94"/>
+      <c r="S41" s="94"/>
+      <c r="T41" s="94"/>
+      <c r="U41" s="94"/>
+      <c r="V41" s="94"/>
+      <c r="W41" s="94"/>
+      <c r="X41" s="94"/>
     </row>
     <row r="42" spans="1:24">
       <c r="A42" s="3"/>
-      <c r="B42" s="103"/>
-      <c r="C42" s="103"/>
-      <c r="D42" s="103"/>
-      <c r="E42" s="103"/>
-      <c r="F42" s="103"/>
-      <c r="G42" s="103"/>
-      <c r="H42" s="103"/>
-      <c r="I42" s="104"/>
-      <c r="J42" s="105"/>
-      <c r="K42" s="105"/>
-      <c r="L42" s="106"/>
-      <c r="M42" s="103"/>
-      <c r="N42" s="103"/>
-      <c r="O42" s="103"/>
-      <c r="P42" s="103"/>
-      <c r="Q42" s="103"/>
-      <c r="R42" s="103"/>
-      <c r="S42" s="103"/>
-      <c r="T42" s="103"/>
-      <c r="U42" s="103"/>
-      <c r="V42" s="103"/>
-      <c r="W42" s="103"/>
-      <c r="X42" s="103"/>
+      <c r="B42" s="94"/>
+      <c r="C42" s="94"/>
+      <c r="D42" s="94"/>
+      <c r="E42" s="94"/>
+      <c r="F42" s="94"/>
+      <c r="G42" s="94"/>
+      <c r="H42" s="94"/>
+      <c r="I42" s="96"/>
+      <c r="J42" s="97"/>
+      <c r="K42" s="97"/>
+      <c r="L42" s="98"/>
+      <c r="M42" s="94"/>
+      <c r="N42" s="94"/>
+      <c r="O42" s="94"/>
+      <c r="P42" s="94"/>
+      <c r="Q42" s="94"/>
+      <c r="R42" s="94"/>
+      <c r="S42" s="94"/>
+      <c r="T42" s="94"/>
+      <c r="U42" s="94"/>
+      <c r="V42" s="94"/>
+      <c r="W42" s="94"/>
+      <c r="X42" s="94"/>
     </row>
     <row r="43" spans="1:24">
       <c r="A43" s="3"/>
-      <c r="B43" s="103"/>
-      <c r="C43" s="103"/>
-      <c r="D43" s="103"/>
-      <c r="E43" s="103"/>
-      <c r="F43" s="103"/>
-      <c r="G43" s="103"/>
-      <c r="H43" s="103"/>
-      <c r="I43" s="104"/>
-      <c r="J43" s="105"/>
-      <c r="K43" s="105"/>
-      <c r="L43" s="106"/>
-      <c r="M43" s="103"/>
-      <c r="N43" s="103"/>
-      <c r="O43" s="103"/>
-      <c r="P43" s="103"/>
-      <c r="Q43" s="103"/>
-      <c r="R43" s="103"/>
-      <c r="S43" s="103"/>
-      <c r="T43" s="103"/>
-      <c r="U43" s="103"/>
-      <c r="V43" s="103"/>
-      <c r="W43" s="103"/>
-      <c r="X43" s="103"/>
+      <c r="B43" s="94"/>
+      <c r="C43" s="94"/>
+      <c r="D43" s="94"/>
+      <c r="E43" s="94"/>
+      <c r="F43" s="94"/>
+      <c r="G43" s="94"/>
+      <c r="H43" s="94"/>
+      <c r="I43" s="96"/>
+      <c r="J43" s="97"/>
+      <c r="K43" s="97"/>
+      <c r="L43" s="98"/>
+      <c r="M43" s="94"/>
+      <c r="N43" s="94"/>
+      <c r="O43" s="94"/>
+      <c r="P43" s="94"/>
+      <c r="Q43" s="94"/>
+      <c r="R43" s="94"/>
+      <c r="S43" s="94"/>
+      <c r="T43" s="94"/>
+      <c r="U43" s="94"/>
+      <c r="V43" s="94"/>
+      <c r="W43" s="94"/>
+      <c r="X43" s="94"/>
     </row>
     <row r="44" spans="1:24">
       <c r="A44" s="3"/>
-      <c r="B44" s="103"/>
-      <c r="C44" s="103"/>
-      <c r="D44" s="103"/>
-      <c r="E44" s="103"/>
-      <c r="F44" s="103"/>
-      <c r="G44" s="103"/>
-      <c r="H44" s="103"/>
-      <c r="I44" s="104"/>
-      <c r="J44" s="105"/>
-      <c r="K44" s="105"/>
-      <c r="L44" s="106"/>
-      <c r="M44" s="103"/>
-      <c r="N44" s="103"/>
-      <c r="O44" s="103"/>
-      <c r="P44" s="103"/>
-      <c r="Q44" s="103"/>
-      <c r="R44" s="103"/>
-      <c r="S44" s="103"/>
-      <c r="T44" s="103"/>
-      <c r="U44" s="103"/>
-      <c r="V44" s="103"/>
-      <c r="W44" s="103"/>
-      <c r="X44" s="103"/>
+      <c r="B44" s="94"/>
+      <c r="C44" s="94"/>
+      <c r="D44" s="94"/>
+      <c r="E44" s="94"/>
+      <c r="F44" s="94"/>
+      <c r="G44" s="94"/>
+      <c r="H44" s="94"/>
+      <c r="I44" s="96"/>
+      <c r="J44" s="97"/>
+      <c r="K44" s="97"/>
+      <c r="L44" s="98"/>
+      <c r="M44" s="94"/>
+      <c r="N44" s="94"/>
+      <c r="O44" s="94"/>
+      <c r="P44" s="94"/>
+      <c r="Q44" s="94"/>
+      <c r="R44" s="94"/>
+      <c r="S44" s="94"/>
+      <c r="T44" s="94"/>
+      <c r="U44" s="94"/>
+      <c r="V44" s="94"/>
+      <c r="W44" s="94"/>
+      <c r="X44" s="94"/>
     </row>
     <row r="45" spans="1:24">
       <c r="A45" s="3"/>
-      <c r="B45" s="103"/>
-      <c r="C45" s="103"/>
-      <c r="D45" s="103"/>
-      <c r="E45" s="103"/>
-      <c r="F45" s="103"/>
-      <c r="G45" s="103"/>
-      <c r="H45" s="103"/>
-      <c r="I45" s="104"/>
-      <c r="J45" s="105"/>
-      <c r="K45" s="105"/>
-      <c r="L45" s="106"/>
-      <c r="M45" s="103"/>
-      <c r="N45" s="103"/>
-      <c r="O45" s="103"/>
-      <c r="P45" s="103"/>
-      <c r="Q45" s="103"/>
-      <c r="R45" s="103"/>
-      <c r="S45" s="103"/>
-      <c r="T45" s="103"/>
-      <c r="U45" s="103"/>
-      <c r="V45" s="103"/>
-      <c r="W45" s="103"/>
-      <c r="X45" s="103"/>
+      <c r="B45" s="94"/>
+      <c r="C45" s="94"/>
+      <c r="D45" s="94"/>
+      <c r="E45" s="94"/>
+      <c r="F45" s="94"/>
+      <c r="G45" s="94"/>
+      <c r="H45" s="94"/>
+      <c r="I45" s="96"/>
+      <c r="J45" s="97"/>
+      <c r="K45" s="97"/>
+      <c r="L45" s="98"/>
+      <c r="M45" s="94"/>
+      <c r="N45" s="94"/>
+      <c r="O45" s="94"/>
+      <c r="P45" s="94"/>
+      <c r="Q45" s="94"/>
+      <c r="R45" s="94"/>
+      <c r="S45" s="94"/>
+      <c r="T45" s="94"/>
+      <c r="U45" s="94"/>
+      <c r="V45" s="94"/>
+      <c r="W45" s="94"/>
+      <c r="X45" s="94"/>
     </row>
     <row r="46" spans="1:24">
       <c r="A46" s="3"/>
-      <c r="B46" s="103"/>
-      <c r="C46" s="103"/>
-      <c r="D46" s="103"/>
-      <c r="E46" s="103"/>
-      <c r="F46" s="103"/>
-      <c r="G46" s="103"/>
-      <c r="H46" s="103"/>
-      <c r="I46" s="104"/>
-      <c r="J46" s="105"/>
-      <c r="K46" s="105"/>
-      <c r="L46" s="106"/>
-      <c r="M46" s="103"/>
-      <c r="N46" s="103"/>
-      <c r="O46" s="103"/>
-      <c r="P46" s="103"/>
-      <c r="Q46" s="103"/>
-      <c r="R46" s="103"/>
-      <c r="S46" s="103"/>
-      <c r="T46" s="103"/>
-      <c r="U46" s="103"/>
-      <c r="V46" s="103"/>
-      <c r="W46" s="103"/>
-      <c r="X46" s="103"/>
+      <c r="B46" s="94"/>
+      <c r="C46" s="94"/>
+      <c r="D46" s="94"/>
+      <c r="E46" s="94"/>
+      <c r="F46" s="94"/>
+      <c r="G46" s="94"/>
+      <c r="H46" s="94"/>
+      <c r="I46" s="96"/>
+      <c r="J46" s="97"/>
+      <c r="K46" s="97"/>
+      <c r="L46" s="98"/>
+      <c r="M46" s="94"/>
+      <c r="N46" s="94"/>
+      <c r="O46" s="94"/>
+      <c r="P46" s="94"/>
+      <c r="Q46" s="94"/>
+      <c r="R46" s="94"/>
+      <c r="S46" s="94"/>
+      <c r="T46" s="94"/>
+      <c r="U46" s="94"/>
+      <c r="V46" s="94"/>
+      <c r="W46" s="94"/>
+      <c r="X46" s="94"/>
     </row>
     <row r="47" spans="1:24">
       <c r="A47" s="3"/>
-      <c r="B47" s="103"/>
-      <c r="C47" s="103"/>
-      <c r="D47" s="103"/>
-      <c r="E47" s="103"/>
-      <c r="F47" s="103"/>
-      <c r="G47" s="103"/>
-      <c r="H47" s="103"/>
-      <c r="I47" s="104"/>
-      <c r="J47" s="105"/>
-      <c r="K47" s="105"/>
-      <c r="L47" s="106"/>
-      <c r="M47" s="103"/>
-      <c r="N47" s="103"/>
-      <c r="O47" s="103"/>
-      <c r="P47" s="103"/>
-      <c r="Q47" s="103"/>
-      <c r="R47" s="103"/>
-      <c r="S47" s="103"/>
-      <c r="T47" s="103"/>
-      <c r="U47" s="103"/>
-      <c r="V47" s="103"/>
-      <c r="W47" s="103"/>
-      <c r="X47" s="103"/>
+      <c r="B47" s="94"/>
+      <c r="C47" s="94"/>
+      <c r="D47" s="94"/>
+      <c r="E47" s="94"/>
+      <c r="F47" s="94"/>
+      <c r="G47" s="94"/>
+      <c r="H47" s="94"/>
+      <c r="I47" s="96"/>
+      <c r="J47" s="97"/>
+      <c r="K47" s="97"/>
+      <c r="L47" s="98"/>
+      <c r="M47" s="94"/>
+      <c r="N47" s="94"/>
+      <c r="O47" s="94"/>
+      <c r="P47" s="94"/>
+      <c r="Q47" s="94"/>
+      <c r="R47" s="94"/>
+      <c r="S47" s="94"/>
+      <c r="T47" s="94"/>
+      <c r="U47" s="94"/>
+      <c r="V47" s="94"/>
+      <c r="W47" s="94"/>
+      <c r="X47" s="94"/>
     </row>
     <row r="48" spans="1:24">
       <c r="A48" s="3"/>
-      <c r="B48" s="103"/>
-      <c r="C48" s="103"/>
-      <c r="D48" s="103"/>
-      <c r="E48" s="103"/>
-      <c r="F48" s="103"/>
-      <c r="G48" s="103"/>
-      <c r="H48" s="103"/>
-      <c r="I48" s="104"/>
-      <c r="J48" s="105"/>
-      <c r="K48" s="105"/>
-      <c r="L48" s="106"/>
-      <c r="M48" s="103"/>
-      <c r="N48" s="103"/>
-      <c r="O48" s="103"/>
-      <c r="P48" s="103"/>
-      <c r="Q48" s="103"/>
-      <c r="R48" s="103"/>
-      <c r="S48" s="103"/>
-      <c r="T48" s="103"/>
-      <c r="U48" s="103"/>
-      <c r="V48" s="103"/>
-      <c r="W48" s="103"/>
-      <c r="X48" s="103"/>
+      <c r="B48" s="94"/>
+      <c r="C48" s="94"/>
+      <c r="D48" s="94"/>
+      <c r="E48" s="94"/>
+      <c r="F48" s="94"/>
+      <c r="G48" s="94"/>
+      <c r="H48" s="94"/>
+      <c r="I48" s="96"/>
+      <c r="J48" s="97"/>
+      <c r="K48" s="97"/>
+      <c r="L48" s="98"/>
+      <c r="M48" s="94"/>
+      <c r="N48" s="94"/>
+      <c r="O48" s="94"/>
+      <c r="P48" s="94"/>
+      <c r="Q48" s="94"/>
+      <c r="R48" s="94"/>
+      <c r="S48" s="94"/>
+      <c r="T48" s="94"/>
+      <c r="U48" s="94"/>
+      <c r="V48" s="94"/>
+      <c r="W48" s="94"/>
+      <c r="X48" s="94"/>
     </row>
     <row r="49" spans="1:24">
       <c r="A49" s="3"/>
-      <c r="B49" s="103"/>
-      <c r="C49" s="103"/>
-      <c r="D49" s="103"/>
-      <c r="E49" s="103"/>
-      <c r="F49" s="103"/>
-      <c r="G49" s="103"/>
-      <c r="H49" s="103"/>
-      <c r="I49" s="104"/>
-      <c r="J49" s="105"/>
-      <c r="K49" s="105"/>
-      <c r="L49" s="106"/>
-      <c r="M49" s="103"/>
-      <c r="N49" s="103"/>
-      <c r="O49" s="103"/>
-      <c r="P49" s="103"/>
-      <c r="Q49" s="103"/>
-      <c r="R49" s="103"/>
-      <c r="S49" s="103"/>
-      <c r="T49" s="103"/>
-      <c r="U49" s="103"/>
-      <c r="V49" s="103"/>
-      <c r="W49" s="103"/>
-      <c r="X49" s="103"/>
+      <c r="B49" s="94"/>
+      <c r="C49" s="94"/>
+      <c r="D49" s="94"/>
+      <c r="E49" s="94"/>
+      <c r="F49" s="94"/>
+      <c r="G49" s="94"/>
+      <c r="H49" s="94"/>
+      <c r="I49" s="96"/>
+      <c r="J49" s="97"/>
+      <c r="K49" s="97"/>
+      <c r="L49" s="98"/>
+      <c r="M49" s="94"/>
+      <c r="N49" s="94"/>
+      <c r="O49" s="94"/>
+      <c r="P49" s="94"/>
+      <c r="Q49" s="94"/>
+      <c r="R49" s="94"/>
+      <c r="S49" s="94"/>
+      <c r="T49" s="94"/>
+      <c r="U49" s="94"/>
+      <c r="V49" s="94"/>
+      <c r="W49" s="94"/>
+      <c r="X49" s="94"/>
     </row>
     <row r="50" spans="1:24">
       <c r="A50" s="3"/>
-      <c r="B50" s="103"/>
-      <c r="C50" s="103"/>
-      <c r="D50" s="103"/>
-      <c r="E50" s="103"/>
-      <c r="F50" s="103"/>
-      <c r="G50" s="103"/>
-      <c r="H50" s="103"/>
-      <c r="I50" s="104"/>
-      <c r="J50" s="105"/>
-      <c r="K50" s="105"/>
-      <c r="L50" s="106"/>
-      <c r="M50" s="103"/>
-      <c r="N50" s="103"/>
-      <c r="O50" s="103"/>
-      <c r="P50" s="103"/>
-      <c r="Q50" s="103"/>
-      <c r="R50" s="103"/>
-      <c r="S50" s="103"/>
-      <c r="T50" s="103"/>
-      <c r="U50" s="103"/>
-      <c r="V50" s="103"/>
-      <c r="W50" s="103"/>
-      <c r="X50" s="103"/>
+      <c r="B50" s="94"/>
+      <c r="C50" s="94"/>
+      <c r="D50" s="94"/>
+      <c r="E50" s="94"/>
+      <c r="F50" s="94"/>
+      <c r="G50" s="94"/>
+      <c r="H50" s="94"/>
+      <c r="I50" s="96"/>
+      <c r="J50" s="97"/>
+      <c r="K50" s="97"/>
+      <c r="L50" s="98"/>
+      <c r="M50" s="94"/>
+      <c r="N50" s="94"/>
+      <c r="O50" s="94"/>
+      <c r="P50" s="94"/>
+      <c r="Q50" s="94"/>
+      <c r="R50" s="94"/>
+      <c r="S50" s="94"/>
+      <c r="T50" s="94"/>
+      <c r="U50" s="94"/>
+      <c r="V50" s="94"/>
+      <c r="W50" s="94"/>
+      <c r="X50" s="94"/>
     </row>
     <row r="51" spans="1:24">
       <c r="A51" s="3"/>
-      <c r="B51" s="103"/>
-      <c r="C51" s="103"/>
-      <c r="D51" s="103"/>
-      <c r="E51" s="103"/>
-      <c r="F51" s="103"/>
-      <c r="G51" s="103"/>
-      <c r="H51" s="103"/>
-      <c r="I51" s="104"/>
-      <c r="J51" s="105"/>
-      <c r="K51" s="105"/>
-      <c r="L51" s="106"/>
-      <c r="M51" s="103"/>
-      <c r="N51" s="103"/>
-      <c r="O51" s="103"/>
-      <c r="P51" s="103"/>
-      <c r="Q51" s="103"/>
-      <c r="R51" s="103"/>
-      <c r="S51" s="103"/>
-      <c r="T51" s="103"/>
-      <c r="U51" s="103"/>
-      <c r="V51" s="103"/>
-      <c r="W51" s="103"/>
-      <c r="X51" s="103"/>
+      <c r="B51" s="94"/>
+      <c r="C51" s="94"/>
+      <c r="D51" s="94"/>
+      <c r="E51" s="94"/>
+      <c r="F51" s="94"/>
+      <c r="G51" s="94"/>
+      <c r="H51" s="94"/>
+      <c r="I51" s="96"/>
+      <c r="J51" s="97"/>
+      <c r="K51" s="97"/>
+      <c r="L51" s="98"/>
+      <c r="M51" s="94"/>
+      <c r="N51" s="94"/>
+      <c r="O51" s="94"/>
+      <c r="P51" s="94"/>
+      <c r="Q51" s="94"/>
+      <c r="R51" s="94"/>
+      <c r="S51" s="94"/>
+      <c r="T51" s="94"/>
+      <c r="U51" s="94"/>
+      <c r="V51" s="94"/>
+      <c r="W51" s="94"/>
+      <c r="X51" s="94"/>
     </row>
     <row r="52" spans="1:24">
       <c r="A52" s="3"/>
-      <c r="B52" s="103"/>
-      <c r="C52" s="103"/>
-      <c r="D52" s="103"/>
-      <c r="E52" s="103"/>
-      <c r="F52" s="103"/>
-      <c r="G52" s="103"/>
-      <c r="H52" s="103"/>
-      <c r="I52" s="104"/>
-      <c r="J52" s="105"/>
-      <c r="K52" s="105"/>
-      <c r="L52" s="106"/>
-      <c r="M52" s="103"/>
-      <c r="N52" s="103"/>
-      <c r="O52" s="103"/>
-      <c r="P52" s="103"/>
-      <c r="Q52" s="103"/>
-      <c r="R52" s="103"/>
-      <c r="S52" s="103"/>
-      <c r="T52" s="103"/>
-      <c r="U52" s="103"/>
-      <c r="V52" s="103"/>
-      <c r="W52" s="103"/>
-      <c r="X52" s="103"/>
+      <c r="B52" s="94"/>
+      <c r="C52" s="94"/>
+      <c r="D52" s="94"/>
+      <c r="E52" s="94"/>
+      <c r="F52" s="94"/>
+      <c r="G52" s="94"/>
+      <c r="H52" s="94"/>
+      <c r="I52" s="96"/>
+      <c r="J52" s="97"/>
+      <c r="K52" s="97"/>
+      <c r="L52" s="98"/>
+      <c r="M52" s="94"/>
+      <c r="N52" s="94"/>
+      <c r="O52" s="94"/>
+      <c r="P52" s="94"/>
+      <c r="Q52" s="94"/>
+      <c r="R52" s="94"/>
+      <c r="S52" s="94"/>
+      <c r="T52" s="94"/>
+      <c r="U52" s="94"/>
+      <c r="V52" s="94"/>
+      <c r="W52" s="94"/>
+      <c r="X52" s="94"/>
     </row>
     <row r="53" spans="1:24">
       <c r="A53" s="3"/>
-      <c r="B53" s="103"/>
-      <c r="C53" s="103"/>
-      <c r="D53" s="103"/>
-      <c r="E53" s="103"/>
-      <c r="F53" s="103"/>
-      <c r="G53" s="103"/>
-      <c r="H53" s="103"/>
-      <c r="I53" s="103"/>
-      <c r="J53" s="103"/>
-      <c r="K53" s="103"/>
-      <c r="L53" s="103"/>
-      <c r="M53" s="103"/>
-      <c r="N53" s="103"/>
-      <c r="O53" s="103"/>
-      <c r="P53" s="103"/>
-      <c r="Q53" s="103"/>
-      <c r="R53" s="103"/>
-      <c r="S53" s="103"/>
-      <c r="T53" s="103"/>
-      <c r="U53" s="103"/>
-      <c r="V53" s="103"/>
-      <c r="W53" s="103"/>
-      <c r="X53" s="103"/>
+      <c r="B53" s="94"/>
+      <c r="C53" s="94"/>
+      <c r="D53" s="94"/>
+      <c r="E53" s="94"/>
+      <c r="F53" s="94"/>
+      <c r="G53" s="94"/>
+      <c r="H53" s="94"/>
+      <c r="I53" s="94"/>
+      <c r="J53" s="94"/>
+      <c r="K53" s="94"/>
+      <c r="L53" s="94"/>
+      <c r="M53" s="94"/>
+      <c r="N53" s="94"/>
+      <c r="O53" s="94"/>
+      <c r="P53" s="94"/>
+      <c r="Q53" s="94"/>
+      <c r="R53" s="94"/>
+      <c r="S53" s="94"/>
+      <c r="T53" s="94"/>
+      <c r="U53" s="94"/>
+      <c r="V53" s="94"/>
+      <c r="W53" s="94"/>
+      <c r="X53" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="256">
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="M20:O20"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="M5:O5"/>
+    <mergeCell ref="M6:O6"/>
+    <mergeCell ref="M7:O7"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="M17:O17"/>
+    <mergeCell ref="M18:O18"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="M16:O16"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="M13:O13"/>
+    <mergeCell ref="M14:O14"/>
+    <mergeCell ref="M15:O15"/>
+    <mergeCell ref="M25:O25"/>
+    <mergeCell ref="M26:O26"/>
+    <mergeCell ref="M27:O27"/>
+    <mergeCell ref="M43:O43"/>
+    <mergeCell ref="P2:X3"/>
+    <mergeCell ref="P16:X16"/>
+    <mergeCell ref="M44:O44"/>
+    <mergeCell ref="M35:O35"/>
+    <mergeCell ref="M36:O36"/>
+    <mergeCell ref="M37:O37"/>
+    <mergeCell ref="M38:O38"/>
+    <mergeCell ref="M39:O39"/>
+    <mergeCell ref="M21:O21"/>
+    <mergeCell ref="M22:O22"/>
+    <mergeCell ref="M23:O23"/>
+    <mergeCell ref="M33:O33"/>
+    <mergeCell ref="M34:O34"/>
+    <mergeCell ref="M28:O28"/>
+    <mergeCell ref="M29:O29"/>
+    <mergeCell ref="M32:O32"/>
+    <mergeCell ref="M30:O30"/>
+    <mergeCell ref="M31:O31"/>
+    <mergeCell ref="M24:O24"/>
+    <mergeCell ref="P12:X12"/>
+    <mergeCell ref="M50:O50"/>
+    <mergeCell ref="M51:O51"/>
+    <mergeCell ref="M52:O52"/>
+    <mergeCell ref="M53:O53"/>
+    <mergeCell ref="I4:L4"/>
+    <mergeCell ref="I5:L5"/>
+    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="I7:L7"/>
+    <mergeCell ref="I8:L8"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="I10:L10"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="M45:O45"/>
+    <mergeCell ref="M46:O46"/>
+    <mergeCell ref="M47:O47"/>
+    <mergeCell ref="M48:O48"/>
+    <mergeCell ref="M49:O49"/>
+    <mergeCell ref="M40:O40"/>
+    <mergeCell ref="M41:O41"/>
+    <mergeCell ref="M42:O42"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="I43:L43"/>
+    <mergeCell ref="I51:L51"/>
+    <mergeCell ref="I52:L52"/>
+    <mergeCell ref="I53:L53"/>
+    <mergeCell ref="P4:X4"/>
+    <mergeCell ref="P5:X5"/>
+    <mergeCell ref="P6:X6"/>
+    <mergeCell ref="P7:X7"/>
+    <mergeCell ref="P8:X8"/>
+    <mergeCell ref="P9:X9"/>
+    <mergeCell ref="P10:X10"/>
+    <mergeCell ref="P11:X11"/>
+    <mergeCell ref="P17:X17"/>
+    <mergeCell ref="P18:X18"/>
+    <mergeCell ref="P19:X19"/>
+    <mergeCell ref="P20:X20"/>
+    <mergeCell ref="I45:L45"/>
+    <mergeCell ref="I46:L46"/>
+    <mergeCell ref="I47:L47"/>
+    <mergeCell ref="I48:L48"/>
+    <mergeCell ref="I49:L49"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="I41:L41"/>
+    <mergeCell ref="I42:L42"/>
+    <mergeCell ref="I44:L44"/>
+    <mergeCell ref="P13:X13"/>
+    <mergeCell ref="P14:X14"/>
+    <mergeCell ref="P15:X15"/>
+    <mergeCell ref="P25:X25"/>
+    <mergeCell ref="P26:X26"/>
+    <mergeCell ref="P27:X27"/>
+    <mergeCell ref="P43:X43"/>
+    <mergeCell ref="I50:L50"/>
+    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="I36:L36"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="I33:L33"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="P44:X44"/>
+    <mergeCell ref="P35:X35"/>
+    <mergeCell ref="P36:X36"/>
+    <mergeCell ref="P37:X37"/>
+    <mergeCell ref="P38:X38"/>
+    <mergeCell ref="P39:X39"/>
+    <mergeCell ref="P21:X21"/>
+    <mergeCell ref="P22:X22"/>
+    <mergeCell ref="P23:X23"/>
+    <mergeCell ref="P33:X33"/>
+    <mergeCell ref="P34:X34"/>
+    <mergeCell ref="P28:X28"/>
+    <mergeCell ref="P29:X29"/>
+    <mergeCell ref="P32:X32"/>
+    <mergeCell ref="P30:X30"/>
+    <mergeCell ref="P31:X31"/>
+    <mergeCell ref="P24:X24"/>
+    <mergeCell ref="P50:X50"/>
+    <mergeCell ref="P51:X51"/>
+    <mergeCell ref="P52:X52"/>
+    <mergeCell ref="P53:X53"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="P45:X45"/>
+    <mergeCell ref="P46:X46"/>
+    <mergeCell ref="P47:X47"/>
+    <mergeCell ref="P48:X48"/>
+    <mergeCell ref="P49:X49"/>
+    <mergeCell ref="P40:X40"/>
+    <mergeCell ref="P41:X41"/>
+    <mergeCell ref="P42:X42"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="F44:H44"/>
+    <mergeCell ref="F45:H45"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F31:H31"/>
     <mergeCell ref="F51:H51"/>
     <mergeCell ref="F52:H52"/>
     <mergeCell ref="F53:H53"/>
@@ -10790,238 +11022,6 @@
     <mergeCell ref="F41:H41"/>
     <mergeCell ref="F42:H42"/>
     <mergeCell ref="F43:H43"/>
-    <mergeCell ref="F44:H44"/>
-    <mergeCell ref="F45:H45"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="P50:X50"/>
-    <mergeCell ref="P51:X51"/>
-    <mergeCell ref="P52:X52"/>
-    <mergeCell ref="P53:X53"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="P45:X45"/>
-    <mergeCell ref="P46:X46"/>
-    <mergeCell ref="P47:X47"/>
-    <mergeCell ref="P48:X48"/>
-    <mergeCell ref="P49:X49"/>
-    <mergeCell ref="P40:X40"/>
-    <mergeCell ref="P41:X41"/>
-    <mergeCell ref="P42:X42"/>
-    <mergeCell ref="P35:X35"/>
-    <mergeCell ref="P36:X36"/>
-    <mergeCell ref="P37:X37"/>
-    <mergeCell ref="P38:X38"/>
-    <mergeCell ref="P39:X39"/>
-    <mergeCell ref="P21:X21"/>
-    <mergeCell ref="P22:X22"/>
-    <mergeCell ref="P23:X23"/>
-    <mergeCell ref="P33:X33"/>
-    <mergeCell ref="P34:X34"/>
-    <mergeCell ref="P28:X28"/>
-    <mergeCell ref="P29:X29"/>
-    <mergeCell ref="P32:X32"/>
-    <mergeCell ref="P30:X30"/>
-    <mergeCell ref="P31:X31"/>
-    <mergeCell ref="P24:X24"/>
-    <mergeCell ref="P13:X13"/>
-    <mergeCell ref="P14:X14"/>
-    <mergeCell ref="P15:X15"/>
-    <mergeCell ref="P25:X25"/>
-    <mergeCell ref="P26:X26"/>
-    <mergeCell ref="P27:X27"/>
-    <mergeCell ref="P43:X43"/>
-    <mergeCell ref="I50:L50"/>
-    <mergeCell ref="I35:L35"/>
-    <mergeCell ref="I36:L36"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="I33:L33"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="P44:X44"/>
-    <mergeCell ref="I51:L51"/>
-    <mergeCell ref="I52:L52"/>
-    <mergeCell ref="I53:L53"/>
-    <mergeCell ref="P4:X4"/>
-    <mergeCell ref="P5:X5"/>
-    <mergeCell ref="P6:X6"/>
-    <mergeCell ref="P7:X7"/>
-    <mergeCell ref="P8:X8"/>
-    <mergeCell ref="P9:X9"/>
-    <mergeCell ref="P10:X10"/>
-    <mergeCell ref="P11:X11"/>
-    <mergeCell ref="P17:X17"/>
-    <mergeCell ref="P18:X18"/>
-    <mergeCell ref="P19:X19"/>
-    <mergeCell ref="P20:X20"/>
-    <mergeCell ref="I45:L45"/>
-    <mergeCell ref="I46:L46"/>
-    <mergeCell ref="I47:L47"/>
-    <mergeCell ref="I48:L48"/>
-    <mergeCell ref="I49:L49"/>
-    <mergeCell ref="I40:L40"/>
-    <mergeCell ref="I41:L41"/>
-    <mergeCell ref="I42:L42"/>
-    <mergeCell ref="I44:L44"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="I27:L27"/>
-    <mergeCell ref="I43:L43"/>
-    <mergeCell ref="M50:O50"/>
-    <mergeCell ref="M51:O51"/>
-    <mergeCell ref="M52:O52"/>
-    <mergeCell ref="M53:O53"/>
-    <mergeCell ref="I4:L4"/>
-    <mergeCell ref="I5:L5"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="I7:L7"/>
-    <mergeCell ref="I8:L8"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="M45:O45"/>
-    <mergeCell ref="M46:O46"/>
-    <mergeCell ref="M47:O47"/>
-    <mergeCell ref="M48:O48"/>
-    <mergeCell ref="M49:O49"/>
-    <mergeCell ref="M40:O40"/>
-    <mergeCell ref="M41:O41"/>
-    <mergeCell ref="M42:O42"/>
-    <mergeCell ref="M25:O25"/>
-    <mergeCell ref="M26:O26"/>
-    <mergeCell ref="M27:O27"/>
-    <mergeCell ref="M43:O43"/>
-    <mergeCell ref="P2:X3"/>
-    <mergeCell ref="P16:X16"/>
-    <mergeCell ref="M44:O44"/>
-    <mergeCell ref="M35:O35"/>
-    <mergeCell ref="M36:O36"/>
-    <mergeCell ref="M37:O37"/>
-    <mergeCell ref="M38:O38"/>
-    <mergeCell ref="M39:O39"/>
-    <mergeCell ref="M21:O21"/>
-    <mergeCell ref="M22:O22"/>
-    <mergeCell ref="M23:O23"/>
-    <mergeCell ref="M33:O33"/>
-    <mergeCell ref="M34:O34"/>
-    <mergeCell ref="M28:O28"/>
-    <mergeCell ref="M29:O29"/>
-    <mergeCell ref="M32:O32"/>
-    <mergeCell ref="M30:O30"/>
-    <mergeCell ref="M31:O31"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="P12:X12"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="M20:O20"/>
-    <mergeCell ref="M4:O4"/>
-    <mergeCell ref="M5:O5"/>
-    <mergeCell ref="M6:O6"/>
-    <mergeCell ref="M7:O7"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="M17:O17"/>
-    <mergeCell ref="M18:O18"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="M16:O16"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="M13:O13"/>
-    <mergeCell ref="M14:O14"/>
-    <mergeCell ref="M15:O15"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11067,14 +11067,14 @@
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="B8" s="113" t="s">
+      <c r="B8" s="99" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="105"/>
-      <c r="D8" s="105"/>
-      <c r="E8" s="105"/>
-      <c r="F8" s="105"/>
-      <c r="G8" s="106"/>
+      <c r="C8" s="97"/>
+      <c r="D8" s="97"/>
+      <c r="E8" s="97"/>
+      <c r="F8" s="97"/>
+      <c r="G8" s="98"/>
     </row>
     <row r="9" spans="1:7">
       <c r="B9" s="116"/>
@@ -11779,22 +11779,22 @@
       <c r="N154" s="88"/>
     </row>
     <row r="155" spans="3:26">
-      <c r="D155" s="113" t="s">
+      <c r="D155" s="99" t="s">
         <v>365</v>
       </c>
-      <c r="E155" s="105"/>
-      <c r="F155" s="105"/>
-      <c r="G155" s="105"/>
-      <c r="H155" s="105"/>
-      <c r="I155" s="106"/>
-      <c r="L155" s="113" t="s">
+      <c r="E155" s="97"/>
+      <c r="F155" s="97"/>
+      <c r="G155" s="97"/>
+      <c r="H155" s="97"/>
+      <c r="I155" s="98"/>
+      <c r="L155" s="99" t="s">
         <v>366</v>
       </c>
-      <c r="M155" s="105"/>
-      <c r="N155" s="105"/>
-      <c r="O155" s="105"/>
-      <c r="P155" s="105"/>
-      <c r="Q155" s="106"/>
+      <c r="M155" s="97"/>
+      <c r="N155" s="97"/>
+      <c r="O155" s="97"/>
+      <c r="P155" s="97"/>
+      <c r="Q155" s="98"/>
       <c r="S155" t="s">
         <v>363</v>
       </c>
@@ -11879,25 +11879,25 @@
       </c>
     </row>
     <row r="163" spans="3:17" ht="14.25" customHeight="1">
-      <c r="D163" s="113" t="s">
+      <c r="D163" s="99" t="s">
         <v>352</v>
       </c>
-      <c r="E163" s="114"/>
-      <c r="F163" s="114"/>
-      <c r="G163" s="114"/>
-      <c r="H163" s="114"/>
-      <c r="I163" s="115"/>
+      <c r="E163" s="100"/>
+      <c r="F163" s="100"/>
+      <c r="G163" s="100"/>
+      <c r="H163" s="100"/>
+      <c r="I163" s="101"/>
       <c r="K163" t="s">
         <v>244</v>
       </c>
-      <c r="L163" s="113" t="s">
+      <c r="L163" s="99" t="s">
         <v>353</v>
       </c>
-      <c r="M163" s="114"/>
-      <c r="N163" s="114"/>
-      <c r="O163" s="114"/>
-      <c r="P163" s="114"/>
-      <c r="Q163" s="115"/>
+      <c r="M163" s="100"/>
+      <c r="N163" s="100"/>
+      <c r="O163" s="100"/>
+      <c r="P163" s="100"/>
+      <c r="Q163" s="101"/>
     </row>
     <row r="164" spans="3:17">
       <c r="D164" s="133"/>
@@ -12138,17 +12138,17 @@
       </c>
     </row>
     <row r="214" spans="1:10">
-      <c r="B214" s="113" t="s">
+      <c r="B214" s="99" t="s">
         <v>360</v>
       </c>
-      <c r="C214" s="105"/>
-      <c r="D214" s="105"/>
-      <c r="E214" s="105"/>
-      <c r="F214" s="105"/>
-      <c r="G214" s="105"/>
-      <c r="H214" s="105"/>
-      <c r="I214" s="105"/>
-      <c r="J214" s="106"/>
+      <c r="C214" s="97"/>
+      <c r="D214" s="97"/>
+      <c r="E214" s="97"/>
+      <c r="F214" s="97"/>
+      <c r="G214" s="97"/>
+      <c r="H214" s="97"/>
+      <c r="I214" s="97"/>
+      <c r="J214" s="98"/>
     </row>
     <row r="215" spans="1:10">
       <c r="B215" s="119"/>
@@ -13234,15 +13234,15 @@
       <c r="H2" s="13"/>
       <c r="I2" s="13"/>
       <c r="J2" s="15"/>
-      <c r="N2" s="113" t="s">
+      <c r="N2" s="99" t="s">
         <v>348</v>
       </c>
-      <c r="O2" s="105"/>
-      <c r="P2" s="105"/>
-      <c r="Q2" s="105"/>
-      <c r="R2" s="105"/>
-      <c r="S2" s="105"/>
-      <c r="T2" s="106"/>
+      <c r="O2" s="97"/>
+      <c r="P2" s="97"/>
+      <c r="Q2" s="97"/>
+      <c r="R2" s="97"/>
+      <c r="S2" s="97"/>
+      <c r="T2" s="98"/>
     </row>
     <row r="3" spans="1:20" ht="15.75">
       <c r="B3" s="26" t="s">
@@ -13412,15 +13412,15 @@
       <c r="H11" s="14"/>
       <c r="I11" s="14"/>
       <c r="J11" s="16"/>
-      <c r="N11" s="113" t="s">
+      <c r="N11" s="99" t="s">
         <v>349</v>
       </c>
-      <c r="O11" s="105"/>
-      <c r="P11" s="105"/>
-      <c r="Q11" s="105"/>
-      <c r="R11" s="105"/>
-      <c r="S11" s="105"/>
-      <c r="T11" s="106"/>
+      <c r="O11" s="97"/>
+      <c r="P11" s="97"/>
+      <c r="Q11" s="97"/>
+      <c r="R11" s="97"/>
+      <c r="S11" s="97"/>
+      <c r="T11" s="98"/>
     </row>
     <row r="12" spans="1:20" ht="15.75">
       <c r="B12" s="26" t="s">
@@ -13590,15 +13590,15 @@
       <c r="H20" s="14"/>
       <c r="I20" s="14"/>
       <c r="J20" s="16"/>
-      <c r="N20" s="113" t="s">
+      <c r="N20" s="99" t="s">
         <v>350</v>
       </c>
-      <c r="O20" s="105"/>
-      <c r="P20" s="105"/>
-      <c r="Q20" s="105"/>
-      <c r="R20" s="105"/>
-      <c r="S20" s="105"/>
-      <c r="T20" s="106"/>
+      <c r="O20" s="97"/>
+      <c r="P20" s="97"/>
+      <c r="Q20" s="97"/>
+      <c r="R20" s="97"/>
+      <c r="S20" s="97"/>
+      <c r="T20" s="98"/>
     </row>
     <row r="21" spans="2:20" ht="15.75">
       <c r="B21" s="27" t="s">
@@ -13876,17 +13876,17 @@
       </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="B40" s="113" t="s">
+      <c r="B40" s="99" t="s">
         <v>182</v>
       </c>
-      <c r="C40" s="105"/>
-      <c r="D40" s="105"/>
-      <c r="E40" s="105"/>
-      <c r="F40" s="105"/>
-      <c r="G40" s="105"/>
-      <c r="H40" s="105"/>
-      <c r="I40" s="105"/>
-      <c r="J40" s="106"/>
+      <c r="C40" s="97"/>
+      <c r="D40" s="97"/>
+      <c r="E40" s="97"/>
+      <c r="F40" s="97"/>
+      <c r="G40" s="97"/>
+      <c r="H40" s="97"/>
+      <c r="I40" s="97"/>
+      <c r="J40" s="98"/>
     </row>
     <row r="41" spans="1:10">
       <c r="B41" s="119"/>

--- a/40_数据库/学习笔记_RDBMS_GaussDB.xlsx
+++ b/40_数据库/学习笔记_RDBMS_GaussDB.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A672A2-5A93-4722-A28F-33564A395253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67FD2EE3-F67D-4865-B63F-36AA5ADF6FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8001,48 +8001,6 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -8066,6 +8024,48 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -9133,7 +9133,7 @@
       </c>
     </row>
     <row r="2" spans="1:24" ht="18">
-      <c r="A2" s="114" t="s">
+      <c r="A2" s="100" t="s">
         <v>41</v>
       </c>
       <c r="B2" s="17" t="s">
@@ -9154,1618 +9154,1850 @@
       <c r="M2" s="11"/>
       <c r="N2" s="11"/>
       <c r="O2" s="12"/>
-      <c r="P2" s="102" t="s">
+      <c r="P2" s="107" t="s">
         <v>32</v>
       </c>
-      <c r="Q2" s="103"/>
-      <c r="R2" s="103"/>
-      <c r="S2" s="103"/>
-      <c r="T2" s="103"/>
-      <c r="U2" s="103"/>
-      <c r="V2" s="103"/>
-      <c r="W2" s="103"/>
-      <c r="X2" s="104"/>
+      <c r="Q2" s="108"/>
+      <c r="R2" s="108"/>
+      <c r="S2" s="108"/>
+      <c r="T2" s="108"/>
+      <c r="U2" s="108"/>
+      <c r="V2" s="108"/>
+      <c r="W2" s="108"/>
+      <c r="X2" s="109"/>
     </row>
     <row r="3" spans="1:24" ht="18">
-      <c r="A3" s="115"/>
-      <c r="B3" s="108" t="s">
+      <c r="A3" s="101"/>
+      <c r="B3" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="109"/>
-      <c r="D3" s="109"/>
-      <c r="E3" s="113"/>
-      <c r="F3" s="110" t="s">
+      <c r="C3" s="95"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="99"/>
+      <c r="F3" s="96" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="111"/>
-      <c r="H3" s="112"/>
-      <c r="I3" s="108" t="s">
+      <c r="G3" s="97"/>
+      <c r="H3" s="98"/>
+      <c r="I3" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="J3" s="109"/>
-      <c r="K3" s="109"/>
-      <c r="L3" s="109"/>
-      <c r="M3" s="110" t="s">
+      <c r="J3" s="95"/>
+      <c r="K3" s="95"/>
+      <c r="L3" s="95"/>
+      <c r="M3" s="96" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="111"/>
-      <c r="O3" s="112"/>
-      <c r="P3" s="105"/>
-      <c r="Q3" s="106"/>
-      <c r="R3" s="106"/>
-      <c r="S3" s="106"/>
-      <c r="T3" s="106"/>
-      <c r="U3" s="106"/>
-      <c r="V3" s="106"/>
-      <c r="W3" s="106"/>
-      <c r="X3" s="107"/>
+      <c r="N3" s="97"/>
+      <c r="O3" s="98"/>
+      <c r="P3" s="110"/>
+      <c r="Q3" s="111"/>
+      <c r="R3" s="111"/>
+      <c r="S3" s="111"/>
+      <c r="T3" s="111"/>
+      <c r="U3" s="111"/>
+      <c r="V3" s="111"/>
+      <c r="W3" s="111"/>
+      <c r="X3" s="112"/>
     </row>
     <row r="4" spans="1:24">
       <c r="A4" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="94" t="s">
+      <c r="B4" s="103" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="94"/>
-      <c r="D4" s="94"/>
-      <c r="E4" s="94"/>
-      <c r="F4" s="94"/>
-      <c r="G4" s="94"/>
-      <c r="H4" s="94"/>
-      <c r="I4" s="96" t="s">
+      <c r="C4" s="103"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="103"/>
+      <c r="G4" s="103"/>
+      <c r="H4" s="103"/>
+      <c r="I4" s="104" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="97"/>
-      <c r="K4" s="97"/>
-      <c r="L4" s="98"/>
-      <c r="M4" s="94"/>
-      <c r="N4" s="94"/>
-      <c r="O4" s="94"/>
-      <c r="P4" s="94"/>
-      <c r="Q4" s="94"/>
-      <c r="R4" s="94"/>
-      <c r="S4" s="94"/>
-      <c r="T4" s="94"/>
-      <c r="U4" s="94"/>
-      <c r="V4" s="94"/>
-      <c r="W4" s="94"/>
-      <c r="X4" s="94"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="105"/>
+      <c r="L4" s="106"/>
+      <c r="M4" s="103"/>
+      <c r="N4" s="103"/>
+      <c r="O4" s="103"/>
+      <c r="P4" s="103"/>
+      <c r="Q4" s="103"/>
+      <c r="R4" s="103"/>
+      <c r="S4" s="103"/>
+      <c r="T4" s="103"/>
+      <c r="U4" s="103"/>
+      <c r="V4" s="103"/>
+      <c r="W4" s="103"/>
+      <c r="X4" s="103"/>
     </row>
     <row r="5" spans="1:24">
       <c r="A5" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="94" t="s">
+      <c r="B5" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="94"/>
-      <c r="D5" s="94"/>
-      <c r="E5" s="94"/>
-      <c r="F5" s="94" t="s">
+      <c r="C5" s="103"/>
+      <c r="D5" s="103"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="103" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="94"/>
-      <c r="H5" s="94"/>
-      <c r="I5" s="96" t="s">
+      <c r="G5" s="103"/>
+      <c r="H5" s="103"/>
+      <c r="I5" s="104" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="97"/>
-      <c r="K5" s="97"/>
-      <c r="L5" s="98"/>
-      <c r="M5" s="94" t="s">
+      <c r="J5" s="105"/>
+      <c r="K5" s="105"/>
+      <c r="L5" s="106"/>
+      <c r="M5" s="103" t="s">
         <v>36</v>
       </c>
-      <c r="N5" s="94"/>
-      <c r="O5" s="94"/>
-      <c r="P5" s="94" t="s">
+      <c r="N5" s="103"/>
+      <c r="O5" s="103"/>
+      <c r="P5" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="Q5" s="94"/>
-      <c r="R5" s="94"/>
-      <c r="S5" s="94"/>
-      <c r="T5" s="94"/>
-      <c r="U5" s="94"/>
-      <c r="V5" s="94"/>
-      <c r="W5" s="94"/>
-      <c r="X5" s="94"/>
+      <c r="Q5" s="103"/>
+      <c r="R5" s="103"/>
+      <c r="S5" s="103"/>
+      <c r="T5" s="103"/>
+      <c r="U5" s="103"/>
+      <c r="V5" s="103"/>
+      <c r="W5" s="103"/>
+      <c r="X5" s="103"/>
     </row>
     <row r="6" spans="1:24">
       <c r="A6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="94" t="s">
+      <c r="B6" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="94"/>
-      <c r="D6" s="94"/>
-      <c r="E6" s="94"/>
-      <c r="F6" s="94" t="s">
+      <c r="C6" s="103"/>
+      <c r="D6" s="103"/>
+      <c r="E6" s="103"/>
+      <c r="F6" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="94"/>
-      <c r="H6" s="94"/>
-      <c r="I6" s="96" t="s">
+      <c r="G6" s="103"/>
+      <c r="H6" s="103"/>
+      <c r="I6" s="104" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="97"/>
-      <c r="K6" s="97"/>
-      <c r="L6" s="98"/>
-      <c r="M6" s="94" t="s">
+      <c r="J6" s="105"/>
+      <c r="K6" s="105"/>
+      <c r="L6" s="106"/>
+      <c r="M6" s="103" t="s">
         <v>24</v>
       </c>
-      <c r="N6" s="94"/>
-      <c r="O6" s="94"/>
-      <c r="P6" s="94"/>
-      <c r="Q6" s="94"/>
-      <c r="R6" s="94"/>
-      <c r="S6" s="94"/>
-      <c r="T6" s="94"/>
-      <c r="U6" s="94"/>
-      <c r="V6" s="94"/>
-      <c r="W6" s="94"/>
-      <c r="X6" s="94"/>
+      <c r="N6" s="103"/>
+      <c r="O6" s="103"/>
+      <c r="P6" s="103"/>
+      <c r="Q6" s="103"/>
+      <c r="R6" s="103"/>
+      <c r="S6" s="103"/>
+      <c r="T6" s="103"/>
+      <c r="U6" s="103"/>
+      <c r="V6" s="103"/>
+      <c r="W6" s="103"/>
+      <c r="X6" s="103"/>
     </row>
     <row r="7" spans="1:24">
       <c r="A7" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B7" s="94" t="s">
+      <c r="B7" s="103" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="94"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
-      <c r="F7" s="94"/>
-      <c r="G7" s="94"/>
-      <c r="H7" s="94"/>
-      <c r="I7" s="96" t="s">
+      <c r="C7" s="103"/>
+      <c r="D7" s="103"/>
+      <c r="E7" s="103"/>
+      <c r="F7" s="103"/>
+      <c r="G7" s="103"/>
+      <c r="H7" s="103"/>
+      <c r="I7" s="104" t="s">
         <v>107</v>
       </c>
-      <c r="J7" s="97"/>
-      <c r="K7" s="97"/>
-      <c r="L7" s="98"/>
-      <c r="M7" s="94"/>
-      <c r="N7" s="94"/>
-      <c r="O7" s="94"/>
-      <c r="P7" s="94"/>
-      <c r="Q7" s="94"/>
-      <c r="R7" s="94"/>
-      <c r="S7" s="94"/>
-      <c r="T7" s="94"/>
-      <c r="U7" s="94"/>
-      <c r="V7" s="94"/>
-      <c r="W7" s="94"/>
-      <c r="X7" s="94"/>
+      <c r="J7" s="105"/>
+      <c r="K7" s="105"/>
+      <c r="L7" s="106"/>
+      <c r="M7" s="103"/>
+      <c r="N7" s="103"/>
+      <c r="O7" s="103"/>
+      <c r="P7" s="103"/>
+      <c r="Q7" s="103"/>
+      <c r="R7" s="103"/>
+      <c r="S7" s="103"/>
+      <c r="T7" s="103"/>
+      <c r="U7" s="103"/>
+      <c r="V7" s="103"/>
+      <c r="W7" s="103"/>
+      <c r="X7" s="103"/>
     </row>
     <row r="8" spans="1:24">
       <c r="A8" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="94" t="s">
+      <c r="B8" s="103" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="94"/>
-      <c r="D8" s="94"/>
-      <c r="E8" s="94"/>
-      <c r="F8" s="94" t="s">
+      <c r="C8" s="103"/>
+      <c r="D8" s="103"/>
+      <c r="E8" s="103"/>
+      <c r="F8" s="103" t="s">
         <v>46</v>
       </c>
-      <c r="G8" s="94"/>
-      <c r="H8" s="94"/>
-      <c r="I8" s="96" t="s">
+      <c r="G8" s="103"/>
+      <c r="H8" s="103"/>
+      <c r="I8" s="104" t="s">
         <v>27</v>
       </c>
-      <c r="J8" s="97"/>
-      <c r="K8" s="97"/>
-      <c r="L8" s="98"/>
-      <c r="M8" s="94" t="s">
+      <c r="J8" s="105"/>
+      <c r="K8" s="105"/>
+      <c r="L8" s="106"/>
+      <c r="M8" s="103" t="s">
         <v>47</v>
       </c>
-      <c r="N8" s="94"/>
-      <c r="O8" s="94"/>
-      <c r="P8" s="94" t="s">
+      <c r="N8" s="103"/>
+      <c r="O8" s="103"/>
+      <c r="P8" s="103" t="s">
         <v>37</v>
       </c>
-      <c r="Q8" s="94"/>
-      <c r="R8" s="94"/>
-      <c r="S8" s="94"/>
-      <c r="T8" s="94"/>
-      <c r="U8" s="94"/>
-      <c r="V8" s="94"/>
-      <c r="W8" s="94"/>
-      <c r="X8" s="94"/>
+      <c r="Q8" s="103"/>
+      <c r="R8" s="103"/>
+      <c r="S8" s="103"/>
+      <c r="T8" s="103"/>
+      <c r="U8" s="103"/>
+      <c r="V8" s="103"/>
+      <c r="W8" s="103"/>
+      <c r="X8" s="103"/>
     </row>
     <row r="9" spans="1:24">
       <c r="A9" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="94" t="s">
+      <c r="B9" s="103" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="94"/>
-      <c r="D9" s="94"/>
-      <c r="E9" s="94"/>
-      <c r="F9" s="94"/>
-      <c r="G9" s="94"/>
-      <c r="H9" s="94"/>
-      <c r="I9" s="96" t="s">
+      <c r="C9" s="103"/>
+      <c r="D9" s="103"/>
+      <c r="E9" s="103"/>
+      <c r="F9" s="103"/>
+      <c r="G9" s="103"/>
+      <c r="H9" s="103"/>
+      <c r="I9" s="104" t="s">
         <v>29</v>
       </c>
-      <c r="J9" s="97"/>
-      <c r="K9" s="97"/>
-      <c r="L9" s="98"/>
-      <c r="M9" s="94"/>
-      <c r="N9" s="94"/>
-      <c r="O9" s="94"/>
-      <c r="P9" s="94"/>
-      <c r="Q9" s="94"/>
-      <c r="R9" s="94"/>
-      <c r="S9" s="94"/>
-      <c r="T9" s="94"/>
-      <c r="U9" s="94"/>
-      <c r="V9" s="94"/>
-      <c r="W9" s="94"/>
-      <c r="X9" s="94"/>
+      <c r="J9" s="105"/>
+      <c r="K9" s="105"/>
+      <c r="L9" s="106"/>
+      <c r="M9" s="103"/>
+      <c r="N9" s="103"/>
+      <c r="O9" s="103"/>
+      <c r="P9" s="103"/>
+      <c r="Q9" s="103"/>
+      <c r="R9" s="103"/>
+      <c r="S9" s="103"/>
+      <c r="T9" s="103"/>
+      <c r="U9" s="103"/>
+      <c r="V9" s="103"/>
+      <c r="W9" s="103"/>
+      <c r="X9" s="103"/>
     </row>
     <row r="10" spans="1:24">
       <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="94" t="s">
+      <c r="B10" s="103" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="94"/>
-      <c r="D10" s="94"/>
-      <c r="E10" s="94"/>
-      <c r="F10" s="94" t="s">
+      <c r="C10" s="103"/>
+      <c r="D10" s="103"/>
+      <c r="E10" s="103"/>
+      <c r="F10" s="103" t="s">
         <v>38</v>
       </c>
-      <c r="G10" s="94"/>
-      <c r="H10" s="94"/>
-      <c r="I10" s="96" t="s">
+      <c r="G10" s="103"/>
+      <c r="H10" s="103"/>
+      <c r="I10" s="104" t="s">
         <v>43</v>
       </c>
-      <c r="J10" s="97"/>
-      <c r="K10" s="97"/>
-      <c r="L10" s="98"/>
-      <c r="M10" s="94" t="s">
+      <c r="J10" s="105"/>
+      <c r="K10" s="105"/>
+      <c r="L10" s="106"/>
+      <c r="M10" s="103" t="s">
         <v>39</v>
       </c>
-      <c r="N10" s="94"/>
-      <c r="O10" s="94"/>
-      <c r="P10" s="94"/>
-      <c r="Q10" s="94"/>
-      <c r="R10" s="94"/>
-      <c r="S10" s="94"/>
-      <c r="T10" s="94"/>
-      <c r="U10" s="94"/>
-      <c r="V10" s="94"/>
-      <c r="W10" s="94"/>
-      <c r="X10" s="94"/>
+      <c r="N10" s="103"/>
+      <c r="O10" s="103"/>
+      <c r="P10" s="103"/>
+      <c r="Q10" s="103"/>
+      <c r="R10" s="103"/>
+      <c r="S10" s="103"/>
+      <c r="T10" s="103"/>
+      <c r="U10" s="103"/>
+      <c r="V10" s="103"/>
+      <c r="W10" s="103"/>
+      <c r="X10" s="103"/>
     </row>
     <row r="11" spans="1:24">
       <c r="A11" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="94" t="s">
+      <c r="B11" s="103" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="94"/>
-      <c r="D11" s="94"/>
-      <c r="E11" s="94"/>
-      <c r="F11" s="94"/>
-      <c r="G11" s="94"/>
-      <c r="H11" s="94"/>
-      <c r="I11" s="96" t="s">
+      <c r="C11" s="103"/>
+      <c r="D11" s="103"/>
+      <c r="E11" s="103"/>
+      <c r="F11" s="103"/>
+      <c r="G11" s="103"/>
+      <c r="H11" s="103"/>
+      <c r="I11" s="104" t="s">
         <v>52</v>
       </c>
-      <c r="J11" s="97"/>
-      <c r="K11" s="97"/>
-      <c r="L11" s="98"/>
-      <c r="M11" s="94"/>
-      <c r="N11" s="94"/>
-      <c r="O11" s="94"/>
-      <c r="P11" s="94" t="s">
+      <c r="J11" s="105"/>
+      <c r="K11" s="105"/>
+      <c r="L11" s="106"/>
+      <c r="M11" s="103"/>
+      <c r="N11" s="103"/>
+      <c r="O11" s="103"/>
+      <c r="P11" s="103" t="s">
         <v>53</v>
       </c>
-      <c r="Q11" s="94"/>
-      <c r="R11" s="94"/>
-      <c r="S11" s="94"/>
-      <c r="T11" s="94"/>
-      <c r="U11" s="94"/>
-      <c r="V11" s="94"/>
-      <c r="W11" s="94"/>
-      <c r="X11" s="94"/>
+      <c r="Q11" s="103"/>
+      <c r="R11" s="103"/>
+      <c r="S11" s="103"/>
+      <c r="T11" s="103"/>
+      <c r="U11" s="103"/>
+      <c r="V11" s="103"/>
+      <c r="W11" s="103"/>
+      <c r="X11" s="103"/>
     </row>
     <row r="12" spans="1:24" ht="34.5" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B12" s="94" t="s">
+      <c r="B12" s="103" t="s">
         <v>92</v>
       </c>
-      <c r="C12" s="94"/>
-      <c r="D12" s="94"/>
-      <c r="E12" s="94"/>
-      <c r="F12" s="94" t="s">
+      <c r="C12" s="103"/>
+      <c r="D12" s="103"/>
+      <c r="E12" s="103"/>
+      <c r="F12" s="103" t="s">
         <v>97</v>
       </c>
-      <c r="G12" s="94"/>
-      <c r="H12" s="94"/>
-      <c r="I12" s="96" t="s">
+      <c r="G12" s="103"/>
+      <c r="H12" s="103"/>
+      <c r="I12" s="104" t="s">
         <v>98</v>
       </c>
-      <c r="J12" s="97"/>
-      <c r="K12" s="97"/>
-      <c r="L12" s="98"/>
-      <c r="M12" s="95" t="s">
+      <c r="J12" s="105"/>
+      <c r="K12" s="105"/>
+      <c r="L12" s="106"/>
+      <c r="M12" s="102" t="s">
         <v>99</v>
       </c>
-      <c r="N12" s="94"/>
-      <c r="O12" s="94"/>
-      <c r="P12" s="94"/>
-      <c r="Q12" s="94"/>
-      <c r="R12" s="94"/>
-      <c r="S12" s="94"/>
-      <c r="T12" s="94"/>
-      <c r="U12" s="94"/>
-      <c r="V12" s="94"/>
-      <c r="W12" s="94"/>
-      <c r="X12" s="94"/>
+      <c r="N12" s="103"/>
+      <c r="O12" s="103"/>
+      <c r="P12" s="103"/>
+      <c r="Q12" s="103"/>
+      <c r="R12" s="103"/>
+      <c r="S12" s="103"/>
+      <c r="T12" s="103"/>
+      <c r="U12" s="103"/>
+      <c r="V12" s="103"/>
+      <c r="W12" s="103"/>
+      <c r="X12" s="103"/>
     </row>
     <row r="13" spans="1:24">
       <c r="A13" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B13" s="94"/>
-      <c r="C13" s="94"/>
-      <c r="D13" s="94"/>
-      <c r="E13" s="94"/>
-      <c r="F13" s="94" t="s">
+      <c r="B13" s="103"/>
+      <c r="C13" s="103"/>
+      <c r="D13" s="103"/>
+      <c r="E13" s="103"/>
+      <c r="F13" s="103" t="s">
         <v>100</v>
       </c>
-      <c r="G13" s="94"/>
-      <c r="H13" s="94"/>
-      <c r="I13" s="96"/>
-      <c r="J13" s="97"/>
-      <c r="K13" s="97"/>
-      <c r="L13" s="98"/>
-      <c r="M13" s="95" t="s">
+      <c r="G13" s="103"/>
+      <c r="H13" s="103"/>
+      <c r="I13" s="104"/>
+      <c r="J13" s="105"/>
+      <c r="K13" s="105"/>
+      <c r="L13" s="106"/>
+      <c r="M13" s="102" t="s">
         <v>102</v>
       </c>
-      <c r="N13" s="94"/>
-      <c r="O13" s="94"/>
-      <c r="P13" s="94"/>
-      <c r="Q13" s="94"/>
-      <c r="R13" s="94"/>
-      <c r="S13" s="94"/>
-      <c r="T13" s="94"/>
-      <c r="U13" s="94"/>
-      <c r="V13" s="94"/>
-      <c r="W13" s="94"/>
-      <c r="X13" s="94"/>
+      <c r="N13" s="103"/>
+      <c r="O13" s="103"/>
+      <c r="P13" s="103"/>
+      <c r="Q13" s="103"/>
+      <c r="R13" s="103"/>
+      <c r="S13" s="103"/>
+      <c r="T13" s="103"/>
+      <c r="U13" s="103"/>
+      <c r="V13" s="103"/>
+      <c r="W13" s="103"/>
+      <c r="X13" s="103"/>
     </row>
     <row r="14" spans="1:24">
       <c r="A14" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B14" s="94"/>
-      <c r="C14" s="94"/>
-      <c r="D14" s="94"/>
-      <c r="E14" s="94"/>
-      <c r="F14" s="94" t="s">
+      <c r="B14" s="103"/>
+      <c r="C14" s="103"/>
+      <c r="D14" s="103"/>
+      <c r="E14" s="103"/>
+      <c r="F14" s="103" t="s">
         <v>100</v>
       </c>
-      <c r="G14" s="94"/>
-      <c r="H14" s="94"/>
-      <c r="I14" s="96"/>
-      <c r="J14" s="97"/>
-      <c r="K14" s="97"/>
-      <c r="L14" s="98"/>
-      <c r="M14" s="95" t="s">
+      <c r="G14" s="103"/>
+      <c r="H14" s="103"/>
+      <c r="I14" s="104"/>
+      <c r="J14" s="105"/>
+      <c r="K14" s="105"/>
+      <c r="L14" s="106"/>
+      <c r="M14" s="102" t="s">
         <v>103</v>
       </c>
-      <c r="N14" s="94"/>
-      <c r="O14" s="94"/>
-      <c r="P14" s="94"/>
-      <c r="Q14" s="94"/>
-      <c r="R14" s="94"/>
-      <c r="S14" s="94"/>
-      <c r="T14" s="94"/>
-      <c r="U14" s="94"/>
-      <c r="V14" s="94"/>
-      <c r="W14" s="94"/>
-      <c r="X14" s="94"/>
+      <c r="N14" s="103"/>
+      <c r="O14" s="103"/>
+      <c r="P14" s="103"/>
+      <c r="Q14" s="103"/>
+      <c r="R14" s="103"/>
+      <c r="S14" s="103"/>
+      <c r="T14" s="103"/>
+      <c r="U14" s="103"/>
+      <c r="V14" s="103"/>
+      <c r="W14" s="103"/>
+      <c r="X14" s="103"/>
     </row>
     <row r="15" spans="1:24">
       <c r="A15" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B15" s="94"/>
-      <c r="C15" s="94"/>
-      <c r="D15" s="94"/>
-      <c r="E15" s="94"/>
-      <c r="F15" s="94" t="s">
+      <c r="B15" s="103"/>
+      <c r="C15" s="103"/>
+      <c r="D15" s="103"/>
+      <c r="E15" s="103"/>
+      <c r="F15" s="103" t="s">
         <v>101</v>
       </c>
-      <c r="G15" s="94"/>
-      <c r="H15" s="94"/>
-      <c r="I15" s="96"/>
-      <c r="J15" s="97"/>
-      <c r="K15" s="97"/>
-      <c r="L15" s="98"/>
-      <c r="M15" s="95" t="s">
+      <c r="G15" s="103"/>
+      <c r="H15" s="103"/>
+      <c r="I15" s="104"/>
+      <c r="J15" s="105"/>
+      <c r="K15" s="105"/>
+      <c r="L15" s="106"/>
+      <c r="M15" s="102" t="s">
         <v>104</v>
       </c>
-      <c r="N15" s="94"/>
-      <c r="O15" s="94"/>
-      <c r="P15" s="94"/>
-      <c r="Q15" s="94"/>
-      <c r="R15" s="94"/>
-      <c r="S15" s="94"/>
-      <c r="T15" s="94"/>
-      <c r="U15" s="94"/>
-      <c r="V15" s="94"/>
-      <c r="W15" s="94"/>
-      <c r="X15" s="94"/>
+      <c r="N15" s="103"/>
+      <c r="O15" s="103"/>
+      <c r="P15" s="103"/>
+      <c r="Q15" s="103"/>
+      <c r="R15" s="103"/>
+      <c r="S15" s="103"/>
+      <c r="T15" s="103"/>
+      <c r="U15" s="103"/>
+      <c r="V15" s="103"/>
+      <c r="W15" s="103"/>
+      <c r="X15" s="103"/>
     </row>
     <row r="16" spans="1:24">
       <c r="A16" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B16" s="94" t="s">
+      <c r="B16" s="103" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="94"/>
-      <c r="D16" s="94"/>
-      <c r="E16" s="94"/>
-      <c r="F16" s="94" t="s">
+      <c r="C16" s="103"/>
+      <c r="D16" s="103"/>
+      <c r="E16" s="103"/>
+      <c r="F16" s="103" t="s">
         <v>105</v>
       </c>
-      <c r="G16" s="94"/>
-      <c r="H16" s="94"/>
-      <c r="I16" s="96" t="s">
+      <c r="G16" s="103"/>
+      <c r="H16" s="103"/>
+      <c r="I16" s="104" t="s">
         <v>86</v>
       </c>
-      <c r="J16" s="97"/>
-      <c r="K16" s="97"/>
-      <c r="L16" s="98"/>
-      <c r="M16" s="94"/>
-      <c r="N16" s="94"/>
-      <c r="O16" s="94"/>
-      <c r="P16" s="94" t="s">
+      <c r="J16" s="105"/>
+      <c r="K16" s="105"/>
+      <c r="L16" s="106"/>
+      <c r="M16" s="103"/>
+      <c r="N16" s="103"/>
+      <c r="O16" s="103"/>
+      <c r="P16" s="103" t="s">
         <v>89</v>
       </c>
-      <c r="Q16" s="94"/>
-      <c r="R16" s="94"/>
-      <c r="S16" s="94"/>
-      <c r="T16" s="94"/>
-      <c r="U16" s="94"/>
-      <c r="V16" s="94"/>
-      <c r="W16" s="94"/>
-      <c r="X16" s="94"/>
+      <c r="Q16" s="103"/>
+      <c r="R16" s="103"/>
+      <c r="S16" s="103"/>
+      <c r="T16" s="103"/>
+      <c r="U16" s="103"/>
+      <c r="V16" s="103"/>
+      <c r="W16" s="103"/>
+      <c r="X16" s="103"/>
     </row>
     <row r="17" spans="1:24">
       <c r="A17" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="94" t="s">
+      <c r="B17" s="103" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="94"/>
-      <c r="D17" s="94"/>
-      <c r="E17" s="94"/>
-      <c r="F17" s="94"/>
-      <c r="G17" s="94"/>
-      <c r="H17" s="94"/>
-      <c r="I17" s="96" t="s">
+      <c r="C17" s="103"/>
+      <c r="D17" s="103"/>
+      <c r="E17" s="103"/>
+      <c r="F17" s="103"/>
+      <c r="G17" s="103"/>
+      <c r="H17" s="103"/>
+      <c r="I17" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="J17" s="97"/>
-      <c r="K17" s="97"/>
-      <c r="L17" s="98"/>
-      <c r="M17" s="94"/>
-      <c r="N17" s="94"/>
-      <c r="O17" s="94"/>
-      <c r="P17" s="94" t="s">
+      <c r="J17" s="105"/>
+      <c r="K17" s="105"/>
+      <c r="L17" s="106"/>
+      <c r="M17" s="103"/>
+      <c r="N17" s="103"/>
+      <c r="O17" s="103"/>
+      <c r="P17" s="103" t="s">
         <v>56</v>
       </c>
-      <c r="Q17" s="94"/>
-      <c r="R17" s="94"/>
-      <c r="S17" s="94"/>
-      <c r="T17" s="94"/>
-      <c r="U17" s="94"/>
-      <c r="V17" s="94"/>
-      <c r="W17" s="94"/>
-      <c r="X17" s="94"/>
+      <c r="Q17" s="103"/>
+      <c r="R17" s="103"/>
+      <c r="S17" s="103"/>
+      <c r="T17" s="103"/>
+      <c r="U17" s="103"/>
+      <c r="V17" s="103"/>
+      <c r="W17" s="103"/>
+      <c r="X17" s="103"/>
     </row>
     <row r="18" spans="1:24">
       <c r="A18" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B18" s="94" t="s">
+      <c r="B18" s="103" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="94"/>
-      <c r="D18" s="94"/>
-      <c r="E18" s="94"/>
-      <c r="F18" s="94"/>
-      <c r="G18" s="94"/>
-      <c r="H18" s="94"/>
-      <c r="I18" s="96" t="s">
+      <c r="C18" s="103"/>
+      <c r="D18" s="103"/>
+      <c r="E18" s="103"/>
+      <c r="F18" s="103"/>
+      <c r="G18" s="103"/>
+      <c r="H18" s="103"/>
+      <c r="I18" s="104" t="s">
         <v>210</v>
       </c>
-      <c r="J18" s="97"/>
-      <c r="K18" s="97"/>
-      <c r="L18" s="98"/>
-      <c r="M18" s="94"/>
-      <c r="N18" s="94"/>
-      <c r="O18" s="94"/>
-      <c r="P18" s="94" t="s">
+      <c r="J18" s="105"/>
+      <c r="K18" s="105"/>
+      <c r="L18" s="106"/>
+      <c r="M18" s="103"/>
+      <c r="N18" s="103"/>
+      <c r="O18" s="103"/>
+      <c r="P18" s="103" t="s">
         <v>60</v>
       </c>
-      <c r="Q18" s="94"/>
-      <c r="R18" s="94"/>
-      <c r="S18" s="94"/>
-      <c r="T18" s="94"/>
-      <c r="U18" s="94"/>
-      <c r="V18" s="94"/>
-      <c r="W18" s="94"/>
-      <c r="X18" s="94"/>
+      <c r="Q18" s="103"/>
+      <c r="R18" s="103"/>
+      <c r="S18" s="103"/>
+      <c r="T18" s="103"/>
+      <c r="U18" s="103"/>
+      <c r="V18" s="103"/>
+      <c r="W18" s="103"/>
+      <c r="X18" s="103"/>
     </row>
     <row r="19" spans="1:24">
       <c r="A19" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B19" s="94" t="s">
+      <c r="B19" s="103" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="94"/>
-      <c r="D19" s="94"/>
-      <c r="E19" s="94"/>
-      <c r="F19" s="94"/>
-      <c r="G19" s="94"/>
-      <c r="H19" s="94"/>
-      <c r="I19" s="96" t="s">
+      <c r="C19" s="103"/>
+      <c r="D19" s="103"/>
+      <c r="E19" s="103"/>
+      <c r="F19" s="103"/>
+      <c r="G19" s="103"/>
+      <c r="H19" s="103"/>
+      <c r="I19" s="104" t="s">
         <v>62</v>
       </c>
-      <c r="J19" s="97"/>
-      <c r="K19" s="97"/>
-      <c r="L19" s="98"/>
-      <c r="M19" s="94"/>
-      <c r="N19" s="94"/>
-      <c r="O19" s="94"/>
-      <c r="P19" s="94" t="s">
+      <c r="J19" s="105"/>
+      <c r="K19" s="105"/>
+      <c r="L19" s="106"/>
+      <c r="M19" s="103"/>
+      <c r="N19" s="103"/>
+      <c r="O19" s="103"/>
+      <c r="P19" s="103" t="s">
         <v>61</v>
       </c>
-      <c r="Q19" s="94"/>
-      <c r="R19" s="94"/>
-      <c r="S19" s="94"/>
-      <c r="T19" s="94"/>
-      <c r="U19" s="94"/>
-      <c r="V19" s="94"/>
-      <c r="W19" s="94"/>
-      <c r="X19" s="94"/>
+      <c r="Q19" s="103"/>
+      <c r="R19" s="103"/>
+      <c r="S19" s="103"/>
+      <c r="T19" s="103"/>
+      <c r="U19" s="103"/>
+      <c r="V19" s="103"/>
+      <c r="W19" s="103"/>
+      <c r="X19" s="103"/>
     </row>
     <row r="20" spans="1:24" ht="45" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B20" s="94" t="s">
+      <c r="B20" s="103" t="s">
         <v>69</v>
       </c>
-      <c r="C20" s="94"/>
-      <c r="D20" s="94"/>
-      <c r="E20" s="94"/>
-      <c r="F20" s="95" t="s">
+      <c r="C20" s="103"/>
+      <c r="D20" s="103"/>
+      <c r="E20" s="103"/>
+      <c r="F20" s="102" t="s">
         <v>71</v>
       </c>
-      <c r="G20" s="94"/>
-      <c r="H20" s="94"/>
-      <c r="I20" s="99" t="s">
+      <c r="G20" s="103"/>
+      <c r="H20" s="103"/>
+      <c r="I20" s="113" t="s">
         <v>73</v>
       </c>
-      <c r="J20" s="100"/>
-      <c r="K20" s="100"/>
-      <c r="L20" s="101"/>
-      <c r="M20" s="95" t="s">
+      <c r="J20" s="114"/>
+      <c r="K20" s="114"/>
+      <c r="L20" s="115"/>
+      <c r="M20" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="N20" s="94"/>
-      <c r="O20" s="94"/>
-      <c r="P20" s="94"/>
-      <c r="Q20" s="94"/>
-      <c r="R20" s="94"/>
-      <c r="S20" s="94"/>
-      <c r="T20" s="94"/>
-      <c r="U20" s="94"/>
-      <c r="V20" s="94"/>
-      <c r="W20" s="94"/>
-      <c r="X20" s="94"/>
+      <c r="N20" s="103"/>
+      <c r="O20" s="103"/>
+      <c r="P20" s="103"/>
+      <c r="Q20" s="103"/>
+      <c r="R20" s="103"/>
+      <c r="S20" s="103"/>
+      <c r="T20" s="103"/>
+      <c r="U20" s="103"/>
+      <c r="V20" s="103"/>
+      <c r="W20" s="103"/>
+      <c r="X20" s="103"/>
     </row>
     <row r="21" spans="1:24" ht="61.5" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B21" s="95" t="s">
+      <c r="B21" s="102" t="s">
         <v>76</v>
       </c>
-      <c r="C21" s="94"/>
-      <c r="D21" s="94"/>
-      <c r="E21" s="94"/>
-      <c r="F21" s="94"/>
-      <c r="G21" s="94"/>
-      <c r="H21" s="94"/>
-      <c r="I21" s="96" t="s">
+      <c r="C21" s="103"/>
+      <c r="D21" s="103"/>
+      <c r="E21" s="103"/>
+      <c r="F21" s="103"/>
+      <c r="G21" s="103"/>
+      <c r="H21" s="103"/>
+      <c r="I21" s="104" t="s">
         <v>78</v>
       </c>
-      <c r="J21" s="97"/>
-      <c r="K21" s="97"/>
-      <c r="L21" s="98"/>
-      <c r="M21" s="95" t="s">
+      <c r="J21" s="105"/>
+      <c r="K21" s="105"/>
+      <c r="L21" s="106"/>
+      <c r="M21" s="102" t="s">
         <v>77</v>
       </c>
-      <c r="N21" s="94"/>
-      <c r="O21" s="94"/>
-      <c r="P21" s="94" t="s">
+      <c r="N21" s="103"/>
+      <c r="O21" s="103"/>
+      <c r="P21" s="103" t="s">
         <v>75</v>
       </c>
-      <c r="Q21" s="94"/>
-      <c r="R21" s="94"/>
-      <c r="S21" s="94"/>
-      <c r="T21" s="94"/>
-      <c r="U21" s="94"/>
-      <c r="V21" s="94"/>
-      <c r="W21" s="94"/>
-      <c r="X21" s="94"/>
+      <c r="Q21" s="103"/>
+      <c r="R21" s="103"/>
+      <c r="S21" s="103"/>
+      <c r="T21" s="103"/>
+      <c r="U21" s="103"/>
+      <c r="V21" s="103"/>
+      <c r="W21" s="103"/>
+      <c r="X21" s="103"/>
     </row>
     <row r="22" spans="1:24">
       <c r="A22" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B22" s="94" t="s">
+      <c r="B22" s="103" t="s">
         <v>81</v>
       </c>
-      <c r="C22" s="94"/>
-      <c r="D22" s="94"/>
-      <c r="E22" s="94"/>
-      <c r="F22" s="94" t="s">
+      <c r="C22" s="103"/>
+      <c r="D22" s="103"/>
+      <c r="E22" s="103"/>
+      <c r="F22" s="103" t="s">
         <v>82</v>
       </c>
-      <c r="G22" s="94"/>
-      <c r="H22" s="94"/>
-      <c r="I22" s="96" t="s">
+      <c r="G22" s="103"/>
+      <c r="H22" s="103"/>
+      <c r="I22" s="104" t="s">
         <v>80</v>
       </c>
-      <c r="J22" s="97"/>
-      <c r="K22" s="97"/>
-      <c r="L22" s="98"/>
-      <c r="M22" s="94" t="s">
+      <c r="J22" s="105"/>
+      <c r="K22" s="105"/>
+      <c r="L22" s="106"/>
+      <c r="M22" s="103" t="s">
         <v>83</v>
       </c>
-      <c r="N22" s="94"/>
-      <c r="O22" s="94"/>
-      <c r="P22" s="94" t="s">
+      <c r="N22" s="103"/>
+      <c r="O22" s="103"/>
+      <c r="P22" s="103" t="s">
         <v>89</v>
       </c>
-      <c r="Q22" s="94"/>
-      <c r="R22" s="94"/>
-      <c r="S22" s="94"/>
-      <c r="T22" s="94"/>
-      <c r="U22" s="94"/>
-      <c r="V22" s="94"/>
-      <c r="W22" s="94"/>
-      <c r="X22" s="94"/>
+      <c r="Q22" s="103"/>
+      <c r="R22" s="103"/>
+      <c r="S22" s="103"/>
+      <c r="T22" s="103"/>
+      <c r="U22" s="103"/>
+      <c r="V22" s="103"/>
+      <c r="W22" s="103"/>
+      <c r="X22" s="103"/>
     </row>
     <row r="23" spans="1:24">
       <c r="A23" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B23" s="94" t="s">
+      <c r="B23" s="103" t="s">
         <v>88</v>
       </c>
-      <c r="C23" s="94"/>
-      <c r="D23" s="94"/>
-      <c r="E23" s="94"/>
-      <c r="F23" s="94"/>
-      <c r="G23" s="94"/>
-      <c r="H23" s="94"/>
-      <c r="I23" s="96" t="s">
+      <c r="C23" s="103"/>
+      <c r="D23" s="103"/>
+      <c r="E23" s="103"/>
+      <c r="F23" s="103"/>
+      <c r="G23" s="103"/>
+      <c r="H23" s="103"/>
+      <c r="I23" s="104" t="s">
         <v>84</v>
       </c>
-      <c r="J23" s="97"/>
-      <c r="K23" s="97"/>
-      <c r="L23" s="98"/>
-      <c r="M23" s="94"/>
-      <c r="N23" s="94"/>
-      <c r="O23" s="94"/>
-      <c r="P23" s="94" t="s">
+      <c r="J23" s="105"/>
+      <c r="K23" s="105"/>
+      <c r="L23" s="106"/>
+      <c r="M23" s="103"/>
+      <c r="N23" s="103"/>
+      <c r="O23" s="103"/>
+      <c r="P23" s="103" t="s">
         <v>89</v>
       </c>
-      <c r="Q23" s="94"/>
-      <c r="R23" s="94"/>
-      <c r="S23" s="94"/>
-      <c r="T23" s="94"/>
-      <c r="U23" s="94"/>
-      <c r="V23" s="94"/>
-      <c r="W23" s="94"/>
-      <c r="X23" s="94"/>
+      <c r="Q23" s="103"/>
+      <c r="R23" s="103"/>
+      <c r="S23" s="103"/>
+      <c r="T23" s="103"/>
+      <c r="U23" s="103"/>
+      <c r="V23" s="103"/>
+      <c r="W23" s="103"/>
+      <c r="X23" s="103"/>
     </row>
     <row r="24" spans="1:24">
       <c r="A24" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B24" s="94"/>
-      <c r="C24" s="94"/>
-      <c r="D24" s="94"/>
-      <c r="E24" s="94"/>
-      <c r="F24" s="94"/>
-      <c r="G24" s="94"/>
-      <c r="H24" s="94"/>
-      <c r="I24" s="96" t="s">
+      <c r="B24" s="103"/>
+      <c r="C24" s="103"/>
+      <c r="D24" s="103"/>
+      <c r="E24" s="103"/>
+      <c r="F24" s="103"/>
+      <c r="G24" s="103"/>
+      <c r="H24" s="103"/>
+      <c r="I24" s="104" t="s">
         <v>90</v>
       </c>
-      <c r="J24" s="97"/>
-      <c r="K24" s="97"/>
-      <c r="L24" s="98"/>
-      <c r="M24" s="94"/>
-      <c r="N24" s="94"/>
-      <c r="O24" s="94"/>
-      <c r="P24" s="94"/>
-      <c r="Q24" s="94"/>
-      <c r="R24" s="94"/>
-      <c r="S24" s="94"/>
-      <c r="T24" s="94"/>
-      <c r="U24" s="94"/>
-      <c r="V24" s="94"/>
-      <c r="W24" s="94"/>
-      <c r="X24" s="94"/>
+      <c r="J24" s="105"/>
+      <c r="K24" s="105"/>
+      <c r="L24" s="106"/>
+      <c r="M24" s="103"/>
+      <c r="N24" s="103"/>
+      <c r="O24" s="103"/>
+      <c r="P24" s="103"/>
+      <c r="Q24" s="103"/>
+      <c r="R24" s="103"/>
+      <c r="S24" s="103"/>
+      <c r="T24" s="103"/>
+      <c r="U24" s="103"/>
+      <c r="V24" s="103"/>
+      <c r="W24" s="103"/>
+      <c r="X24" s="103"/>
     </row>
     <row r="25" spans="1:24">
       <c r="A25" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B25" s="94"/>
-      <c r="C25" s="94"/>
-      <c r="D25" s="94"/>
-      <c r="E25" s="94"/>
-      <c r="F25" s="94" t="s">
+      <c r="B25" s="103"/>
+      <c r="C25" s="103"/>
+      <c r="D25" s="103"/>
+      <c r="E25" s="103"/>
+      <c r="F25" s="103" t="s">
         <v>109</v>
       </c>
-      <c r="G25" s="94"/>
-      <c r="H25" s="94"/>
-      <c r="I25" s="96" t="s">
+      <c r="G25" s="103"/>
+      <c r="H25" s="103"/>
+      <c r="I25" s="104" t="s">
         <v>112</v>
       </c>
-      <c r="J25" s="97"/>
-      <c r="K25" s="97"/>
-      <c r="L25" s="98"/>
-      <c r="M25" s="95" t="s">
+      <c r="J25" s="105"/>
+      <c r="K25" s="105"/>
+      <c r="L25" s="106"/>
+      <c r="M25" s="102" t="s">
         <v>110</v>
       </c>
-      <c r="N25" s="94"/>
-      <c r="O25" s="94"/>
-      <c r="P25" s="94" t="s">
+      <c r="N25" s="103"/>
+      <c r="O25" s="103"/>
+      <c r="P25" s="103" t="s">
         <v>111</v>
       </c>
-      <c r="Q25" s="94"/>
-      <c r="R25" s="94"/>
-      <c r="S25" s="94"/>
-      <c r="T25" s="94"/>
-      <c r="U25" s="94"/>
-      <c r="V25" s="94"/>
-      <c r="W25" s="94"/>
-      <c r="X25" s="94"/>
+      <c r="Q25" s="103"/>
+      <c r="R25" s="103"/>
+      <c r="S25" s="103"/>
+      <c r="T25" s="103"/>
+      <c r="U25" s="103"/>
+      <c r="V25" s="103"/>
+      <c r="W25" s="103"/>
+      <c r="X25" s="103"/>
     </row>
     <row r="26" spans="1:24" ht="45.75" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B26" s="94" t="s">
+      <c r="B26" s="103" t="s">
         <v>114</v>
       </c>
-      <c r="C26" s="94"/>
-      <c r="D26" s="94"/>
-      <c r="E26" s="94"/>
-      <c r="F26" s="95" t="s">
+      <c r="C26" s="103"/>
+      <c r="D26" s="103"/>
+      <c r="E26" s="103"/>
+      <c r="F26" s="102" t="s">
         <v>132</v>
       </c>
-      <c r="G26" s="94"/>
-      <c r="H26" s="94"/>
-      <c r="I26" s="96" t="s">
+      <c r="G26" s="103"/>
+      <c r="H26" s="103"/>
+      <c r="I26" s="104" t="s">
         <v>113</v>
       </c>
-      <c r="J26" s="97"/>
-      <c r="K26" s="97"/>
-      <c r="L26" s="98"/>
-      <c r="M26" s="95" t="s">
+      <c r="J26" s="105"/>
+      <c r="K26" s="105"/>
+      <c r="L26" s="106"/>
+      <c r="M26" s="102" t="s">
         <v>133</v>
       </c>
-      <c r="N26" s="94"/>
-      <c r="O26" s="94"/>
-      <c r="P26" s="95" t="s">
+      <c r="N26" s="103"/>
+      <c r="O26" s="103"/>
+      <c r="P26" s="102" t="s">
         <v>126</v>
       </c>
-      <c r="Q26" s="95"/>
-      <c r="R26" s="95"/>
-      <c r="S26" s="95"/>
-      <c r="T26" s="95"/>
-      <c r="U26" s="95"/>
-      <c r="V26" s="95"/>
-      <c r="W26" s="95"/>
-      <c r="X26" s="95"/>
+      <c r="Q26" s="102"/>
+      <c r="R26" s="102"/>
+      <c r="S26" s="102"/>
+      <c r="T26" s="102"/>
+      <c r="U26" s="102"/>
+      <c r="V26" s="102"/>
+      <c r="W26" s="102"/>
+      <c r="X26" s="102"/>
     </row>
     <row r="27" spans="1:24">
       <c r="A27" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B27" s="94"/>
-      <c r="C27" s="94"/>
-      <c r="D27" s="94"/>
-      <c r="E27" s="94"/>
-      <c r="F27" s="94"/>
-      <c r="G27" s="94"/>
-      <c r="H27" s="94"/>
-      <c r="I27" s="96" t="s">
+      <c r="B27" s="103"/>
+      <c r="C27" s="103"/>
+      <c r="D27" s="103"/>
+      <c r="E27" s="103"/>
+      <c r="F27" s="103"/>
+      <c r="G27" s="103"/>
+      <c r="H27" s="103"/>
+      <c r="I27" s="104" t="s">
         <v>117</v>
       </c>
-      <c r="J27" s="97"/>
-      <c r="K27" s="97"/>
-      <c r="L27" s="98"/>
-      <c r="M27" s="94"/>
-      <c r="N27" s="94"/>
-      <c r="O27" s="94"/>
-      <c r="P27" s="94"/>
-      <c r="Q27" s="94"/>
-      <c r="R27" s="94"/>
-      <c r="S27" s="94"/>
-      <c r="T27" s="94"/>
-      <c r="U27" s="94"/>
-      <c r="V27" s="94"/>
-      <c r="W27" s="94"/>
-      <c r="X27" s="94"/>
+      <c r="J27" s="105"/>
+      <c r="K27" s="105"/>
+      <c r="L27" s="106"/>
+      <c r="M27" s="103"/>
+      <c r="N27" s="103"/>
+      <c r="O27" s="103"/>
+      <c r="P27" s="103"/>
+      <c r="Q27" s="103"/>
+      <c r="R27" s="103"/>
+      <c r="S27" s="103"/>
+      <c r="T27" s="103"/>
+      <c r="U27" s="103"/>
+      <c r="V27" s="103"/>
+      <c r="W27" s="103"/>
+      <c r="X27" s="103"/>
     </row>
     <row r="28" spans="1:24">
       <c r="A28" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B28" s="94"/>
-      <c r="C28" s="94"/>
-      <c r="D28" s="94"/>
-      <c r="E28" s="94"/>
-      <c r="F28" s="94"/>
-      <c r="G28" s="94"/>
-      <c r="H28" s="94"/>
-      <c r="I28" s="96" t="s">
+      <c r="B28" s="103"/>
+      <c r="C28" s="103"/>
+      <c r="D28" s="103"/>
+      <c r="E28" s="103"/>
+      <c r="F28" s="103"/>
+      <c r="G28" s="103"/>
+      <c r="H28" s="103"/>
+      <c r="I28" s="104" t="s">
         <v>119</v>
       </c>
-      <c r="J28" s="97"/>
-      <c r="K28" s="97"/>
-      <c r="L28" s="98"/>
-      <c r="M28" s="94"/>
-      <c r="N28" s="94"/>
-      <c r="O28" s="94"/>
-      <c r="P28" s="94"/>
-      <c r="Q28" s="94"/>
-      <c r="R28" s="94"/>
-      <c r="S28" s="94"/>
-      <c r="T28" s="94"/>
-      <c r="U28" s="94"/>
-      <c r="V28" s="94"/>
-      <c r="W28" s="94"/>
-      <c r="X28" s="94"/>
+      <c r="J28" s="105"/>
+      <c r="K28" s="105"/>
+      <c r="L28" s="106"/>
+      <c r="M28" s="103"/>
+      <c r="N28" s="103"/>
+      <c r="O28" s="103"/>
+      <c r="P28" s="103"/>
+      <c r="Q28" s="103"/>
+      <c r="R28" s="103"/>
+      <c r="S28" s="103"/>
+      <c r="T28" s="103"/>
+      <c r="U28" s="103"/>
+      <c r="V28" s="103"/>
+      <c r="W28" s="103"/>
+      <c r="X28" s="103"/>
     </row>
     <row r="29" spans="1:24" ht="56.25" customHeight="1">
       <c r="A29" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B29" s="95" t="s">
+      <c r="B29" s="102" t="s">
         <v>125</v>
       </c>
-      <c r="C29" s="95"/>
-      <c r="D29" s="95"/>
-      <c r="E29" s="95"/>
-      <c r="F29" s="95" t="s">
+      <c r="C29" s="102"/>
+      <c r="D29" s="102"/>
+      <c r="E29" s="102"/>
+      <c r="F29" s="102" t="s">
         <v>120</v>
       </c>
-      <c r="G29" s="94"/>
-      <c r="H29" s="94"/>
-      <c r="I29" s="96" t="s">
+      <c r="G29" s="103"/>
+      <c r="H29" s="103"/>
+      <c r="I29" s="104" t="s">
         <v>122</v>
       </c>
-      <c r="J29" s="97"/>
-      <c r="K29" s="97"/>
-      <c r="L29" s="98"/>
-      <c r="M29" s="95" t="s">
+      <c r="J29" s="105"/>
+      <c r="K29" s="105"/>
+      <c r="L29" s="106"/>
+      <c r="M29" s="102" t="s">
         <v>123</v>
       </c>
-      <c r="N29" s="94"/>
-      <c r="O29" s="94"/>
-      <c r="P29" s="95" t="s">
+      <c r="N29" s="103"/>
+      <c r="O29" s="103"/>
+      <c r="P29" s="102" t="s">
         <v>124</v>
       </c>
-      <c r="Q29" s="95"/>
-      <c r="R29" s="95"/>
-      <c r="S29" s="95"/>
-      <c r="T29" s="95"/>
-      <c r="U29" s="95"/>
-      <c r="V29" s="95"/>
-      <c r="W29" s="95"/>
-      <c r="X29" s="95"/>
+      <c r="Q29" s="102"/>
+      <c r="R29" s="102"/>
+      <c r="S29" s="102"/>
+      <c r="T29" s="102"/>
+      <c r="U29" s="102"/>
+      <c r="V29" s="102"/>
+      <c r="W29" s="102"/>
+      <c r="X29" s="102"/>
     </row>
     <row r="30" spans="1:24">
       <c r="A30" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B30" s="94"/>
-      <c r="C30" s="94"/>
-      <c r="D30" s="94"/>
-      <c r="E30" s="94"/>
-      <c r="F30" s="94" t="s">
+      <c r="B30" s="103"/>
+      <c r="C30" s="103"/>
+      <c r="D30" s="103"/>
+      <c r="E30" s="103"/>
+      <c r="F30" s="103" t="s">
         <v>136</v>
       </c>
-      <c r="G30" s="94"/>
-      <c r="H30" s="94"/>
-      <c r="I30" s="96" t="s">
+      <c r="G30" s="103"/>
+      <c r="H30" s="103"/>
+      <c r="I30" s="104" t="s">
         <v>135</v>
       </c>
-      <c r="J30" s="97"/>
-      <c r="K30" s="97"/>
-      <c r="L30" s="98"/>
-      <c r="M30" s="94" t="s">
+      <c r="J30" s="105"/>
+      <c r="K30" s="105"/>
+      <c r="L30" s="106"/>
+      <c r="M30" s="103" t="s">
         <v>137</v>
       </c>
-      <c r="N30" s="94"/>
-      <c r="O30" s="94"/>
-      <c r="P30" s="94"/>
-      <c r="Q30" s="94"/>
-      <c r="R30" s="94"/>
-      <c r="S30" s="94"/>
-      <c r="T30" s="94"/>
-      <c r="U30" s="94"/>
-      <c r="V30" s="94"/>
-      <c r="W30" s="94"/>
-      <c r="X30" s="94"/>
+      <c r="N30" s="103"/>
+      <c r="O30" s="103"/>
+      <c r="P30" s="103"/>
+      <c r="Q30" s="103"/>
+      <c r="R30" s="103"/>
+      <c r="S30" s="103"/>
+      <c r="T30" s="103"/>
+      <c r="U30" s="103"/>
+      <c r="V30" s="103"/>
+      <c r="W30" s="103"/>
+      <c r="X30" s="103"/>
     </row>
     <row r="31" spans="1:24">
       <c r="A31" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B31" s="94" t="s">
+      <c r="B31" s="103" t="s">
         <v>144</v>
       </c>
-      <c r="C31" s="94"/>
-      <c r="D31" s="94"/>
-      <c r="E31" s="94"/>
-      <c r="F31" s="95" t="s">
+      <c r="C31" s="103"/>
+      <c r="D31" s="103"/>
+      <c r="E31" s="103"/>
+      <c r="F31" s="102" t="s">
         <v>143</v>
       </c>
-      <c r="G31" s="94"/>
-      <c r="H31" s="94"/>
-      <c r="I31" s="96" t="s">
+      <c r="G31" s="103"/>
+      <c r="H31" s="103"/>
+      <c r="I31" s="104" t="s">
         <v>145</v>
       </c>
-      <c r="J31" s="97"/>
-      <c r="K31" s="97"/>
-      <c r="L31" s="98"/>
-      <c r="M31" s="95" t="s">
+      <c r="J31" s="105"/>
+      <c r="K31" s="105"/>
+      <c r="L31" s="106"/>
+      <c r="M31" s="102" t="s">
         <v>146</v>
       </c>
-      <c r="N31" s="94"/>
-      <c r="O31" s="94"/>
-      <c r="P31" s="94"/>
-      <c r="Q31" s="94"/>
-      <c r="R31" s="94"/>
-      <c r="S31" s="94"/>
-      <c r="T31" s="94"/>
-      <c r="U31" s="94"/>
-      <c r="V31" s="94"/>
-      <c r="W31" s="94"/>
-      <c r="X31" s="94"/>
+      <c r="N31" s="103"/>
+      <c r="O31" s="103"/>
+      <c r="P31" s="103"/>
+      <c r="Q31" s="103"/>
+      <c r="R31" s="103"/>
+      <c r="S31" s="103"/>
+      <c r="T31" s="103"/>
+      <c r="U31" s="103"/>
+      <c r="V31" s="103"/>
+      <c r="W31" s="103"/>
+      <c r="X31" s="103"/>
     </row>
     <row r="32" spans="1:24">
       <c r="A32" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="B32" s="94"/>
-      <c r="C32" s="94"/>
-      <c r="D32" s="94"/>
-      <c r="E32" s="94"/>
-      <c r="F32" s="95" t="s">
+      <c r="B32" s="103"/>
+      <c r="C32" s="103"/>
+      <c r="D32" s="103"/>
+      <c r="E32" s="103"/>
+      <c r="F32" s="102" t="s">
         <v>203</v>
       </c>
-      <c r="G32" s="94"/>
-      <c r="H32" s="94"/>
-      <c r="I32" s="96"/>
-      <c r="J32" s="97"/>
-      <c r="K32" s="97"/>
-      <c r="L32" s="98"/>
-      <c r="M32" s="95" t="s">
+      <c r="G32" s="103"/>
+      <c r="H32" s="103"/>
+      <c r="I32" s="104"/>
+      <c r="J32" s="105"/>
+      <c r="K32" s="105"/>
+      <c r="L32" s="106"/>
+      <c r="M32" s="102" t="s">
         <v>204</v>
       </c>
-      <c r="N32" s="94"/>
-      <c r="O32" s="94"/>
-      <c r="P32" s="94" t="s">
+      <c r="N32" s="103"/>
+      <c r="O32" s="103"/>
+      <c r="P32" s="103" t="s">
         <v>209</v>
       </c>
-      <c r="Q32" s="94"/>
-      <c r="R32" s="94"/>
-      <c r="S32" s="94"/>
-      <c r="T32" s="94"/>
-      <c r="U32" s="94"/>
-      <c r="V32" s="94"/>
-      <c r="W32" s="94"/>
-      <c r="X32" s="94"/>
+      <c r="Q32" s="103"/>
+      <c r="R32" s="103"/>
+      <c r="S32" s="103"/>
+      <c r="T32" s="103"/>
+      <c r="U32" s="103"/>
+      <c r="V32" s="103"/>
+      <c r="W32" s="103"/>
+      <c r="X32" s="103"/>
     </row>
     <row r="33" spans="1:24">
       <c r="A33" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="B33" s="94"/>
-      <c r="C33" s="94"/>
-      <c r="D33" s="94"/>
-      <c r="E33" s="94"/>
-      <c r="F33" s="94" t="s">
+      <c r="B33" s="103"/>
+      <c r="C33" s="103"/>
+      <c r="D33" s="103"/>
+      <c r="E33" s="103"/>
+      <c r="F33" s="103" t="s">
         <v>206</v>
       </c>
-      <c r="G33" s="94"/>
-      <c r="H33" s="94"/>
-      <c r="I33" s="96"/>
-      <c r="J33" s="97"/>
-      <c r="K33" s="97"/>
-      <c r="L33" s="98"/>
-      <c r="M33" s="94" t="s">
+      <c r="G33" s="103"/>
+      <c r="H33" s="103"/>
+      <c r="I33" s="104"/>
+      <c r="J33" s="105"/>
+      <c r="K33" s="105"/>
+      <c r="L33" s="106"/>
+      <c r="M33" s="103" t="s">
         <v>205</v>
       </c>
-      <c r="N33" s="94"/>
-      <c r="O33" s="94"/>
-      <c r="P33" s="94"/>
-      <c r="Q33" s="94"/>
-      <c r="R33" s="94"/>
-      <c r="S33" s="94"/>
-      <c r="T33" s="94"/>
-      <c r="U33" s="94"/>
-      <c r="V33" s="94"/>
-      <c r="W33" s="94"/>
-      <c r="X33" s="94"/>
+      <c r="N33" s="103"/>
+      <c r="O33" s="103"/>
+      <c r="P33" s="103"/>
+      <c r="Q33" s="103"/>
+      <c r="R33" s="103"/>
+      <c r="S33" s="103"/>
+      <c r="T33" s="103"/>
+      <c r="U33" s="103"/>
+      <c r="V33" s="103"/>
+      <c r="W33" s="103"/>
+      <c r="X33" s="103"/>
     </row>
     <row r="34" spans="1:24">
       <c r="A34" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="B34" s="94" t="s">
+      <c r="B34" s="103" t="s">
         <v>370</v>
       </c>
-      <c r="C34" s="94"/>
-      <c r="D34" s="94"/>
-      <c r="E34" s="94"/>
-      <c r="F34" s="94"/>
-      <c r="G34" s="94"/>
-      <c r="H34" s="94"/>
-      <c r="I34" s="96" t="s">
+      <c r="C34" s="103"/>
+      <c r="D34" s="103"/>
+      <c r="E34" s="103"/>
+      <c r="F34" s="103"/>
+      <c r="G34" s="103"/>
+      <c r="H34" s="103"/>
+      <c r="I34" s="104" t="s">
         <v>369</v>
       </c>
-      <c r="J34" s="97"/>
-      <c r="K34" s="97"/>
-      <c r="L34" s="98"/>
-      <c r="M34" s="94"/>
-      <c r="N34" s="94"/>
-      <c r="O34" s="94"/>
-      <c r="P34" s="94"/>
-      <c r="Q34" s="94"/>
-      <c r="R34" s="94"/>
-      <c r="S34" s="94"/>
-      <c r="T34" s="94"/>
-      <c r="U34" s="94"/>
-      <c r="V34" s="94"/>
-      <c r="W34" s="94"/>
-      <c r="X34" s="94"/>
+      <c r="J34" s="105"/>
+      <c r="K34" s="105"/>
+      <c r="L34" s="106"/>
+      <c r="M34" s="103"/>
+      <c r="N34" s="103"/>
+      <c r="O34" s="103"/>
+      <c r="P34" s="103"/>
+      <c r="Q34" s="103"/>
+      <c r="R34" s="103"/>
+      <c r="S34" s="103"/>
+      <c r="T34" s="103"/>
+      <c r="U34" s="103"/>
+      <c r="V34" s="103"/>
+      <c r="W34" s="103"/>
+      <c r="X34" s="103"/>
     </row>
     <row r="35" spans="1:24">
       <c r="A35" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="B35" s="94" t="s">
+      <c r="B35" s="103" t="s">
         <v>372</v>
       </c>
-      <c r="C35" s="94"/>
-      <c r="D35" s="94"/>
-      <c r="E35" s="94"/>
-      <c r="F35" s="94"/>
-      <c r="G35" s="94"/>
-      <c r="H35" s="94"/>
-      <c r="I35" s="96" t="s">
+      <c r="C35" s="103"/>
+      <c r="D35" s="103"/>
+      <c r="E35" s="103"/>
+      <c r="F35" s="103"/>
+      <c r="G35" s="103"/>
+      <c r="H35" s="103"/>
+      <c r="I35" s="104" t="s">
         <v>372</v>
       </c>
-      <c r="J35" s="97"/>
-      <c r="K35" s="97"/>
-      <c r="L35" s="98"/>
-      <c r="M35" s="94"/>
-      <c r="N35" s="94"/>
-      <c r="O35" s="94"/>
-      <c r="P35" s="94" t="s">
+      <c r="J35" s="105"/>
+      <c r="K35" s="105"/>
+      <c r="L35" s="106"/>
+      <c r="M35" s="103"/>
+      <c r="N35" s="103"/>
+      <c r="O35" s="103"/>
+      <c r="P35" s="103" t="s">
         <v>374</v>
       </c>
-      <c r="Q35" s="94"/>
-      <c r="R35" s="94"/>
-      <c r="S35" s="94"/>
-      <c r="T35" s="94"/>
-      <c r="U35" s="94"/>
-      <c r="V35" s="94"/>
-      <c r="W35" s="94"/>
-      <c r="X35" s="94"/>
+      <c r="Q35" s="103"/>
+      <c r="R35" s="103"/>
+      <c r="S35" s="103"/>
+      <c r="T35" s="103"/>
+      <c r="U35" s="103"/>
+      <c r="V35" s="103"/>
+      <c r="W35" s="103"/>
+      <c r="X35" s="103"/>
     </row>
     <row r="36" spans="1:24">
       <c r="A36" s="3"/>
-      <c r="B36" s="94"/>
-      <c r="C36" s="94"/>
-      <c r="D36" s="94"/>
-      <c r="E36" s="94"/>
-      <c r="F36" s="94"/>
-      <c r="G36" s="94"/>
-      <c r="H36" s="94"/>
-      <c r="I36" s="96"/>
-      <c r="J36" s="97"/>
-      <c r="K36" s="97"/>
-      <c r="L36" s="98"/>
-      <c r="M36" s="94"/>
-      <c r="N36" s="94"/>
-      <c r="O36" s="94"/>
-      <c r="P36" s="94"/>
-      <c r="Q36" s="94"/>
-      <c r="R36" s="94"/>
-      <c r="S36" s="94"/>
-      <c r="T36" s="94"/>
-      <c r="U36" s="94"/>
-      <c r="V36" s="94"/>
-      <c r="W36" s="94"/>
-      <c r="X36" s="94"/>
+      <c r="B36" s="103"/>
+      <c r="C36" s="103"/>
+      <c r="D36" s="103"/>
+      <c r="E36" s="103"/>
+      <c r="F36" s="103"/>
+      <c r="G36" s="103"/>
+      <c r="H36" s="103"/>
+      <c r="I36" s="104"/>
+      <c r="J36" s="105"/>
+      <c r="K36" s="105"/>
+      <c r="L36" s="106"/>
+      <c r="M36" s="103"/>
+      <c r="N36" s="103"/>
+      <c r="O36" s="103"/>
+      <c r="P36" s="103"/>
+      <c r="Q36" s="103"/>
+      <c r="R36" s="103"/>
+      <c r="S36" s="103"/>
+      <c r="T36" s="103"/>
+      <c r="U36" s="103"/>
+      <c r="V36" s="103"/>
+      <c r="W36" s="103"/>
+      <c r="X36" s="103"/>
     </row>
     <row r="37" spans="1:24">
       <c r="A37" s="3"/>
-      <c r="B37" s="94"/>
-      <c r="C37" s="94"/>
-      <c r="D37" s="94"/>
-      <c r="E37" s="94"/>
-      <c r="F37" s="94"/>
-      <c r="G37" s="94"/>
-      <c r="H37" s="94"/>
-      <c r="I37" s="96"/>
-      <c r="J37" s="97"/>
-      <c r="K37" s="97"/>
-      <c r="L37" s="98"/>
-      <c r="M37" s="94"/>
-      <c r="N37" s="94"/>
-      <c r="O37" s="94"/>
-      <c r="P37" s="94"/>
-      <c r="Q37" s="94"/>
-      <c r="R37" s="94"/>
-      <c r="S37" s="94"/>
-      <c r="T37" s="94"/>
-      <c r="U37" s="94"/>
-      <c r="V37" s="94"/>
-      <c r="W37" s="94"/>
-      <c r="X37" s="94"/>
+      <c r="B37" s="103"/>
+      <c r="C37" s="103"/>
+      <c r="D37" s="103"/>
+      <c r="E37" s="103"/>
+      <c r="F37" s="103"/>
+      <c r="G37" s="103"/>
+      <c r="H37" s="103"/>
+      <c r="I37" s="104"/>
+      <c r="J37" s="105"/>
+      <c r="K37" s="105"/>
+      <c r="L37" s="106"/>
+      <c r="M37" s="103"/>
+      <c r="N37" s="103"/>
+      <c r="O37" s="103"/>
+      <c r="P37" s="103"/>
+      <c r="Q37" s="103"/>
+      <c r="R37" s="103"/>
+      <c r="S37" s="103"/>
+      <c r="T37" s="103"/>
+      <c r="U37" s="103"/>
+      <c r="V37" s="103"/>
+      <c r="W37" s="103"/>
+      <c r="X37" s="103"/>
     </row>
     <row r="38" spans="1:24">
       <c r="A38" s="3"/>
-      <c r="B38" s="94"/>
-      <c r="C38" s="94"/>
-      <c r="D38" s="94"/>
-      <c r="E38" s="94"/>
-      <c r="F38" s="94"/>
-      <c r="G38" s="94"/>
-      <c r="H38" s="94"/>
-      <c r="I38" s="96"/>
-      <c r="J38" s="97"/>
-      <c r="K38" s="97"/>
-      <c r="L38" s="98"/>
-      <c r="M38" s="94"/>
-      <c r="N38" s="94"/>
-      <c r="O38" s="94"/>
-      <c r="P38" s="94"/>
-      <c r="Q38" s="94"/>
-      <c r="R38" s="94"/>
-      <c r="S38" s="94"/>
-      <c r="T38" s="94"/>
-      <c r="U38" s="94"/>
-      <c r="V38" s="94"/>
-      <c r="W38" s="94"/>
-      <c r="X38" s="94"/>
+      <c r="B38" s="103"/>
+      <c r="C38" s="103"/>
+      <c r="D38" s="103"/>
+      <c r="E38" s="103"/>
+      <c r="F38" s="103"/>
+      <c r="G38" s="103"/>
+      <c r="H38" s="103"/>
+      <c r="I38" s="104"/>
+      <c r="J38" s="105"/>
+      <c r="K38" s="105"/>
+      <c r="L38" s="106"/>
+      <c r="M38" s="103"/>
+      <c r="N38" s="103"/>
+      <c r="O38" s="103"/>
+      <c r="P38" s="103"/>
+      <c r="Q38" s="103"/>
+      <c r="R38" s="103"/>
+      <c r="S38" s="103"/>
+      <c r="T38" s="103"/>
+      <c r="U38" s="103"/>
+      <c r="V38" s="103"/>
+      <c r="W38" s="103"/>
+      <c r="X38" s="103"/>
     </row>
     <row r="39" spans="1:24">
       <c r="A39" s="3"/>
-      <c r="B39" s="94"/>
-      <c r="C39" s="94"/>
-      <c r="D39" s="94"/>
-      <c r="E39" s="94"/>
-      <c r="F39" s="94"/>
-      <c r="G39" s="94"/>
-      <c r="H39" s="94"/>
-      <c r="I39" s="96"/>
-      <c r="J39" s="97"/>
-      <c r="K39" s="97"/>
-      <c r="L39" s="98"/>
-      <c r="M39" s="94"/>
-      <c r="N39" s="94"/>
-      <c r="O39" s="94"/>
-      <c r="P39" s="94"/>
-      <c r="Q39" s="94"/>
-      <c r="R39" s="94"/>
-      <c r="S39" s="94"/>
-      <c r="T39" s="94"/>
-      <c r="U39" s="94"/>
-      <c r="V39" s="94"/>
-      <c r="W39" s="94"/>
-      <c r="X39" s="94"/>
+      <c r="B39" s="103"/>
+      <c r="C39" s="103"/>
+      <c r="D39" s="103"/>
+      <c r="E39" s="103"/>
+      <c r="F39" s="103"/>
+      <c r="G39" s="103"/>
+      <c r="H39" s="103"/>
+      <c r="I39" s="104"/>
+      <c r="J39" s="105"/>
+      <c r="K39" s="105"/>
+      <c r="L39" s="106"/>
+      <c r="M39" s="103"/>
+      <c r="N39" s="103"/>
+      <c r="O39" s="103"/>
+      <c r="P39" s="103"/>
+      <c r="Q39" s="103"/>
+      <c r="R39" s="103"/>
+      <c r="S39" s="103"/>
+      <c r="T39" s="103"/>
+      <c r="U39" s="103"/>
+      <c r="V39" s="103"/>
+      <c r="W39" s="103"/>
+      <c r="X39" s="103"/>
     </row>
     <row r="40" spans="1:24">
       <c r="A40" s="3"/>
-      <c r="B40" s="94"/>
-      <c r="C40" s="94"/>
-      <c r="D40" s="94"/>
-      <c r="E40" s="94"/>
-      <c r="F40" s="94"/>
-      <c r="G40" s="94"/>
-      <c r="H40" s="94"/>
-      <c r="I40" s="96"/>
-      <c r="J40" s="97"/>
-      <c r="K40" s="97"/>
-      <c r="L40" s="98"/>
-      <c r="M40" s="94"/>
-      <c r="N40" s="94"/>
-      <c r="O40" s="94"/>
-      <c r="P40" s="94"/>
-      <c r="Q40" s="94"/>
-      <c r="R40" s="94"/>
-      <c r="S40" s="94"/>
-      <c r="T40" s="94"/>
-      <c r="U40" s="94"/>
-      <c r="V40" s="94"/>
-      <c r="W40" s="94"/>
-      <c r="X40" s="94"/>
+      <c r="B40" s="103"/>
+      <c r="C40" s="103"/>
+      <c r="D40" s="103"/>
+      <c r="E40" s="103"/>
+      <c r="F40" s="103"/>
+      <c r="G40" s="103"/>
+      <c r="H40" s="103"/>
+      <c r="I40" s="104"/>
+      <c r="J40" s="105"/>
+      <c r="K40" s="105"/>
+      <c r="L40" s="106"/>
+      <c r="M40" s="103"/>
+      <c r="N40" s="103"/>
+      <c r="O40" s="103"/>
+      <c r="P40" s="103"/>
+      <c r="Q40" s="103"/>
+      <c r="R40" s="103"/>
+      <c r="S40" s="103"/>
+      <c r="T40" s="103"/>
+      <c r="U40" s="103"/>
+      <c r="V40" s="103"/>
+      <c r="W40" s="103"/>
+      <c r="X40" s="103"/>
     </row>
     <row r="41" spans="1:24">
       <c r="A41" s="3"/>
-      <c r="B41" s="94"/>
-      <c r="C41" s="94"/>
-      <c r="D41" s="94"/>
-      <c r="E41" s="94"/>
-      <c r="F41" s="94"/>
-      <c r="G41" s="94"/>
-      <c r="H41" s="94"/>
-      <c r="I41" s="96"/>
-      <c r="J41" s="97"/>
-      <c r="K41" s="97"/>
-      <c r="L41" s="98"/>
-      <c r="M41" s="94"/>
-      <c r="N41" s="94"/>
-      <c r="O41" s="94"/>
-      <c r="P41" s="94"/>
-      <c r="Q41" s="94"/>
-      <c r="R41" s="94"/>
-      <c r="S41" s="94"/>
-      <c r="T41" s="94"/>
-      <c r="U41" s="94"/>
-      <c r="V41" s="94"/>
-      <c r="W41" s="94"/>
-      <c r="X41" s="94"/>
+      <c r="B41" s="103"/>
+      <c r="C41" s="103"/>
+      <c r="D41" s="103"/>
+      <c r="E41" s="103"/>
+      <c r="F41" s="103"/>
+      <c r="G41" s="103"/>
+      <c r="H41" s="103"/>
+      <c r="I41" s="104"/>
+      <c r="J41" s="105"/>
+      <c r="K41" s="105"/>
+      <c r="L41" s="106"/>
+      <c r="M41" s="103"/>
+      <c r="N41" s="103"/>
+      <c r="O41" s="103"/>
+      <c r="P41" s="103"/>
+      <c r="Q41" s="103"/>
+      <c r="R41" s="103"/>
+      <c r="S41" s="103"/>
+      <c r="T41" s="103"/>
+      <c r="U41" s="103"/>
+      <c r="V41" s="103"/>
+      <c r="W41" s="103"/>
+      <c r="X41" s="103"/>
     </row>
     <row r="42" spans="1:24">
       <c r="A42" s="3"/>
-      <c r="B42" s="94"/>
-      <c r="C42" s="94"/>
-      <c r="D42" s="94"/>
-      <c r="E42" s="94"/>
-      <c r="F42" s="94"/>
-      <c r="G42" s="94"/>
-      <c r="H42" s="94"/>
-      <c r="I42" s="96"/>
-      <c r="J42" s="97"/>
-      <c r="K42" s="97"/>
-      <c r="L42" s="98"/>
-      <c r="M42" s="94"/>
-      <c r="N42" s="94"/>
-      <c r="O42" s="94"/>
-      <c r="P42" s="94"/>
-      <c r="Q42" s="94"/>
-      <c r="R42" s="94"/>
-      <c r="S42" s="94"/>
-      <c r="T42" s="94"/>
-      <c r="U42" s="94"/>
-      <c r="V42" s="94"/>
-      <c r="W42" s="94"/>
-      <c r="X42" s="94"/>
+      <c r="B42" s="103"/>
+      <c r="C42" s="103"/>
+      <c r="D42" s="103"/>
+      <c r="E42" s="103"/>
+      <c r="F42" s="103"/>
+      <c r="G42" s="103"/>
+      <c r="H42" s="103"/>
+      <c r="I42" s="104"/>
+      <c r="J42" s="105"/>
+      <c r="K42" s="105"/>
+      <c r="L42" s="106"/>
+      <c r="M42" s="103"/>
+      <c r="N42" s="103"/>
+      <c r="O42" s="103"/>
+      <c r="P42" s="103"/>
+      <c r="Q42" s="103"/>
+      <c r="R42" s="103"/>
+      <c r="S42" s="103"/>
+      <c r="T42" s="103"/>
+      <c r="U42" s="103"/>
+      <c r="V42" s="103"/>
+      <c r="W42" s="103"/>
+      <c r="X42" s="103"/>
     </row>
     <row r="43" spans="1:24">
       <c r="A43" s="3"/>
-      <c r="B43" s="94"/>
-      <c r="C43" s="94"/>
-      <c r="D43" s="94"/>
-      <c r="E43" s="94"/>
-      <c r="F43" s="94"/>
-      <c r="G43" s="94"/>
-      <c r="H43" s="94"/>
-      <c r="I43" s="96"/>
-      <c r="J43" s="97"/>
-      <c r="K43" s="97"/>
-      <c r="L43" s="98"/>
-      <c r="M43" s="94"/>
-      <c r="N43" s="94"/>
-      <c r="O43" s="94"/>
-      <c r="P43" s="94"/>
-      <c r="Q43" s="94"/>
-      <c r="R43" s="94"/>
-      <c r="S43" s="94"/>
-      <c r="T43" s="94"/>
-      <c r="U43" s="94"/>
-      <c r="V43" s="94"/>
-      <c r="W43" s="94"/>
-      <c r="X43" s="94"/>
+      <c r="B43" s="103"/>
+      <c r="C43" s="103"/>
+      <c r="D43" s="103"/>
+      <c r="E43" s="103"/>
+      <c r="F43" s="103"/>
+      <c r="G43" s="103"/>
+      <c r="H43" s="103"/>
+      <c r="I43" s="104"/>
+      <c r="J43" s="105"/>
+      <c r="K43" s="105"/>
+      <c r="L43" s="106"/>
+      <c r="M43" s="103"/>
+      <c r="N43" s="103"/>
+      <c r="O43" s="103"/>
+      <c r="P43" s="103"/>
+      <c r="Q43" s="103"/>
+      <c r="R43" s="103"/>
+      <c r="S43" s="103"/>
+      <c r="T43" s="103"/>
+      <c r="U43" s="103"/>
+      <c r="V43" s="103"/>
+      <c r="W43" s="103"/>
+      <c r="X43" s="103"/>
     </row>
     <row r="44" spans="1:24">
       <c r="A44" s="3"/>
-      <c r="B44" s="94"/>
-      <c r="C44" s="94"/>
-      <c r="D44" s="94"/>
-      <c r="E44" s="94"/>
-      <c r="F44" s="94"/>
-      <c r="G44" s="94"/>
-      <c r="H44" s="94"/>
-      <c r="I44" s="96"/>
-      <c r="J44" s="97"/>
-      <c r="K44" s="97"/>
-      <c r="L44" s="98"/>
-      <c r="M44" s="94"/>
-      <c r="N44" s="94"/>
-      <c r="O44" s="94"/>
-      <c r="P44" s="94"/>
-      <c r="Q44" s="94"/>
-      <c r="R44" s="94"/>
-      <c r="S44" s="94"/>
-      <c r="T44" s="94"/>
-      <c r="U44" s="94"/>
-      <c r="V44" s="94"/>
-      <c r="W44" s="94"/>
-      <c r="X44" s="94"/>
+      <c r="B44" s="103"/>
+      <c r="C44" s="103"/>
+      <c r="D44" s="103"/>
+      <c r="E44" s="103"/>
+      <c r="F44" s="103"/>
+      <c r="G44" s="103"/>
+      <c r="H44" s="103"/>
+      <c r="I44" s="104"/>
+      <c r="J44" s="105"/>
+      <c r="K44" s="105"/>
+      <c r="L44" s="106"/>
+      <c r="M44" s="103"/>
+      <c r="N44" s="103"/>
+      <c r="O44" s="103"/>
+      <c r="P44" s="103"/>
+      <c r="Q44" s="103"/>
+      <c r="R44" s="103"/>
+      <c r="S44" s="103"/>
+      <c r="T44" s="103"/>
+      <c r="U44" s="103"/>
+      <c r="V44" s="103"/>
+      <c r="W44" s="103"/>
+      <c r="X44" s="103"/>
     </row>
     <row r="45" spans="1:24">
       <c r="A45" s="3"/>
-      <c r="B45" s="94"/>
-      <c r="C45" s="94"/>
-      <c r="D45" s="94"/>
-      <c r="E45" s="94"/>
-      <c r="F45" s="94"/>
-      <c r="G45" s="94"/>
-      <c r="H45" s="94"/>
-      <c r="I45" s="96"/>
-      <c r="J45" s="97"/>
-      <c r="K45" s="97"/>
-      <c r="L45" s="98"/>
-      <c r="M45" s="94"/>
-      <c r="N45" s="94"/>
-      <c r="O45" s="94"/>
-      <c r="P45" s="94"/>
-      <c r="Q45" s="94"/>
-      <c r="R45" s="94"/>
-      <c r="S45" s="94"/>
-      <c r="T45" s="94"/>
-      <c r="U45" s="94"/>
-      <c r="V45" s="94"/>
-      <c r="W45" s="94"/>
-      <c r="X45" s="94"/>
+      <c r="B45" s="103"/>
+      <c r="C45" s="103"/>
+      <c r="D45" s="103"/>
+      <c r="E45" s="103"/>
+      <c r="F45" s="103"/>
+      <c r="G45" s="103"/>
+      <c r="H45" s="103"/>
+      <c r="I45" s="104"/>
+      <c r="J45" s="105"/>
+      <c r="K45" s="105"/>
+      <c r="L45" s="106"/>
+      <c r="M45" s="103"/>
+      <c r="N45" s="103"/>
+      <c r="O45" s="103"/>
+      <c r="P45" s="103"/>
+      <c r="Q45" s="103"/>
+      <c r="R45" s="103"/>
+      <c r="S45" s="103"/>
+      <c r="T45" s="103"/>
+      <c r="U45" s="103"/>
+      <c r="V45" s="103"/>
+      <c r="W45" s="103"/>
+      <c r="X45" s="103"/>
     </row>
     <row r="46" spans="1:24">
       <c r="A46" s="3"/>
-      <c r="B46" s="94"/>
-      <c r="C46" s="94"/>
-      <c r="D46" s="94"/>
-      <c r="E46" s="94"/>
-      <c r="F46" s="94"/>
-      <c r="G46" s="94"/>
-      <c r="H46" s="94"/>
-      <c r="I46" s="96"/>
-      <c r="J46" s="97"/>
-      <c r="K46" s="97"/>
-      <c r="L46" s="98"/>
-      <c r="M46" s="94"/>
-      <c r="N46" s="94"/>
-      <c r="O46" s="94"/>
-      <c r="P46" s="94"/>
-      <c r="Q46" s="94"/>
-      <c r="R46" s="94"/>
-      <c r="S46" s="94"/>
-      <c r="T46" s="94"/>
-      <c r="U46" s="94"/>
-      <c r="V46" s="94"/>
-      <c r="W46" s="94"/>
-      <c r="X46" s="94"/>
+      <c r="B46" s="103"/>
+      <c r="C46" s="103"/>
+      <c r="D46" s="103"/>
+      <c r="E46" s="103"/>
+      <c r="F46" s="103"/>
+      <c r="G46" s="103"/>
+      <c r="H46" s="103"/>
+      <c r="I46" s="104"/>
+      <c r="J46" s="105"/>
+      <c r="K46" s="105"/>
+      <c r="L46" s="106"/>
+      <c r="M46" s="103"/>
+      <c r="N46" s="103"/>
+      <c r="O46" s="103"/>
+      <c r="P46" s="103"/>
+      <c r="Q46" s="103"/>
+      <c r="R46" s="103"/>
+      <c r="S46" s="103"/>
+      <c r="T46" s="103"/>
+      <c r="U46" s="103"/>
+      <c r="V46" s="103"/>
+      <c r="W46" s="103"/>
+      <c r="X46" s="103"/>
     </row>
     <row r="47" spans="1:24">
       <c r="A47" s="3"/>
-      <c r="B47" s="94"/>
-      <c r="C47" s="94"/>
-      <c r="D47" s="94"/>
-      <c r="E47" s="94"/>
-      <c r="F47" s="94"/>
-      <c r="G47" s="94"/>
-      <c r="H47" s="94"/>
-      <c r="I47" s="96"/>
-      <c r="J47" s="97"/>
-      <c r="K47" s="97"/>
-      <c r="L47" s="98"/>
-      <c r="M47" s="94"/>
-      <c r="N47" s="94"/>
-      <c r="O47" s="94"/>
-      <c r="P47" s="94"/>
-      <c r="Q47" s="94"/>
-      <c r="R47" s="94"/>
-      <c r="S47" s="94"/>
-      <c r="T47" s="94"/>
-      <c r="U47" s="94"/>
-      <c r="V47" s="94"/>
-      <c r="W47" s="94"/>
-      <c r="X47" s="94"/>
+      <c r="B47" s="103"/>
+      <c r="C47" s="103"/>
+      <c r="D47" s="103"/>
+      <c r="E47" s="103"/>
+      <c r="F47" s="103"/>
+      <c r="G47" s="103"/>
+      <c r="H47" s="103"/>
+      <c r="I47" s="104"/>
+      <c r="J47" s="105"/>
+      <c r="K47" s="105"/>
+      <c r="L47" s="106"/>
+      <c r="M47" s="103"/>
+      <c r="N47" s="103"/>
+      <c r="O47" s="103"/>
+      <c r="P47" s="103"/>
+      <c r="Q47" s="103"/>
+      <c r="R47" s="103"/>
+      <c r="S47" s="103"/>
+      <c r="T47" s="103"/>
+      <c r="U47" s="103"/>
+      <c r="V47" s="103"/>
+      <c r="W47" s="103"/>
+      <c r="X47" s="103"/>
     </row>
     <row r="48" spans="1:24">
       <c r="A48" s="3"/>
-      <c r="B48" s="94"/>
-      <c r="C48" s="94"/>
-      <c r="D48" s="94"/>
-      <c r="E48" s="94"/>
-      <c r="F48" s="94"/>
-      <c r="G48" s="94"/>
-      <c r="H48" s="94"/>
-      <c r="I48" s="96"/>
-      <c r="J48" s="97"/>
-      <c r="K48" s="97"/>
-      <c r="L48" s="98"/>
-      <c r="M48" s="94"/>
-      <c r="N48" s="94"/>
-      <c r="O48" s="94"/>
-      <c r="P48" s="94"/>
-      <c r="Q48" s="94"/>
-      <c r="R48" s="94"/>
-      <c r="S48" s="94"/>
-      <c r="T48" s="94"/>
-      <c r="U48" s="94"/>
-      <c r="V48" s="94"/>
-      <c r="W48" s="94"/>
-      <c r="X48" s="94"/>
+      <c r="B48" s="103"/>
+      <c r="C48" s="103"/>
+      <c r="D48" s="103"/>
+      <c r="E48" s="103"/>
+      <c r="F48" s="103"/>
+      <c r="G48" s="103"/>
+      <c r="H48" s="103"/>
+      <c r="I48" s="104"/>
+      <c r="J48" s="105"/>
+      <c r="K48" s="105"/>
+      <c r="L48" s="106"/>
+      <c r="M48" s="103"/>
+      <c r="N48" s="103"/>
+      <c r="O48" s="103"/>
+      <c r="P48" s="103"/>
+      <c r="Q48" s="103"/>
+      <c r="R48" s="103"/>
+      <c r="S48" s="103"/>
+      <c r="T48" s="103"/>
+      <c r="U48" s="103"/>
+      <c r="V48" s="103"/>
+      <c r="W48" s="103"/>
+      <c r="X48" s="103"/>
     </row>
     <row r="49" spans="1:24">
       <c r="A49" s="3"/>
-      <c r="B49" s="94"/>
-      <c r="C49" s="94"/>
-      <c r="D49" s="94"/>
-      <c r="E49" s="94"/>
-      <c r="F49" s="94"/>
-      <c r="G49" s="94"/>
-      <c r="H49" s="94"/>
-      <c r="I49" s="96"/>
-      <c r="J49" s="97"/>
-      <c r="K49" s="97"/>
-      <c r="L49" s="98"/>
-      <c r="M49" s="94"/>
-      <c r="N49" s="94"/>
-      <c r="O49" s="94"/>
-      <c r="P49" s="94"/>
-      <c r="Q49" s="94"/>
-      <c r="R49" s="94"/>
-      <c r="S49" s="94"/>
-      <c r="T49" s="94"/>
-      <c r="U49" s="94"/>
-      <c r="V49" s="94"/>
-      <c r="W49" s="94"/>
-      <c r="X49" s="94"/>
+      <c r="B49" s="103"/>
+      <c r="C49" s="103"/>
+      <c r="D49" s="103"/>
+      <c r="E49" s="103"/>
+      <c r="F49" s="103"/>
+      <c r="G49" s="103"/>
+      <c r="H49" s="103"/>
+      <c r="I49" s="104"/>
+      <c r="J49" s="105"/>
+      <c r="K49" s="105"/>
+      <c r="L49" s="106"/>
+      <c r="M49" s="103"/>
+      <c r="N49" s="103"/>
+      <c r="O49" s="103"/>
+      <c r="P49" s="103"/>
+      <c r="Q49" s="103"/>
+      <c r="R49" s="103"/>
+      <c r="S49" s="103"/>
+      <c r="T49" s="103"/>
+      <c r="U49" s="103"/>
+      <c r="V49" s="103"/>
+      <c r="W49" s="103"/>
+      <c r="X49" s="103"/>
     </row>
     <row r="50" spans="1:24">
       <c r="A50" s="3"/>
-      <c r="B50" s="94"/>
-      <c r="C50" s="94"/>
-      <c r="D50" s="94"/>
-      <c r="E50" s="94"/>
-      <c r="F50" s="94"/>
-      <c r="G50" s="94"/>
-      <c r="H50" s="94"/>
-      <c r="I50" s="96"/>
-      <c r="J50" s="97"/>
-      <c r="K50" s="97"/>
-      <c r="L50" s="98"/>
-      <c r="M50" s="94"/>
-      <c r="N50" s="94"/>
-      <c r="O50" s="94"/>
-      <c r="P50" s="94"/>
-      <c r="Q50" s="94"/>
-      <c r="R50" s="94"/>
-      <c r="S50" s="94"/>
-      <c r="T50" s="94"/>
-      <c r="U50" s="94"/>
-      <c r="V50" s="94"/>
-      <c r="W50" s="94"/>
-      <c r="X50" s="94"/>
+      <c r="B50" s="103"/>
+      <c r="C50" s="103"/>
+      <c r="D50" s="103"/>
+      <c r="E50" s="103"/>
+      <c r="F50" s="103"/>
+      <c r="G50" s="103"/>
+      <c r="H50" s="103"/>
+      <c r="I50" s="104"/>
+      <c r="J50" s="105"/>
+      <c r="K50" s="105"/>
+      <c r="L50" s="106"/>
+      <c r="M50" s="103"/>
+      <c r="N50" s="103"/>
+      <c r="O50" s="103"/>
+      <c r="P50" s="103"/>
+      <c r="Q50" s="103"/>
+      <c r="R50" s="103"/>
+      <c r="S50" s="103"/>
+      <c r="T50" s="103"/>
+      <c r="U50" s="103"/>
+      <c r="V50" s="103"/>
+      <c r="W50" s="103"/>
+      <c r="X50" s="103"/>
     </row>
     <row r="51" spans="1:24">
       <c r="A51" s="3"/>
-      <c r="B51" s="94"/>
-      <c r="C51" s="94"/>
-      <c r="D51" s="94"/>
-      <c r="E51" s="94"/>
-      <c r="F51" s="94"/>
-      <c r="G51" s="94"/>
-      <c r="H51" s="94"/>
-      <c r="I51" s="96"/>
-      <c r="J51" s="97"/>
-      <c r="K51" s="97"/>
-      <c r="L51" s="98"/>
-      <c r="M51" s="94"/>
-      <c r="N51" s="94"/>
-      <c r="O51" s="94"/>
-      <c r="P51" s="94"/>
-      <c r="Q51" s="94"/>
-      <c r="R51" s="94"/>
-      <c r="S51" s="94"/>
-      <c r="T51" s="94"/>
-      <c r="U51" s="94"/>
-      <c r="V51" s="94"/>
-      <c r="W51" s="94"/>
-      <c r="X51" s="94"/>
+      <c r="B51" s="103"/>
+      <c r="C51" s="103"/>
+      <c r="D51" s="103"/>
+      <c r="E51" s="103"/>
+      <c r="F51" s="103"/>
+      <c r="G51" s="103"/>
+      <c r="H51" s="103"/>
+      <c r="I51" s="104"/>
+      <c r="J51" s="105"/>
+      <c r="K51" s="105"/>
+      <c r="L51" s="106"/>
+      <c r="M51" s="103"/>
+      <c r="N51" s="103"/>
+      <c r="O51" s="103"/>
+      <c r="P51" s="103"/>
+      <c r="Q51" s="103"/>
+      <c r="R51" s="103"/>
+      <c r="S51" s="103"/>
+      <c r="T51" s="103"/>
+      <c r="U51" s="103"/>
+      <c r="V51" s="103"/>
+      <c r="W51" s="103"/>
+      <c r="X51" s="103"/>
     </row>
     <row r="52" spans="1:24">
       <c r="A52" s="3"/>
-      <c r="B52" s="94"/>
-      <c r="C52" s="94"/>
-      <c r="D52" s="94"/>
-      <c r="E52" s="94"/>
-      <c r="F52" s="94"/>
-      <c r="G52" s="94"/>
-      <c r="H52" s="94"/>
-      <c r="I52" s="96"/>
-      <c r="J52" s="97"/>
-      <c r="K52" s="97"/>
-      <c r="L52" s="98"/>
-      <c r="M52" s="94"/>
-      <c r="N52" s="94"/>
-      <c r="O52" s="94"/>
-      <c r="P52" s="94"/>
-      <c r="Q52" s="94"/>
-      <c r="R52" s="94"/>
-      <c r="S52" s="94"/>
-      <c r="T52" s="94"/>
-      <c r="U52" s="94"/>
-      <c r="V52" s="94"/>
-      <c r="W52" s="94"/>
-      <c r="X52" s="94"/>
+      <c r="B52" s="103"/>
+      <c r="C52" s="103"/>
+      <c r="D52" s="103"/>
+      <c r="E52" s="103"/>
+      <c r="F52" s="103"/>
+      <c r="G52" s="103"/>
+      <c r="H52" s="103"/>
+      <c r="I52" s="104"/>
+      <c r="J52" s="105"/>
+      <c r="K52" s="105"/>
+      <c r="L52" s="106"/>
+      <c r="M52" s="103"/>
+      <c r="N52" s="103"/>
+      <c r="O52" s="103"/>
+      <c r="P52" s="103"/>
+      <c r="Q52" s="103"/>
+      <c r="R52" s="103"/>
+      <c r="S52" s="103"/>
+      <c r="T52" s="103"/>
+      <c r="U52" s="103"/>
+      <c r="V52" s="103"/>
+      <c r="W52" s="103"/>
+      <c r="X52" s="103"/>
     </row>
     <row r="53" spans="1:24">
       <c r="A53" s="3"/>
-      <c r="B53" s="94"/>
-      <c r="C53" s="94"/>
-      <c r="D53" s="94"/>
-      <c r="E53" s="94"/>
-      <c r="F53" s="94"/>
-      <c r="G53" s="94"/>
-      <c r="H53" s="94"/>
-      <c r="I53" s="94"/>
-      <c r="J53" s="94"/>
-      <c r="K53" s="94"/>
-      <c r="L53" s="94"/>
-      <c r="M53" s="94"/>
-      <c r="N53" s="94"/>
-      <c r="O53" s="94"/>
-      <c r="P53" s="94"/>
-      <c r="Q53" s="94"/>
-      <c r="R53" s="94"/>
-      <c r="S53" s="94"/>
-      <c r="T53" s="94"/>
-      <c r="U53" s="94"/>
-      <c r="V53" s="94"/>
-      <c r="W53" s="94"/>
-      <c r="X53" s="94"/>
+      <c r="B53" s="103"/>
+      <c r="C53" s="103"/>
+      <c r="D53" s="103"/>
+      <c r="E53" s="103"/>
+      <c r="F53" s="103"/>
+      <c r="G53" s="103"/>
+      <c r="H53" s="103"/>
+      <c r="I53" s="103"/>
+      <c r="J53" s="103"/>
+      <c r="K53" s="103"/>
+      <c r="L53" s="103"/>
+      <c r="M53" s="103"/>
+      <c r="N53" s="103"/>
+      <c r="O53" s="103"/>
+      <c r="P53" s="103"/>
+      <c r="Q53" s="103"/>
+      <c r="R53" s="103"/>
+      <c r="S53" s="103"/>
+      <c r="T53" s="103"/>
+      <c r="U53" s="103"/>
+      <c r="V53" s="103"/>
+      <c r="W53" s="103"/>
+      <c r="X53" s="103"/>
     </row>
   </sheetData>
   <mergeCells count="256">
+    <mergeCell ref="F51:H51"/>
+    <mergeCell ref="F52:H52"/>
+    <mergeCell ref="F53:H53"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="F48:H48"/>
+    <mergeCell ref="F49:H49"/>
+    <mergeCell ref="F50:H50"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="F44:H44"/>
+    <mergeCell ref="F45:H45"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="P50:X50"/>
+    <mergeCell ref="P51:X51"/>
+    <mergeCell ref="P52:X52"/>
+    <mergeCell ref="P53:X53"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="P45:X45"/>
+    <mergeCell ref="P46:X46"/>
+    <mergeCell ref="P47:X47"/>
+    <mergeCell ref="P48:X48"/>
+    <mergeCell ref="P49:X49"/>
+    <mergeCell ref="P40:X40"/>
+    <mergeCell ref="P41:X41"/>
+    <mergeCell ref="P42:X42"/>
+    <mergeCell ref="P35:X35"/>
+    <mergeCell ref="P36:X36"/>
+    <mergeCell ref="P37:X37"/>
+    <mergeCell ref="P38:X38"/>
+    <mergeCell ref="P39:X39"/>
+    <mergeCell ref="P21:X21"/>
+    <mergeCell ref="P22:X22"/>
+    <mergeCell ref="P23:X23"/>
+    <mergeCell ref="P33:X33"/>
+    <mergeCell ref="P34:X34"/>
+    <mergeCell ref="P28:X28"/>
+    <mergeCell ref="P29:X29"/>
+    <mergeCell ref="P32:X32"/>
+    <mergeCell ref="P30:X30"/>
+    <mergeCell ref="P31:X31"/>
+    <mergeCell ref="P24:X24"/>
+    <mergeCell ref="P13:X13"/>
+    <mergeCell ref="P14:X14"/>
+    <mergeCell ref="P15:X15"/>
+    <mergeCell ref="P25:X25"/>
+    <mergeCell ref="P26:X26"/>
+    <mergeCell ref="P27:X27"/>
+    <mergeCell ref="P43:X43"/>
+    <mergeCell ref="I50:L50"/>
+    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="I36:L36"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="I33:L33"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="P44:X44"/>
+    <mergeCell ref="I51:L51"/>
+    <mergeCell ref="I52:L52"/>
+    <mergeCell ref="I53:L53"/>
+    <mergeCell ref="P4:X4"/>
+    <mergeCell ref="P5:X5"/>
+    <mergeCell ref="P6:X6"/>
+    <mergeCell ref="P7:X7"/>
+    <mergeCell ref="P8:X8"/>
+    <mergeCell ref="P9:X9"/>
+    <mergeCell ref="P10:X10"/>
+    <mergeCell ref="P11:X11"/>
+    <mergeCell ref="P17:X17"/>
+    <mergeCell ref="P18:X18"/>
+    <mergeCell ref="P19:X19"/>
+    <mergeCell ref="P20:X20"/>
+    <mergeCell ref="I45:L45"/>
+    <mergeCell ref="I46:L46"/>
+    <mergeCell ref="I47:L47"/>
+    <mergeCell ref="I48:L48"/>
+    <mergeCell ref="I49:L49"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="I41:L41"/>
+    <mergeCell ref="I42:L42"/>
+    <mergeCell ref="I44:L44"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="I43:L43"/>
+    <mergeCell ref="M50:O50"/>
+    <mergeCell ref="M51:O51"/>
+    <mergeCell ref="M52:O52"/>
+    <mergeCell ref="M53:O53"/>
+    <mergeCell ref="I4:L4"/>
+    <mergeCell ref="I5:L5"/>
+    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="I7:L7"/>
+    <mergeCell ref="I8:L8"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="I10:L10"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="M45:O45"/>
+    <mergeCell ref="M46:O46"/>
+    <mergeCell ref="M47:O47"/>
+    <mergeCell ref="M48:O48"/>
+    <mergeCell ref="M49:O49"/>
+    <mergeCell ref="M40:O40"/>
+    <mergeCell ref="M41:O41"/>
+    <mergeCell ref="M42:O42"/>
+    <mergeCell ref="M25:O25"/>
+    <mergeCell ref="M26:O26"/>
+    <mergeCell ref="M27:O27"/>
+    <mergeCell ref="M43:O43"/>
+    <mergeCell ref="P2:X3"/>
+    <mergeCell ref="P16:X16"/>
+    <mergeCell ref="M44:O44"/>
+    <mergeCell ref="M35:O35"/>
+    <mergeCell ref="M36:O36"/>
+    <mergeCell ref="M37:O37"/>
+    <mergeCell ref="M38:O38"/>
+    <mergeCell ref="M39:O39"/>
+    <mergeCell ref="M21:O21"/>
+    <mergeCell ref="M22:O22"/>
+    <mergeCell ref="M23:O23"/>
+    <mergeCell ref="M33:O33"/>
+    <mergeCell ref="M34:O34"/>
+    <mergeCell ref="M28:O28"/>
+    <mergeCell ref="M29:O29"/>
+    <mergeCell ref="M32:O32"/>
+    <mergeCell ref="M30:O30"/>
+    <mergeCell ref="M31:O31"/>
+    <mergeCell ref="M24:O24"/>
+    <mergeCell ref="P12:X12"/>
     <mergeCell ref="I3:L3"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="F3:H3"/>
@@ -10790,238 +11022,6 @@
     <mergeCell ref="M13:O13"/>
     <mergeCell ref="M14:O14"/>
     <mergeCell ref="M15:O15"/>
-    <mergeCell ref="M25:O25"/>
-    <mergeCell ref="M26:O26"/>
-    <mergeCell ref="M27:O27"/>
-    <mergeCell ref="M43:O43"/>
-    <mergeCell ref="P2:X3"/>
-    <mergeCell ref="P16:X16"/>
-    <mergeCell ref="M44:O44"/>
-    <mergeCell ref="M35:O35"/>
-    <mergeCell ref="M36:O36"/>
-    <mergeCell ref="M37:O37"/>
-    <mergeCell ref="M38:O38"/>
-    <mergeCell ref="M39:O39"/>
-    <mergeCell ref="M21:O21"/>
-    <mergeCell ref="M22:O22"/>
-    <mergeCell ref="M23:O23"/>
-    <mergeCell ref="M33:O33"/>
-    <mergeCell ref="M34:O34"/>
-    <mergeCell ref="M28:O28"/>
-    <mergeCell ref="M29:O29"/>
-    <mergeCell ref="M32:O32"/>
-    <mergeCell ref="M30:O30"/>
-    <mergeCell ref="M31:O31"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="P12:X12"/>
-    <mergeCell ref="M50:O50"/>
-    <mergeCell ref="M51:O51"/>
-    <mergeCell ref="M52:O52"/>
-    <mergeCell ref="M53:O53"/>
-    <mergeCell ref="I4:L4"/>
-    <mergeCell ref="I5:L5"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="I7:L7"/>
-    <mergeCell ref="I8:L8"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="M45:O45"/>
-    <mergeCell ref="M46:O46"/>
-    <mergeCell ref="M47:O47"/>
-    <mergeCell ref="M48:O48"/>
-    <mergeCell ref="M49:O49"/>
-    <mergeCell ref="M40:O40"/>
-    <mergeCell ref="M41:O41"/>
-    <mergeCell ref="M42:O42"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="I27:L27"/>
-    <mergeCell ref="I43:L43"/>
-    <mergeCell ref="I51:L51"/>
-    <mergeCell ref="I52:L52"/>
-    <mergeCell ref="I53:L53"/>
-    <mergeCell ref="P4:X4"/>
-    <mergeCell ref="P5:X5"/>
-    <mergeCell ref="P6:X6"/>
-    <mergeCell ref="P7:X7"/>
-    <mergeCell ref="P8:X8"/>
-    <mergeCell ref="P9:X9"/>
-    <mergeCell ref="P10:X10"/>
-    <mergeCell ref="P11:X11"/>
-    <mergeCell ref="P17:X17"/>
-    <mergeCell ref="P18:X18"/>
-    <mergeCell ref="P19:X19"/>
-    <mergeCell ref="P20:X20"/>
-    <mergeCell ref="I45:L45"/>
-    <mergeCell ref="I46:L46"/>
-    <mergeCell ref="I47:L47"/>
-    <mergeCell ref="I48:L48"/>
-    <mergeCell ref="I49:L49"/>
-    <mergeCell ref="I40:L40"/>
-    <mergeCell ref="I41:L41"/>
-    <mergeCell ref="I42:L42"/>
-    <mergeCell ref="I44:L44"/>
-    <mergeCell ref="P13:X13"/>
-    <mergeCell ref="P14:X14"/>
-    <mergeCell ref="P15:X15"/>
-    <mergeCell ref="P25:X25"/>
-    <mergeCell ref="P26:X26"/>
-    <mergeCell ref="P27:X27"/>
-    <mergeCell ref="P43:X43"/>
-    <mergeCell ref="I50:L50"/>
-    <mergeCell ref="I35:L35"/>
-    <mergeCell ref="I36:L36"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="I33:L33"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="P44:X44"/>
-    <mergeCell ref="P35:X35"/>
-    <mergeCell ref="P36:X36"/>
-    <mergeCell ref="P37:X37"/>
-    <mergeCell ref="P38:X38"/>
-    <mergeCell ref="P39:X39"/>
-    <mergeCell ref="P21:X21"/>
-    <mergeCell ref="P22:X22"/>
-    <mergeCell ref="P23:X23"/>
-    <mergeCell ref="P33:X33"/>
-    <mergeCell ref="P34:X34"/>
-    <mergeCell ref="P28:X28"/>
-    <mergeCell ref="P29:X29"/>
-    <mergeCell ref="P32:X32"/>
-    <mergeCell ref="P30:X30"/>
-    <mergeCell ref="P31:X31"/>
-    <mergeCell ref="P24:X24"/>
-    <mergeCell ref="P50:X50"/>
-    <mergeCell ref="P51:X51"/>
-    <mergeCell ref="P52:X52"/>
-    <mergeCell ref="P53:X53"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="P45:X45"/>
-    <mergeCell ref="P46:X46"/>
-    <mergeCell ref="P47:X47"/>
-    <mergeCell ref="P48:X48"/>
-    <mergeCell ref="P49:X49"/>
-    <mergeCell ref="P40:X40"/>
-    <mergeCell ref="P41:X41"/>
-    <mergeCell ref="P42:X42"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="F44:H44"/>
-    <mergeCell ref="F45:H45"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="F51:H51"/>
-    <mergeCell ref="F52:H52"/>
-    <mergeCell ref="F53:H53"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="F48:H48"/>
-    <mergeCell ref="F49:H49"/>
-    <mergeCell ref="F50:H50"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="F43:H43"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11067,14 +11067,14 @@
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="B8" s="99" t="s">
+      <c r="B8" s="113" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="97"/>
-      <c r="D8" s="97"/>
-      <c r="E8" s="97"/>
-      <c r="F8" s="97"/>
-      <c r="G8" s="98"/>
+      <c r="C8" s="105"/>
+      <c r="D8" s="105"/>
+      <c r="E8" s="105"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="106"/>
     </row>
     <row r="9" spans="1:7">
       <c r="B9" s="116"/>
@@ -11779,22 +11779,22 @@
       <c r="N154" s="88"/>
     </row>
     <row r="155" spans="3:26">
-      <c r="D155" s="99" t="s">
+      <c r="D155" s="113" t="s">
         <v>365</v>
       </c>
-      <c r="E155" s="97"/>
-      <c r="F155" s="97"/>
-      <c r="G155" s="97"/>
-      <c r="H155" s="97"/>
-      <c r="I155" s="98"/>
-      <c r="L155" s="99" t="s">
+      <c r="E155" s="105"/>
+      <c r="F155" s="105"/>
+      <c r="G155" s="105"/>
+      <c r="H155" s="105"/>
+      <c r="I155" s="106"/>
+      <c r="L155" s="113" t="s">
         <v>366</v>
       </c>
-      <c r="M155" s="97"/>
-      <c r="N155" s="97"/>
-      <c r="O155" s="97"/>
-      <c r="P155" s="97"/>
-      <c r="Q155" s="98"/>
+      <c r="M155" s="105"/>
+      <c r="N155" s="105"/>
+      <c r="O155" s="105"/>
+      <c r="P155" s="105"/>
+      <c r="Q155" s="106"/>
       <c r="S155" t="s">
         <v>363</v>
       </c>
@@ -11879,25 +11879,25 @@
       </c>
     </row>
     <row r="163" spans="3:17" ht="14.25" customHeight="1">
-      <c r="D163" s="99" t="s">
+      <c r="D163" s="113" t="s">
         <v>352</v>
       </c>
-      <c r="E163" s="100"/>
-      <c r="F163" s="100"/>
-      <c r="G163" s="100"/>
-      <c r="H163" s="100"/>
-      <c r="I163" s="101"/>
+      <c r="E163" s="114"/>
+      <c r="F163" s="114"/>
+      <c r="G163" s="114"/>
+      <c r="H163" s="114"/>
+      <c r="I163" s="115"/>
       <c r="K163" t="s">
         <v>244</v>
       </c>
-      <c r="L163" s="99" t="s">
+      <c r="L163" s="113" t="s">
         <v>353</v>
       </c>
-      <c r="M163" s="100"/>
-      <c r="N163" s="100"/>
-      <c r="O163" s="100"/>
-      <c r="P163" s="100"/>
-      <c r="Q163" s="101"/>
+      <c r="M163" s="114"/>
+      <c r="N163" s="114"/>
+      <c r="O163" s="114"/>
+      <c r="P163" s="114"/>
+      <c r="Q163" s="115"/>
     </row>
     <row r="164" spans="3:17">
       <c r="D164" s="133"/>
@@ -12138,17 +12138,17 @@
       </c>
     </row>
     <row r="214" spans="1:10">
-      <c r="B214" s="99" t="s">
+      <c r="B214" s="113" t="s">
         <v>360</v>
       </c>
-      <c r="C214" s="97"/>
-      <c r="D214" s="97"/>
-      <c r="E214" s="97"/>
-      <c r="F214" s="97"/>
-      <c r="G214" s="97"/>
-      <c r="H214" s="97"/>
-      <c r="I214" s="97"/>
-      <c r="J214" s="98"/>
+      <c r="C214" s="105"/>
+      <c r="D214" s="105"/>
+      <c r="E214" s="105"/>
+      <c r="F214" s="105"/>
+      <c r="G214" s="105"/>
+      <c r="H214" s="105"/>
+      <c r="I214" s="105"/>
+      <c r="J214" s="106"/>
     </row>
     <row r="215" spans="1:10">
       <c r="B215" s="119"/>
@@ -13234,15 +13234,15 @@
       <c r="H2" s="13"/>
       <c r="I2" s="13"/>
       <c r="J2" s="15"/>
-      <c r="N2" s="99" t="s">
+      <c r="N2" s="113" t="s">
         <v>348</v>
       </c>
-      <c r="O2" s="97"/>
-      <c r="P2" s="97"/>
-      <c r="Q2" s="97"/>
-      <c r="R2" s="97"/>
-      <c r="S2" s="97"/>
-      <c r="T2" s="98"/>
+      <c r="O2" s="105"/>
+      <c r="P2" s="105"/>
+      <c r="Q2" s="105"/>
+      <c r="R2" s="105"/>
+      <c r="S2" s="105"/>
+      <c r="T2" s="106"/>
     </row>
     <row r="3" spans="1:20" ht="15.75">
       <c r="B3" s="26" t="s">
@@ -13412,15 +13412,15 @@
       <c r="H11" s="14"/>
       <c r="I11" s="14"/>
       <c r="J11" s="16"/>
-      <c r="N11" s="99" t="s">
+      <c r="N11" s="113" t="s">
         <v>349</v>
       </c>
-      <c r="O11" s="97"/>
-      <c r="P11" s="97"/>
-      <c r="Q11" s="97"/>
-      <c r="R11" s="97"/>
-      <c r="S11" s="97"/>
-      <c r="T11" s="98"/>
+      <c r="O11" s="105"/>
+      <c r="P11" s="105"/>
+      <c r="Q11" s="105"/>
+      <c r="R11" s="105"/>
+      <c r="S11" s="105"/>
+      <c r="T11" s="106"/>
     </row>
     <row r="12" spans="1:20" ht="15.75">
       <c r="B12" s="26" t="s">
@@ -13590,15 +13590,15 @@
       <c r="H20" s="14"/>
       <c r="I20" s="14"/>
       <c r="J20" s="16"/>
-      <c r="N20" s="99" t="s">
+      <c r="N20" s="113" t="s">
         <v>350</v>
       </c>
-      <c r="O20" s="97"/>
-      <c r="P20" s="97"/>
-      <c r="Q20" s="97"/>
-      <c r="R20" s="97"/>
-      <c r="S20" s="97"/>
-      <c r="T20" s="98"/>
+      <c r="O20" s="105"/>
+      <c r="P20" s="105"/>
+      <c r="Q20" s="105"/>
+      <c r="R20" s="105"/>
+      <c r="S20" s="105"/>
+      <c r="T20" s="106"/>
     </row>
     <row r="21" spans="2:20" ht="15.75">
       <c r="B21" s="27" t="s">
@@ -13876,17 +13876,17 @@
       </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="B40" s="99" t="s">
+      <c r="B40" s="113" t="s">
         <v>182</v>
       </c>
-      <c r="C40" s="97"/>
-      <c r="D40" s="97"/>
-      <c r="E40" s="97"/>
-      <c r="F40" s="97"/>
-      <c r="G40" s="97"/>
-      <c r="H40" s="97"/>
-      <c r="I40" s="97"/>
-      <c r="J40" s="98"/>
+      <c r="C40" s="105"/>
+      <c r="D40" s="105"/>
+      <c r="E40" s="105"/>
+      <c r="F40" s="105"/>
+      <c r="G40" s="105"/>
+      <c r="H40" s="105"/>
+      <c r="I40" s="105"/>
+      <c r="J40" s="106"/>
     </row>
     <row r="41" spans="1:10">
       <c r="B41" s="119"/>

--- a/40_数据库/学习笔记_RDBMS_GaussDB.xlsx
+++ b/40_数据库/学习笔记_RDBMS_GaussDB.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67FD2EE3-F67D-4865-B63F-36AA5ADF6FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0626580-D022-447A-B508-1F03628C6608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5773,31 +5773,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>sys.diutil.int_to_bool(n =&gt; var_isExists)</t>
-  </si>
-  <si>
-    <t>7.13 转换为boolean类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>var_isExists::</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color rgb="FF000080"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>boolean</t>
-    </r>
-  </si>
-  <si>
-    <t>Insert Values var_ItemSubject</t>
-  </si>
-  <si>
     <t>Insert (FACTORY_ID, VEHICLE_CODE, ITEM_ID, SUBJECT_ID, 
                   CREATER, CREATE_TIME, MODIFYER, MODIFY_TIME)
           Values (src.FACTORY_ID, src.VEHICLE_CODE, src.ITEM_ID, src.SUBJECT_ID,
@@ -7133,6 +7108,22 @@
   </si>
   <si>
     <t>两者语法一样</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Insert Values var_ItemSubject</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.13 转换为boolean函数，可直接修改为数量的判断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sys.diutil.int_to_bool(n =&gt; var_isExists)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>if var_isExists &gt;0 then</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8001,6 +7992,48 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -8024,48 +8057,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -9133,7 +9124,7 @@
       </c>
     </row>
     <row r="2" spans="1:24" ht="18">
-      <c r="A2" s="100" t="s">
+      <c r="A2" s="114" t="s">
         <v>41</v>
       </c>
       <c r="B2" s="17" t="s">
@@ -9154,1618 +9145,1850 @@
       <c r="M2" s="11"/>
       <c r="N2" s="11"/>
       <c r="O2" s="12"/>
-      <c r="P2" s="107" t="s">
+      <c r="P2" s="102" t="s">
         <v>32</v>
       </c>
-      <c r="Q2" s="108"/>
-      <c r="R2" s="108"/>
-      <c r="S2" s="108"/>
-      <c r="T2" s="108"/>
-      <c r="U2" s="108"/>
-      <c r="V2" s="108"/>
-      <c r="W2" s="108"/>
-      <c r="X2" s="109"/>
+      <c r="Q2" s="103"/>
+      <c r="R2" s="103"/>
+      <c r="S2" s="103"/>
+      <c r="T2" s="103"/>
+      <c r="U2" s="103"/>
+      <c r="V2" s="103"/>
+      <c r="W2" s="103"/>
+      <c r="X2" s="104"/>
     </row>
     <row r="3" spans="1:24" ht="18">
-      <c r="A3" s="101"/>
-      <c r="B3" s="94" t="s">
+      <c r="A3" s="115"/>
+      <c r="B3" s="108" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="95"/>
-      <c r="D3" s="95"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="96" t="s">
+      <c r="C3" s="109"/>
+      <c r="D3" s="109"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="110" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="97"/>
-      <c r="H3" s="98"/>
-      <c r="I3" s="94" t="s">
+      <c r="G3" s="111"/>
+      <c r="H3" s="112"/>
+      <c r="I3" s="108" t="s">
         <v>34</v>
       </c>
-      <c r="J3" s="95"/>
-      <c r="K3" s="95"/>
-      <c r="L3" s="95"/>
-      <c r="M3" s="96" t="s">
+      <c r="J3" s="109"/>
+      <c r="K3" s="109"/>
+      <c r="L3" s="109"/>
+      <c r="M3" s="110" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="97"/>
-      <c r="O3" s="98"/>
-      <c r="P3" s="110"/>
-      <c r="Q3" s="111"/>
-      <c r="R3" s="111"/>
-      <c r="S3" s="111"/>
-      <c r="T3" s="111"/>
-      <c r="U3" s="111"/>
-      <c r="V3" s="111"/>
-      <c r="W3" s="111"/>
-      <c r="X3" s="112"/>
+      <c r="N3" s="111"/>
+      <c r="O3" s="112"/>
+      <c r="P3" s="105"/>
+      <c r="Q3" s="106"/>
+      <c r="R3" s="106"/>
+      <c r="S3" s="106"/>
+      <c r="T3" s="106"/>
+      <c r="U3" s="106"/>
+      <c r="V3" s="106"/>
+      <c r="W3" s="106"/>
+      <c r="X3" s="107"/>
     </row>
     <row r="4" spans="1:24">
       <c r="A4" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="103" t="s">
+      <c r="B4" s="94" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="103"/>
-      <c r="D4" s="103"/>
-      <c r="E4" s="103"/>
-      <c r="F4" s="103"/>
-      <c r="G4" s="103"/>
-      <c r="H4" s="103"/>
-      <c r="I4" s="104" t="s">
+      <c r="C4" s="94"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="94"/>
+      <c r="I4" s="96" t="s">
         <v>25</v>
       </c>
-      <c r="J4" s="105"/>
-      <c r="K4" s="105"/>
-      <c r="L4" s="106"/>
-      <c r="M4" s="103"/>
-      <c r="N4" s="103"/>
-      <c r="O4" s="103"/>
-      <c r="P4" s="103"/>
-      <c r="Q4" s="103"/>
-      <c r="R4" s="103"/>
-      <c r="S4" s="103"/>
-      <c r="T4" s="103"/>
-      <c r="U4" s="103"/>
-      <c r="V4" s="103"/>
-      <c r="W4" s="103"/>
-      <c r="X4" s="103"/>
+      <c r="J4" s="97"/>
+      <c r="K4" s="97"/>
+      <c r="L4" s="98"/>
+      <c r="M4" s="94"/>
+      <c r="N4" s="94"/>
+      <c r="O4" s="94"/>
+      <c r="P4" s="94"/>
+      <c r="Q4" s="94"/>
+      <c r="R4" s="94"/>
+      <c r="S4" s="94"/>
+      <c r="T4" s="94"/>
+      <c r="U4" s="94"/>
+      <c r="V4" s="94"/>
+      <c r="W4" s="94"/>
+      <c r="X4" s="94"/>
     </row>
     <row r="5" spans="1:24">
       <c r="A5" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="103" t="s">
+      <c r="B5" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="103"/>
-      <c r="D5" s="103"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="103" t="s">
+      <c r="C5" s="94"/>
+      <c r="D5" s="94"/>
+      <c r="E5" s="94"/>
+      <c r="F5" s="94" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="103"/>
-      <c r="H5" s="103"/>
-      <c r="I5" s="104" t="s">
+      <c r="G5" s="94"/>
+      <c r="H5" s="94"/>
+      <c r="I5" s="96" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="105"/>
-      <c r="K5" s="105"/>
-      <c r="L5" s="106"/>
-      <c r="M5" s="103" t="s">
+      <c r="J5" s="97"/>
+      <c r="K5" s="97"/>
+      <c r="L5" s="98"/>
+      <c r="M5" s="94" t="s">
         <v>36</v>
       </c>
-      <c r="N5" s="103"/>
-      <c r="O5" s="103"/>
-      <c r="P5" s="103" t="s">
+      <c r="N5" s="94"/>
+      <c r="O5" s="94"/>
+      <c r="P5" s="94" t="s">
         <v>33</v>
       </c>
-      <c r="Q5" s="103"/>
-      <c r="R5" s="103"/>
-      <c r="S5" s="103"/>
-      <c r="T5" s="103"/>
-      <c r="U5" s="103"/>
-      <c r="V5" s="103"/>
-      <c r="W5" s="103"/>
-      <c r="X5" s="103"/>
+      <c r="Q5" s="94"/>
+      <c r="R5" s="94"/>
+      <c r="S5" s="94"/>
+      <c r="T5" s="94"/>
+      <c r="U5" s="94"/>
+      <c r="V5" s="94"/>
+      <c r="W5" s="94"/>
+      <c r="X5" s="94"/>
     </row>
     <row r="6" spans="1:24">
       <c r="A6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="103" t="s">
+      <c r="B6" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="103"/>
-      <c r="D6" s="103"/>
-      <c r="E6" s="103"/>
-      <c r="F6" s="103" t="s">
+      <c r="C6" s="94"/>
+      <c r="D6" s="94"/>
+      <c r="E6" s="94"/>
+      <c r="F6" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="103"/>
-      <c r="H6" s="103"/>
-      <c r="I6" s="104" t="s">
+      <c r="G6" s="94"/>
+      <c r="H6" s="94"/>
+      <c r="I6" s="96" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="105"/>
-      <c r="K6" s="105"/>
-      <c r="L6" s="106"/>
-      <c r="M6" s="103" t="s">
+      <c r="J6" s="97"/>
+      <c r="K6" s="97"/>
+      <c r="L6" s="98"/>
+      <c r="M6" s="94" t="s">
         <v>24</v>
       </c>
-      <c r="N6" s="103"/>
-      <c r="O6" s="103"/>
-      <c r="P6" s="103"/>
-      <c r="Q6" s="103"/>
-      <c r="R6" s="103"/>
-      <c r="S6" s="103"/>
-      <c r="T6" s="103"/>
-      <c r="U6" s="103"/>
-      <c r="V6" s="103"/>
-      <c r="W6" s="103"/>
-      <c r="X6" s="103"/>
+      <c r="N6" s="94"/>
+      <c r="O6" s="94"/>
+      <c r="P6" s="94"/>
+      <c r="Q6" s="94"/>
+      <c r="R6" s="94"/>
+      <c r="S6" s="94"/>
+      <c r="T6" s="94"/>
+      <c r="U6" s="94"/>
+      <c r="V6" s="94"/>
+      <c r="W6" s="94"/>
+      <c r="X6" s="94"/>
     </row>
     <row r="7" spans="1:24">
       <c r="A7" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B7" s="103" t="s">
+      <c r="B7" s="94" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="103"/>
-      <c r="D7" s="103"/>
-      <c r="E7" s="103"/>
-      <c r="F7" s="103"/>
-      <c r="G7" s="103"/>
-      <c r="H7" s="103"/>
-      <c r="I7" s="104" t="s">
+      <c r="C7" s="94"/>
+      <c r="D7" s="94"/>
+      <c r="E7" s="94"/>
+      <c r="F7" s="94"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="94"/>
+      <c r="I7" s="96" t="s">
         <v>107</v>
       </c>
-      <c r="J7" s="105"/>
-      <c r="K7" s="105"/>
-      <c r="L7" s="106"/>
-      <c r="M7" s="103"/>
-      <c r="N7" s="103"/>
-      <c r="O7" s="103"/>
-      <c r="P7" s="103"/>
-      <c r="Q7" s="103"/>
-      <c r="R7" s="103"/>
-      <c r="S7" s="103"/>
-      <c r="T7" s="103"/>
-      <c r="U7" s="103"/>
-      <c r="V7" s="103"/>
-      <c r="W7" s="103"/>
-      <c r="X7" s="103"/>
+      <c r="J7" s="97"/>
+      <c r="K7" s="97"/>
+      <c r="L7" s="98"/>
+      <c r="M7" s="94"/>
+      <c r="N7" s="94"/>
+      <c r="O7" s="94"/>
+      <c r="P7" s="94"/>
+      <c r="Q7" s="94"/>
+      <c r="R7" s="94"/>
+      <c r="S7" s="94"/>
+      <c r="T7" s="94"/>
+      <c r="U7" s="94"/>
+      <c r="V7" s="94"/>
+      <c r="W7" s="94"/>
+      <c r="X7" s="94"/>
     </row>
     <row r="8" spans="1:24">
       <c r="A8" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="103" t="s">
+      <c r="B8" s="94" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="103"/>
-      <c r="D8" s="103"/>
-      <c r="E8" s="103"/>
-      <c r="F8" s="103" t="s">
+      <c r="C8" s="94"/>
+      <c r="D8" s="94"/>
+      <c r="E8" s="94"/>
+      <c r="F8" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="G8" s="103"/>
-      <c r="H8" s="103"/>
-      <c r="I8" s="104" t="s">
+      <c r="G8" s="94"/>
+      <c r="H8" s="94"/>
+      <c r="I8" s="96" t="s">
         <v>27</v>
       </c>
-      <c r="J8" s="105"/>
-      <c r="K8" s="105"/>
-      <c r="L8" s="106"/>
-      <c r="M8" s="103" t="s">
+      <c r="J8" s="97"/>
+      <c r="K8" s="97"/>
+      <c r="L8" s="98"/>
+      <c r="M8" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="N8" s="103"/>
-      <c r="O8" s="103"/>
-      <c r="P8" s="103" t="s">
+      <c r="N8" s="94"/>
+      <c r="O8" s="94"/>
+      <c r="P8" s="94" t="s">
         <v>37</v>
       </c>
-      <c r="Q8" s="103"/>
-      <c r="R8" s="103"/>
-      <c r="S8" s="103"/>
-      <c r="T8" s="103"/>
-      <c r="U8" s="103"/>
-      <c r="V8" s="103"/>
-      <c r="W8" s="103"/>
-      <c r="X8" s="103"/>
+      <c r="Q8" s="94"/>
+      <c r="R8" s="94"/>
+      <c r="S8" s="94"/>
+      <c r="T8" s="94"/>
+      <c r="U8" s="94"/>
+      <c r="V8" s="94"/>
+      <c r="W8" s="94"/>
+      <c r="X8" s="94"/>
     </row>
     <row r="9" spans="1:24">
       <c r="A9" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="103" t="s">
+      <c r="B9" s="94" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="103"/>
-      <c r="D9" s="103"/>
-      <c r="E9" s="103"/>
-      <c r="F9" s="103"/>
-      <c r="G9" s="103"/>
-      <c r="H9" s="103"/>
-      <c r="I9" s="104" t="s">
+      <c r="C9" s="94"/>
+      <c r="D9" s="94"/>
+      <c r="E9" s="94"/>
+      <c r="F9" s="94"/>
+      <c r="G9" s="94"/>
+      <c r="H9" s="94"/>
+      <c r="I9" s="96" t="s">
         <v>29</v>
       </c>
-      <c r="J9" s="105"/>
-      <c r="K9" s="105"/>
-      <c r="L9" s="106"/>
-      <c r="M9" s="103"/>
-      <c r="N9" s="103"/>
-      <c r="O9" s="103"/>
-      <c r="P9" s="103"/>
-      <c r="Q9" s="103"/>
-      <c r="R9" s="103"/>
-      <c r="S9" s="103"/>
-      <c r="T9" s="103"/>
-      <c r="U9" s="103"/>
-      <c r="V9" s="103"/>
-      <c r="W9" s="103"/>
-      <c r="X9" s="103"/>
+      <c r="J9" s="97"/>
+      <c r="K9" s="97"/>
+      <c r="L9" s="98"/>
+      <c r="M9" s="94"/>
+      <c r="N9" s="94"/>
+      <c r="O9" s="94"/>
+      <c r="P9" s="94"/>
+      <c r="Q9" s="94"/>
+      <c r="R9" s="94"/>
+      <c r="S9" s="94"/>
+      <c r="T9" s="94"/>
+      <c r="U9" s="94"/>
+      <c r="V9" s="94"/>
+      <c r="W9" s="94"/>
+      <c r="X9" s="94"/>
     </row>
     <row r="10" spans="1:24">
       <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="103" t="s">
+      <c r="B10" s="94" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="103"/>
-      <c r="D10" s="103"/>
-      <c r="E10" s="103"/>
-      <c r="F10" s="103" t="s">
+      <c r="C10" s="94"/>
+      <c r="D10" s="94"/>
+      <c r="E10" s="94"/>
+      <c r="F10" s="94" t="s">
         <v>38</v>
       </c>
-      <c r="G10" s="103"/>
-      <c r="H10" s="103"/>
-      <c r="I10" s="104" t="s">
+      <c r="G10" s="94"/>
+      <c r="H10" s="94"/>
+      <c r="I10" s="96" t="s">
         <v>43</v>
       </c>
-      <c r="J10" s="105"/>
-      <c r="K10" s="105"/>
-      <c r="L10" s="106"/>
-      <c r="M10" s="103" t="s">
+      <c r="J10" s="97"/>
+      <c r="K10" s="97"/>
+      <c r="L10" s="98"/>
+      <c r="M10" s="94" t="s">
         <v>39</v>
       </c>
-      <c r="N10" s="103"/>
-      <c r="O10" s="103"/>
-      <c r="P10" s="103"/>
-      <c r="Q10" s="103"/>
-      <c r="R10" s="103"/>
-      <c r="S10" s="103"/>
-      <c r="T10" s="103"/>
-      <c r="U10" s="103"/>
-      <c r="V10" s="103"/>
-      <c r="W10" s="103"/>
-      <c r="X10" s="103"/>
+      <c r="N10" s="94"/>
+      <c r="O10" s="94"/>
+      <c r="P10" s="94"/>
+      <c r="Q10" s="94"/>
+      <c r="R10" s="94"/>
+      <c r="S10" s="94"/>
+      <c r="T10" s="94"/>
+      <c r="U10" s="94"/>
+      <c r="V10" s="94"/>
+      <c r="W10" s="94"/>
+      <c r="X10" s="94"/>
     </row>
     <row r="11" spans="1:24">
       <c r="A11" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B11" s="103" t="s">
+      <c r="B11" s="94" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="103"/>
-      <c r="D11" s="103"/>
-      <c r="E11" s="103"/>
-      <c r="F11" s="103"/>
-      <c r="G11" s="103"/>
-      <c r="H11" s="103"/>
-      <c r="I11" s="104" t="s">
+      <c r="C11" s="94"/>
+      <c r="D11" s="94"/>
+      <c r="E11" s="94"/>
+      <c r="F11" s="94"/>
+      <c r="G11" s="94"/>
+      <c r="H11" s="94"/>
+      <c r="I11" s="96" t="s">
         <v>52</v>
       </c>
-      <c r="J11" s="105"/>
-      <c r="K11" s="105"/>
-      <c r="L11" s="106"/>
-      <c r="M11" s="103"/>
-      <c r="N11" s="103"/>
-      <c r="O11" s="103"/>
-      <c r="P11" s="103" t="s">
+      <c r="J11" s="97"/>
+      <c r="K11" s="97"/>
+      <c r="L11" s="98"/>
+      <c r="M11" s="94"/>
+      <c r="N11" s="94"/>
+      <c r="O11" s="94"/>
+      <c r="P11" s="94" t="s">
         <v>53</v>
       </c>
-      <c r="Q11" s="103"/>
-      <c r="R11" s="103"/>
-      <c r="S11" s="103"/>
-      <c r="T11" s="103"/>
-      <c r="U11" s="103"/>
-      <c r="V11" s="103"/>
-      <c r="W11" s="103"/>
-      <c r="X11" s="103"/>
+      <c r="Q11" s="94"/>
+      <c r="R11" s="94"/>
+      <c r="S11" s="94"/>
+      <c r="T11" s="94"/>
+      <c r="U11" s="94"/>
+      <c r="V11" s="94"/>
+      <c r="W11" s="94"/>
+      <c r="X11" s="94"/>
     </row>
     <row r="12" spans="1:24" ht="34.5" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B12" s="103" t="s">
+      <c r="B12" s="94" t="s">
         <v>92</v>
       </c>
-      <c r="C12" s="103"/>
-      <c r="D12" s="103"/>
-      <c r="E12" s="103"/>
-      <c r="F12" s="103" t="s">
+      <c r="C12" s="94"/>
+      <c r="D12" s="94"/>
+      <c r="E12" s="94"/>
+      <c r="F12" s="94" t="s">
         <v>97</v>
       </c>
-      <c r="G12" s="103"/>
-      <c r="H12" s="103"/>
-      <c r="I12" s="104" t="s">
+      <c r="G12" s="94"/>
+      <c r="H12" s="94"/>
+      <c r="I12" s="96" t="s">
         <v>98</v>
       </c>
-      <c r="J12" s="105"/>
-      <c r="K12" s="105"/>
-      <c r="L12" s="106"/>
-      <c r="M12" s="102" t="s">
+      <c r="J12" s="97"/>
+      <c r="K12" s="97"/>
+      <c r="L12" s="98"/>
+      <c r="M12" s="95" t="s">
         <v>99</v>
       </c>
-      <c r="N12" s="103"/>
-      <c r="O12" s="103"/>
-      <c r="P12" s="103"/>
-      <c r="Q12" s="103"/>
-      <c r="R12" s="103"/>
-      <c r="S12" s="103"/>
-      <c r="T12" s="103"/>
-      <c r="U12" s="103"/>
-      <c r="V12" s="103"/>
-      <c r="W12" s="103"/>
-      <c r="X12" s="103"/>
+      <c r="N12" s="94"/>
+      <c r="O12" s="94"/>
+      <c r="P12" s="94"/>
+      <c r="Q12" s="94"/>
+      <c r="R12" s="94"/>
+      <c r="S12" s="94"/>
+      <c r="T12" s="94"/>
+      <c r="U12" s="94"/>
+      <c r="V12" s="94"/>
+      <c r="W12" s="94"/>
+      <c r="X12" s="94"/>
     </row>
     <row r="13" spans="1:24">
       <c r="A13" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B13" s="103"/>
-      <c r="C13" s="103"/>
-      <c r="D13" s="103"/>
-      <c r="E13" s="103"/>
-      <c r="F13" s="103" t="s">
+      <c r="B13" s="94"/>
+      <c r="C13" s="94"/>
+      <c r="D13" s="94"/>
+      <c r="E13" s="94"/>
+      <c r="F13" s="94" t="s">
         <v>100</v>
       </c>
-      <c r="G13" s="103"/>
-      <c r="H13" s="103"/>
-      <c r="I13" s="104"/>
-      <c r="J13" s="105"/>
-      <c r="K13" s="105"/>
-      <c r="L13" s="106"/>
-      <c r="M13" s="102" t="s">
+      <c r="G13" s="94"/>
+      <c r="H13" s="94"/>
+      <c r="I13" s="96"/>
+      <c r="J13" s="97"/>
+      <c r="K13" s="97"/>
+      <c r="L13" s="98"/>
+      <c r="M13" s="95" t="s">
         <v>102</v>
       </c>
-      <c r="N13" s="103"/>
-      <c r="O13" s="103"/>
-      <c r="P13" s="103"/>
-      <c r="Q13" s="103"/>
-      <c r="R13" s="103"/>
-      <c r="S13" s="103"/>
-      <c r="T13" s="103"/>
-      <c r="U13" s="103"/>
-      <c r="V13" s="103"/>
-      <c r="W13" s="103"/>
-      <c r="X13" s="103"/>
+      <c r="N13" s="94"/>
+      <c r="O13" s="94"/>
+      <c r="P13" s="94"/>
+      <c r="Q13" s="94"/>
+      <c r="R13" s="94"/>
+      <c r="S13" s="94"/>
+      <c r="T13" s="94"/>
+      <c r="U13" s="94"/>
+      <c r="V13" s="94"/>
+      <c r="W13" s="94"/>
+      <c r="X13" s="94"/>
     </row>
     <row r="14" spans="1:24">
       <c r="A14" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B14" s="103"/>
-      <c r="C14" s="103"/>
-      <c r="D14" s="103"/>
-      <c r="E14" s="103"/>
-      <c r="F14" s="103" t="s">
+      <c r="B14" s="94"/>
+      <c r="C14" s="94"/>
+      <c r="D14" s="94"/>
+      <c r="E14" s="94"/>
+      <c r="F14" s="94" t="s">
         <v>100</v>
       </c>
-      <c r="G14" s="103"/>
-      <c r="H14" s="103"/>
-      <c r="I14" s="104"/>
-      <c r="J14" s="105"/>
-      <c r="K14" s="105"/>
-      <c r="L14" s="106"/>
-      <c r="M14" s="102" t="s">
+      <c r="G14" s="94"/>
+      <c r="H14" s="94"/>
+      <c r="I14" s="96"/>
+      <c r="J14" s="97"/>
+      <c r="K14" s="97"/>
+      <c r="L14" s="98"/>
+      <c r="M14" s="95" t="s">
         <v>103</v>
       </c>
-      <c r="N14" s="103"/>
-      <c r="O14" s="103"/>
-      <c r="P14" s="103"/>
-      <c r="Q14" s="103"/>
-      <c r="R14" s="103"/>
-      <c r="S14" s="103"/>
-      <c r="T14" s="103"/>
-      <c r="U14" s="103"/>
-      <c r="V14" s="103"/>
-      <c r="W14" s="103"/>
-      <c r="X14" s="103"/>
+      <c r="N14" s="94"/>
+      <c r="O14" s="94"/>
+      <c r="P14" s="94"/>
+      <c r="Q14" s="94"/>
+      <c r="R14" s="94"/>
+      <c r="S14" s="94"/>
+      <c r="T14" s="94"/>
+      <c r="U14" s="94"/>
+      <c r="V14" s="94"/>
+      <c r="W14" s="94"/>
+      <c r="X14" s="94"/>
     </row>
     <row r="15" spans="1:24">
       <c r="A15" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B15" s="103"/>
-      <c r="C15" s="103"/>
-      <c r="D15" s="103"/>
-      <c r="E15" s="103"/>
-      <c r="F15" s="103" t="s">
+      <c r="B15" s="94"/>
+      <c r="C15" s="94"/>
+      <c r="D15" s="94"/>
+      <c r="E15" s="94"/>
+      <c r="F15" s="94" t="s">
         <v>101</v>
       </c>
-      <c r="G15" s="103"/>
-      <c r="H15" s="103"/>
-      <c r="I15" s="104"/>
-      <c r="J15" s="105"/>
-      <c r="K15" s="105"/>
-      <c r="L15" s="106"/>
-      <c r="M15" s="102" t="s">
+      <c r="G15" s="94"/>
+      <c r="H15" s="94"/>
+      <c r="I15" s="96"/>
+      <c r="J15" s="97"/>
+      <c r="K15" s="97"/>
+      <c r="L15" s="98"/>
+      <c r="M15" s="95" t="s">
         <v>104</v>
       </c>
-      <c r="N15" s="103"/>
-      <c r="O15" s="103"/>
-      <c r="P15" s="103"/>
-      <c r="Q15" s="103"/>
-      <c r="R15" s="103"/>
-      <c r="S15" s="103"/>
-      <c r="T15" s="103"/>
-      <c r="U15" s="103"/>
-      <c r="V15" s="103"/>
-      <c r="W15" s="103"/>
-      <c r="X15" s="103"/>
+      <c r="N15" s="94"/>
+      <c r="O15" s="94"/>
+      <c r="P15" s="94"/>
+      <c r="Q15" s="94"/>
+      <c r="R15" s="94"/>
+      <c r="S15" s="94"/>
+      <c r="T15" s="94"/>
+      <c r="U15" s="94"/>
+      <c r="V15" s="94"/>
+      <c r="W15" s="94"/>
+      <c r="X15" s="94"/>
     </row>
     <row r="16" spans="1:24">
       <c r="A16" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B16" s="103" t="s">
+      <c r="B16" s="94" t="s">
         <v>106</v>
       </c>
-      <c r="C16" s="103"/>
-      <c r="D16" s="103"/>
-      <c r="E16" s="103"/>
-      <c r="F16" s="103" t="s">
+      <c r="C16" s="94"/>
+      <c r="D16" s="94"/>
+      <c r="E16" s="94"/>
+      <c r="F16" s="94" t="s">
         <v>105</v>
       </c>
-      <c r="G16" s="103"/>
-      <c r="H16" s="103"/>
-      <c r="I16" s="104" t="s">
+      <c r="G16" s="94"/>
+      <c r="H16" s="94"/>
+      <c r="I16" s="96" t="s">
         <v>86</v>
       </c>
-      <c r="J16" s="105"/>
-      <c r="K16" s="105"/>
-      <c r="L16" s="106"/>
-      <c r="M16" s="103"/>
-      <c r="N16" s="103"/>
-      <c r="O16" s="103"/>
-      <c r="P16" s="103" t="s">
+      <c r="J16" s="97"/>
+      <c r="K16" s="97"/>
+      <c r="L16" s="98"/>
+      <c r="M16" s="94"/>
+      <c r="N16" s="94"/>
+      <c r="O16" s="94"/>
+      <c r="P16" s="94" t="s">
         <v>89</v>
       </c>
-      <c r="Q16" s="103"/>
-      <c r="R16" s="103"/>
-      <c r="S16" s="103"/>
-      <c r="T16" s="103"/>
-      <c r="U16" s="103"/>
-      <c r="V16" s="103"/>
-      <c r="W16" s="103"/>
-      <c r="X16" s="103"/>
+      <c r="Q16" s="94"/>
+      <c r="R16" s="94"/>
+      <c r="S16" s="94"/>
+      <c r="T16" s="94"/>
+      <c r="U16" s="94"/>
+      <c r="V16" s="94"/>
+      <c r="W16" s="94"/>
+      <c r="X16" s="94"/>
     </row>
     <row r="17" spans="1:24">
       <c r="A17" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="103" t="s">
+      <c r="B17" s="94" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="103"/>
-      <c r="D17" s="103"/>
-      <c r="E17" s="103"/>
-      <c r="F17" s="103"/>
-      <c r="G17" s="103"/>
-      <c r="H17" s="103"/>
-      <c r="I17" s="104" t="s">
+      <c r="C17" s="94"/>
+      <c r="D17" s="94"/>
+      <c r="E17" s="94"/>
+      <c r="F17" s="94"/>
+      <c r="G17" s="94"/>
+      <c r="H17" s="94"/>
+      <c r="I17" s="96" t="s">
         <v>55</v>
       </c>
-      <c r="J17" s="105"/>
-      <c r="K17" s="105"/>
-      <c r="L17" s="106"/>
-      <c r="M17" s="103"/>
-      <c r="N17" s="103"/>
-      <c r="O17" s="103"/>
-      <c r="P17" s="103" t="s">
+      <c r="J17" s="97"/>
+      <c r="K17" s="97"/>
+      <c r="L17" s="98"/>
+      <c r="M17" s="94"/>
+      <c r="N17" s="94"/>
+      <c r="O17" s="94"/>
+      <c r="P17" s="94" t="s">
         <v>56</v>
       </c>
-      <c r="Q17" s="103"/>
-      <c r="R17" s="103"/>
-      <c r="S17" s="103"/>
-      <c r="T17" s="103"/>
-      <c r="U17" s="103"/>
-      <c r="V17" s="103"/>
-      <c r="W17" s="103"/>
-      <c r="X17" s="103"/>
+      <c r="Q17" s="94"/>
+      <c r="R17" s="94"/>
+      <c r="S17" s="94"/>
+      <c r="T17" s="94"/>
+      <c r="U17" s="94"/>
+      <c r="V17" s="94"/>
+      <c r="W17" s="94"/>
+      <c r="X17" s="94"/>
     </row>
     <row r="18" spans="1:24">
       <c r="A18" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B18" s="103" t="s">
+      <c r="B18" s="94" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="103"/>
-      <c r="D18" s="103"/>
-      <c r="E18" s="103"/>
-      <c r="F18" s="103"/>
-      <c r="G18" s="103"/>
-      <c r="H18" s="103"/>
-      <c r="I18" s="104" t="s">
+      <c r="C18" s="94"/>
+      <c r="D18" s="94"/>
+      <c r="E18" s="94"/>
+      <c r="F18" s="94"/>
+      <c r="G18" s="94"/>
+      <c r="H18" s="94"/>
+      <c r="I18" s="96" t="s">
         <v>210</v>
       </c>
-      <c r="J18" s="105"/>
-      <c r="K18" s="105"/>
-      <c r="L18" s="106"/>
-      <c r="M18" s="103"/>
-      <c r="N18" s="103"/>
-      <c r="O18" s="103"/>
-      <c r="P18" s="103" t="s">
+      <c r="J18" s="97"/>
+      <c r="K18" s="97"/>
+      <c r="L18" s="98"/>
+      <c r="M18" s="94"/>
+      <c r="N18" s="94"/>
+      <c r="O18" s="94"/>
+      <c r="P18" s="94" t="s">
         <v>60</v>
       </c>
-      <c r="Q18" s="103"/>
-      <c r="R18" s="103"/>
-      <c r="S18" s="103"/>
-      <c r="T18" s="103"/>
-      <c r="U18" s="103"/>
-      <c r="V18" s="103"/>
-      <c r="W18" s="103"/>
-      <c r="X18" s="103"/>
+      <c r="Q18" s="94"/>
+      <c r="R18" s="94"/>
+      <c r="S18" s="94"/>
+      <c r="T18" s="94"/>
+      <c r="U18" s="94"/>
+      <c r="V18" s="94"/>
+      <c r="W18" s="94"/>
+      <c r="X18" s="94"/>
     </row>
     <row r="19" spans="1:24">
       <c r="A19" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B19" s="103" t="s">
+      <c r="B19" s="94" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="103"/>
-      <c r="D19" s="103"/>
-      <c r="E19" s="103"/>
-      <c r="F19" s="103"/>
-      <c r="G19" s="103"/>
-      <c r="H19" s="103"/>
-      <c r="I19" s="104" t="s">
+      <c r="C19" s="94"/>
+      <c r="D19" s="94"/>
+      <c r="E19" s="94"/>
+      <c r="F19" s="94"/>
+      <c r="G19" s="94"/>
+      <c r="H19" s="94"/>
+      <c r="I19" s="96" t="s">
         <v>62</v>
       </c>
-      <c r="J19" s="105"/>
-      <c r="K19" s="105"/>
-      <c r="L19" s="106"/>
-      <c r="M19" s="103"/>
-      <c r="N19" s="103"/>
-      <c r="O19" s="103"/>
-      <c r="P19" s="103" t="s">
+      <c r="J19" s="97"/>
+      <c r="K19" s="97"/>
+      <c r="L19" s="98"/>
+      <c r="M19" s="94"/>
+      <c r="N19" s="94"/>
+      <c r="O19" s="94"/>
+      <c r="P19" s="94" t="s">
         <v>61</v>
       </c>
-      <c r="Q19" s="103"/>
-      <c r="R19" s="103"/>
-      <c r="S19" s="103"/>
-      <c r="T19" s="103"/>
-      <c r="U19" s="103"/>
-      <c r="V19" s="103"/>
-      <c r="W19" s="103"/>
-      <c r="X19" s="103"/>
+      <c r="Q19" s="94"/>
+      <c r="R19" s="94"/>
+      <c r="S19" s="94"/>
+      <c r="T19" s="94"/>
+      <c r="U19" s="94"/>
+      <c r="V19" s="94"/>
+      <c r="W19" s="94"/>
+      <c r="X19" s="94"/>
     </row>
     <row r="20" spans="1:24" ht="45" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B20" s="103" t="s">
+      <c r="B20" s="94" t="s">
         <v>69</v>
       </c>
-      <c r="C20" s="103"/>
-      <c r="D20" s="103"/>
-      <c r="E20" s="103"/>
-      <c r="F20" s="102" t="s">
+      <c r="C20" s="94"/>
+      <c r="D20" s="94"/>
+      <c r="E20" s="94"/>
+      <c r="F20" s="95" t="s">
         <v>71</v>
       </c>
-      <c r="G20" s="103"/>
-      <c r="H20" s="103"/>
-      <c r="I20" s="113" t="s">
+      <c r="G20" s="94"/>
+      <c r="H20" s="94"/>
+      <c r="I20" s="99" t="s">
         <v>73</v>
       </c>
-      <c r="J20" s="114"/>
-      <c r="K20" s="114"/>
-      <c r="L20" s="115"/>
-      <c r="M20" s="102" t="s">
+      <c r="J20" s="100"/>
+      <c r="K20" s="100"/>
+      <c r="L20" s="101"/>
+      <c r="M20" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="N20" s="103"/>
-      <c r="O20" s="103"/>
-      <c r="P20" s="103"/>
-      <c r="Q20" s="103"/>
-      <c r="R20" s="103"/>
-      <c r="S20" s="103"/>
-      <c r="T20" s="103"/>
-      <c r="U20" s="103"/>
-      <c r="V20" s="103"/>
-      <c r="W20" s="103"/>
-      <c r="X20" s="103"/>
+      <c r="N20" s="94"/>
+      <c r="O20" s="94"/>
+      <c r="P20" s="94"/>
+      <c r="Q20" s="94"/>
+      <c r="R20" s="94"/>
+      <c r="S20" s="94"/>
+      <c r="T20" s="94"/>
+      <c r="U20" s="94"/>
+      <c r="V20" s="94"/>
+      <c r="W20" s="94"/>
+      <c r="X20" s="94"/>
     </row>
     <row r="21" spans="1:24" ht="61.5" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B21" s="102" t="s">
+      <c r="B21" s="95" t="s">
         <v>76</v>
       </c>
-      <c r="C21" s="103"/>
-      <c r="D21" s="103"/>
-      <c r="E21" s="103"/>
-      <c r="F21" s="103"/>
-      <c r="G21" s="103"/>
-      <c r="H21" s="103"/>
-      <c r="I21" s="104" t="s">
+      <c r="C21" s="94"/>
+      <c r="D21" s="94"/>
+      <c r="E21" s="94"/>
+      <c r="F21" s="94"/>
+      <c r="G21" s="94"/>
+      <c r="H21" s="94"/>
+      <c r="I21" s="96" t="s">
         <v>78</v>
       </c>
-      <c r="J21" s="105"/>
-      <c r="K21" s="105"/>
-      <c r="L21" s="106"/>
-      <c r="M21" s="102" t="s">
+      <c r="J21" s="97"/>
+      <c r="K21" s="97"/>
+      <c r="L21" s="98"/>
+      <c r="M21" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="N21" s="103"/>
-      <c r="O21" s="103"/>
-      <c r="P21" s="103" t="s">
+      <c r="N21" s="94"/>
+      <c r="O21" s="94"/>
+      <c r="P21" s="94" t="s">
         <v>75</v>
       </c>
-      <c r="Q21" s="103"/>
-      <c r="R21" s="103"/>
-      <c r="S21" s="103"/>
-      <c r="T21" s="103"/>
-      <c r="U21" s="103"/>
-      <c r="V21" s="103"/>
-      <c r="W21" s="103"/>
-      <c r="X21" s="103"/>
+      <c r="Q21" s="94"/>
+      <c r="R21" s="94"/>
+      <c r="S21" s="94"/>
+      <c r="T21" s="94"/>
+      <c r="U21" s="94"/>
+      <c r="V21" s="94"/>
+      <c r="W21" s="94"/>
+      <c r="X21" s="94"/>
     </row>
     <row r="22" spans="1:24">
       <c r="A22" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B22" s="103" t="s">
+      <c r="B22" s="94" t="s">
         <v>81</v>
       </c>
-      <c r="C22" s="103"/>
-      <c r="D22" s="103"/>
-      <c r="E22" s="103"/>
-      <c r="F22" s="103" t="s">
+      <c r="C22" s="94"/>
+      <c r="D22" s="94"/>
+      <c r="E22" s="94"/>
+      <c r="F22" s="94" t="s">
         <v>82</v>
       </c>
-      <c r="G22" s="103"/>
-      <c r="H22" s="103"/>
-      <c r="I22" s="104" t="s">
+      <c r="G22" s="94"/>
+      <c r="H22" s="94"/>
+      <c r="I22" s="96" t="s">
         <v>80</v>
       </c>
-      <c r="J22" s="105"/>
-      <c r="K22" s="105"/>
-      <c r="L22" s="106"/>
-      <c r="M22" s="103" t="s">
+      <c r="J22" s="97"/>
+      <c r="K22" s="97"/>
+      <c r="L22" s="98"/>
+      <c r="M22" s="94" t="s">
         <v>83</v>
       </c>
-      <c r="N22" s="103"/>
-      <c r="O22" s="103"/>
-      <c r="P22" s="103" t="s">
+      <c r="N22" s="94"/>
+      <c r="O22" s="94"/>
+      <c r="P22" s="94" t="s">
         <v>89</v>
       </c>
-      <c r="Q22" s="103"/>
-      <c r="R22" s="103"/>
-      <c r="S22" s="103"/>
-      <c r="T22" s="103"/>
-      <c r="U22" s="103"/>
-      <c r="V22" s="103"/>
-      <c r="W22" s="103"/>
-      <c r="X22" s="103"/>
+      <c r="Q22" s="94"/>
+      <c r="R22" s="94"/>
+      <c r="S22" s="94"/>
+      <c r="T22" s="94"/>
+      <c r="U22" s="94"/>
+      <c r="V22" s="94"/>
+      <c r="W22" s="94"/>
+      <c r="X22" s="94"/>
     </row>
     <row r="23" spans="1:24">
       <c r="A23" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B23" s="103" t="s">
+      <c r="B23" s="94" t="s">
         <v>88</v>
       </c>
-      <c r="C23" s="103"/>
-      <c r="D23" s="103"/>
-      <c r="E23" s="103"/>
-      <c r="F23" s="103"/>
-      <c r="G23" s="103"/>
-      <c r="H23" s="103"/>
-      <c r="I23" s="104" t="s">
+      <c r="C23" s="94"/>
+      <c r="D23" s="94"/>
+      <c r="E23" s="94"/>
+      <c r="F23" s="94"/>
+      <c r="G23" s="94"/>
+      <c r="H23" s="94"/>
+      <c r="I23" s="96" t="s">
         <v>84</v>
       </c>
-      <c r="J23" s="105"/>
-      <c r="K23" s="105"/>
-      <c r="L23" s="106"/>
-      <c r="M23" s="103"/>
-      <c r="N23" s="103"/>
-      <c r="O23" s="103"/>
-      <c r="P23" s="103" t="s">
+      <c r="J23" s="97"/>
+      <c r="K23" s="97"/>
+      <c r="L23" s="98"/>
+      <c r="M23" s="94"/>
+      <c r="N23" s="94"/>
+      <c r="O23" s="94"/>
+      <c r="P23" s="94" t="s">
         <v>89</v>
       </c>
-      <c r="Q23" s="103"/>
-      <c r="R23" s="103"/>
-      <c r="S23" s="103"/>
-      <c r="T23" s="103"/>
-      <c r="U23" s="103"/>
-      <c r="V23" s="103"/>
-      <c r="W23" s="103"/>
-      <c r="X23" s="103"/>
+      <c r="Q23" s="94"/>
+      <c r="R23" s="94"/>
+      <c r="S23" s="94"/>
+      <c r="T23" s="94"/>
+      <c r="U23" s="94"/>
+      <c r="V23" s="94"/>
+      <c r="W23" s="94"/>
+      <c r="X23" s="94"/>
     </row>
     <row r="24" spans="1:24">
       <c r="A24" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B24" s="103"/>
-      <c r="C24" s="103"/>
-      <c r="D24" s="103"/>
-      <c r="E24" s="103"/>
-      <c r="F24" s="103"/>
-      <c r="G24" s="103"/>
-      <c r="H24" s="103"/>
-      <c r="I24" s="104" t="s">
+      <c r="B24" s="94"/>
+      <c r="C24" s="94"/>
+      <c r="D24" s="94"/>
+      <c r="E24" s="94"/>
+      <c r="F24" s="94"/>
+      <c r="G24" s="94"/>
+      <c r="H24" s="94"/>
+      <c r="I24" s="96" t="s">
         <v>90</v>
       </c>
-      <c r="J24" s="105"/>
-      <c r="K24" s="105"/>
-      <c r="L24" s="106"/>
-      <c r="M24" s="103"/>
-      <c r="N24" s="103"/>
-      <c r="O24" s="103"/>
-      <c r="P24" s="103"/>
-      <c r="Q24" s="103"/>
-      <c r="R24" s="103"/>
-      <c r="S24" s="103"/>
-      <c r="T24" s="103"/>
-      <c r="U24" s="103"/>
-      <c r="V24" s="103"/>
-      <c r="W24" s="103"/>
-      <c r="X24" s="103"/>
+      <c r="J24" s="97"/>
+      <c r="K24" s="97"/>
+      <c r="L24" s="98"/>
+      <c r="M24" s="94"/>
+      <c r="N24" s="94"/>
+      <c r="O24" s="94"/>
+      <c r="P24" s="94"/>
+      <c r="Q24" s="94"/>
+      <c r="R24" s="94"/>
+      <c r="S24" s="94"/>
+      <c r="T24" s="94"/>
+      <c r="U24" s="94"/>
+      <c r="V24" s="94"/>
+      <c r="W24" s="94"/>
+      <c r="X24" s="94"/>
     </row>
     <row r="25" spans="1:24">
       <c r="A25" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B25" s="103"/>
-      <c r="C25" s="103"/>
-      <c r="D25" s="103"/>
-      <c r="E25" s="103"/>
-      <c r="F25" s="103" t="s">
+      <c r="B25" s="94"/>
+      <c r="C25" s="94"/>
+      <c r="D25" s="94"/>
+      <c r="E25" s="94"/>
+      <c r="F25" s="94" t="s">
         <v>109</v>
       </c>
-      <c r="G25" s="103"/>
-      <c r="H25" s="103"/>
-      <c r="I25" s="104" t="s">
+      <c r="G25" s="94"/>
+      <c r="H25" s="94"/>
+      <c r="I25" s="96" t="s">
         <v>112</v>
       </c>
-      <c r="J25" s="105"/>
-      <c r="K25" s="105"/>
-      <c r="L25" s="106"/>
-      <c r="M25" s="102" t="s">
+      <c r="J25" s="97"/>
+      <c r="K25" s="97"/>
+      <c r="L25" s="98"/>
+      <c r="M25" s="95" t="s">
         <v>110</v>
       </c>
-      <c r="N25" s="103"/>
-      <c r="O25" s="103"/>
-      <c r="P25" s="103" t="s">
+      <c r="N25" s="94"/>
+      <c r="O25" s="94"/>
+      <c r="P25" s="94" t="s">
         <v>111</v>
       </c>
-      <c r="Q25" s="103"/>
-      <c r="R25" s="103"/>
-      <c r="S25" s="103"/>
-      <c r="T25" s="103"/>
-      <c r="U25" s="103"/>
-      <c r="V25" s="103"/>
-      <c r="W25" s="103"/>
-      <c r="X25" s="103"/>
+      <c r="Q25" s="94"/>
+      <c r="R25" s="94"/>
+      <c r="S25" s="94"/>
+      <c r="T25" s="94"/>
+      <c r="U25" s="94"/>
+      <c r="V25" s="94"/>
+      <c r="W25" s="94"/>
+      <c r="X25" s="94"/>
     </row>
     <row r="26" spans="1:24" ht="45.75" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B26" s="103" t="s">
+      <c r="B26" s="94" t="s">
         <v>114</v>
       </c>
-      <c r="C26" s="103"/>
-      <c r="D26" s="103"/>
-      <c r="E26" s="103"/>
-      <c r="F26" s="102" t="s">
+      <c r="C26" s="94"/>
+      <c r="D26" s="94"/>
+      <c r="E26" s="94"/>
+      <c r="F26" s="95" t="s">
         <v>132</v>
       </c>
-      <c r="G26" s="103"/>
-      <c r="H26" s="103"/>
-      <c r="I26" s="104" t="s">
+      <c r="G26" s="94"/>
+      <c r="H26" s="94"/>
+      <c r="I26" s="96" t="s">
         <v>113</v>
       </c>
-      <c r="J26" s="105"/>
-      <c r="K26" s="105"/>
-      <c r="L26" s="106"/>
-      <c r="M26" s="102" t="s">
+      <c r="J26" s="97"/>
+      <c r="K26" s="97"/>
+      <c r="L26" s="98"/>
+      <c r="M26" s="95" t="s">
         <v>133</v>
       </c>
-      <c r="N26" s="103"/>
-      <c r="O26" s="103"/>
-      <c r="P26" s="102" t="s">
+      <c r="N26" s="94"/>
+      <c r="O26" s="94"/>
+      <c r="P26" s="95" t="s">
         <v>126</v>
       </c>
-      <c r="Q26" s="102"/>
-      <c r="R26" s="102"/>
-      <c r="S26" s="102"/>
-      <c r="T26" s="102"/>
-      <c r="U26" s="102"/>
-      <c r="V26" s="102"/>
-      <c r="W26" s="102"/>
-      <c r="X26" s="102"/>
+      <c r="Q26" s="95"/>
+      <c r="R26" s="95"/>
+      <c r="S26" s="95"/>
+      <c r="T26" s="95"/>
+      <c r="U26" s="95"/>
+      <c r="V26" s="95"/>
+      <c r="W26" s="95"/>
+      <c r="X26" s="95"/>
     </row>
     <row r="27" spans="1:24">
       <c r="A27" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B27" s="103"/>
-      <c r="C27" s="103"/>
-      <c r="D27" s="103"/>
-      <c r="E27" s="103"/>
-      <c r="F27" s="103"/>
-      <c r="G27" s="103"/>
-      <c r="H27" s="103"/>
-      <c r="I27" s="104" t="s">
+      <c r="B27" s="94"/>
+      <c r="C27" s="94"/>
+      <c r="D27" s="94"/>
+      <c r="E27" s="94"/>
+      <c r="F27" s="94"/>
+      <c r="G27" s="94"/>
+      <c r="H27" s="94"/>
+      <c r="I27" s="96" t="s">
         <v>117</v>
       </c>
-      <c r="J27" s="105"/>
-      <c r="K27" s="105"/>
-      <c r="L27" s="106"/>
-      <c r="M27" s="103"/>
-      <c r="N27" s="103"/>
-      <c r="O27" s="103"/>
-      <c r="P27" s="103"/>
-      <c r="Q27" s="103"/>
-      <c r="R27" s="103"/>
-      <c r="S27" s="103"/>
-      <c r="T27" s="103"/>
-      <c r="U27" s="103"/>
-      <c r="V27" s="103"/>
-      <c r="W27" s="103"/>
-      <c r="X27" s="103"/>
+      <c r="J27" s="97"/>
+      <c r="K27" s="97"/>
+      <c r="L27" s="98"/>
+      <c r="M27" s="94"/>
+      <c r="N27" s="94"/>
+      <c r="O27" s="94"/>
+      <c r="P27" s="94"/>
+      <c r="Q27" s="94"/>
+      <c r="R27" s="94"/>
+      <c r="S27" s="94"/>
+      <c r="T27" s="94"/>
+      <c r="U27" s="94"/>
+      <c r="V27" s="94"/>
+      <c r="W27" s="94"/>
+      <c r="X27" s="94"/>
     </row>
     <row r="28" spans="1:24">
       <c r="A28" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B28" s="103"/>
-      <c r="C28" s="103"/>
-      <c r="D28" s="103"/>
-      <c r="E28" s="103"/>
-      <c r="F28" s="103"/>
-      <c r="G28" s="103"/>
-      <c r="H28" s="103"/>
-      <c r="I28" s="104" t="s">
+      <c r="B28" s="94"/>
+      <c r="C28" s="94"/>
+      <c r="D28" s="94"/>
+      <c r="E28" s="94"/>
+      <c r="F28" s="94"/>
+      <c r="G28" s="94"/>
+      <c r="H28" s="94"/>
+      <c r="I28" s="96" t="s">
         <v>119</v>
       </c>
-      <c r="J28" s="105"/>
-      <c r="K28" s="105"/>
-      <c r="L28" s="106"/>
-      <c r="M28" s="103"/>
-      <c r="N28" s="103"/>
-      <c r="O28" s="103"/>
-      <c r="P28" s="103"/>
-      <c r="Q28" s="103"/>
-      <c r="R28" s="103"/>
-      <c r="S28" s="103"/>
-      <c r="T28" s="103"/>
-      <c r="U28" s="103"/>
-      <c r="V28" s="103"/>
-      <c r="W28" s="103"/>
-      <c r="X28" s="103"/>
+      <c r="J28" s="97"/>
+      <c r="K28" s="97"/>
+      <c r="L28" s="98"/>
+      <c r="M28" s="94"/>
+      <c r="N28" s="94"/>
+      <c r="O28" s="94"/>
+      <c r="P28" s="94"/>
+      <c r="Q28" s="94"/>
+      <c r="R28" s="94"/>
+      <c r="S28" s="94"/>
+      <c r="T28" s="94"/>
+      <c r="U28" s="94"/>
+      <c r="V28" s="94"/>
+      <c r="W28" s="94"/>
+      <c r="X28" s="94"/>
     </row>
     <row r="29" spans="1:24" ht="56.25" customHeight="1">
       <c r="A29" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B29" s="102" t="s">
+      <c r="B29" s="95" t="s">
         <v>125</v>
       </c>
-      <c r="C29" s="102"/>
-      <c r="D29" s="102"/>
-      <c r="E29" s="102"/>
-      <c r="F29" s="102" t="s">
+      <c r="C29" s="95"/>
+      <c r="D29" s="95"/>
+      <c r="E29" s="95"/>
+      <c r="F29" s="95" t="s">
         <v>120</v>
       </c>
-      <c r="G29" s="103"/>
-      <c r="H29" s="103"/>
-      <c r="I29" s="104" t="s">
+      <c r="G29" s="94"/>
+      <c r="H29" s="94"/>
+      <c r="I29" s="96" t="s">
         <v>122</v>
       </c>
-      <c r="J29" s="105"/>
-      <c r="K29" s="105"/>
-      <c r="L29" s="106"/>
-      <c r="M29" s="102" t="s">
+      <c r="J29" s="97"/>
+      <c r="K29" s="97"/>
+      <c r="L29" s="98"/>
+      <c r="M29" s="95" t="s">
         <v>123</v>
       </c>
-      <c r="N29" s="103"/>
-      <c r="O29" s="103"/>
-      <c r="P29" s="102" t="s">
+      <c r="N29" s="94"/>
+      <c r="O29" s="94"/>
+      <c r="P29" s="95" t="s">
         <v>124</v>
       </c>
-      <c r="Q29" s="102"/>
-      <c r="R29" s="102"/>
-      <c r="S29" s="102"/>
-      <c r="T29" s="102"/>
-      <c r="U29" s="102"/>
-      <c r="V29" s="102"/>
-      <c r="W29" s="102"/>
-      <c r="X29" s="102"/>
+      <c r="Q29" s="95"/>
+      <c r="R29" s="95"/>
+      <c r="S29" s="95"/>
+      <c r="T29" s="95"/>
+      <c r="U29" s="95"/>
+      <c r="V29" s="95"/>
+      <c r="W29" s="95"/>
+      <c r="X29" s="95"/>
     </row>
     <row r="30" spans="1:24">
       <c r="A30" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B30" s="103"/>
-      <c r="C30" s="103"/>
-      <c r="D30" s="103"/>
-      <c r="E30" s="103"/>
-      <c r="F30" s="103" t="s">
+      <c r="B30" s="94"/>
+      <c r="C30" s="94"/>
+      <c r="D30" s="94"/>
+      <c r="E30" s="94"/>
+      <c r="F30" s="94" t="s">
         <v>136</v>
       </c>
-      <c r="G30" s="103"/>
-      <c r="H30" s="103"/>
-      <c r="I30" s="104" t="s">
+      <c r="G30" s="94"/>
+      <c r="H30" s="94"/>
+      <c r="I30" s="96" t="s">
         <v>135</v>
       </c>
-      <c r="J30" s="105"/>
-      <c r="K30" s="105"/>
-      <c r="L30" s="106"/>
-      <c r="M30" s="103" t="s">
+      <c r="J30" s="97"/>
+      <c r="K30" s="97"/>
+      <c r="L30" s="98"/>
+      <c r="M30" s="94" t="s">
         <v>137</v>
       </c>
-      <c r="N30" s="103"/>
-      <c r="O30" s="103"/>
-      <c r="P30" s="103"/>
-      <c r="Q30" s="103"/>
-      <c r="R30" s="103"/>
-      <c r="S30" s="103"/>
-      <c r="T30" s="103"/>
-      <c r="U30" s="103"/>
-      <c r="V30" s="103"/>
-      <c r="W30" s="103"/>
-      <c r="X30" s="103"/>
+      <c r="N30" s="94"/>
+      <c r="O30" s="94"/>
+      <c r="P30" s="94"/>
+      <c r="Q30" s="94"/>
+      <c r="R30" s="94"/>
+      <c r="S30" s="94"/>
+      <c r="T30" s="94"/>
+      <c r="U30" s="94"/>
+      <c r="V30" s="94"/>
+      <c r="W30" s="94"/>
+      <c r="X30" s="94"/>
     </row>
     <row r="31" spans="1:24">
       <c r="A31" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B31" s="103" t="s">
+      <c r="B31" s="94" t="s">
         <v>144</v>
       </c>
-      <c r="C31" s="103"/>
-      <c r="D31" s="103"/>
-      <c r="E31" s="103"/>
-      <c r="F31" s="102" t="s">
+      <c r="C31" s="94"/>
+      <c r="D31" s="94"/>
+      <c r="E31" s="94"/>
+      <c r="F31" s="95" t="s">
         <v>143</v>
       </c>
-      <c r="G31" s="103"/>
-      <c r="H31" s="103"/>
-      <c r="I31" s="104" t="s">
+      <c r="G31" s="94"/>
+      <c r="H31" s="94"/>
+      <c r="I31" s="96" t="s">
         <v>145</v>
       </c>
-      <c r="J31" s="105"/>
-      <c r="K31" s="105"/>
-      <c r="L31" s="106"/>
-      <c r="M31" s="102" t="s">
+      <c r="J31" s="97"/>
+      <c r="K31" s="97"/>
+      <c r="L31" s="98"/>
+      <c r="M31" s="95" t="s">
         <v>146</v>
       </c>
-      <c r="N31" s="103"/>
-      <c r="O31" s="103"/>
-      <c r="P31" s="103"/>
-      <c r="Q31" s="103"/>
-      <c r="R31" s="103"/>
-      <c r="S31" s="103"/>
-      <c r="T31" s="103"/>
-      <c r="U31" s="103"/>
-      <c r="V31" s="103"/>
-      <c r="W31" s="103"/>
-      <c r="X31" s="103"/>
+      <c r="N31" s="94"/>
+      <c r="O31" s="94"/>
+      <c r="P31" s="94"/>
+      <c r="Q31" s="94"/>
+      <c r="R31" s="94"/>
+      <c r="S31" s="94"/>
+      <c r="T31" s="94"/>
+      <c r="U31" s="94"/>
+      <c r="V31" s="94"/>
+      <c r="W31" s="94"/>
+      <c r="X31" s="94"/>
     </row>
     <row r="32" spans="1:24">
       <c r="A32" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="B32" s="103"/>
-      <c r="C32" s="103"/>
-      <c r="D32" s="103"/>
-      <c r="E32" s="103"/>
-      <c r="F32" s="102" t="s">
+      <c r="B32" s="94"/>
+      <c r="C32" s="94"/>
+      <c r="D32" s="94"/>
+      <c r="E32" s="94"/>
+      <c r="F32" s="95" t="s">
         <v>203</v>
       </c>
-      <c r="G32" s="103"/>
-      <c r="H32" s="103"/>
-      <c r="I32" s="104"/>
-      <c r="J32" s="105"/>
-      <c r="K32" s="105"/>
-      <c r="L32" s="106"/>
-      <c r="M32" s="102" t="s">
+      <c r="G32" s="94"/>
+      <c r="H32" s="94"/>
+      <c r="I32" s="96"/>
+      <c r="J32" s="97"/>
+      <c r="K32" s="97"/>
+      <c r="L32" s="98"/>
+      <c r="M32" s="95" t="s">
         <v>204</v>
       </c>
-      <c r="N32" s="103"/>
-      <c r="O32" s="103"/>
-      <c r="P32" s="103" t="s">
+      <c r="N32" s="94"/>
+      <c r="O32" s="94"/>
+      <c r="P32" s="94" t="s">
         <v>209</v>
       </c>
-      <c r="Q32" s="103"/>
-      <c r="R32" s="103"/>
-      <c r="S32" s="103"/>
-      <c r="T32" s="103"/>
-      <c r="U32" s="103"/>
-      <c r="V32" s="103"/>
-      <c r="W32" s="103"/>
-      <c r="X32" s="103"/>
+      <c r="Q32" s="94"/>
+      <c r="R32" s="94"/>
+      <c r="S32" s="94"/>
+      <c r="T32" s="94"/>
+      <c r="U32" s="94"/>
+      <c r="V32" s="94"/>
+      <c r="W32" s="94"/>
+      <c r="X32" s="94"/>
     </row>
     <row r="33" spans="1:24">
       <c r="A33" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="B33" s="103"/>
-      <c r="C33" s="103"/>
-      <c r="D33" s="103"/>
-      <c r="E33" s="103"/>
-      <c r="F33" s="103" t="s">
+      <c r="B33" s="94"/>
+      <c r="C33" s="94"/>
+      <c r="D33" s="94"/>
+      <c r="E33" s="94"/>
+      <c r="F33" s="94" t="s">
         <v>206</v>
       </c>
-      <c r="G33" s="103"/>
-      <c r="H33" s="103"/>
-      <c r="I33" s="104"/>
-      <c r="J33" s="105"/>
-      <c r="K33" s="105"/>
-      <c r="L33" s="106"/>
-      <c r="M33" s="103" t="s">
+      <c r="G33" s="94"/>
+      <c r="H33" s="94"/>
+      <c r="I33" s="96"/>
+      <c r="J33" s="97"/>
+      <c r="K33" s="97"/>
+      <c r="L33" s="98"/>
+      <c r="M33" s="94" t="s">
         <v>205</v>
       </c>
-      <c r="N33" s="103"/>
-      <c r="O33" s="103"/>
-      <c r="P33" s="103"/>
-      <c r="Q33" s="103"/>
-      <c r="R33" s="103"/>
-      <c r="S33" s="103"/>
-      <c r="T33" s="103"/>
-      <c r="U33" s="103"/>
-      <c r="V33" s="103"/>
-      <c r="W33" s="103"/>
-      <c r="X33" s="103"/>
+      <c r="N33" s="94"/>
+      <c r="O33" s="94"/>
+      <c r="P33" s="94"/>
+      <c r="Q33" s="94"/>
+      <c r="R33" s="94"/>
+      <c r="S33" s="94"/>
+      <c r="T33" s="94"/>
+      <c r="U33" s="94"/>
+      <c r="V33" s="94"/>
+      <c r="W33" s="94"/>
+      <c r="X33" s="94"/>
     </row>
     <row r="34" spans="1:24">
       <c r="A34" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="B34" s="103" t="s">
-        <v>370</v>
-      </c>
-      <c r="C34" s="103"/>
-      <c r="D34" s="103"/>
-      <c r="E34" s="103"/>
-      <c r="F34" s="103"/>
-      <c r="G34" s="103"/>
-      <c r="H34" s="103"/>
-      <c r="I34" s="104" t="s">
-        <v>369</v>
-      </c>
-      <c r="J34" s="105"/>
-      <c r="K34" s="105"/>
-      <c r="L34" s="106"/>
-      <c r="M34" s="103"/>
-      <c r="N34" s="103"/>
-      <c r="O34" s="103"/>
-      <c r="P34" s="103"/>
-      <c r="Q34" s="103"/>
-      <c r="R34" s="103"/>
-      <c r="S34" s="103"/>
-      <c r="T34" s="103"/>
-      <c r="U34" s="103"/>
-      <c r="V34" s="103"/>
-      <c r="W34" s="103"/>
-      <c r="X34" s="103"/>
+        <v>367</v>
+      </c>
+      <c r="B34" s="94" t="s">
+        <v>366</v>
+      </c>
+      <c r="C34" s="94"/>
+      <c r="D34" s="94"/>
+      <c r="E34" s="94"/>
+      <c r="F34" s="94"/>
+      <c r="G34" s="94"/>
+      <c r="H34" s="94"/>
+      <c r="I34" s="96" t="s">
+        <v>365</v>
+      </c>
+      <c r="J34" s="97"/>
+      <c r="K34" s="97"/>
+      <c r="L34" s="98"/>
+      <c r="M34" s="94"/>
+      <c r="N34" s="94"/>
+      <c r="O34" s="94"/>
+      <c r="P34" s="94"/>
+      <c r="Q34" s="94"/>
+      <c r="R34" s="94"/>
+      <c r="S34" s="94"/>
+      <c r="T34" s="94"/>
+      <c r="U34" s="94"/>
+      <c r="V34" s="94"/>
+      <c r="W34" s="94"/>
+      <c r="X34" s="94"/>
     </row>
     <row r="35" spans="1:24">
       <c r="A35" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="B35" s="103" t="s">
-        <v>372</v>
-      </c>
-      <c r="C35" s="103"/>
-      <c r="D35" s="103"/>
-      <c r="E35" s="103"/>
-      <c r="F35" s="103"/>
-      <c r="G35" s="103"/>
-      <c r="H35" s="103"/>
-      <c r="I35" s="104" t="s">
-        <v>372</v>
-      </c>
-      <c r="J35" s="105"/>
-      <c r="K35" s="105"/>
-      <c r="L35" s="106"/>
-      <c r="M35" s="103"/>
-      <c r="N35" s="103"/>
-      <c r="O35" s="103"/>
-      <c r="P35" s="103" t="s">
-        <v>374</v>
-      </c>
-      <c r="Q35" s="103"/>
-      <c r="R35" s="103"/>
-      <c r="S35" s="103"/>
-      <c r="T35" s="103"/>
-      <c r="U35" s="103"/>
-      <c r="V35" s="103"/>
-      <c r="W35" s="103"/>
-      <c r="X35" s="103"/>
+        <v>369</v>
+      </c>
+      <c r="B35" s="94" t="s">
+        <v>368</v>
+      </c>
+      <c r="C35" s="94"/>
+      <c r="D35" s="94"/>
+      <c r="E35" s="94"/>
+      <c r="F35" s="94"/>
+      <c r="G35" s="94"/>
+      <c r="H35" s="94"/>
+      <c r="I35" s="96" t="s">
+        <v>368</v>
+      </c>
+      <c r="J35" s="97"/>
+      <c r="K35" s="97"/>
+      <c r="L35" s="98"/>
+      <c r="M35" s="94"/>
+      <c r="N35" s="94"/>
+      <c r="O35" s="94"/>
+      <c r="P35" s="94" t="s">
+        <v>370</v>
+      </c>
+      <c r="Q35" s="94"/>
+      <c r="R35" s="94"/>
+      <c r="S35" s="94"/>
+      <c r="T35" s="94"/>
+      <c r="U35" s="94"/>
+      <c r="V35" s="94"/>
+      <c r="W35" s="94"/>
+      <c r="X35" s="94"/>
     </row>
     <row r="36" spans="1:24">
       <c r="A36" s="3"/>
-      <c r="B36" s="103"/>
-      <c r="C36" s="103"/>
-      <c r="D36" s="103"/>
-      <c r="E36" s="103"/>
-      <c r="F36" s="103"/>
-      <c r="G36" s="103"/>
-      <c r="H36" s="103"/>
-      <c r="I36" s="104"/>
-      <c r="J36" s="105"/>
-      <c r="K36" s="105"/>
-      <c r="L36" s="106"/>
-      <c r="M36" s="103"/>
-      <c r="N36" s="103"/>
-      <c r="O36" s="103"/>
-      <c r="P36" s="103"/>
-      <c r="Q36" s="103"/>
-      <c r="R36" s="103"/>
-      <c r="S36" s="103"/>
-      <c r="T36" s="103"/>
-      <c r="U36" s="103"/>
-      <c r="V36" s="103"/>
-      <c r="W36" s="103"/>
-      <c r="X36" s="103"/>
+      <c r="B36" s="94"/>
+      <c r="C36" s="94"/>
+      <c r="D36" s="94"/>
+      <c r="E36" s="94"/>
+      <c r="F36" s="94"/>
+      <c r="G36" s="94"/>
+      <c r="H36" s="94"/>
+      <c r="I36" s="96"/>
+      <c r="J36" s="97"/>
+      <c r="K36" s="97"/>
+      <c r="L36" s="98"/>
+      <c r="M36" s="94"/>
+      <c r="N36" s="94"/>
+      <c r="O36" s="94"/>
+      <c r="P36" s="94"/>
+      <c r="Q36" s="94"/>
+      <c r="R36" s="94"/>
+      <c r="S36" s="94"/>
+      <c r="T36" s="94"/>
+      <c r="U36" s="94"/>
+      <c r="V36" s="94"/>
+      <c r="W36" s="94"/>
+      <c r="X36" s="94"/>
     </row>
     <row r="37" spans="1:24">
       <c r="A37" s="3"/>
-      <c r="B37" s="103"/>
-      <c r="C37" s="103"/>
-      <c r="D37" s="103"/>
-      <c r="E37" s="103"/>
-      <c r="F37" s="103"/>
-      <c r="G37" s="103"/>
-      <c r="H37" s="103"/>
-      <c r="I37" s="104"/>
-      <c r="J37" s="105"/>
-      <c r="K37" s="105"/>
-      <c r="L37" s="106"/>
-      <c r="M37" s="103"/>
-      <c r="N37" s="103"/>
-      <c r="O37" s="103"/>
-      <c r="P37" s="103"/>
-      <c r="Q37" s="103"/>
-      <c r="R37" s="103"/>
-      <c r="S37" s="103"/>
-      <c r="T37" s="103"/>
-      <c r="U37" s="103"/>
-      <c r="V37" s="103"/>
-      <c r="W37" s="103"/>
-      <c r="X37" s="103"/>
+      <c r="B37" s="94"/>
+      <c r="C37" s="94"/>
+      <c r="D37" s="94"/>
+      <c r="E37" s="94"/>
+      <c r="F37" s="94"/>
+      <c r="G37" s="94"/>
+      <c r="H37" s="94"/>
+      <c r="I37" s="96"/>
+      <c r="J37" s="97"/>
+      <c r="K37" s="97"/>
+      <c r="L37" s="98"/>
+      <c r="M37" s="94"/>
+      <c r="N37" s="94"/>
+      <c r="O37" s="94"/>
+      <c r="P37" s="94"/>
+      <c r="Q37" s="94"/>
+      <c r="R37" s="94"/>
+      <c r="S37" s="94"/>
+      <c r="T37" s="94"/>
+      <c r="U37" s="94"/>
+      <c r="V37" s="94"/>
+      <c r="W37" s="94"/>
+      <c r="X37" s="94"/>
     </row>
     <row r="38" spans="1:24">
       <c r="A38" s="3"/>
-      <c r="B38" s="103"/>
-      <c r="C38" s="103"/>
-      <c r="D38" s="103"/>
-      <c r="E38" s="103"/>
-      <c r="F38" s="103"/>
-      <c r="G38" s="103"/>
-      <c r="H38" s="103"/>
-      <c r="I38" s="104"/>
-      <c r="J38" s="105"/>
-      <c r="K38" s="105"/>
-      <c r="L38" s="106"/>
-      <c r="M38" s="103"/>
-      <c r="N38" s="103"/>
-      <c r="O38" s="103"/>
-      <c r="P38" s="103"/>
-      <c r="Q38" s="103"/>
-      <c r="R38" s="103"/>
-      <c r="S38" s="103"/>
-      <c r="T38" s="103"/>
-      <c r="U38" s="103"/>
-      <c r="V38" s="103"/>
-      <c r="W38" s="103"/>
-      <c r="X38" s="103"/>
+      <c r="B38" s="94"/>
+      <c r="C38" s="94"/>
+      <c r="D38" s="94"/>
+      <c r="E38" s="94"/>
+      <c r="F38" s="94"/>
+      <c r="G38" s="94"/>
+      <c r="H38" s="94"/>
+      <c r="I38" s="96"/>
+      <c r="J38" s="97"/>
+      <c r="K38" s="97"/>
+      <c r="L38" s="98"/>
+      <c r="M38" s="94"/>
+      <c r="N38" s="94"/>
+      <c r="O38" s="94"/>
+      <c r="P38" s="94"/>
+      <c r="Q38" s="94"/>
+      <c r="R38" s="94"/>
+      <c r="S38" s="94"/>
+      <c r="T38" s="94"/>
+      <c r="U38" s="94"/>
+      <c r="V38" s="94"/>
+      <c r="W38" s="94"/>
+      <c r="X38" s="94"/>
     </row>
     <row r="39" spans="1:24">
       <c r="A39" s="3"/>
-      <c r="B39" s="103"/>
-      <c r="C39" s="103"/>
-      <c r="D39" s="103"/>
-      <c r="E39" s="103"/>
-      <c r="F39" s="103"/>
-      <c r="G39" s="103"/>
-      <c r="H39" s="103"/>
-      <c r="I39" s="104"/>
-      <c r="J39" s="105"/>
-      <c r="K39" s="105"/>
-      <c r="L39" s="106"/>
-      <c r="M39" s="103"/>
-      <c r="N39" s="103"/>
-      <c r="O39" s="103"/>
-      <c r="P39" s="103"/>
-      <c r="Q39" s="103"/>
-      <c r="R39" s="103"/>
-      <c r="S39" s="103"/>
-      <c r="T39" s="103"/>
-      <c r="U39" s="103"/>
-      <c r="V39" s="103"/>
-      <c r="W39" s="103"/>
-      <c r="X39" s="103"/>
+      <c r="B39" s="94"/>
+      <c r="C39" s="94"/>
+      <c r="D39" s="94"/>
+      <c r="E39" s="94"/>
+      <c r="F39" s="94"/>
+      <c r="G39" s="94"/>
+      <c r="H39" s="94"/>
+      <c r="I39" s="96"/>
+      <c r="J39" s="97"/>
+      <c r="K39" s="97"/>
+      <c r="L39" s="98"/>
+      <c r="M39" s="94"/>
+      <c r="N39" s="94"/>
+      <c r="O39" s="94"/>
+      <c r="P39" s="94"/>
+      <c r="Q39" s="94"/>
+      <c r="R39" s="94"/>
+      <c r="S39" s="94"/>
+      <c r="T39" s="94"/>
+      <c r="U39" s="94"/>
+      <c r="V39" s="94"/>
+      <c r="W39" s="94"/>
+      <c r="X39" s="94"/>
     </row>
     <row r="40" spans="1:24">
       <c r="A40" s="3"/>
-      <c r="B40" s="103"/>
-      <c r="C40" s="103"/>
-      <c r="D40" s="103"/>
-      <c r="E40" s="103"/>
-      <c r="F40" s="103"/>
-      <c r="G40" s="103"/>
-      <c r="H40" s="103"/>
-      <c r="I40" s="104"/>
-      <c r="J40" s="105"/>
-      <c r="K40" s="105"/>
-      <c r="L40" s="106"/>
-      <c r="M40" s="103"/>
-      <c r="N40" s="103"/>
-      <c r="O40" s="103"/>
-      <c r="P40" s="103"/>
-      <c r="Q40" s="103"/>
-      <c r="R40" s="103"/>
-      <c r="S40" s="103"/>
-      <c r="T40" s="103"/>
-      <c r="U40" s="103"/>
-      <c r="V40" s="103"/>
-      <c r="W40" s="103"/>
-      <c r="X40" s="103"/>
+      <c r="B40" s="94"/>
+      <c r="C40" s="94"/>
+      <c r="D40" s="94"/>
+      <c r="E40" s="94"/>
+      <c r="F40" s="94"/>
+      <c r="G40" s="94"/>
+      <c r="H40" s="94"/>
+      <c r="I40" s="96"/>
+      <c r="J40" s="97"/>
+      <c r="K40" s="97"/>
+      <c r="L40" s="98"/>
+      <c r="M40" s="94"/>
+      <c r="N40" s="94"/>
+      <c r="O40" s="94"/>
+      <c r="P40" s="94"/>
+      <c r="Q40" s="94"/>
+      <c r="R40" s="94"/>
+      <c r="S40" s="94"/>
+      <c r="T40" s="94"/>
+      <c r="U40" s="94"/>
+      <c r="V40" s="94"/>
+      <c r="W40" s="94"/>
+      <c r="X40" s="94"/>
     </row>
     <row r="41" spans="1:24">
       <c r="A41" s="3"/>
-      <c r="B41" s="103"/>
-      <c r="C41" s="103"/>
-      <c r="D41" s="103"/>
-      <c r="E41" s="103"/>
-      <c r="F41" s="103"/>
-      <c r="G41" s="103"/>
-      <c r="H41" s="103"/>
-      <c r="I41" s="104"/>
-      <c r="J41" s="105"/>
-      <c r="K41" s="105"/>
-      <c r="L41" s="106"/>
-      <c r="M41" s="103"/>
-      <c r="N41" s="103"/>
-      <c r="O41" s="103"/>
-      <c r="P41" s="103"/>
-      <c r="Q41" s="103"/>
-      <c r="R41" s="103"/>
-      <c r="S41" s="103"/>
-      <c r="T41" s="103"/>
-      <c r="U41" s="103"/>
-      <c r="V41" s="103"/>
-      <c r="W41" s="103"/>
-      <c r="X41" s="103"/>
+      <c r="B41" s="94"/>
+      <c r="C41" s="94"/>
+      <c r="D41" s="94"/>
+      <c r="E41" s="94"/>
+      <c r="F41" s="94"/>
+      <c r="G41" s="94"/>
+      <c r="H41" s="94"/>
+      <c r="I41" s="96"/>
+      <c r="J41" s="97"/>
+      <c r="K41" s="97"/>
+      <c r="L41" s="98"/>
+      <c r="M41" s="94"/>
+      <c r="N41" s="94"/>
+      <c r="O41" s="94"/>
+      <c r="P41" s="94"/>
+      <c r="Q41" s="94"/>
+      <c r="R41" s="94"/>
+      <c r="S41" s="94"/>
+      <c r="T41" s="94"/>
+      <c r="U41" s="94"/>
+      <c r="V41" s="94"/>
+      <c r="W41" s="94"/>
+      <c r="X41" s="94"/>
     </row>
     <row r="42" spans="1:24">
       <c r="A42" s="3"/>
-      <c r="B42" s="103"/>
-      <c r="C42" s="103"/>
-      <c r="D42" s="103"/>
-      <c r="E42" s="103"/>
-      <c r="F42" s="103"/>
-      <c r="G42" s="103"/>
-      <c r="H42" s="103"/>
-      <c r="I42" s="104"/>
-      <c r="J42" s="105"/>
-      <c r="K42" s="105"/>
-      <c r="L42" s="106"/>
-      <c r="M42" s="103"/>
-      <c r="N42" s="103"/>
-      <c r="O42" s="103"/>
-      <c r="P42" s="103"/>
-      <c r="Q42" s="103"/>
-      <c r="R42" s="103"/>
-      <c r="S42" s="103"/>
-      <c r="T42" s="103"/>
-      <c r="U42" s="103"/>
-      <c r="V42" s="103"/>
-      <c r="W42" s="103"/>
-      <c r="X42" s="103"/>
+      <c r="B42" s="94"/>
+      <c r="C42" s="94"/>
+      <c r="D42" s="94"/>
+      <c r="E42" s="94"/>
+      <c r="F42" s="94"/>
+      <c r="G42" s="94"/>
+      <c r="H42" s="94"/>
+      <c r="I42" s="96"/>
+      <c r="J42" s="97"/>
+      <c r="K42" s="97"/>
+      <c r="L42" s="98"/>
+      <c r="M42" s="94"/>
+      <c r="N42" s="94"/>
+      <c r="O42" s="94"/>
+      <c r="P42" s="94"/>
+      <c r="Q42" s="94"/>
+      <c r="R42" s="94"/>
+      <c r="S42" s="94"/>
+      <c r="T42" s="94"/>
+      <c r="U42" s="94"/>
+      <c r="V42" s="94"/>
+      <c r="W42" s="94"/>
+      <c r="X42" s="94"/>
     </row>
     <row r="43" spans="1:24">
       <c r="A43" s="3"/>
-      <c r="B43" s="103"/>
-      <c r="C43" s="103"/>
-      <c r="D43" s="103"/>
-      <c r="E43" s="103"/>
-      <c r="F43" s="103"/>
-      <c r="G43" s="103"/>
-      <c r="H43" s="103"/>
-      <c r="I43" s="104"/>
-      <c r="J43" s="105"/>
-      <c r="K43" s="105"/>
-      <c r="L43" s="106"/>
-      <c r="M43" s="103"/>
-      <c r="N43" s="103"/>
-      <c r="O43" s="103"/>
-      <c r="P43" s="103"/>
-      <c r="Q43" s="103"/>
-      <c r="R43" s="103"/>
-      <c r="S43" s="103"/>
-      <c r="T43" s="103"/>
-      <c r="U43" s="103"/>
-      <c r="V43" s="103"/>
-      <c r="W43" s="103"/>
-      <c r="X43" s="103"/>
+      <c r="B43" s="94"/>
+      <c r="C43" s="94"/>
+      <c r="D43" s="94"/>
+      <c r="E43" s="94"/>
+      <c r="F43" s="94"/>
+      <c r="G43" s="94"/>
+      <c r="H43" s="94"/>
+      <c r="I43" s="96"/>
+      <c r="J43" s="97"/>
+      <c r="K43" s="97"/>
+      <c r="L43" s="98"/>
+      <c r="M43" s="94"/>
+      <c r="N43" s="94"/>
+      <c r="O43" s="94"/>
+      <c r="P43" s="94"/>
+      <c r="Q43" s="94"/>
+      <c r="R43" s="94"/>
+      <c r="S43" s="94"/>
+      <c r="T43" s="94"/>
+      <c r="U43" s="94"/>
+      <c r="V43" s="94"/>
+      <c r="W43" s="94"/>
+      <c r="X43" s="94"/>
     </row>
     <row r="44" spans="1:24">
       <c r="A44" s="3"/>
-      <c r="B44" s="103"/>
-      <c r="C44" s="103"/>
-      <c r="D44" s="103"/>
-      <c r="E44" s="103"/>
-      <c r="F44" s="103"/>
-      <c r="G44" s="103"/>
-      <c r="H44" s="103"/>
-      <c r="I44" s="104"/>
-      <c r="J44" s="105"/>
-      <c r="K44" s="105"/>
-      <c r="L44" s="106"/>
-      <c r="M44" s="103"/>
-      <c r="N44" s="103"/>
-      <c r="O44" s="103"/>
-      <c r="P44" s="103"/>
-      <c r="Q44" s="103"/>
-      <c r="R44" s="103"/>
-      <c r="S44" s="103"/>
-      <c r="T44" s="103"/>
-      <c r="U44" s="103"/>
-      <c r="V44" s="103"/>
-      <c r="W44" s="103"/>
-      <c r="X44" s="103"/>
+      <c r="B44" s="94"/>
+      <c r="C44" s="94"/>
+      <c r="D44" s="94"/>
+      <c r="E44" s="94"/>
+      <c r="F44" s="94"/>
+      <c r="G44" s="94"/>
+      <c r="H44" s="94"/>
+      <c r="I44" s="96"/>
+      <c r="J44" s="97"/>
+      <c r="K44" s="97"/>
+      <c r="L44" s="98"/>
+      <c r="M44" s="94"/>
+      <c r="N44" s="94"/>
+      <c r="O44" s="94"/>
+      <c r="P44" s="94"/>
+      <c r="Q44" s="94"/>
+      <c r="R44" s="94"/>
+      <c r="S44" s="94"/>
+      <c r="T44" s="94"/>
+      <c r="U44" s="94"/>
+      <c r="V44" s="94"/>
+      <c r="W44" s="94"/>
+      <c r="X44" s="94"/>
     </row>
     <row r="45" spans="1:24">
       <c r="A45" s="3"/>
-      <c r="B45" s="103"/>
-      <c r="C45" s="103"/>
-      <c r="D45" s="103"/>
-      <c r="E45" s="103"/>
-      <c r="F45" s="103"/>
-      <c r="G45" s="103"/>
-      <c r="H45" s="103"/>
-      <c r="I45" s="104"/>
-      <c r="J45" s="105"/>
-      <c r="K45" s="105"/>
-      <c r="L45" s="106"/>
-      <c r="M45" s="103"/>
-      <c r="N45" s="103"/>
-      <c r="O45" s="103"/>
-      <c r="P45" s="103"/>
-      <c r="Q45" s="103"/>
-      <c r="R45" s="103"/>
-      <c r="S45" s="103"/>
-      <c r="T45" s="103"/>
-      <c r="U45" s="103"/>
-      <c r="V45" s="103"/>
-      <c r="W45" s="103"/>
-      <c r="X45" s="103"/>
+      <c r="B45" s="94"/>
+      <c r="C45" s="94"/>
+      <c r="D45" s="94"/>
+      <c r="E45" s="94"/>
+      <c r="F45" s="94"/>
+      <c r="G45" s="94"/>
+      <c r="H45" s="94"/>
+      <c r="I45" s="96"/>
+      <c r="J45" s="97"/>
+      <c r="K45" s="97"/>
+      <c r="L45" s="98"/>
+      <c r="M45" s="94"/>
+      <c r="N45" s="94"/>
+      <c r="O45" s="94"/>
+      <c r="P45" s="94"/>
+      <c r="Q45" s="94"/>
+      <c r="R45" s="94"/>
+      <c r="S45" s="94"/>
+      <c r="T45" s="94"/>
+      <c r="U45" s="94"/>
+      <c r="V45" s="94"/>
+      <c r="W45" s="94"/>
+      <c r="X45" s="94"/>
     </row>
     <row r="46" spans="1:24">
       <c r="A46" s="3"/>
-      <c r="B46" s="103"/>
-      <c r="C46" s="103"/>
-      <c r="D46" s="103"/>
-      <c r="E46" s="103"/>
-      <c r="F46" s="103"/>
-      <c r="G46" s="103"/>
-      <c r="H46" s="103"/>
-      <c r="I46" s="104"/>
-      <c r="J46" s="105"/>
-      <c r="K46" s="105"/>
-      <c r="L46" s="106"/>
-      <c r="M46" s="103"/>
-      <c r="N46" s="103"/>
-      <c r="O46" s="103"/>
-      <c r="P46" s="103"/>
-      <c r="Q46" s="103"/>
-      <c r="R46" s="103"/>
-      <c r="S46" s="103"/>
-      <c r="T46" s="103"/>
-      <c r="U46" s="103"/>
-      <c r="V46" s="103"/>
-      <c r="W46" s="103"/>
-      <c r="X46" s="103"/>
+      <c r="B46" s="94"/>
+      <c r="C46" s="94"/>
+      <c r="D46" s="94"/>
+      <c r="E46" s="94"/>
+      <c r="F46" s="94"/>
+      <c r="G46" s="94"/>
+      <c r="H46" s="94"/>
+      <c r="I46" s="96"/>
+      <c r="J46" s="97"/>
+      <c r="K46" s="97"/>
+      <c r="L46" s="98"/>
+      <c r="M46" s="94"/>
+      <c r="N46" s="94"/>
+      <c r="O46" s="94"/>
+      <c r="P46" s="94"/>
+      <c r="Q46" s="94"/>
+      <c r="R46" s="94"/>
+      <c r="S46" s="94"/>
+      <c r="T46" s="94"/>
+      <c r="U46" s="94"/>
+      <c r="V46" s="94"/>
+      <c r="W46" s="94"/>
+      <c r="X46" s="94"/>
     </row>
     <row r="47" spans="1:24">
       <c r="A47" s="3"/>
-      <c r="B47" s="103"/>
-      <c r="C47" s="103"/>
-      <c r="D47" s="103"/>
-      <c r="E47" s="103"/>
-      <c r="F47" s="103"/>
-      <c r="G47" s="103"/>
-      <c r="H47" s="103"/>
-      <c r="I47" s="104"/>
-      <c r="J47" s="105"/>
-      <c r="K47" s="105"/>
-      <c r="L47" s="106"/>
-      <c r="M47" s="103"/>
-      <c r="N47" s="103"/>
-      <c r="O47" s="103"/>
-      <c r="P47" s="103"/>
-      <c r="Q47" s="103"/>
-      <c r="R47" s="103"/>
-      <c r="S47" s="103"/>
-      <c r="T47" s="103"/>
-      <c r="U47" s="103"/>
-      <c r="V47" s="103"/>
-      <c r="W47" s="103"/>
-      <c r="X47" s="103"/>
+      <c r="B47" s="94"/>
+      <c r="C47" s="94"/>
+      <c r="D47" s="94"/>
+      <c r="E47" s="94"/>
+      <c r="F47" s="94"/>
+      <c r="G47" s="94"/>
+      <c r="H47" s="94"/>
+      <c r="I47" s="96"/>
+      <c r="J47" s="97"/>
+      <c r="K47" s="97"/>
+      <c r="L47" s="98"/>
+      <c r="M47" s="94"/>
+      <c r="N47" s="94"/>
+      <c r="O47" s="94"/>
+      <c r="P47" s="94"/>
+      <c r="Q47" s="94"/>
+      <c r="R47" s="94"/>
+      <c r="S47" s="94"/>
+      <c r="T47" s="94"/>
+      <c r="U47" s="94"/>
+      <c r="V47" s="94"/>
+      <c r="W47" s="94"/>
+      <c r="X47" s="94"/>
     </row>
     <row r="48" spans="1:24">
       <c r="A48" s="3"/>
-      <c r="B48" s="103"/>
-      <c r="C48" s="103"/>
-      <c r="D48" s="103"/>
-      <c r="E48" s="103"/>
-      <c r="F48" s="103"/>
-      <c r="G48" s="103"/>
-      <c r="H48" s="103"/>
-      <c r="I48" s="104"/>
-      <c r="J48" s="105"/>
-      <c r="K48" s="105"/>
-      <c r="L48" s="106"/>
-      <c r="M48" s="103"/>
-      <c r="N48" s="103"/>
-      <c r="O48" s="103"/>
-      <c r="P48" s="103"/>
-      <c r="Q48" s="103"/>
-      <c r="R48" s="103"/>
-      <c r="S48" s="103"/>
-      <c r="T48" s="103"/>
-      <c r="U48" s="103"/>
-      <c r="V48" s="103"/>
-      <c r="W48" s="103"/>
-      <c r="X48" s="103"/>
+      <c r="B48" s="94"/>
+      <c r="C48" s="94"/>
+      <c r="D48" s="94"/>
+      <c r="E48" s="94"/>
+      <c r="F48" s="94"/>
+      <c r="G48" s="94"/>
+      <c r="H48" s="94"/>
+      <c r="I48" s="96"/>
+      <c r="J48" s="97"/>
+      <c r="K48" s="97"/>
+      <c r="L48" s="98"/>
+      <c r="M48" s="94"/>
+      <c r="N48" s="94"/>
+      <c r="O48" s="94"/>
+      <c r="P48" s="94"/>
+      <c r="Q48" s="94"/>
+      <c r="R48" s="94"/>
+      <c r="S48" s="94"/>
+      <c r="T48" s="94"/>
+      <c r="U48" s="94"/>
+      <c r="V48" s="94"/>
+      <c r="W48" s="94"/>
+      <c r="X48" s="94"/>
     </row>
     <row r="49" spans="1:24">
       <c r="A49" s="3"/>
-      <c r="B49" s="103"/>
-      <c r="C49" s="103"/>
-      <c r="D49" s="103"/>
-      <c r="E49" s="103"/>
-      <c r="F49" s="103"/>
-      <c r="G49" s="103"/>
-      <c r="H49" s="103"/>
-      <c r="I49" s="104"/>
-      <c r="J49" s="105"/>
-      <c r="K49" s="105"/>
-      <c r="L49" s="106"/>
-      <c r="M49" s="103"/>
-      <c r="N49" s="103"/>
-      <c r="O49" s="103"/>
-      <c r="P49" s="103"/>
-      <c r="Q49" s="103"/>
-      <c r="R49" s="103"/>
-      <c r="S49" s="103"/>
-      <c r="T49" s="103"/>
-      <c r="U49" s="103"/>
-      <c r="V49" s="103"/>
-      <c r="W49" s="103"/>
-      <c r="X49" s="103"/>
+      <c r="B49" s="94"/>
+      <c r="C49" s="94"/>
+      <c r="D49" s="94"/>
+      <c r="E49" s="94"/>
+      <c r="F49" s="94"/>
+      <c r="G49" s="94"/>
+      <c r="H49" s="94"/>
+      <c r="I49" s="96"/>
+      <c r="J49" s="97"/>
+      <c r="K49" s="97"/>
+      <c r="L49" s="98"/>
+      <c r="M49" s="94"/>
+      <c r="N49" s="94"/>
+      <c r="O49" s="94"/>
+      <c r="P49" s="94"/>
+      <c r="Q49" s="94"/>
+      <c r="R49" s="94"/>
+      <c r="S49" s="94"/>
+      <c r="T49" s="94"/>
+      <c r="U49" s="94"/>
+      <c r="V49" s="94"/>
+      <c r="W49" s="94"/>
+      <c r="X49" s="94"/>
     </row>
     <row r="50" spans="1:24">
       <c r="A50" s="3"/>
-      <c r="B50" s="103"/>
-      <c r="C50" s="103"/>
-      <c r="D50" s="103"/>
-      <c r="E50" s="103"/>
-      <c r="F50" s="103"/>
-      <c r="G50" s="103"/>
-      <c r="H50" s="103"/>
-      <c r="I50" s="104"/>
-      <c r="J50" s="105"/>
-      <c r="K50" s="105"/>
-      <c r="L50" s="106"/>
-      <c r="M50" s="103"/>
-      <c r="N50" s="103"/>
-      <c r="O50" s="103"/>
-      <c r="P50" s="103"/>
-      <c r="Q50" s="103"/>
-      <c r="R50" s="103"/>
-      <c r="S50" s="103"/>
-      <c r="T50" s="103"/>
-      <c r="U50" s="103"/>
-      <c r="V50" s="103"/>
-      <c r="W50" s="103"/>
-      <c r="X50" s="103"/>
+      <c r="B50" s="94"/>
+      <c r="C50" s="94"/>
+      <c r="D50" s="94"/>
+      <c r="E50" s="94"/>
+      <c r="F50" s="94"/>
+      <c r="G50" s="94"/>
+      <c r="H50" s="94"/>
+      <c r="I50" s="96"/>
+      <c r="J50" s="97"/>
+      <c r="K50" s="97"/>
+      <c r="L50" s="98"/>
+      <c r="M50" s="94"/>
+      <c r="N50" s="94"/>
+      <c r="O50" s="94"/>
+      <c r="P50" s="94"/>
+      <c r="Q50" s="94"/>
+      <c r="R50" s="94"/>
+      <c r="S50" s="94"/>
+      <c r="T50" s="94"/>
+      <c r="U50" s="94"/>
+      <c r="V50" s="94"/>
+      <c r="W50" s="94"/>
+      <c r="X50" s="94"/>
     </row>
     <row r="51" spans="1:24">
       <c r="A51" s="3"/>
-      <c r="B51" s="103"/>
-      <c r="C51" s="103"/>
-      <c r="D51" s="103"/>
-      <c r="E51" s="103"/>
-      <c r="F51" s="103"/>
-      <c r="G51" s="103"/>
-      <c r="H51" s="103"/>
-      <c r="I51" s="104"/>
-      <c r="J51" s="105"/>
-      <c r="K51" s="105"/>
-      <c r="L51" s="106"/>
-      <c r="M51" s="103"/>
-      <c r="N51" s="103"/>
-      <c r="O51" s="103"/>
-      <c r="P51" s="103"/>
-      <c r="Q51" s="103"/>
-      <c r="R51" s="103"/>
-      <c r="S51" s="103"/>
-      <c r="T51" s="103"/>
-      <c r="U51" s="103"/>
-      <c r="V51" s="103"/>
-      <c r="W51" s="103"/>
-      <c r="X51" s="103"/>
+      <c r="B51" s="94"/>
+      <c r="C51" s="94"/>
+      <c r="D51" s="94"/>
+      <c r="E51" s="94"/>
+      <c r="F51" s="94"/>
+      <c r="G51" s="94"/>
+      <c r="H51" s="94"/>
+      <c r="I51" s="96"/>
+      <c r="J51" s="97"/>
+      <c r="K51" s="97"/>
+      <c r="L51" s="98"/>
+      <c r="M51" s="94"/>
+      <c r="N51" s="94"/>
+      <c r="O51" s="94"/>
+      <c r="P51" s="94"/>
+      <c r="Q51" s="94"/>
+      <c r="R51" s="94"/>
+      <c r="S51" s="94"/>
+      <c r="T51" s="94"/>
+      <c r="U51" s="94"/>
+      <c r="V51" s="94"/>
+      <c r="W51" s="94"/>
+      <c r="X51" s="94"/>
     </row>
     <row r="52" spans="1:24">
       <c r="A52" s="3"/>
-      <c r="B52" s="103"/>
-      <c r="C52" s="103"/>
-      <c r="D52" s="103"/>
-      <c r="E52" s="103"/>
-      <c r="F52" s="103"/>
-      <c r="G52" s="103"/>
-      <c r="H52" s="103"/>
-      <c r="I52" s="104"/>
-      <c r="J52" s="105"/>
-      <c r="K52" s="105"/>
-      <c r="L52" s="106"/>
-      <c r="M52" s="103"/>
-      <c r="N52" s="103"/>
-      <c r="O52" s="103"/>
-      <c r="P52" s="103"/>
-      <c r="Q52" s="103"/>
-      <c r="R52" s="103"/>
-      <c r="S52" s="103"/>
-      <c r="T52" s="103"/>
-      <c r="U52" s="103"/>
-      <c r="V52" s="103"/>
-      <c r="W52" s="103"/>
-      <c r="X52" s="103"/>
+      <c r="B52" s="94"/>
+      <c r="C52" s="94"/>
+      <c r="D52" s="94"/>
+      <c r="E52" s="94"/>
+      <c r="F52" s="94"/>
+      <c r="G52" s="94"/>
+      <c r="H52" s="94"/>
+      <c r="I52" s="96"/>
+      <c r="J52" s="97"/>
+      <c r="K52" s="97"/>
+      <c r="L52" s="98"/>
+      <c r="M52" s="94"/>
+      <c r="N52" s="94"/>
+      <c r="O52" s="94"/>
+      <c r="P52" s="94"/>
+      <c r="Q52" s="94"/>
+      <c r="R52" s="94"/>
+      <c r="S52" s="94"/>
+      <c r="T52" s="94"/>
+      <c r="U52" s="94"/>
+      <c r="V52" s="94"/>
+      <c r="W52" s="94"/>
+      <c r="X52" s="94"/>
     </row>
     <row r="53" spans="1:24">
       <c r="A53" s="3"/>
-      <c r="B53" s="103"/>
-      <c r="C53" s="103"/>
-      <c r="D53" s="103"/>
-      <c r="E53" s="103"/>
-      <c r="F53" s="103"/>
-      <c r="G53" s="103"/>
-      <c r="H53" s="103"/>
-      <c r="I53" s="103"/>
-      <c r="J53" s="103"/>
-      <c r="K53" s="103"/>
-      <c r="L53" s="103"/>
-      <c r="M53" s="103"/>
-      <c r="N53" s="103"/>
-      <c r="O53" s="103"/>
-      <c r="P53" s="103"/>
-      <c r="Q53" s="103"/>
-      <c r="R53" s="103"/>
-      <c r="S53" s="103"/>
-      <c r="T53" s="103"/>
-      <c r="U53" s="103"/>
-      <c r="V53" s="103"/>
-      <c r="W53" s="103"/>
-      <c r="X53" s="103"/>
+      <c r="B53" s="94"/>
+      <c r="C53" s="94"/>
+      <c r="D53" s="94"/>
+      <c r="E53" s="94"/>
+      <c r="F53" s="94"/>
+      <c r="G53" s="94"/>
+      <c r="H53" s="94"/>
+      <c r="I53" s="94"/>
+      <c r="J53" s="94"/>
+      <c r="K53" s="94"/>
+      <c r="L53" s="94"/>
+      <c r="M53" s="94"/>
+      <c r="N53" s="94"/>
+      <c r="O53" s="94"/>
+      <c r="P53" s="94"/>
+      <c r="Q53" s="94"/>
+      <c r="R53" s="94"/>
+      <c r="S53" s="94"/>
+      <c r="T53" s="94"/>
+      <c r="U53" s="94"/>
+      <c r="V53" s="94"/>
+      <c r="W53" s="94"/>
+      <c r="X53" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="256">
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="M3:O3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="M20:O20"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="M5:O5"/>
+    <mergeCell ref="M6:O6"/>
+    <mergeCell ref="M7:O7"/>
+    <mergeCell ref="M8:O8"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="M17:O17"/>
+    <mergeCell ref="M18:O18"/>
+    <mergeCell ref="M19:O19"/>
+    <mergeCell ref="M16:O16"/>
+    <mergeCell ref="I16:L16"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="M13:O13"/>
+    <mergeCell ref="M14:O14"/>
+    <mergeCell ref="M15:O15"/>
+    <mergeCell ref="M25:O25"/>
+    <mergeCell ref="M26:O26"/>
+    <mergeCell ref="M27:O27"/>
+    <mergeCell ref="M43:O43"/>
+    <mergeCell ref="P2:X3"/>
+    <mergeCell ref="P16:X16"/>
+    <mergeCell ref="M44:O44"/>
+    <mergeCell ref="M35:O35"/>
+    <mergeCell ref="M36:O36"/>
+    <mergeCell ref="M37:O37"/>
+    <mergeCell ref="M38:O38"/>
+    <mergeCell ref="M39:O39"/>
+    <mergeCell ref="M21:O21"/>
+    <mergeCell ref="M22:O22"/>
+    <mergeCell ref="M23:O23"/>
+    <mergeCell ref="M33:O33"/>
+    <mergeCell ref="M34:O34"/>
+    <mergeCell ref="M28:O28"/>
+    <mergeCell ref="M29:O29"/>
+    <mergeCell ref="M32:O32"/>
+    <mergeCell ref="M30:O30"/>
+    <mergeCell ref="M31:O31"/>
+    <mergeCell ref="M24:O24"/>
+    <mergeCell ref="P12:X12"/>
+    <mergeCell ref="M50:O50"/>
+    <mergeCell ref="M51:O51"/>
+    <mergeCell ref="M52:O52"/>
+    <mergeCell ref="M53:O53"/>
+    <mergeCell ref="I4:L4"/>
+    <mergeCell ref="I5:L5"/>
+    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="I7:L7"/>
+    <mergeCell ref="I8:L8"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="I10:L10"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="I18:L18"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="I20:L20"/>
+    <mergeCell ref="M45:O45"/>
+    <mergeCell ref="M46:O46"/>
+    <mergeCell ref="M47:O47"/>
+    <mergeCell ref="M48:O48"/>
+    <mergeCell ref="M49:O49"/>
+    <mergeCell ref="M40:O40"/>
+    <mergeCell ref="M41:O41"/>
+    <mergeCell ref="M42:O42"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="I12:L12"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="I14:L14"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="I26:L26"/>
+    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="I43:L43"/>
+    <mergeCell ref="I51:L51"/>
+    <mergeCell ref="I52:L52"/>
+    <mergeCell ref="I53:L53"/>
+    <mergeCell ref="P4:X4"/>
+    <mergeCell ref="P5:X5"/>
+    <mergeCell ref="P6:X6"/>
+    <mergeCell ref="P7:X7"/>
+    <mergeCell ref="P8:X8"/>
+    <mergeCell ref="P9:X9"/>
+    <mergeCell ref="P10:X10"/>
+    <mergeCell ref="P11:X11"/>
+    <mergeCell ref="P17:X17"/>
+    <mergeCell ref="P18:X18"/>
+    <mergeCell ref="P19:X19"/>
+    <mergeCell ref="P20:X20"/>
+    <mergeCell ref="I45:L45"/>
+    <mergeCell ref="I46:L46"/>
+    <mergeCell ref="I47:L47"/>
+    <mergeCell ref="I48:L48"/>
+    <mergeCell ref="I49:L49"/>
+    <mergeCell ref="I40:L40"/>
+    <mergeCell ref="I41:L41"/>
+    <mergeCell ref="I42:L42"/>
+    <mergeCell ref="I44:L44"/>
+    <mergeCell ref="P13:X13"/>
+    <mergeCell ref="P14:X14"/>
+    <mergeCell ref="P15:X15"/>
+    <mergeCell ref="P25:X25"/>
+    <mergeCell ref="P26:X26"/>
+    <mergeCell ref="P27:X27"/>
+    <mergeCell ref="P43:X43"/>
+    <mergeCell ref="I50:L50"/>
+    <mergeCell ref="I35:L35"/>
+    <mergeCell ref="I36:L36"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="I38:L38"/>
+    <mergeCell ref="I39:L39"/>
+    <mergeCell ref="I21:L21"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="I23:L23"/>
+    <mergeCell ref="I33:L33"/>
+    <mergeCell ref="I34:L34"/>
+    <mergeCell ref="I28:L28"/>
+    <mergeCell ref="I29:L29"/>
+    <mergeCell ref="I32:L32"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="P44:X44"/>
+    <mergeCell ref="P35:X35"/>
+    <mergeCell ref="P36:X36"/>
+    <mergeCell ref="P37:X37"/>
+    <mergeCell ref="P38:X38"/>
+    <mergeCell ref="P39:X39"/>
+    <mergeCell ref="P21:X21"/>
+    <mergeCell ref="P22:X22"/>
+    <mergeCell ref="P23:X23"/>
+    <mergeCell ref="P33:X33"/>
+    <mergeCell ref="P34:X34"/>
+    <mergeCell ref="P28:X28"/>
+    <mergeCell ref="P29:X29"/>
+    <mergeCell ref="P32:X32"/>
+    <mergeCell ref="P30:X30"/>
+    <mergeCell ref="P31:X31"/>
+    <mergeCell ref="P24:X24"/>
+    <mergeCell ref="P50:X50"/>
+    <mergeCell ref="P51:X51"/>
+    <mergeCell ref="P52:X52"/>
+    <mergeCell ref="P53:X53"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="P45:X45"/>
+    <mergeCell ref="P46:X46"/>
+    <mergeCell ref="P47:X47"/>
+    <mergeCell ref="P48:X48"/>
+    <mergeCell ref="P49:X49"/>
+    <mergeCell ref="P40:X40"/>
+    <mergeCell ref="P41:X41"/>
+    <mergeCell ref="P42:X42"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="F44:H44"/>
+    <mergeCell ref="F45:H45"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="F37:H37"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F31:H31"/>
     <mergeCell ref="F51:H51"/>
     <mergeCell ref="F52:H52"/>
     <mergeCell ref="F53:H53"/>
@@ -10790,238 +11013,6 @@
     <mergeCell ref="F41:H41"/>
     <mergeCell ref="F42:H42"/>
     <mergeCell ref="F43:H43"/>
-    <mergeCell ref="F44:H44"/>
-    <mergeCell ref="F45:H45"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="F37:H37"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B37:E37"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="P50:X50"/>
-    <mergeCell ref="P51:X51"/>
-    <mergeCell ref="P52:X52"/>
-    <mergeCell ref="P53:X53"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="P45:X45"/>
-    <mergeCell ref="P46:X46"/>
-    <mergeCell ref="P47:X47"/>
-    <mergeCell ref="P48:X48"/>
-    <mergeCell ref="P49:X49"/>
-    <mergeCell ref="P40:X40"/>
-    <mergeCell ref="P41:X41"/>
-    <mergeCell ref="P42:X42"/>
-    <mergeCell ref="P35:X35"/>
-    <mergeCell ref="P36:X36"/>
-    <mergeCell ref="P37:X37"/>
-    <mergeCell ref="P38:X38"/>
-    <mergeCell ref="P39:X39"/>
-    <mergeCell ref="P21:X21"/>
-    <mergeCell ref="P22:X22"/>
-    <mergeCell ref="P23:X23"/>
-    <mergeCell ref="P33:X33"/>
-    <mergeCell ref="P34:X34"/>
-    <mergeCell ref="P28:X28"/>
-    <mergeCell ref="P29:X29"/>
-    <mergeCell ref="P32:X32"/>
-    <mergeCell ref="P30:X30"/>
-    <mergeCell ref="P31:X31"/>
-    <mergeCell ref="P24:X24"/>
-    <mergeCell ref="P13:X13"/>
-    <mergeCell ref="P14:X14"/>
-    <mergeCell ref="P15:X15"/>
-    <mergeCell ref="P25:X25"/>
-    <mergeCell ref="P26:X26"/>
-    <mergeCell ref="P27:X27"/>
-    <mergeCell ref="P43:X43"/>
-    <mergeCell ref="I50:L50"/>
-    <mergeCell ref="I35:L35"/>
-    <mergeCell ref="I36:L36"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="I38:L38"/>
-    <mergeCell ref="I39:L39"/>
-    <mergeCell ref="I21:L21"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="I23:L23"/>
-    <mergeCell ref="I33:L33"/>
-    <mergeCell ref="I34:L34"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="I29:L29"/>
-    <mergeCell ref="I32:L32"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="P44:X44"/>
-    <mergeCell ref="I51:L51"/>
-    <mergeCell ref="I52:L52"/>
-    <mergeCell ref="I53:L53"/>
-    <mergeCell ref="P4:X4"/>
-    <mergeCell ref="P5:X5"/>
-    <mergeCell ref="P6:X6"/>
-    <mergeCell ref="P7:X7"/>
-    <mergeCell ref="P8:X8"/>
-    <mergeCell ref="P9:X9"/>
-    <mergeCell ref="P10:X10"/>
-    <mergeCell ref="P11:X11"/>
-    <mergeCell ref="P17:X17"/>
-    <mergeCell ref="P18:X18"/>
-    <mergeCell ref="P19:X19"/>
-    <mergeCell ref="P20:X20"/>
-    <mergeCell ref="I45:L45"/>
-    <mergeCell ref="I46:L46"/>
-    <mergeCell ref="I47:L47"/>
-    <mergeCell ref="I48:L48"/>
-    <mergeCell ref="I49:L49"/>
-    <mergeCell ref="I40:L40"/>
-    <mergeCell ref="I41:L41"/>
-    <mergeCell ref="I42:L42"/>
-    <mergeCell ref="I44:L44"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="I12:L12"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="I14:L14"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="I26:L26"/>
-    <mergeCell ref="I27:L27"/>
-    <mergeCell ref="I43:L43"/>
-    <mergeCell ref="M50:O50"/>
-    <mergeCell ref="M51:O51"/>
-    <mergeCell ref="M52:O52"/>
-    <mergeCell ref="M53:O53"/>
-    <mergeCell ref="I4:L4"/>
-    <mergeCell ref="I5:L5"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="I7:L7"/>
-    <mergeCell ref="I8:L8"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="I18:L18"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="M45:O45"/>
-    <mergeCell ref="M46:O46"/>
-    <mergeCell ref="M47:O47"/>
-    <mergeCell ref="M48:O48"/>
-    <mergeCell ref="M49:O49"/>
-    <mergeCell ref="M40:O40"/>
-    <mergeCell ref="M41:O41"/>
-    <mergeCell ref="M42:O42"/>
-    <mergeCell ref="M25:O25"/>
-    <mergeCell ref="M26:O26"/>
-    <mergeCell ref="M27:O27"/>
-    <mergeCell ref="M43:O43"/>
-    <mergeCell ref="P2:X3"/>
-    <mergeCell ref="P16:X16"/>
-    <mergeCell ref="M44:O44"/>
-    <mergeCell ref="M35:O35"/>
-    <mergeCell ref="M36:O36"/>
-    <mergeCell ref="M37:O37"/>
-    <mergeCell ref="M38:O38"/>
-    <mergeCell ref="M39:O39"/>
-    <mergeCell ref="M21:O21"/>
-    <mergeCell ref="M22:O22"/>
-    <mergeCell ref="M23:O23"/>
-    <mergeCell ref="M33:O33"/>
-    <mergeCell ref="M34:O34"/>
-    <mergeCell ref="M28:O28"/>
-    <mergeCell ref="M29:O29"/>
-    <mergeCell ref="M32:O32"/>
-    <mergeCell ref="M30:O30"/>
-    <mergeCell ref="M31:O31"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="P12:X12"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="M3:O3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="M20:O20"/>
-    <mergeCell ref="M4:O4"/>
-    <mergeCell ref="M5:O5"/>
-    <mergeCell ref="M6:O6"/>
-    <mergeCell ref="M7:O7"/>
-    <mergeCell ref="M8:O8"/>
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="M17:O17"/>
-    <mergeCell ref="M18:O18"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="M16:O16"/>
-    <mergeCell ref="I16:L16"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="M13:O13"/>
-    <mergeCell ref="M14:O14"/>
-    <mergeCell ref="M15:O15"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11067,14 +11058,14 @@
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="B8" s="113" t="s">
+      <c r="B8" s="99" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="105"/>
-      <c r="D8" s="105"/>
-      <c r="E8" s="105"/>
-      <c r="F8" s="105"/>
-      <c r="G8" s="106"/>
+      <c r="C8" s="97"/>
+      <c r="D8" s="97"/>
+      <c r="E8" s="97"/>
+      <c r="F8" s="97"/>
+      <c r="G8" s="98"/>
     </row>
     <row r="9" spans="1:7">
       <c r="B9" s="116"/>
@@ -11370,7 +11361,7 @@
     </row>
     <row r="133" spans="3:23">
       <c r="D133" s="40" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E133" s="40"/>
       <c r="F133" s="40"/>
@@ -11385,7 +11376,7 @@
     </row>
     <row r="134" spans="3:23" ht="15">
       <c r="C134" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="K134" s="54" t="s">
         <v>261</v>
@@ -11615,7 +11606,7 @@
       <c r="I145" s="18"/>
       <c r="J145" s="19"/>
       <c r="M145" s="31" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="N145" s="18"/>
       <c r="O145" s="18"/>
@@ -11643,7 +11634,7 @@
     </row>
     <row r="147" spans="3:26" ht="17.25">
       <c r="C147" t="s">
-        <v>313</v>
+        <v>372</v>
       </c>
       <c r="D147" s="60"/>
       <c r="K147" s="57"/>
@@ -11662,11 +11653,11 @@
     </row>
     <row r="148" spans="3:26" ht="20.25">
       <c r="D148" s="78" t="s">
-        <v>312</v>
+        <v>373</v>
       </c>
       <c r="K148" s="57"/>
       <c r="L148" s="77" t="s">
-        <v>314</v>
+        <v>374</v>
       </c>
       <c r="M148" s="57"/>
       <c r="N148" s="14"/>
@@ -11682,11 +11673,11 @@
     </row>
     <row r="149" spans="3:26" ht="20.25">
       <c r="C149" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D149" s="78"/>
       <c r="I149" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="K149" s="57"/>
       <c r="L149" s="77"/>
@@ -11704,7 +11695,7 @@
     </row>
     <row r="150" spans="3:26" ht="18.75" customHeight="1">
       <c r="D150" s="81" t="s">
-        <v>315</v>
+        <v>371</v>
       </c>
       <c r="E150" s="11"/>
       <c r="F150" s="11"/>
@@ -11713,7 +11704,7 @@
       <c r="I150" s="12"/>
       <c r="K150" s="57"/>
       <c r="L150" s="89" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="M150" s="79"/>
       <c r="N150" s="79"/>
@@ -11729,15 +11720,15 @@
     </row>
     <row r="151" spans="3:26">
       <c r="C151" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="152" spans="3:26" ht="15.75">
       <c r="C152" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="N152" s="91" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="O152" s="13"/>
       <c r="P152" s="13"/>
@@ -11754,10 +11745,10 @@
     </row>
     <row r="153" spans="3:26" ht="15">
       <c r="D153" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="N153" s="92" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="O153" s="18"/>
       <c r="P153" s="18"/>
@@ -11774,29 +11765,29 @@
     </row>
     <row r="154" spans="3:26" ht="15">
       <c r="D154" t="s">
+        <v>358</v>
+      </c>
+      <c r="N154" s="88"/>
+    </row>
+    <row r="155" spans="3:26">
+      <c r="D155" s="99" t="s">
+        <v>361</v>
+      </c>
+      <c r="E155" s="97"/>
+      <c r="F155" s="97"/>
+      <c r="G155" s="97"/>
+      <c r="H155" s="97"/>
+      <c r="I155" s="98"/>
+      <c r="L155" s="99" t="s">
         <v>362</v>
       </c>
-      <c r="N154" s="88"/>
-    </row>
-    <row r="155" spans="3:26">
-      <c r="D155" s="113" t="s">
-        <v>365</v>
-      </c>
-      <c r="E155" s="105"/>
-      <c r="F155" s="105"/>
-      <c r="G155" s="105"/>
-      <c r="H155" s="105"/>
-      <c r="I155" s="106"/>
-      <c r="L155" s="113" t="s">
-        <v>366</v>
-      </c>
-      <c r="M155" s="105"/>
-      <c r="N155" s="105"/>
-      <c r="O155" s="105"/>
-      <c r="P155" s="105"/>
-      <c r="Q155" s="106"/>
+      <c r="M155" s="97"/>
+      <c r="N155" s="97"/>
+      <c r="O155" s="97"/>
+      <c r="P155" s="97"/>
+      <c r="Q155" s="98"/>
       <c r="S155" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="156" spans="3:26">
@@ -11816,7 +11807,7 @@
       <c r="P156" s="126"/>
       <c r="Q156" s="118"/>
       <c r="S156" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="157" spans="3:26">
@@ -11835,17 +11826,17 @@
     </row>
     <row r="158" spans="3:26">
       <c r="C158" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="159" spans="3:26">
       <c r="C159" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="160" spans="3:26">
       <c r="D160" s="123" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="E160" s="124"/>
       <c r="F160" s="124"/>
@@ -11864,40 +11855,40 @@
     </row>
     <row r="161" spans="3:17" ht="15.75">
       <c r="D161" s="42" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="L161" s="42" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="162" spans="3:17" ht="15.75">
       <c r="C162" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="L162" s="42" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="163" spans="3:17" ht="14.25" customHeight="1">
-      <c r="D163" s="113" t="s">
-        <v>352</v>
-      </c>
-      <c r="E163" s="114"/>
-      <c r="F163" s="114"/>
-      <c r="G163" s="114"/>
-      <c r="H163" s="114"/>
-      <c r="I163" s="115"/>
+      <c r="D163" s="99" t="s">
+        <v>348</v>
+      </c>
+      <c r="E163" s="100"/>
+      <c r="F163" s="100"/>
+      <c r="G163" s="100"/>
+      <c r="H163" s="100"/>
+      <c r="I163" s="101"/>
       <c r="K163" t="s">
         <v>244</v>
       </c>
-      <c r="L163" s="113" t="s">
-        <v>353</v>
-      </c>
-      <c r="M163" s="114"/>
-      <c r="N163" s="114"/>
-      <c r="O163" s="114"/>
-      <c r="P163" s="114"/>
-      <c r="Q163" s="115"/>
+      <c r="L163" s="99" t="s">
+        <v>349</v>
+      </c>
+      <c r="M163" s="100"/>
+      <c r="N163" s="100"/>
+      <c r="O163" s="100"/>
+      <c r="P163" s="100"/>
+      <c r="Q163" s="101"/>
     </row>
     <row r="164" spans="3:17">
       <c r="D164" s="133"/>
@@ -11915,12 +11906,12 @@
     </row>
     <row r="165" spans="3:17">
       <c r="C165" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="166" spans="3:17">
       <c r="D166" s="127" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="E166" s="128"/>
       <c r="F166" s="128"/>
@@ -11928,7 +11919,7 @@
       <c r="H166" s="128"/>
       <c r="I166" s="129"/>
       <c r="L166" s="127" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="M166" s="128"/>
       <c r="N166" s="128"/>
@@ -11952,12 +11943,12 @@
     </row>
     <row r="168" spans="3:17">
       <c r="C168" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="169" spans="3:17">
       <c r="D169" s="93" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E169" s="11"/>
       <c r="F169" s="11"/>
@@ -12131,24 +12122,24 @@
     </row>
     <row r="213" spans="1:10" ht="18">
       <c r="A213" s="23" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="E213" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="214" spans="1:10">
-      <c r="B214" s="113" t="s">
-        <v>360</v>
-      </c>
-      <c r="C214" s="105"/>
-      <c r="D214" s="105"/>
-      <c r="E214" s="105"/>
-      <c r="F214" s="105"/>
-      <c r="G214" s="105"/>
-      <c r="H214" s="105"/>
-      <c r="I214" s="105"/>
-      <c r="J214" s="106"/>
+      <c r="B214" s="99" t="s">
+        <v>356</v>
+      </c>
+      <c r="C214" s="97"/>
+      <c r="D214" s="97"/>
+      <c r="E214" s="97"/>
+      <c r="F214" s="97"/>
+      <c r="G214" s="97"/>
+      <c r="H214" s="97"/>
+      <c r="I214" s="97"/>
+      <c r="J214" s="98"/>
     </row>
     <row r="215" spans="1:10">
       <c r="B215" s="119"/>
@@ -12287,17 +12278,17 @@
     </row>
     <row r="15" spans="1:11">
       <c r="B15" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="18">
       <c r="A16" s="23" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="20.25">
       <c r="B17" s="90" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.75">
@@ -12703,45 +12694,45 @@
   <sheetData>
     <row r="1" spans="1:4" ht="23.25">
       <c r="A1" s="67" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75">
       <c r="B2" s="86" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75">
       <c r="B3" s="82" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C3" s="83"/>
       <c r="D3" s="83"/>
     </row>
     <row r="4" spans="1:4" ht="15.75">
       <c r="B4" s="84" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C4" s="83"/>
       <c r="D4" s="83"/>
     </row>
     <row r="5" spans="1:4" ht="15.75">
       <c r="B5" s="82" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C5" s="83"/>
       <c r="D5" s="83"/>
     </row>
     <row r="6" spans="1:4" ht="15.75">
       <c r="B6" s="82" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C6" s="83"/>
       <c r="D6" s="83"/>
     </row>
     <row r="7" spans="1:4" ht="15.75">
       <c r="B7" s="82" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C7" s="83"/>
       <c r="D7" s="83"/>
@@ -12753,42 +12744,42 @@
     </row>
     <row r="9" spans="1:4" ht="15.75">
       <c r="B9" s="86" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C9" s="83"/>
       <c r="D9" s="83"/>
     </row>
     <row r="10" spans="1:4" ht="15.75">
       <c r="B10" s="82" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C10" s="83"/>
       <c r="D10" s="83"/>
     </row>
     <row r="11" spans="1:4" ht="15.75">
       <c r="B11" s="87" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C11" s="83"/>
       <c r="D11" s="83"/>
     </row>
     <row r="12" spans="1:4" ht="15.75">
       <c r="B12" s="82" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C12" s="83"/>
       <c r="D12" s="83"/>
     </row>
     <row r="13" spans="1:4" ht="15.75">
       <c r="B13" s="82" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C13" s="83"/>
       <c r="D13" s="83"/>
     </row>
     <row r="14" spans="1:4" ht="15.75">
       <c r="B14" s="82" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C14" s="83"/>
       <c r="D14" s="83"/>
@@ -13219,7 +13210,7 @@
         <v>254</v>
       </c>
       <c r="P1" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="15.75">
@@ -13234,15 +13225,15 @@
       <c r="H2" s="13"/>
       <c r="I2" s="13"/>
       <c r="J2" s="15"/>
-      <c r="N2" s="113" t="s">
-        <v>348</v>
-      </c>
-      <c r="O2" s="105"/>
-      <c r="P2" s="105"/>
-      <c r="Q2" s="105"/>
-      <c r="R2" s="105"/>
-      <c r="S2" s="105"/>
-      <c r="T2" s="106"/>
+      <c r="N2" s="99" t="s">
+        <v>344</v>
+      </c>
+      <c r="O2" s="97"/>
+      <c r="P2" s="97"/>
+      <c r="Q2" s="97"/>
+      <c r="R2" s="97"/>
+      <c r="S2" s="97"/>
+      <c r="T2" s="98"/>
     </row>
     <row r="3" spans="1:20" ht="15.75">
       <c r="B3" s="26" t="s">
@@ -13412,15 +13403,15 @@
       <c r="H11" s="14"/>
       <c r="I11" s="14"/>
       <c r="J11" s="16"/>
-      <c r="N11" s="113" t="s">
-        <v>349</v>
-      </c>
-      <c r="O11" s="105"/>
-      <c r="P11" s="105"/>
-      <c r="Q11" s="105"/>
-      <c r="R11" s="105"/>
-      <c r="S11" s="105"/>
-      <c r="T11" s="106"/>
+      <c r="N11" s="99" t="s">
+        <v>345</v>
+      </c>
+      <c r="O11" s="97"/>
+      <c r="P11" s="97"/>
+      <c r="Q11" s="97"/>
+      <c r="R11" s="97"/>
+      <c r="S11" s="97"/>
+      <c r="T11" s="98"/>
     </row>
     <row r="12" spans="1:20" ht="15.75">
       <c r="B12" s="26" t="s">
@@ -13590,15 +13581,15 @@
       <c r="H20" s="14"/>
       <c r="I20" s="14"/>
       <c r="J20" s="16"/>
-      <c r="N20" s="113" t="s">
-        <v>350</v>
-      </c>
-      <c r="O20" s="105"/>
-      <c r="P20" s="105"/>
-      <c r="Q20" s="105"/>
-      <c r="R20" s="105"/>
-      <c r="S20" s="105"/>
-      <c r="T20" s="106"/>
+      <c r="N20" s="99" t="s">
+        <v>346</v>
+      </c>
+      <c r="O20" s="97"/>
+      <c r="P20" s="97"/>
+      <c r="Q20" s="97"/>
+      <c r="R20" s="97"/>
+      <c r="S20" s="97"/>
+      <c r="T20" s="98"/>
     </row>
     <row r="21" spans="2:20" ht="15.75">
       <c r="B21" s="27" t="s">
@@ -13876,17 +13867,17 @@
       </c>
     </row>
     <row r="40" spans="1:10">
-      <c r="B40" s="113" t="s">
+      <c r="B40" s="99" t="s">
         <v>182</v>
       </c>
-      <c r="C40" s="105"/>
-      <c r="D40" s="105"/>
-      <c r="E40" s="105"/>
-      <c r="F40" s="105"/>
-      <c r="G40" s="105"/>
-      <c r="H40" s="105"/>
-      <c r="I40" s="105"/>
-      <c r="J40" s="106"/>
+      <c r="C40" s="97"/>
+      <c r="D40" s="97"/>
+      <c r="E40" s="97"/>
+      <c r="F40" s="97"/>
+      <c r="G40" s="97"/>
+      <c r="H40" s="97"/>
+      <c r="I40" s="97"/>
+      <c r="J40" s="98"/>
     </row>
     <row r="41" spans="1:10">
       <c r="B41" s="119"/>
